--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -6,15 +6,16 @@
   </bookViews>
   <sheets>
     <sheet name="earth" sheetId="1" r:id="rId2"/>
-    <sheet name="moon" sheetId="2" r:id="rId3"/>
-    <sheet name="nether" sheetId="3" r:id="rId4"/>
+    <sheet name="mars" sheetId="2" r:id="rId3"/>
+    <sheet name="moon" sheetId="3" r:id="rId4"/>
+    <sheet name="nether" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="453">
   <si>
     <t>Vein ID</t>
   </si>
@@ -421,6 +422,21 @@
     <t>coal: 30</t>
   </si>
   <si>
+    <t>normal_gypsum</t>
+  </si>
+  <si>
+    <t>borax: 20</t>
+  </si>
+  <si>
+    <t>calcite: 30</t>
+  </si>
+  <si>
+    <t>fullers_earth: 15</t>
+  </si>
+  <si>
+    <t>gypsum: 35</t>
+  </si>
+  <si>
     <t>normal_hematite</t>
   </si>
   <si>
@@ -724,6 +740,21 @@
     <t>copper: 20</t>
   </si>
   <si>
+    <t>mars_stone</t>
+  </si>
+  <si>
+    <t>red_granite</t>
+  </si>
+  <si>
+    <t>venus_stone</t>
+  </si>
+  <si>
+    <t>mars_hematite</t>
+  </si>
+  <si>
+    <t>hematite: 100 [1]</t>
+  </si>
+  <si>
     <t>glacio_stone</t>
   </si>
   <si>
@@ -748,10 +779,10 @@
     <t>moon_bauxite</t>
   </si>
   <si>
-    <t>bauxite: 35</t>
-  </si>
-  <si>
-    <t>ilmenite: 40</t>
+    <t>bauxite: 35 [1]</t>
+  </si>
+  <si>
+    <t>ilmenite: 40 [1]</t>
   </si>
   <si>
     <t>armalcolite: 20</t>
@@ -769,6 +800,21 @@
     <t>thorium: 1</t>
   </si>
   <si>
+    <t>moon_cassiterite</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 30 [1]</t>
+  </si>
+  <si>
+    <t>zeolite: 5</t>
+  </si>
+  <si>
+    <t>cassiterite: 35 [1]</t>
+  </si>
+  <si>
+    <t>tin: 15</t>
+  </si>
+  <si>
     <t>moon_desh</t>
   </si>
   <si>
@@ -784,6 +830,21 @@
     <t>armalcolite: 15</t>
   </si>
   <si>
+    <t>moon_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet: 10</t>
+  </si>
+  <si>
+    <t>yellow_garnet: 15</t>
+  </si>
+  <si>
+    <t>amethyst: 40 [1]</t>
+  </si>
+  <si>
+    <t>opal: 40 [1]</t>
+  </si>
+  <si>
     <t>moon_garnierite</t>
   </si>
   <si>
@@ -796,6 +857,18 @@
     <t>pentlandite: 25 [1]</t>
   </si>
   <si>
+    <t>moon_gold</t>
+  </si>
+  <si>
+    <t>green_sapphire: 5</t>
+  </si>
+  <si>
+    <t>bauxite: 20</t>
+  </si>
+  <si>
+    <t>magnetite: 20</t>
+  </si>
+  <si>
     <t>moon_graphite</t>
   </si>
   <si>
@@ -808,6 +881,15 @@
     <t>olivine: 10</t>
   </si>
   <si>
+    <t>moon_gypsum</t>
+  </si>
+  <si>
+    <t>calcite: 25</t>
+  </si>
+  <si>
+    <t>gypsum: 35 [1]</t>
+  </si>
+  <si>
     <t>moon_lubricant</t>
   </si>
   <si>
@@ -829,6 +911,9 @@
     <t>kyanite: 35 [1]</t>
   </si>
   <si>
+    <t>aluminium: 15</t>
+  </si>
+  <si>
     <t>moon_molybdenum</t>
   </si>
   <si>
@@ -940,6 +1025,18 @@
     <t>sphalerite: 50 [1]</t>
   </si>
   <si>
+    <t>moon_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 40 [1]</t>
+  </si>
+  <si>
+    <t>copper: 15</t>
+  </si>
+  <si>
+    <t>chalcocite: 25</t>
+  </si>
+  <si>
     <t>moon_topaz</t>
   </si>
   <si>
@@ -1055,6 +1152,15 @@
   </si>
   <si>
     <t>coal: 15</t>
+  </si>
+  <si>
+    <t>nether_gypsum</t>
+  </si>
+  <si>
+    <t>borax: 20 [1]</t>
+  </si>
+  <si>
+    <t>calcite: 30 [1]</t>
   </si>
   <si>
     <t>nether_hematite</t>
@@ -1340,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH48"/>
+  <dimension ref="A1:AH49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.943572998046875" customWidth="1" style="3"/>
@@ -1386,7 +1492,8 @@
     <col min="41" max="41" width="9.140625" customWidth="1" style="3"/>
     <col min="42" max="42" width="9.140625" customWidth="1" style="3"/>
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
-    <col min="44" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
+    <col min="45" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -3662,23 +3769,26 @@
         <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C25" s="3">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D25" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E25" s="3">
         <v>-32</v>
       </c>
       <c r="F25" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G25" s="3">
         <v>40</v>
       </c>
+      <c r="H25" s="3">
+        <v>9</v>
+      </c>
       <c r="J25" s="3" t="s">
         <v>136</v>
       </c>
@@ -3689,34 +3799,34 @@
         <v>138</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>37</v>
+        <v>139</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W25" s="2" t="s">
-        <v>36</v>
+      <c r="W25" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="X25" s="2" t="s">
         <v>36</v>
@@ -3727,8 +3837,8 @@
       <c r="Z25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA25" s="2" t="s">
-        <v>36</v>
+      <c r="AA25" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>36</v>
@@ -3739,14 +3849,14 @@
       <c r="AD25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AE25" s="1" t="s">
-        <v>37</v>
+      <c r="AE25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AF25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AG25" s="2" t="s">
-        <v>36</v>
+      <c r="AG25" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AH25" s="2" t="s">
         <v>36</v>
@@ -3754,43 +3864,43 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="3">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="D26" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E26" s="3">
-        <v>-60</v>
+        <v>-32</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G26" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q26" s="2" t="s">
         <v>36</v>
@@ -3804,8 +3914,8 @@
       <c r="T26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U26" s="2" t="s">
-        <v>36</v>
+      <c r="U26" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>36</v>
@@ -3816,8 +3926,8 @@
       <c r="X26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y26" s="1" t="s">
-        <v>37</v>
+      <c r="Y26" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>36</v>
@@ -3825,26 +3935,26 @@
       <c r="AA26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF26" s="1" t="s">
-        <v>37</v>
+      <c r="AB26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH26" s="1" t="s">
-        <v>37</v>
+      <c r="AH26" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -3855,31 +3965,31 @@
         <v>42</v>
       </c>
       <c r="C27" s="3">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D27" s="3">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E27" s="3">
-        <v>-32</v>
+        <v>-60</v>
       </c>
       <c r="F27" s="3">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="G27" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>36</v>
@@ -3911,40 +4021,40 @@
       <c r="X27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y27" s="2" t="s">
-        <v>36</v>
+      <c r="Y27" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA27" s="1" t="s">
-        <v>37</v>
+      <c r="AA27" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AB27" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AC27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>36</v>
+      <c r="AC27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD27" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AE27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AF27" s="2" t="s">
-        <v>36</v>
+      <c r="AF27" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH27" s="2" t="s">
-        <v>36</v>
+      <c r="AH27" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>42</v>
@@ -3953,32 +4063,29 @@
         <v>190</v>
       </c>
       <c r="D28" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E28" s="3">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="F28" s="3">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G28" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O28" s="2" t="s">
         <v>36</v>
       </c>
@@ -4000,26 +4107,26 @@
       <c r="U28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V28" s="1" t="s">
-        <v>37</v>
+      <c r="V28" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X28" s="1" t="s">
-        <v>37</v>
+      <c r="X28" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB28" s="2" t="s">
-        <v>36</v>
+      <c r="Z28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>36</v>
@@ -4042,36 +4149,39 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E29" s="3">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F29" s="3">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G29" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>157</v>
       </c>
       <c r="O29" s="2" t="s">
@@ -4080,38 +4190,38 @@
       <c r="P29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>37</v>
+      <c r="Q29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X29" s="2" t="s">
-        <v>36</v>
+      <c r="V29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA29" s="1" t="s">
-        <v>37</v>
+      <c r="Z29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>36</v>
@@ -4128,8 +4238,8 @@
       <c r="AF29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AG29" s="1" t="s">
-        <v>37</v>
+      <c r="AG29" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AH29" s="2" t="s">
         <v>36</v>
@@ -4143,7 +4253,7 @@
         <v>42</v>
       </c>
       <c r="C30" s="3">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D30" s="3">
         <v>0.3</v>
@@ -4152,7 +4262,7 @@
         <v>-32</v>
       </c>
       <c r="F30" s="3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G30" s="3">
         <v>30</v>
@@ -4169,11 +4279,11 @@
       <c r="M30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>37</v>
+      <c r="O30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q30" s="1" t="s">
         <v>37</v>
@@ -4187,8 +4297,8 @@
       <c r="T30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U30" s="1" t="s">
-        <v>37</v>
+      <c r="U30" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>36</v>
@@ -4217,8 +4327,8 @@
       <c r="AD30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AE30" s="1" t="s">
-        <v>37</v>
+      <c r="AE30" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AF30" s="2" t="s">
         <v>36</v>
@@ -4238,19 +4348,19 @@
         <v>42</v>
       </c>
       <c r="C31" s="3">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D31" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E31" s="3">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F31" s="3">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="G31" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>164</v>
@@ -4264,65 +4374,65 @@
       <c r="M31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH31" s="1" t="s">
-        <v>37</v>
+      <c r="O31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH31" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -4333,19 +4443,19 @@
         <v>42</v>
       </c>
       <c r="C32" s="3">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D32" s="3">
         <v>0.25</v>
       </c>
       <c r="E32" s="3">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="G32" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>169</v>
@@ -4356,6 +4466,9 @@
       <c r="L32" s="3" t="s">
         <v>171</v>
       </c>
+      <c r="M32" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="O32" s="2" t="s">
         <v>36</v>
       </c>
@@ -4386,8 +4499,8 @@
       <c r="X32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y32" s="2" t="s">
-        <v>36</v>
+      <c r="Y32" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Z32" s="1" t="s">
         <v>37</v>
@@ -4395,52 +4508,58 @@
       <c r="AA32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD32" s="2" t="s">
-        <v>36</v>
+      <c r="AB32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AE32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AF32" s="2" t="s">
-        <v>36</v>
+      <c r="AF32" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH32" s="2" t="s">
-        <v>36</v>
+      <c r="AH32" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D33" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F33" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G33" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>36</v>
@@ -4448,38 +4567,38 @@
       <c r="P33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>37</v>
+      <c r="Q33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X33" s="2" t="s">
-        <v>36</v>
+      <c r="V33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Y33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA33" s="1" t="s">
-        <v>37</v>
+      <c r="Z33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>36</v>
@@ -4496,8 +4615,8 @@
       <c r="AF33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AG33" s="1" t="s">
-        <v>37</v>
+      <c r="AG33" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AH33" s="2" t="s">
         <v>36</v>
@@ -4505,76 +4624,67 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="3">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D34" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E34" s="3">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G34" s="3">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="M34" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>37</v>
+      <c r="O34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Y34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>36</v>
+      <c r="Z34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>36</v>
@@ -4585,14 +4695,14 @@
       <c r="AD34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AE34" s="1" t="s">
-        <v>37</v>
+      <c r="AE34" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AF34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AG34" s="2" t="s">
-        <v>36</v>
+      <c r="AG34" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AH34" s="2" t="s">
         <v>36</v>
@@ -4606,19 +4716,19 @@
         <v>42</v>
       </c>
       <c r="C35" s="3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D35" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E35" s="3">
-        <v>-32</v>
+        <v>-40</v>
       </c>
       <c r="F35" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G35" s="3">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>180</v>
@@ -4629,11 +4739,14 @@
       <c r="L35" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="O35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>36</v>
+      <c r="M35" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q35" s="2" t="s">
         <v>36</v>
@@ -4647,23 +4760,23 @@
       <c r="T35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>36</v>
+      <c r="U35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z35" s="2" t="s">
-        <v>36</v>
+      <c r="X35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AA35" s="2" t="s">
         <v>36</v>
@@ -4674,17 +4787,17 @@
       <c r="AC35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AD35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG35" s="1" t="s">
-        <v>37</v>
+      <c r="AD35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AH35" s="2" t="s">
         <v>36</v>
@@ -4692,16 +4805,16 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="3">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D36" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E36" s="3">
         <v>-32</v>
@@ -4713,13 +4826,13 @@
         <v>40</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>36</v>
@@ -4751,11 +4864,11 @@
       <c r="X36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z36" s="1" t="s">
-        <v>37</v>
+      <c r="Y36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AA36" s="2" t="s">
         <v>36</v>
@@ -4766,17 +4879,17 @@
       <c r="AC36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AD36" s="2" t="s">
-        <v>36</v>
+      <c r="AD36" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AE36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AF36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG36" s="2" t="s">
-        <v>36</v>
+      <c r="AF36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AH36" s="2" t="s">
         <v>36</v>
@@ -4784,39 +4897,33 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C37" s="3">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D37" s="3">
         <v>0.4</v>
       </c>
       <c r="E37" s="3">
-        <v>30</v>
+        <v>-32</v>
       </c>
       <c r="F37" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G37" s="3">
         <v>40</v>
       </c>
-      <c r="H37" s="3">
-        <v>4</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M37" s="3" t="s">
         <v>191</v>
       </c>
       <c r="O37" s="2" t="s">
@@ -4831,8 +4938,8 @@
       <c r="R37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S37" s="1" t="s">
-        <v>37</v>
+      <c r="S37" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>36</v>
@@ -4852,11 +4959,11 @@
       <c r="Y37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA37" s="1" t="s">
-        <v>37</v>
+      <c r="Z37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>36</v>
@@ -4873,8 +4980,8 @@
       <c r="AF37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AG37" s="1" t="s">
-        <v>37</v>
+      <c r="AG37" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AH37" s="2" t="s">
         <v>36</v>
@@ -4885,23 +4992,26 @@
         <v>192</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="D38" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E38" s="3">
-        <v>-32</v>
+        <v>30</v>
       </c>
       <c r="F38" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G38" s="3">
         <v>40</v>
       </c>
+      <c r="H38" s="3">
+        <v>4</v>
+      </c>
       <c r="J38" s="3" t="s">
         <v>193</v>
       </c>
@@ -4926,8 +5036,8 @@
       <c r="R38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>36</v>
+      <c r="S38" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>36</v>
@@ -4935,44 +5045,44 @@
       <c r="U38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V38" s="1" t="s">
-        <v>37</v>
+      <c r="V38" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD38" s="1" t="s">
-        <v>37</v>
+      <c r="X38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AF38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH38" s="1" t="s">
-        <v>37</v>
+      <c r="AF38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH38" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="39">
@@ -4983,16 +5093,16 @@
         <v>42</v>
       </c>
       <c r="C39" s="3">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="D39" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E39" s="3">
         <v>-32</v>
       </c>
       <c r="F39" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G39" s="3">
         <v>40</v>
@@ -5006,6 +5116,9 @@
       <c r="L39" s="3" t="s">
         <v>200</v>
       </c>
+      <c r="M39" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="O39" s="2" t="s">
         <v>36</v>
       </c>
@@ -5027,14 +5140,14 @@
       <c r="U39" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V39" s="2" t="s">
-        <v>36</v>
+      <c r="V39" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X39" s="2" t="s">
-        <v>36</v>
+      <c r="X39" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Y39" s="1" t="s">
         <v>37</v>
@@ -5045,37 +5158,37 @@
       <c r="AA39" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD39" s="2" t="s">
-        <v>36</v>
+      <c r="AB39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD39" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AE39" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AF39" s="2" t="s">
-        <v>36</v>
+      <c r="AF39" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH39" s="2" t="s">
-        <v>36</v>
+      <c r="AH39" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D40" s="3">
         <v>0.4</v>
@@ -5090,19 +5203,19 @@
         <v>40</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>37</v>
+        <v>205</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>36</v>
@@ -5116,8 +5229,8 @@
       <c r="T40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U40" s="1" t="s">
-        <v>37</v>
+      <c r="U40" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>36</v>
@@ -5131,76 +5244,70 @@
       <c r="Y40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Z40" s="2" t="s">
-        <v>36</v>
+      <c r="Z40" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AA40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF40" s="1" t="s">
-        <v>37</v>
+      <c r="AB40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF40" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH40" s="1" t="s">
-        <v>37</v>
+      <c r="AH40" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C41" s="3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D41" s="3">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="E41" s="3">
-        <v>20</v>
+        <v>-32</v>
       </c>
       <c r="F41" s="3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G41" s="3">
-        <v>35</v>
-      </c>
-      <c r="H41" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>36</v>
+        <v>209</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>36</v>
@@ -5214,23 +5321,23 @@
       <c r="T41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>37</v>
+      <c r="U41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X41" s="1" t="s">
-        <v>37</v>
+      <c r="X41" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Y41" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Z41" s="1" t="s">
-        <v>37</v>
+      <c r="Z41" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AA41" s="2" t="s">
         <v>36</v>
@@ -5244,8 +5351,8 @@
       <c r="AD41" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AE41" s="2" t="s">
-        <v>36</v>
+      <c r="AE41" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>37</v>
@@ -5259,40 +5366,46 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C42" s="3">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D42" s="3">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="G42" s="3">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="H42" s="3">
+        <v>6</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>37</v>
+        <v>195</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>36</v>
@@ -5306,85 +5419,85 @@
       <c r="T42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>36</v>
+      <c r="U42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z42" s="2" t="s">
-        <v>36</v>
+      <c r="X42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z42" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AA42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF42" s="2" t="s">
-        <v>36</v>
+      <c r="AB42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF42" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AG42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH42" s="2" t="s">
-        <v>36</v>
+      <c r="AH42" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="3">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D43" s="3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E43" s="3">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="G43" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>36</v>
+        <v>217</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>36</v>
@@ -5398,8 +5511,8 @@
       <c r="T43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U43" s="2" t="s">
-        <v>36</v>
+      <c r="U43" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V43" s="2" t="s">
         <v>36</v>
@@ -5410,8 +5523,8 @@
       <c r="X43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y43" s="1" t="s">
-        <v>37</v>
+      <c r="Y43" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>36</v>
@@ -5419,58 +5532,58 @@
       <c r="AA43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE43" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF43" s="1" t="s">
-        <v>37</v>
+      <c r="AB43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF43" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH43" s="1" t="s">
-        <v>37</v>
+      <c r="AH43" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D44" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E44" s="3">
-        <v>60</v>
+        <v>-32</v>
       </c>
       <c r="F44" s="3">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="G44" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>36</v>
@@ -5478,70 +5591,70 @@
       <c r="P44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>37</v>
+      <c r="Q44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD44" s="2" t="s">
-        <v>36</v>
+      <c r="V44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD44" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AE44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AF44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH44" s="2" t="s">
-        <v>36</v>
+      <c r="AF44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH44" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="3">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D45" s="3">
         <v>0.25</v>
@@ -5556,10 +5669,13 @@
         <v>50</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>36</v>
@@ -5567,17 +5683,17 @@
       <c r="P45" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>36</v>
+      <c r="Q45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="U45" s="2" t="s">
         <v>36</v>
@@ -5585,8 +5701,8 @@
       <c r="V45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W45" s="2" t="s">
-        <v>36</v>
+      <c r="W45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="X45" s="1" t="s">
         <v>37</v>
@@ -5597,8 +5713,8 @@
       <c r="Z45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AA45" s="2" t="s">
-        <v>36</v>
+      <c r="AA45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AB45" s="2" t="s">
         <v>36</v>
@@ -5615,8 +5731,8 @@
       <c r="AF45" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AG45" s="2" t="s">
-        <v>36</v>
+      <c r="AG45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AH45" s="2" t="s">
         <v>36</v>
@@ -5624,43 +5740,37 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="3">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="D46" s="3">
         <v>0.25</v>
       </c>
       <c r="E46" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F46" s="3">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G46" s="3">
         <v>50</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="M46" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="O46" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>37</v>
+      <c r="O46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>36</v>
@@ -5674,23 +5784,23 @@
       <c r="T46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U46" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>36</v>
+      <c r="U46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X46" s="2" t="s">
-        <v>36</v>
+      <c r="X46" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Y46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z46" s="2" t="s">
-        <v>36</v>
+      <c r="Z46" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AA46" s="2" t="s">
         <v>36</v>
@@ -5704,8 +5814,8 @@
       <c r="AD46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AE46" s="1" t="s">
-        <v>37</v>
+      <c r="AE46" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AF46" s="2" t="s">
         <v>36</v>
@@ -5725,16 +5835,16 @@
         <v>42</v>
       </c>
       <c r="C47" s="3">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="D47" s="3">
         <v>0.25</v>
       </c>
       <c r="E47" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F47" s="3">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G47" s="3">
         <v>50</v>
@@ -5748,6 +5858,9 @@
       <c r="L47" s="3" t="s">
         <v>232</v>
       </c>
+      <c r="M47" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="O47" s="1" t="s">
         <v>37</v>
       </c>
@@ -5778,8 +5891,8 @@
       <c r="X47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y47" s="1" t="s">
-        <v>37</v>
+      <c r="Y47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>36</v>
@@ -5787,37 +5900,37 @@
       <c r="AA47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD47" s="1" t="s">
-        <v>37</v>
+      <c r="AB47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AF47" s="1" t="s">
-        <v>37</v>
+      <c r="AF47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AG47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AH47" s="1" t="s">
-        <v>37</v>
+      <c r="AH47" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="3">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D48" s="3">
         <v>0.25</v>
@@ -5832,19 +5945,19 @@
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>36</v>
+        <v>237</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>36</v>
@@ -5858,8 +5971,8 @@
       <c r="T48" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U48" s="2" t="s">
-        <v>36</v>
+      <c r="U48" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>36</v>
@@ -5888,8 +6001,8 @@
       <c r="AD48" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AE48" s="2" t="s">
-        <v>36</v>
+      <c r="AE48" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>37</v>
@@ -5898,6 +6011,98 @@
         <v>36</v>
       </c>
       <c r="AH48" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="3">
+        <v>140</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E49" s="3">
+        <v>60</v>
+      </c>
+      <c r="F49" s="3">
+        <v>210</v>
+      </c>
+      <c r="G49" s="3">
+        <v>50</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH49" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5908,7 +6113,212 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.822014808654785" customWidth="1" style="3"/>
+    <col min="2" max="2" width="14.972405433654785" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9.140625" customWidth="1" style="3"/>
+    <col min="4" max="4" width="9.140625" customWidth="1" style="3"/>
+    <col min="5" max="5" width="9.140625" customWidth="1" style="3"/>
+    <col min="6" max="6" width="9.140625" customWidth="1" style="3"/>
+    <col min="7" max="7" width="9.140625" customWidth="1" style="3"/>
+    <col min="8" max="8" width="9.140625" customWidth="1" style="3"/>
+    <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
+    <col min="10" max="10" width="16.645116806030273" customWidth="1" style="3"/>
+    <col min="11" max="11" width="9.140625" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9.140625" customWidth="1" style="3"/>
+    <col min="13" max="13" width="9.140625" customWidth="1" style="3"/>
+    <col min="14" max="14" width="9.140625" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
+    <col min="16" max="16" width="9.140625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="9.140625" customWidth="1" style="3"/>
+    <col min="18" max="18" width="9.947108268737793" customWidth="1" style="3"/>
+    <col min="19" max="19" width="13.856241226196289" customWidth="1" style="3"/>
+    <col min="20" max="20" width="9.140625" customWidth="1" style="3"/>
+    <col min="21" max="21" width="9.140625" customWidth="1" style="3"/>
+    <col min="22" max="22" width="9.540952682495117" customWidth="1" style="3"/>
+    <col min="23" max="23" width="9.140625" customWidth="1" style="3"/>
+    <col min="24" max="24" width="9.140625" customWidth="1" style="3"/>
+    <col min="25" max="25" width="10.328712463378906" customWidth="1" style="3"/>
+    <col min="26" max="26" width="11.9512939453125" customWidth="1" style="3"/>
+    <col min="27" max="27" width="11.877633094787598" customWidth="1" style="3"/>
+    <col min="28" max="28" width="9.140625" customWidth="1" style="3"/>
+    <col min="29" max="29" width="12.787137985229492" customWidth="1" style="3"/>
+    <col min="30" max="30" width="9.140625" customWidth="1" style="3"/>
+    <col min="31" max="31" width="9.140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="9.140625" customWidth="1" style="3"/>
+    <col min="33" max="33" width="9.140625" customWidth="1" style="3"/>
+    <col min="34" max="34" width="9.140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="9.140625" customWidth="1" style="3"/>
+    <col min="36" max="36" width="9.140625" customWidth="1" style="3"/>
+    <col min="37" max="37" width="9.140625" customWidth="1" style="3"/>
+    <col min="38" max="38" width="9.140625" customWidth="1" style="3"/>
+    <col min="39" max="39" width="9.140625" customWidth="1" style="3"/>
+    <col min="40" max="40" width="9.140625" customWidth="1" style="3"/>
+    <col min="41" max="41" width="9.140625" customWidth="1" style="3"/>
+    <col min="42" max="42" width="9.140625" customWidth="1" style="3"/>
+    <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
+    <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
+    <col min="45" max="16384" width="9.140625" customWidth="1" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="4" customFormat="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3">
+        <v>210</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E2" s="3">
+        <v>-16</v>
+      </c>
+      <c r="F2" s="3">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3">
+        <v>40</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:X28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.286670684814453" customWidth="1" style="3"/>
@@ -5920,7 +6330,7 @@
     <col min="7" max="7" width="9.140625" customWidth="1" style="3"/>
     <col min="8" max="8" width="9.140625" customWidth="1" style="3"/>
     <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
-    <col min="10" max="10" width="17.362285614013672" customWidth="1" style="3"/>
+    <col min="10" max="10" width="18.350568771362305" customWidth="1" style="3"/>
     <col min="11" max="11" width="23.763607025146484" customWidth="1" style="3"/>
     <col min="12" max="12" width="20.164461135864258" customWidth="1" style="3"/>
     <col min="13" max="13" width="18.38944435119629" customWidth="1" style="3"/>
@@ -5931,9 +6341,9 @@
     <col min="18" max="18" width="9.140625" customWidth="1" style="3"/>
     <col min="19" max="19" width="9.140625" customWidth="1" style="3"/>
     <col min="20" max="20" width="12.71347713470459" customWidth="1" style="3"/>
-    <col min="21" max="21" width="16.501888275146484" customWidth="1" style="3"/>
-    <col min="22" max="22" width="12.735984802246094" customWidth="1" style="3"/>
-    <col min="23" max="23" width="9.140625" customWidth="1" style="3"/>
+    <col min="21" max="21" width="9.140625" customWidth="1" style="3"/>
+    <col min="22" max="22" width="16.501888275146484" customWidth="1" style="3"/>
+    <col min="23" max="23" width="12.735984802246094" customWidth="1" style="3"/>
     <col min="24" max="24" width="9.140625" customWidth="1" style="3"/>
     <col min="25" max="25" width="9.140625" customWidth="1" style="3"/>
     <col min="26" max="26" width="9.140625" customWidth="1" style="3"/>
@@ -5954,7 +6364,8 @@
     <col min="41" max="41" width="9.140625" customWidth="1" style="3"/>
     <col min="42" max="42" width="9.140625" customWidth="1" style="3"/>
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
-    <col min="44" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
+    <col min="45" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -6004,21 +6415,24 @@
         <v>19</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="W1" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -6039,16 +6453,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>90</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>36</v>
@@ -6068,19 +6482,22 @@
       <c r="T2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>37</v>
+      <c r="U2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -6101,13 +6518,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>36</v>
@@ -6127,19 +6544,22 @@
       <c r="T3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>37</v>
+      <c r="U3" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>98</v>
@@ -6163,19 +6583,19 @@
         <v>10</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>36</v>
@@ -6198,58 +6618,61 @@
       <c r="U4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W4" s="2" t="s">
+      <c r="V4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X4" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="3">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D5" s="3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="3">
         <v>10</v>
       </c>
       <c r="F5" s="3">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="G5" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>36</v>
+        <v>265</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>37</v>
@@ -6257,64 +6680,64 @@
       <c r="T5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>36</v>
+      <c r="U5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="3">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="D6" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E6" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" s="3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>37</v>
+        <v>270</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>37</v>
@@ -6328,46 +6751,52 @@
       <c r="V6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W6" s="1" t="s">
-        <v>37</v>
+      <c r="W6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="D7" s="3">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="E7" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>120</v>
+        <v>128</v>
+      </c>
+      <c r="G7" s="3">
+        <v>35</v>
       </c>
       <c r="H7" s="3">
-        <v>60</v>
-      </c>
-      <c r="I7" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>36</v>
+        <v>274</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>37</v>
@@ -6378,64 +6807,67 @@
       <c r="R7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>37</v>
+      <c r="S7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>37</v>
+      <c r="V7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="3">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="D8" s="3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" s="3">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>148</v>
+        <v>277</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>149</v>
+        <v>278</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>151</v>
+        <v>279</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>37</v>
+      <c r="P8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>36</v>
@@ -6449,58 +6881,61 @@
       <c r="T8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>37</v>
+      <c r="U8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3">
-        <v>280</v>
+        <v>170</v>
       </c>
       <c r="D9" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3">
-        <v>70</v>
+        <v>40</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>59</v>
+        <v>282</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>36</v>
+      <c r="P9" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>36</v>
@@ -6508,8 +6943,8 @@
       <c r="R9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S9" s="1" t="s">
-        <v>37</v>
+      <c r="S9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>36</v>
@@ -6517,55 +6952,58 @@
       <c r="U9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V9" s="1" t="s">
-        <v>37</v>
+      <c r="V9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C10" s="3">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D10" s="3">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
-      </c>
-      <c r="G10" s="3">
-        <v>40</v>
+        <v>120</v>
+      </c>
+      <c r="H10" s="3">
+        <v>60</v>
+      </c>
+      <c r="I10" s="3">
+        <v>12</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>159</v>
+        <v>285</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>37</v>
+        <v>287</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>37</v>
+      <c r="Q10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>36</v>
@@ -6573,55 +7011,61 @@
       <c r="S10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>37</v>
+      <c r="T10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X10" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="D11" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="H11" s="3">
+        <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>36</v>
@@ -6632,58 +7076,64 @@
       <c r="Q11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>37</v>
+      <c r="R11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="3">
-        <v>245</v>
+        <v>190</v>
       </c>
       <c r="D12" s="3">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G12" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>242</v>
+        <v>156</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>36</v>
@@ -6691,11 +7141,11 @@
       <c r="P12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>36</v>
+      <c r="Q12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>37</v>
@@ -6703,93 +7153,102 @@
       <c r="T12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12" s="2" t="s">
+      <c r="U12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X12" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="3">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="D13" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
       </c>
       <c r="F13" s="3">
+        <v>90</v>
+      </c>
+      <c r="G13" s="3">
         <v>70</v>
       </c>
-      <c r="G13" s="3">
-        <v>50</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>171</v>
+        <v>294</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>37</v>
+      <c r="Q13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>36</v>
+      <c r="V13" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="3">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D14" s="3">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>80</v>
@@ -6798,16 +7257,16 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>277</v>
+        <v>165</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>278</v>
+        <v>166</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>279</v>
+        <v>167</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>37</v>
@@ -6815,8 +7274,8 @@
       <c r="P14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>36</v>
+      <c r="Q14" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>36</v>
@@ -6827,58 +7286,64 @@
       <c r="T14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U14" s="1" t="s">
-        <v>37</v>
+      <c r="U14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="3">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D15" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>282</v>
+        <v>170</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>283</v>
+        <v>171</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>37</v>
+        <v>298</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>37</v>
@@ -6886,58 +7351,61 @@
       <c r="S15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>37</v>
+      <c r="T15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V15" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="3">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D16" s="3">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="E16" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G16" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>185</v>
+        <v>65</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>186</v>
+        <v>66</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>36</v>
+        <v>252</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>37</v>
@@ -6945,55 +7413,58 @@
       <c r="R16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>37</v>
+      <c r="S16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V16" s="2" t="s">
-        <v>36</v>
+      <c r="V16" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="3">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="D17" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G17" s="3">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>288</v>
+        <v>175</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>289</v>
+        <v>176</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>37</v>
@@ -7010,61 +7481,58 @@
       <c r="S17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>37</v>
+      <c r="T17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W17" s="1" t="s">
+      <c r="W17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X17" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="D18" s="3">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G18" s="3">
-        <v>28</v>
-      </c>
-      <c r="H18" s="3">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>71</v>
+        <v>304</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>36</v>
+        <v>307</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>37</v>
@@ -7075,64 +7543,70 @@
       <c r="R18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S18" s="2" t="s">
-        <v>36</v>
+      <c r="S18" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W18" s="2" t="s">
+      <c r="U18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X18" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="D19" s="3">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G19" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>36</v>
+        <v>311</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>37</v>
@@ -7143,55 +7617,58 @@
       <c r="U19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>36</v>
+      <c r="V19" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="3">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D20" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>299</v>
+        <v>190</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>300</v>
+        <v>191</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>36</v>
+      <c r="P20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>36</v>
@@ -7209,12 +7686,15 @@
         <v>36</v>
       </c>
       <c r="W20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X20" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -7223,31 +7703,31 @@
         <v>210</v>
       </c>
       <c r="D21" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E21" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G21" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>198</v>
+        <v>315</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>36</v>
+        <v>318</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>36</v>
@@ -7255,8 +7735,8 @@
       <c r="Q21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>37</v>
+      <c r="R21" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>36</v>
@@ -7264,137 +7744,474 @@
       <c r="T21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>37</v>
+      <c r="U21" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W21" s="1" t="s">
+      <c r="W21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3">
-        <v>205</v>
+        <v>280</v>
       </c>
       <c r="D22" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E22" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="H22" s="3">
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q22" s="1" t="s">
-        <v>37</v>
+      <c r="Q22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>37</v>
+      <c r="S22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>36</v>
+      <c r="V22" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X22" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C23" s="3">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D23" s="3">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="3">
+        <v>70</v>
+      </c>
+      <c r="G23" s="3">
+        <v>20</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="3">
+        <v>260</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>70</v>
+      </c>
+      <c r="G24" s="3">
+        <v>30</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="3">
+        <v>210</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="3">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3">
+        <v>75</v>
+      </c>
+      <c r="G25" s="3">
+        <v>30</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3">
+        <v>205</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>75</v>
+      </c>
+      <c r="G26" s="3">
+        <v>40</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3">
+        <v>190</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>50</v>
+      </c>
+      <c r="F27" s="3">
+        <v>128</v>
+      </c>
+      <c r="G27" s="3">
+        <v>40</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3">
+        <v>210</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
         <v>120</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G28" s="3">
         <v>64</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H28" s="3">
         <v>25</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M28" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W23" s="1" t="s">
+      <c r="O28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X28" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -7403,9 +8220,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.112842559814453" customWidth="1" style="3"/>
@@ -7451,7 +8268,8 @@
     <col min="41" max="41" width="9.140625" customWidth="1" style="3"/>
     <col min="42" max="42" width="9.140625" customWidth="1" style="3"/>
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
-    <col min="44" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
+    <col min="45" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -7489,16 +8307,16 @@
         <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>19</v>
@@ -7515,7 +8333,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -7539,7 +8357,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>36</v>
@@ -7571,7 +8389,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -7592,10 +8410,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>91</v>
@@ -7630,7 +8448,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -7654,13 +8472,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>96</v>
@@ -7695,7 +8513,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>98</v>
@@ -7719,16 +8537,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>37</v>
@@ -7760,7 +8578,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -7781,10 +8599,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>36</v>
@@ -7816,7 +8634,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -7837,16 +8655,16 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>113</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>37</v>
@@ -7878,7 +8696,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -7902,16 +8720,16 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>37</v>
@@ -7943,7 +8761,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -7964,13 +8782,13 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>120</v>
@@ -8005,7 +8823,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>42</v>
@@ -8026,16 +8844,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>126</v>
@@ -8070,7 +8888,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -8091,10 +8909,10 @@
         <v>37</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>45</v>
@@ -8132,7 +8950,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -8194,7 +9012,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>98</v>
@@ -8218,13 +9036,13 @@
         <v>12</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>36</v>
@@ -8256,43 +9074,43 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D14" s="3">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3">
         <v>128</v>
       </c>
       <c r="G14" s="3">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="H14" s="3">
+        <v>9</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>380</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>49</v>
+        <v>381</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>348</v>
+        <v>138</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>37</v>
+        <v>290</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>37</v>
@@ -8321,7 +9139,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -8330,31 +9148,34 @@
         <v>220</v>
       </c>
       <c r="D15" s="3">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="E15" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>128</v>
       </c>
       <c r="G15" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>350</v>
+        <v>48</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>351</v>
+        <v>49</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>37</v>
@@ -8383,13 +9204,13 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="3">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="D16" s="3">
         <v>0.35</v>
@@ -8401,22 +9222,19 @@
         <v>128</v>
       </c>
       <c r="G16" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>36</v>
@@ -8424,126 +9242,129 @@
       <c r="P16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>37</v>
+      <c r="Q16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="3">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="D17" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3">
         <v>128</v>
       </c>
       <c r="G17" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="L17" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>37</v>
+      <c r="O17" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>36</v>
+      <c r="Q17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="3">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="D18" s="3">
         <v>0.4</v>
       </c>
       <c r="E18" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>128</v>
       </c>
       <c r="G18" s="3">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>365</v>
+        <v>162</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>162</v>
+        <v>396</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>37</v>
@@ -8575,16 +9396,16 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="3">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E19" s="3">
         <v>32</v>
@@ -8593,78 +9414,78 @@
         <v>128</v>
       </c>
       <c r="G19" s="3">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>270</v>
+        <v>398</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>36</v>
+        <v>400</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>37</v>
+      <c r="Q19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="3">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="D20" s="3">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3">
         <v>128</v>
       </c>
       <c r="G20" s="3">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>64</v>
+        <v>297</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>65</v>
+        <v>402</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>36</v>
@@ -8696,7 +9517,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -8705,25 +9526,28 @@
         <v>245</v>
       </c>
       <c r="D21" s="3">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="E21" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>128</v>
       </c>
       <c r="G21" s="3">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>373</v>
+        <v>64</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>374</v>
+        <v>65</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>375</v>
+        <v>405</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>36</v>
@@ -8755,34 +9579,37 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="3">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D22" s="3">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="G22" s="3">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>37</v>
+        <v>409</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>37</v>
@@ -8790,28 +9617,28 @@
       <c r="Q22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>36</v>
+      <c r="R22" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>36</v>
+      <c r="T22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -8820,28 +9647,22 @@
         <v>250</v>
       </c>
       <c r="D23" s="3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="G23" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>178</v>
+        <v>413</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>37</v>
@@ -8849,14 +9670,14 @@
       <c r="P23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q23" s="1" t="s">
-        <v>37</v>
+      <c r="Q23" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>37</v>
+      <c r="S23" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>36</v>
@@ -8873,72 +9694,78 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="3">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D24" s="3">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3">
         <v>128</v>
       </c>
       <c r="G24" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>68</v>
+        <v>415</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>36</v>
+        <v>416</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>37</v>
+      <c r="Q24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D25" s="3">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -8947,57 +9774,54 @@
         <v>128</v>
       </c>
       <c r="G25" s="3">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>385</v>
+        <v>68</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q25" s="1" t="s">
-        <v>37</v>
+      <c r="Q25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S25" s="1" t="s">
-        <v>37</v>
+      <c r="S25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U25" s="2" t="s">
-        <v>36</v>
+      <c r="U25" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W25" s="2" t="s">
-        <v>36</v>
+      <c r="W25" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D26" s="3">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
@@ -9009,31 +9833,31 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>184</v>
+        <v>420</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>422</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>36</v>
+      <c r="Q26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>36</v>
@@ -9047,37 +9871,34 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="3">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D27" s="3">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
         <v>128</v>
       </c>
       <c r="G27" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>196</v>
+        <v>425</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>36</v>
@@ -9088,61 +9909,58 @@
       <c r="Q27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R27" s="1" t="s">
-        <v>37</v>
+      <c r="R27" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="S27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>37</v>
+      <c r="T27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V27" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W27" s="1" t="s">
-        <v>37</v>
+      <c r="W27" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C28" s="3">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D28" s="3">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E28" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F28" s="3">
         <v>128</v>
       </c>
       <c r="G28" s="3">
-        <v>33</v>
-      </c>
-      <c r="H28" s="3">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>71</v>
+        <v>315</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>72</v>
+        <v>427</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>396</v>
+        <v>201</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>36</v>
@@ -9174,10 +9992,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C29" s="3">
         <v>180</v>
@@ -9192,16 +10010,22 @@
         <v>128</v>
       </c>
       <c r="G29" s="3">
-        <v>25</v>
+        <v>33</v>
+      </c>
+      <c r="H29" s="3">
+        <v>8</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>398</v>
+        <v>71</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>399</v>
+        <v>430</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>36</v>
@@ -9233,16 +10057,16 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="3">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="D30" s="3">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E30" s="3">
         <v>0</v>
@@ -9251,102 +10075,102 @@
         <v>128</v>
       </c>
       <c r="G30" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>80</v>
+        <v>433</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>37</v>
+        <v>434</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>36</v>
+      <c r="Q30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="3">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D31" s="3">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E31" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3">
         <v>128</v>
       </c>
       <c r="G31" s="3">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>36</v>
+        <v>82</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>36</v>
+      <c r="Q31" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S31" s="2" t="s">
-        <v>36</v>
+      <c r="S31" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>37</v>
+      <c r="U31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>36</v>
@@ -9354,19 +10178,19 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D32" s="3">
         <v>0.5</v>
       </c>
       <c r="E32" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F32" s="3">
         <v>128</v>
@@ -9375,37 +10199,37 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>37</v>
+        <v>439</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q32" s="1" t="s">
-        <v>37</v>
+      <c r="Q32" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S32" s="1" t="s">
-        <v>37</v>
+      <c r="S32" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>36</v>
+      <c r="U32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>36</v>
@@ -9413,34 +10237,34 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D33" s="3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F33" s="3">
         <v>128</v>
       </c>
       <c r="G33" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>410</v>
+        <v>208</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>37</v>
@@ -9448,14 +10272,14 @@
       <c r="P33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>36</v>
+      <c r="Q33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>36</v>
@@ -9466,37 +10290,43 @@
       <c r="V33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W33" s="1" t="s">
-        <v>37</v>
+      <c r="W33" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>412</v>
+        <v>443</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="3">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G34" s="3">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>36</v>
+        <v>444</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>37</v>
@@ -9504,8 +10334,8 @@
       <c r="Q34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R34" s="2" t="s">
-        <v>36</v>
+      <c r="R34" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>36</v>
@@ -9519,40 +10349,34 @@
       <c r="V34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W34" s="2" t="s">
-        <v>36</v>
+      <c r="W34" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>414</v>
+        <v>447</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="3">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="D35" s="3">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E35" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G35" s="3">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>216</v>
+        <v>448</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>36</v>
@@ -9560,90 +10384,149 @@
       <c r="P35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q35" s="1" t="s">
-        <v>37</v>
+      <c r="Q35" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S35" s="1" t="s">
-        <v>37</v>
+      <c r="S35" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="U35" s="1" t="s">
-        <v>37</v>
+      <c r="U35" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W35" s="1" t="s">
-        <v>37</v>
+      <c r="W35" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D36" s="3">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E36" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F36" s="3">
         <v>128</v>
       </c>
       <c r="G36" s="3">
+        <v>45</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="3">
+        <v>180</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>128</v>
+      </c>
+      <c r="G37" s="3">
         <v>33</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H37" s="3">
         <v>7</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W36" s="2" t="s">
+      <c r="O37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W37" s="2" t="s">
         <v>36</v>
       </c>
     </row>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1004,16 +1004,13 @@
     <t>moon_desh</t>
   </si>
   <si>
-    <t>desh: 40 [2]</t>
-  </si>
-  <si>
-    <t>ilmenite: 25 [1]</t>
-  </si>
-  <si>
-    <t>aluminium: 20</t>
-  </si>
-  <si>
-    <t>armalcolite: 15</t>
+    <t>desh: 25 [2]</t>
+  </si>
+  <si>
+    <t>ilmenite: 30 [1]</t>
+  </si>
+  <si>
+    <t>aluminium: 25</t>
   </si>
   <si>
     <t>moon_garnet</t>
@@ -4121,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>146</v>
@@ -8821,7 +8818,7 @@
         <v>200</v>
       </c>
       <c r="D3" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -8830,7 +8827,7 @@
         <v>80</v>
       </c>
       <c r="G3" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>315</v>
@@ -8883,7 +8880,7 @@
         <v>260</v>
       </c>
       <c r="D4" s="3">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -8895,7 +8892,7 @@
         <v>70</v>
       </c>
       <c r="I4" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>319</v>
@@ -8963,7 +8960,7 @@
         <v>128</v>
       </c>
       <c r="G5" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>323</v>
@@ -9093,7 +9090,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="3">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>329</v>
@@ -9105,7 +9102,7 @@
         <v>331</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>36</v>
@@ -9140,7 +9137,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9164,16 +9161,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
@@ -9208,7 +9205,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9217,7 +9214,7 @@
         <v>250</v>
       </c>
       <c r="D9" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E9" s="3">
         <v>5</v>
@@ -9226,7 +9223,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>276</v>
@@ -9238,7 +9235,7 @@
         <v>125</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>127</v>
@@ -9276,7 +9273,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9285,7 +9282,7 @@
         <v>170</v>
       </c>
       <c r="D10" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E10" s="3">
         <v>10</v>
@@ -9294,7 +9291,7 @@
         <v>80</v>
       </c>
       <c r="G10" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3">
         <v>10</v>
@@ -9306,7 +9303,7 @@
         <v>268</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>131</v>
@@ -9344,7 +9341,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9353,7 +9350,7 @@
         <v>260</v>
       </c>
       <c r="D11" s="3">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -9365,16 +9362,16 @@
         <v>60</v>
       </c>
       <c r="I11" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>345</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>35</v>
@@ -9409,7 +9406,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9427,7 +9424,7 @@
         <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3">
         <v>9</v>
@@ -9436,13 +9433,13 @@
         <v>137</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>202</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>313</v>
@@ -9480,7 +9477,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9498,7 +9495,7 @@
         <v>66</v>
       </c>
       <c r="G13" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>154</v>
@@ -9548,7 +9545,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9557,7 +9554,7 @@
         <v>280</v>
       </c>
       <c r="D14" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -9566,16 +9563,16 @@
         <v>90</v>
       </c>
       <c r="G14" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9616,7 +9613,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9625,7 +9622,7 @@
         <v>215</v>
       </c>
       <c r="D15" s="3">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E15" s="3">
         <v>5</v>
@@ -9634,7 +9631,7 @@
         <v>80</v>
       </c>
       <c r="G15" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>165</v>
@@ -9681,7 +9678,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9702,7 +9699,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>171</v>
@@ -9711,7 +9708,7 @@
         <v>172</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>313</v>
@@ -9749,7 +9746,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9758,7 +9755,7 @@
         <v>245</v>
       </c>
       <c r="D17" s="3">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -9767,7 +9764,7 @@
         <v>50</v>
       </c>
       <c r="G17" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>68</v>
@@ -9814,7 +9811,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9832,7 +9829,7 @@
         <v>70</v>
       </c>
       <c r="G18" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>274</v>
@@ -9844,7 +9841,7 @@
         <v>177</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>36</v>
@@ -9879,7 +9876,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -9897,19 +9894,19 @@
         <v>80</v>
       </c>
       <c r="G19" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>36</v>
@@ -9944,7 +9941,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -9962,19 +9959,19 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>36</v>
@@ -10009,7 +10006,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10027,7 +10024,7 @@
         <v>100</v>
       </c>
       <c r="G21" s="3">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>190</v>
@@ -10074,7 +10071,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10092,19 +10089,19 @@
         <v>90</v>
       </c>
       <c r="G22" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>36</v>
@@ -10139,7 +10136,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10175,7 +10172,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -10210,7 +10207,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10219,7 +10216,7 @@
         <v>200</v>
       </c>
       <c r="D24" s="3">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -10231,13 +10228,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>35</v>
@@ -10272,7 +10269,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10281,7 +10278,7 @@
         <v>210</v>
       </c>
       <c r="D25" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E25" s="3">
         <v>20</v>
@@ -10296,7 +10293,7 @@
         <v>204</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>265</v>
@@ -10337,7 +10334,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10346,7 +10343,7 @@
         <v>205</v>
       </c>
       <c r="D26" s="3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E26" s="3">
         <v>2</v>
@@ -10355,13 +10352,13 @@
         <v>75</v>
       </c>
       <c r="G26" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>217</v>
@@ -10399,7 +10396,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10417,19 +10414,19 @@
         <v>128</v>
       </c>
       <c r="G27" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>222</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -10464,7 +10461,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10473,7 +10470,7 @@
         <v>210</v>
       </c>
       <c r="D28" s="3">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E28" s="3">
         <v>0</v>
@@ -10482,10 +10479,10 @@
         <v>120</v>
       </c>
       <c r="G28" s="3">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H28" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>85</v>
@@ -10622,16 +10619,16 @@
         <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>19</v>
@@ -10648,7 +10645,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10672,7 +10669,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>35</v>
@@ -10704,7 +10701,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10725,10 +10722,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10763,7 +10760,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10787,13 +10784,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>403</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10828,7 +10825,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10893,7 +10890,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -10914,10 +10911,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>35</v>
@@ -10949,7 +10946,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11011,7 +11008,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11032,16 +11029,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>114</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
@@ -11073,7 +11070,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11097,16 +11094,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>36</v>
@@ -11138,7 +11135,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11159,13 +11156,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>121</v>
@@ -11200,7 +11197,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11227,10 +11224,10 @@
         <v>277</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>127</v>
@@ -11265,7 +11262,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11286,10 +11283,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11327,7 +11324,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11389,7 +11386,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11413,13 +11410,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>35</v>
@@ -11451,7 +11448,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11475,16 +11472,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>139</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>35</v>
@@ -11516,7 +11513,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11543,7 +11540,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11581,7 +11578,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11602,13 +11599,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>149</v>
@@ -11643,7 +11640,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11667,13 +11664,13 @@
         <v>272</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>158</v>
@@ -11708,7 +11705,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11729,16 +11726,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>163</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11773,7 +11770,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11797,10 +11794,10 @@
         <v>290</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>168</v>
@@ -11835,7 +11832,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11856,13 +11853,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K21" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>35</v>
@@ -11894,7 +11891,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -11921,10 +11918,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>35</v>
@@ -11956,7 +11953,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -11977,13 +11974,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -12015,7 +12012,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12036,7 +12033,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>36</v>
@@ -12068,7 +12065,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12089,13 +12086,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>184</v>
@@ -12130,7 +12127,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12189,7 +12186,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12210,13 +12207,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>36</v>
@@ -12248,7 +12245,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12272,10 +12269,10 @@
         <v>190</v>
       </c>
       <c r="K28" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>35</v>
@@ -12307,7 +12304,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12328,13 +12325,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K29" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>477</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>202</v>
@@ -12369,7 +12366,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12399,10 +12396,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>35</v>
@@ -12434,7 +12431,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12455,13 +12452,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>35</v>
@@ -12493,7 +12490,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12517,10 +12514,10 @@
         <v>264</v>
       </c>
       <c r="K32" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>35</v>
@@ -12552,7 +12549,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12573,13 +12570,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>209</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>36</v>
@@ -12611,7 +12608,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12632,13 +12629,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>36</v>
@@ -12670,7 +12667,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12691,7 +12688,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>35</v>
@@ -12723,7 +12720,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12744,10 +12741,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>222</v>
@@ -12782,7 +12779,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t>Vein ID</t>
   </si>
@@ -329,379 +329,376 @@
     <t>normal_bismuthinite</t>
   </si>
   <si>
+    <t>bismuth: 70</t>
+  </si>
+  <si>
+    <t>sulfur: 9</t>
+  </si>
+  <si>
+    <t>lead: 11</t>
+  </si>
+  <si>
+    <t>silver: 10</t>
+  </si>
+  <si>
+    <t>normal_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 40 [1]</t>
+  </si>
+  <si>
+    <t>tin: 60 [1]</t>
+  </si>
+  <si>
+    <t>normal_coal</t>
+  </si>
+  <si>
+    <t>coal: 100 [1]</t>
+  </si>
+  <si>
+    <t>normal_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 20</t>
+  </si>
+  <si>
+    <t>hematite: 5</t>
+  </si>
+  <si>
+    <t>pyrite: 10</t>
+  </si>
+  <si>
+    <t>copper: 65 [1]</t>
+  </si>
+  <si>
+    <t>normal_garnet_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 35</t>
+  </si>
+  <si>
+    <t>garnet_sand: 25</t>
+  </si>
+  <si>
+    <t>asbestos: 25</t>
+  </si>
+  <si>
+    <t>diatomite: 15</t>
+  </si>
+  <si>
+    <t>normal_garnierite</t>
+  </si>
+  <si>
+    <t>garnierite: 30 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 10</t>
+  </si>
+  <si>
+    <t>cobaltite: 20</t>
+  </si>
+  <si>
+    <t>pentlandite: 25</t>
+  </si>
+  <si>
+    <t>cobalt: 15</t>
+  </si>
+  <si>
+    <t>normal_gold</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 20</t>
+  </si>
+  <si>
+    <t>hematite: 20</t>
+  </si>
+  <si>
+    <t>gold: 55 [1]</t>
+  </si>
+  <si>
+    <t>normal_graphite</t>
+  </si>
+  <si>
+    <t>graphite: 45</t>
+  </si>
+  <si>
+    <t>diamond: 25</t>
+  </si>
+  <si>
+    <t>coal: 30</t>
+  </si>
+  <si>
+    <t>normal_gypsum</t>
+  </si>
+  <si>
+    <t>borax: 20</t>
+  </si>
+  <si>
+    <t>calcite: 30</t>
+  </si>
+  <si>
+    <t>fullers_earth: 15</t>
+  </si>
+  <si>
+    <t>gypsum: 35</t>
+  </si>
+  <si>
+    <t>normal_hematite</t>
+  </si>
+  <si>
+    <t>goethite: 15</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 30</t>
+  </si>
+  <si>
+    <t>hematite: 50 [1]</t>
+  </si>
+  <si>
+    <t>normal_lapis</t>
+  </si>
+  <si>
+    <t>lazurite: 35</t>
+  </si>
+  <si>
+    <t>sodalite: 25</t>
+  </si>
+  <si>
+    <t>lapis: 25</t>
+  </si>
+  <si>
+    <t>calcite: 15</t>
+  </si>
+  <si>
+    <t>normal_limonite</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 50 [1]</t>
+  </si>
+  <si>
+    <t>malachite: 15</t>
+  </si>
+  <si>
+    <t>normal_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone: 30</t>
+  </si>
+  <si>
+    <t>talc: 20</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 25</t>
+  </si>
+  <si>
+    <t>pentlandite: 15</t>
+  </si>
+  <si>
+    <t>trona: 10</t>
+  </si>
+  <si>
+    <t>normal_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 70 [1]</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 25</t>
+  </si>
+  <si>
+    <t>gold: 10</t>
+  </si>
+  <si>
+    <t>chromite: 5</t>
+  </si>
+  <si>
+    <t>normal_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 30</t>
+  </si>
+  <si>
+    <t>spessartine: 20</t>
+  </si>
+  <si>
+    <t>pyrolusite: 20</t>
+  </si>
+  <si>
+    <t>tantalite: 10</t>
+  </si>
+  <si>
+    <t>normal_mica</t>
+  </si>
+  <si>
+    <t>kyanite: 35</t>
+  </si>
+  <si>
+    <t>mica: 25</t>
+  </si>
+  <si>
+    <t>bauxite: 25</t>
+  </si>
+  <si>
+    <t>pollucite: 15</t>
+  </si>
+  <si>
+    <t>normal_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite: 50</t>
+  </si>
+  <si>
+    <t>monazite: 25</t>
+  </si>
+  <si>
+    <t>neodymium: 5</t>
+  </si>
+  <si>
+    <t>normal_oilsands</t>
+  </si>
+  <si>
+    <t>oilsands: 100 [1]</t>
+  </si>
+  <si>
+    <t>normal_olivine</t>
+  </si>
+  <si>
+    <t>bentonite: 35</t>
+  </si>
+  <si>
+    <t>magnesite: 25</t>
+  </si>
+  <si>
+    <t>olivine: 25</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 15</t>
+  </si>
+  <si>
+    <t>normal_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 35 [1]</t>
+  </si>
+  <si>
+    <t>barite: 30</t>
+  </si>
+  <si>
+    <t>asbestos: 15</t>
+  </si>
+  <si>
+    <t>normal_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 45 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 35</t>
+  </si>
+  <si>
+    <t>cinnabar: 20</t>
+  </si>
+  <si>
+    <t>normal_salt</t>
+  </si>
+  <si>
+    <t>rock_salt: 40 [1]</t>
+  </si>
+  <si>
+    <t>salt: 30 [1]</t>
+  </si>
+  <si>
+    <t>lepidolite: 15</t>
+  </si>
+  <si>
+    <t>borax: 15</t>
+  </si>
+  <si>
+    <t>normal_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 35</t>
+  </si>
+  <si>
+    <t>diatomite: 25</t>
+  </si>
+  <si>
+    <t>electrotine: 25</t>
+  </si>
+  <si>
+    <t>alunite: 15</t>
+  </si>
+  <si>
+    <t>normal_silver</t>
+  </si>
+  <si>
+    <t>galena: 30</t>
+  </si>
+  <si>
+    <t>silver: 15</t>
+  </si>
+  <si>
+    <t>lead: 55 [1]</t>
+  </si>
+  <si>
+    <t>normal_sphalerite</t>
+  </si>
+  <si>
+    <t>sulfur: 35</t>
+  </si>
+  <si>
+    <t>sphalerite: 40 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 25</t>
+  </si>
+  <si>
+    <t>normal_spodumene</t>
+  </si>
+  <si>
+    <t>rock_salt: 20</t>
+  </si>
+  <si>
+    <t>salt: 30</t>
+  </si>
+  <si>
+    <t>spodumene: 35</t>
+  </si>
+  <si>
+    <t>normal_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 50 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 35</t>
+  </si>
+  <si>
+    <t>sphalerite: 15</t>
+  </si>
+  <si>
+    <t>normal_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 50 [1]</t>
+  </si>
+  <si>
+    <t>copper: 30</t>
+  </si>
+  <si>
+    <t>stibnite: 20</t>
+  </si>
+  <si>
+    <t>surface_bismuthinite</t>
+  </si>
+  <si>
     <t>bismuth: 80</t>
   </si>
   <si>
-    <t>sulfur: 9</t>
-  </si>
-  <si>
-    <t>lead: 11</t>
-  </si>
-  <si>
-    <t>silver: 10</t>
-  </si>
-  <si>
-    <t>normal_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 40 [1]</t>
-  </si>
-  <si>
-    <t>tin: 60 [1]</t>
-  </si>
-  <si>
-    <t>normal_coal</t>
-  </si>
-  <si>
-    <t>coal: 100 [1]</t>
-  </si>
-  <si>
-    <t>normal_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite: 20</t>
-  </si>
-  <si>
-    <t>hematite: 5</t>
-  </si>
-  <si>
-    <t>pyrite: 10</t>
-  </si>
-  <si>
-    <t>copper: 65 [1]</t>
-  </si>
-  <si>
-    <t>normal_garnet_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 35</t>
-  </si>
-  <si>
-    <t>garnet_sand: 25</t>
-  </si>
-  <si>
-    <t>asbestos: 25</t>
-  </si>
-  <si>
-    <t>diatomite: 15</t>
-  </si>
-  <si>
-    <t>normal_garnierite</t>
-  </si>
-  <si>
-    <t>garnierite: 30 [1]</t>
-  </si>
-  <si>
-    <t>nickel: 10</t>
-  </si>
-  <si>
-    <t>cobaltite: 20</t>
-  </si>
-  <si>
-    <t>pentlandite: 25</t>
-  </si>
-  <si>
-    <t>cobalt: 15</t>
-  </si>
-  <si>
-    <t>normal_gold</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 20</t>
-  </si>
-  <si>
-    <t>hematite: 20</t>
-  </si>
-  <si>
-    <t>gold: 55 [1]</t>
-  </si>
-  <si>
-    <t>normal_graphite</t>
-  </si>
-  <si>
-    <t>graphite: 45</t>
-  </si>
-  <si>
-    <t>diamond: 25</t>
-  </si>
-  <si>
-    <t>coal: 30</t>
-  </si>
-  <si>
-    <t>normal_gypsum</t>
-  </si>
-  <si>
-    <t>borax: 20</t>
-  </si>
-  <si>
-    <t>calcite: 30</t>
-  </si>
-  <si>
-    <t>fullers_earth: 15</t>
-  </si>
-  <si>
-    <t>gypsum: 35</t>
-  </si>
-  <si>
-    <t>normal_hematite</t>
-  </si>
-  <si>
-    <t>goethite: 15</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 30</t>
-  </si>
-  <si>
-    <t>hematite: 50 [1]</t>
-  </si>
-  <si>
-    <t>normal_lapis</t>
-  </si>
-  <si>
-    <t>lazurite: 35</t>
-  </si>
-  <si>
-    <t>sodalite: 25</t>
-  </si>
-  <si>
-    <t>lapis: 25</t>
-  </si>
-  <si>
-    <t>calcite: 15</t>
-  </si>
-  <si>
-    <t>normal_limonite</t>
-  </si>
-  <si>
-    <t>yellow_limonite: 50 [1]</t>
-  </si>
-  <si>
-    <t>malachite: 15</t>
-  </si>
-  <si>
-    <t>normal_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone: 30</t>
-  </si>
-  <si>
-    <t>talc: 20</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 25</t>
-  </si>
-  <si>
-    <t>pentlandite: 15</t>
-  </si>
-  <si>
-    <t>trona: 10</t>
-  </si>
-  <si>
-    <t>normal_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite: 70 [1]</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 25</t>
-  </si>
-  <si>
-    <t>gold: 10</t>
-  </si>
-  <si>
-    <t>chromite: 5</t>
-  </si>
-  <si>
-    <t>normal_manganese</t>
-  </si>
-  <si>
-    <t>grossular: 30</t>
-  </si>
-  <si>
-    <t>spessartine: 20</t>
-  </si>
-  <si>
-    <t>pyrolusite: 20</t>
-  </si>
-  <si>
-    <t>tantalite: 10</t>
-  </si>
-  <si>
-    <t>normal_mica</t>
-  </si>
-  <si>
-    <t>kyanite: 35</t>
-  </si>
-  <si>
-    <t>mica: 25</t>
-  </si>
-  <si>
-    <t>bauxite: 25</t>
-  </si>
-  <si>
-    <t>pollucite: 15</t>
-  </si>
-  <si>
-    <t>normal_monazite</t>
-  </si>
-  <si>
-    <t>bastnasite: 50</t>
-  </si>
-  <si>
-    <t>monazite: 25</t>
-  </si>
-  <si>
-    <t>neodymium: 5</t>
-  </si>
-  <si>
-    <t>normal_oilsands</t>
-  </si>
-  <si>
-    <t>oilsands: 100 [1]</t>
-  </si>
-  <si>
-    <t>normal_olivine</t>
-  </si>
-  <si>
-    <t>bentonite: 35</t>
-  </si>
-  <si>
-    <t>magnesite: 25</t>
-  </si>
-  <si>
-    <t>olivine: 25</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 15</t>
-  </si>
-  <si>
-    <t>normal_quartz</t>
-  </si>
-  <si>
-    <t>quartzite: 35 [1]</t>
-  </si>
-  <si>
-    <t>barite: 30</t>
-  </si>
-  <si>
-    <t>asbestos: 15</t>
-  </si>
-  <si>
-    <t>normal_redstone</t>
-  </si>
-  <si>
-    <t>redstone: 45 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 35</t>
-  </si>
-  <si>
-    <t>cinnabar: 20</t>
-  </si>
-  <si>
-    <t>normal_salt</t>
-  </si>
-  <si>
-    <t>rock_salt: 40 [1]</t>
-  </si>
-  <si>
-    <t>salt: 30 [1]</t>
-  </si>
-  <si>
-    <t>lepidolite: 15</t>
-  </si>
-  <si>
-    <t>borax: 15</t>
-  </si>
-  <si>
-    <t>normal_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter: 35</t>
-  </si>
-  <si>
-    <t>diatomite: 25</t>
-  </si>
-  <si>
-    <t>electrotine: 25</t>
-  </si>
-  <si>
-    <t>alunite: 15</t>
-  </si>
-  <si>
-    <t>normal_silver</t>
-  </si>
-  <si>
-    <t>galena: 30</t>
-  </si>
-  <si>
-    <t>silver: 15</t>
-  </si>
-  <si>
-    <t>lead: 55 [1]</t>
-  </si>
-  <si>
-    <t>normal_sphalerite</t>
-  </si>
-  <si>
-    <t>sulfur: 35</t>
-  </si>
-  <si>
-    <t>sphalerite: 40 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 25</t>
-  </si>
-  <si>
-    <t>normal_spodumene</t>
-  </si>
-  <si>
-    <t>rock_salt: 20</t>
-  </si>
-  <si>
-    <t>salt: 30</t>
-  </si>
-  <si>
-    <t>spodumene: 35</t>
-  </si>
-  <si>
-    <t>normal_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur: 50 [1]</t>
-  </si>
-  <si>
-    <t>pyrite: 35</t>
-  </si>
-  <si>
-    <t>sphalerite: 15</t>
-  </si>
-  <si>
-    <t>normal_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite: 50 [1]</t>
-  </si>
-  <si>
-    <t>copper: 30</t>
-  </si>
-  <si>
-    <t>stibnite: 20</t>
-  </si>
-  <si>
-    <t>surface_bismuthinite</t>
-  </si>
-  <si>
-    <t>bismuth: 85</t>
-  </si>
-  <si>
     <t>sulfur: 3</t>
   </si>
   <si>
     <t>lead: 7</t>
-  </si>
-  <si>
-    <t>silver: 5</t>
   </si>
   <si>
     <t>surface_cassiterite</t>
@@ -2424,8 +2421,8 @@
       <c r="AB8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>35</v>
+      <c r="AC8" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD8" s="2" t="s">
         <v>35</v>
@@ -2647,7 +2644,7 @@
         <v>-64</v>
       </c>
       <c r="F11" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3">
         <v>28</v>
@@ -2688,8 +2685,8 @@
       <c r="V11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W11" s="2" t="s">
-        <v>35</v>
+      <c r="W11" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>35</v>
@@ -2926,16 +2923,16 @@
         <v>31</v>
       </c>
       <c r="C14" s="3">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="D14" s="3">
         <v>0.25</v>
       </c>
       <c r="E14" s="3">
-        <v>-32</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G14" s="3">
         <v>34</v>
@@ -5868,7 +5865,7 @@
         <v>227</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>35</v>
@@ -5933,7 +5930,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
@@ -5954,10 +5951,10 @@
         <v>50</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>35</v>
@@ -6022,7 +6019,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>31</v>
@@ -6043,16 +6040,16 @@
         <v>50</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>36</v>
@@ -6117,7 +6114,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>31</v>
@@ -6138,13 +6135,13 @@
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>36</v>
@@ -6209,7 +6206,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>31</v>
@@ -6230,10 +6227,10 @@
         <v>50</v>
       </c>
       <c r="J49" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>223</v>
@@ -6425,10 +6422,10 @@
         <v>22</v>
       </c>
       <c r="AB1" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC1" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="AD1" s="4" t="s">
         <v>26</v>
@@ -6437,12 +6434,12 @@
         <v>28</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -6469,7 +6466,7 @@
         <v>192</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -6525,7 +6522,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -6549,7 +6546,7 @@
         <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>73</v>
@@ -6608,7 +6605,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -6632,13 +6629,13 @@
         <v>32</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -6694,7 +6691,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -6721,7 +6718,7 @@
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>78</v>
@@ -6786,7 +6783,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -6872,7 +6869,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>99</v>
@@ -6902,7 +6899,7 @@
         <v>101</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -6958,7 +6955,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -6979,10 +6976,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>35</v>
@@ -7038,7 +7035,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -7059,10 +7056,10 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>116</v>
@@ -7124,7 +7121,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -7145,13 +7142,13 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>206</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>115</v>
@@ -7210,7 +7207,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7231,13 +7228,13 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>132</v>
@@ -7296,7 +7293,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>99</v>
@@ -7320,16 +7317,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -7385,7 +7382,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -7471,7 +7468,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -7492,19 +7489,19 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>115</v>
@@ -7563,7 +7560,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -7584,7 +7581,7 @@
         <v>45</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>177</v>
@@ -7649,7 +7646,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -7670,10 +7667,10 @@
         <v>55</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>126</v>
@@ -7735,7 +7732,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -7756,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -7818,7 +7815,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -7904,7 +7901,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -7928,7 +7925,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>214</v>
@@ -7993,7 +7990,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -8079,7 +8076,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -8100,13 +8097,13 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>131</v>
@@ -8165,7 +8162,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -8186,16 +8183,16 @@
         <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8251,7 +8248,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8275,7 +8272,7 @@
         <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>83</v>
@@ -8337,7 +8334,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8358,16 +8355,16 @@
         <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>309</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8423,7 +8420,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8444,13 +8441,13 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>313</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8506,7 +8503,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8536,7 +8533,7 @@
         <v>55</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8592,7 +8589,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8616,7 +8613,7 @@
         <v>219</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>205</v>
@@ -8625,7 +8622,7 @@
         <v>107</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8681,7 +8678,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -8702,16 +8699,16 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>223</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -8870,16 +8867,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -8887,7 +8884,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -8908,16 +8905,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -8952,7 +8949,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -8973,13 +8970,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>331</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9014,7 +9011,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -9038,16 +9035,16 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>213</v>
@@ -9085,7 +9082,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9106,16 +9103,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9150,7 +9147,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9174,13 +9171,13 @@
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -9215,7 +9212,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9236,16 +9233,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9280,7 +9277,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9304,16 +9301,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9348,7 +9345,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9369,16 +9366,16 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>126</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>128</v>
@@ -9416,7 +9413,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9440,13 +9437,13 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>132</v>
@@ -9484,7 +9481,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9508,13 +9505,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9549,7 +9546,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9576,16 +9573,16 @@
         <v>138</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9620,7 +9617,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9688,7 +9685,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9709,13 +9706,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9756,7 +9753,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9821,7 +9818,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9842,7 +9839,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>172</v>
@@ -9851,10 +9848,10 @@
         <v>173</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -9889,7 +9886,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -9919,7 +9916,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -9954,7 +9951,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -9975,7 +9972,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>177</v>
@@ -9984,7 +9981,7 @@
         <v>178</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10019,7 +10016,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10040,16 +10037,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10084,7 +10081,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10105,16 +10102,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10149,7 +10146,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10179,7 +10176,7 @@
         <v>193</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10214,7 +10211,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10235,16 +10232,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>387</v>
-      </c>
       <c r="M22" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10279,7 +10276,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10306,7 +10303,7 @@
         <v>76</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>78</v>
@@ -10315,7 +10312,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10350,7 +10347,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10371,13 +10368,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10412,7 +10409,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10436,13 +10433,13 @@
         <v>205</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10477,7 +10474,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10498,13 +10495,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10539,7 +10536,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10560,16 +10557,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>223</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10604,7 +10601,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10763,16 +10760,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>406</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -10789,7 +10786,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10813,7 +10810,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -10845,7 +10842,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10866,10 +10863,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -10904,7 +10901,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -10928,13 +10925,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -10969,7 +10966,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -10993,13 +10990,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>213</v>
@@ -11034,7 +11031,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11055,10 +11052,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>35</v>
@@ -11090,7 +11087,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11120,7 +11117,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11152,7 +11149,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11173,16 +11170,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>115</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11214,7 +11211,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11238,16 +11235,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11279,7 +11276,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11300,13 +11297,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>122</v>
@@ -11341,7 +11338,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11362,16 +11359,16 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="L11" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>128</v>
@@ -11406,7 +11403,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11427,10 +11424,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11468,7 +11465,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11530,7 +11527,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11554,13 +11551,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K14" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11592,7 +11589,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11616,16 +11613,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>140</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11657,7 +11654,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11684,7 +11681,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11722,7 +11719,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11743,13 +11740,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>150</v>
@@ -11784,7 +11781,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11805,16 +11802,16 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>159</v>
@@ -11849,7 +11846,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -11870,16 +11867,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>164</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -11914,7 +11911,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -11935,13 +11932,13 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>169</v>
@@ -11976,7 +11973,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -11997,13 +11994,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K21" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12035,7 +12032,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12062,10 +12059,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12097,7 +12094,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12118,13 +12115,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12156,7 +12153,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12177,7 +12174,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12209,7 +12206,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12230,13 +12227,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>185</v>
@@ -12271,7 +12268,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12330,7 +12327,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12351,13 +12348,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>485</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12389,7 +12386,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12413,10 +12410,10 @@
         <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12448,7 +12445,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12469,13 +12466,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K29" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>203</v>
@@ -12510,7 +12507,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12540,10 +12537,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>494</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12575,7 +12572,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12596,13 +12593,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12634,7 +12631,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12655,13 +12652,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K32" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12693,7 +12690,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12714,13 +12711,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12752,7 +12749,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12773,13 +12770,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12811,7 +12808,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12832,7 +12829,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12864,7 +12861,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -12885,10 +12882,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>223</v>
@@ -12923,7 +12920,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -9,13 +9,14 @@
     <sheet name="mars" sheetId="2" r:id="rId3"/>
     <sheet name="moon" sheetId="3" r:id="rId4"/>
     <sheet name="nether" sheetId="4" r:id="rId5"/>
+    <sheet name="venus" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1557,6 +1558,21 @@
   </si>
   <si>
     <t>nether_topaz</t>
+  </si>
+  <si>
+    <t>venus_manual_salt</t>
+  </si>
+  <si>
+    <t>salt: 50</t>
+  </si>
+  <si>
+    <t>spodumene: 15</t>
+  </si>
+  <si>
+    <t>venus_manual_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur: 50</t>
   </si>
 </sst>
 </file>
@@ -13096,4 +13112,218 @@
   </sheetData>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.293367385864258" customWidth="1" style="3"/>
+    <col min="2" max="2" width="14.972405433654785" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9.140625" customWidth="1" style="3"/>
+    <col min="4" max="4" width="9.140625" customWidth="1" style="3"/>
+    <col min="5" max="5" width="9.140625" customWidth="1" style="3"/>
+    <col min="6" max="6" width="9.140625" customWidth="1" style="3"/>
+    <col min="7" max="7" width="9.140625" customWidth="1" style="3"/>
+    <col min="8" max="8" width="9.140625" customWidth="1" style="3"/>
+    <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
+    <col min="10" max="10" width="9.682135581970215" customWidth="1" style="3"/>
+    <col min="11" max="11" width="12.619355201721191" customWidth="1" style="3"/>
+    <col min="12" max="12" width="13.423484802246094" customWidth="1" style="3"/>
+    <col min="13" max="13" width="15.053228378295898" customWidth="1" style="3"/>
+    <col min="14" max="14" width="9.140625" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
+    <col min="16" max="16" width="9.140625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="9.140625" customWidth="1" style="3"/>
+    <col min="18" max="18" width="9.140625" customWidth="1" style="3"/>
+    <col min="19" max="19" width="10.040207862854004" customWidth="1" style="3"/>
+    <col min="20" max="20" width="9.140625" customWidth="1" style="3"/>
+    <col min="21" max="21" width="12.787137985229492" customWidth="1" style="3"/>
+    <col min="22" max="22" width="9.140625" customWidth="1" style="3"/>
+    <col min="23" max="23" width="9.140625" customWidth="1" style="3"/>
+    <col min="24" max="24" width="9.140625" customWidth="1" style="3"/>
+    <col min="25" max="25" width="9.140625" customWidth="1" style="3"/>
+    <col min="26" max="26" width="9.140625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="9.140625" customWidth="1" style="3"/>
+    <col min="28" max="28" width="9.140625" customWidth="1" style="3"/>
+    <col min="29" max="29" width="9.140625" customWidth="1" style="3"/>
+    <col min="30" max="30" width="9.140625" customWidth="1" style="3"/>
+    <col min="31" max="31" width="9.140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="9.140625" customWidth="1" style="3"/>
+    <col min="33" max="33" width="9.140625" customWidth="1" style="3"/>
+    <col min="34" max="34" width="9.140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="9.140625" customWidth="1" style="3"/>
+    <col min="36" max="36" width="9.140625" customWidth="1" style="3"/>
+    <col min="37" max="37" width="9.140625" customWidth="1" style="3"/>
+    <col min="38" max="38" width="9.140625" customWidth="1" style="3"/>
+    <col min="39" max="39" width="9.140625" customWidth="1" style="3"/>
+    <col min="40" max="40" width="9.140625" customWidth="1" style="3"/>
+    <col min="41" max="41" width="9.140625" customWidth="1" style="3"/>
+    <col min="42" max="42" width="9.140625" customWidth="1" style="3"/>
+    <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
+    <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
+    <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
+    <col min="46" max="16384" width="9.140625" customWidth="1" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="4" customFormat="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3">
+        <v>100</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3">
+        <v>65</v>
+      </c>
+      <c r="G2" s="3">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3">
+        <v>100</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>40</v>
+      </c>
+      <c r="F3" s="3">
+        <v>65</v>
+      </c>
+      <c r="G3" s="3">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
   <si>
     <t>Vein ID</t>
   </si>
@@ -856,6 +856,9 @@
   </si>
   <si>
     <t>mars_hematite</t>
+  </si>
+  <si>
+    <t>mars_lapis</t>
   </si>
   <si>
     <t>mars_lubricant</t>
@@ -6438,7 +6441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AF28"/>
+  <dimension ref="A1:AF29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.277278900146484" customWidth="1" style="3"/>
@@ -7609,7 +7612,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="3">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D14" s="3">
         <v>0.25</v>
@@ -7621,25 +7624,19 @@
         <v>70</v>
       </c>
       <c r="G14" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>281</v>
+        <v>148</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>282</v>
+        <v>149</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>283</v>
+        <v>150</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -7647,23 +7644,23 @@
       <c r="Q14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>36</v>
+      <c r="R14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X14" s="1" t="s">
         <v>36</v>
@@ -7671,8 +7668,8 @@
       <c r="Y14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z14" s="1" t="s">
-        <v>36</v>
+      <c r="Z14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>36</v>
@@ -7680,8 +7677,8 @@
       <c r="AB14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC14" s="1" t="s">
-        <v>36</v>
+      <c r="AC14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>35</v>
@@ -7695,16 +7692,16 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="3">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D15" s="3">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -7713,40 +7710,46 @@
         <v>70</v>
       </c>
       <c r="G15" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>178</v>
+        <v>283</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>116</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>35</v>
+      <c r="Q15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>36</v>
@@ -7754,40 +7757,40 @@
       <c r="X15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>35</v>
+      <c r="Y15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC15" s="2" t="s">
-        <v>35</v>
+      <c r="AC15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>36</v>
+      <c r="AE15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="3">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="D16" s="3">
         <v>0.4</v>
@@ -7799,16 +7802,16 @@
         <v>70</v>
       </c>
       <c r="G16" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>290</v>
+        <v>178</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>116</v>
@@ -7822,61 +7825,61 @@
       <c r="R16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>36</v>
+      <c r="S16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>36</v>
+      <c r="V16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC16" s="1" t="s">
-        <v>36</v>
+      <c r="AC16" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF16" s="2" t="s">
-        <v>35</v>
+      <c r="AE16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="3">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D17" s="3">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -7885,52 +7888,55 @@
         <v>70</v>
       </c>
       <c r="G17" s="3">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>293</v>
+        <v>127</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>35</v>
+      <c r="Q17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>36</v>
+      <c r="T17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>35</v>
+      <c r="W17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB17" s="1" t="s">
         <v>36</v>
@@ -7944,22 +7950,22 @@
       <c r="AE17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF17" s="1" t="s">
-        <v>36</v>
+      <c r="AF17" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D18" s="3">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -7968,19 +7974,16 @@
         <v>70</v>
       </c>
       <c r="G18" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>189</v>
+        <v>253</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -7988,35 +7991,35 @@
       <c r="Q18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>36</v>
+      <c r="R18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB18" s="1" t="s">
         <v>36</v>
@@ -8039,13 +8042,13 @@
         <v>295</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3">
         <v>210</v>
       </c>
       <c r="D19" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
@@ -8056,20 +8059,17 @@
       <c r="G19" s="3">
         <v>40</v>
       </c>
-      <c r="H19" s="3">
-        <v>6</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>296</v>
+        <v>188</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>216</v>
+        <v>116</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>35</v>
@@ -8092,8 +8092,8 @@
       <c r="V19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W19" s="1" t="s">
-        <v>36</v>
+      <c r="W19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>35</v>
@@ -8116,8 +8116,8 @@
       <c r="AD19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE19" s="2" t="s">
-        <v>35</v>
+      <c r="AE19" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF19" s="1" t="s">
         <v>36</v>
@@ -8125,10 +8125,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C20" s="3">
         <v>210</v>
@@ -8145,23 +8145,26 @@
       <c r="G20" s="3">
         <v>40</v>
       </c>
+      <c r="H20" s="3">
+        <v>6</v>
+      </c>
       <c r="J20" s="3" t="s">
-        <v>225</v>
+        <v>297</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q20" s="1" t="s">
-        <v>36</v>
+      <c r="Q20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>36</v>
@@ -8169,29 +8172,29 @@
       <c r="S20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T20" s="2" t="s">
-        <v>35</v>
+      <c r="T20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="U20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V20" s="1" t="s">
-        <v>36</v>
+      <c r="V20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>35</v>
+      <c r="X20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AB20" s="1" t="s">
         <v>36</v>
@@ -8202,8 +8205,8 @@
       <c r="AD20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE20" s="1" t="s">
-        <v>36</v>
+      <c r="AE20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>36</v>
@@ -8217,10 +8220,10 @@
         <v>31</v>
       </c>
       <c r="C21" s="3">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D21" s="3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -8229,19 +8232,19 @@
         <v>70</v>
       </c>
       <c r="G21" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>300</v>
+        <v>226</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -8267,14 +8270,14 @@
       <c r="W21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>35</v>
+      <c r="X21" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Y21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z21" s="1" t="s">
-        <v>36</v>
+      <c r="Z21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA21" s="2" t="s">
         <v>35</v>
@@ -8282,14 +8285,14 @@
       <c r="AB21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC21" s="2" t="s">
-        <v>35</v>
+      <c r="AC21" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE21" s="2" t="s">
-        <v>35</v>
+      <c r="AE21" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AF21" s="1" t="s">
         <v>36</v>
@@ -8297,16 +8300,16 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="3">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D22" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -8315,19 +8318,19 @@
         <v>70</v>
       </c>
       <c r="G22" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>306</v>
+        <v>132</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -8341,17 +8344,17 @@
       <c r="S22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T22" s="1" t="s">
-        <v>36</v>
+      <c r="T22" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>35</v>
+      <c r="V22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>35</v>
@@ -8359,23 +8362,23 @@
       <c r="Y22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>36</v>
+      <c r="Z22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AB22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AC22" s="1" t="s">
-        <v>36</v>
+      <c r="AC22" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AD22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE22" s="1" t="s">
-        <v>36</v>
+      <c r="AE22" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AF22" s="1" t="s">
         <v>36</v>
@@ -8383,16 +8386,16 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="3">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="D23" s="3">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -8401,19 +8404,19 @@
         <v>70</v>
       </c>
       <c r="G23" s="3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>116</v>
+        <v>307</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -8439,11 +8442,11 @@
       <c r="W23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y23" s="2" t="s">
-        <v>35</v>
+      <c r="X23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>35</v>
@@ -8451,8 +8454,8 @@
       <c r="AA23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB23" s="2" t="s">
-        <v>35</v>
+      <c r="AB23" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AC23" s="1" t="s">
         <v>36</v>
@@ -8463,43 +8466,43 @@
       <c r="AE23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF23" s="2" t="s">
-        <v>35</v>
+      <c r="AF23" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="3">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="D24" s="3">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G24" s="3">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>312</v>
+        <v>116</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -8516,29 +8519,29 @@
       <c r="T24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>36</v>
+      <c r="U24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>36</v>
+      <c r="Y24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>36</v>
+      <c r="AB24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>36</v>
@@ -8549,19 +8552,19 @@
       <c r="AE24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF24" s="1" t="s">
-        <v>36</v>
+      <c r="AF24" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="3">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D25" s="3">
         <v>0.25</v>
@@ -8576,13 +8579,16 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>111</v>
+        <v>312</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8638,13 +8644,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="3">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3">
         <v>0.25</v>
@@ -8659,16 +8665,13 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>146</v>
+        <v>315</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>35</v>
@@ -8724,13 +8727,13 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D27" s="3">
         <v>0.25</v>
@@ -8745,19 +8748,16 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>220</v>
+        <v>146</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>290</v>
+        <v>145</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>206</v>
+        <v>55</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8813,13 +8813,13 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3">
         <v>0.25</v>
@@ -8834,66 +8834,155 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF28" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="3">
+        <v>140</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>80</v>
+      </c>
+      <c r="F29" s="3">
+        <v>180</v>
+      </c>
+      <c r="G29" s="3">
+        <v>45</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="M28" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF28" s="1" t="s">
+      <c r="M29" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF29" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -9002,16 +9091,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -9019,7 +9108,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -9040,16 +9129,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -9084,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -9105,13 +9194,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9146,7 +9235,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>99</v>
@@ -9170,16 +9259,16 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>214</v>
@@ -9217,7 +9306,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9238,16 +9327,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>109</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9282,7 +9371,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9347,7 +9436,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9368,16 +9457,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9412,7 +9501,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9436,16 +9525,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9480,7 +9569,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9501,16 +9590,16 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>127</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>129</v>
@@ -9548,7 +9637,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9578,7 +9667,7 @@
         <v>272</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>133</v>
@@ -9616,7 +9705,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>99</v>
@@ -9640,13 +9729,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9681,7 +9770,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9708,16 +9797,16 @@
         <v>139</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>204</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -9752,7 +9841,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -9820,7 +9909,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -9841,13 +9930,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -9888,7 +9977,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -9953,7 +10042,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -9974,7 +10063,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>173</v>
@@ -9983,10 +10072,10 @@
         <v>174</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -10021,7 +10110,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -10051,7 +10140,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -10086,7 +10175,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -10107,7 +10196,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>178</v>
@@ -10116,7 +10205,7 @@
         <v>179</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10151,7 +10240,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10172,16 +10261,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10216,7 +10305,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10237,16 +10326,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10281,7 +10370,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10311,7 +10400,7 @@
         <v>194</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10346,7 +10435,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10367,16 +10456,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10411,7 +10500,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10447,7 +10536,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10482,7 +10571,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10503,13 +10592,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10544,7 +10633,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10568,13 +10657,13 @@
         <v>206</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>269</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10609,7 +10698,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10630,13 +10719,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10671,7 +10760,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10692,16 +10781,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>227</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -10736,7 +10825,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -10895,16 +10984,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -10921,7 +11010,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -10945,7 +11034,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -10977,7 +11066,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -10998,10 +11087,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>92</v>
@@ -11036,7 +11125,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -11060,13 +11149,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>97</v>
@@ -11101,7 +11190,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
@@ -11125,13 +11214,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>214</v>
@@ -11166,7 +11255,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11187,10 +11276,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>111</v>
@@ -11225,7 +11314,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11255,7 +11344,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11287,7 +11376,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11308,16 +11397,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>116</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11349,7 +11438,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11373,16 +11462,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11414,7 +11503,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11435,13 +11524,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>123</v>
@@ -11476,7 +11565,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11497,16 +11586,16 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>129</v>
@@ -11541,7 +11630,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11562,10 +11651,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11603,7 +11692,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11665,7 +11754,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
@@ -11692,10 +11781,10 @@
         <v>275</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -11727,7 +11816,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -11751,16 +11840,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>141</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -11792,7 +11881,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -11819,7 +11908,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -11857,7 +11946,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -11878,13 +11967,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>151</v>
@@ -11919,7 +12008,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -11940,16 +12029,16 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>160</v>
@@ -11984,7 +12073,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -12005,16 +12094,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>165</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -12049,7 +12138,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -12070,13 +12159,13 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>170</v>
@@ -12111,7 +12200,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -12132,13 +12221,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12170,7 +12259,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12197,10 +12286,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12232,7 +12321,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12253,13 +12342,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12291,7 +12380,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12312,7 +12401,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12344,7 +12433,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12365,13 +12454,13 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>186</v>
@@ -12406,7 +12495,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12465,7 +12554,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12486,13 +12575,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12524,7 +12613,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12548,10 +12637,10 @@
         <v>192</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12583,7 +12672,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12604,13 +12693,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>204</v>
@@ -12645,7 +12734,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12675,10 +12764,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12710,7 +12799,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -12731,13 +12820,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -12769,7 +12858,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -12793,10 +12882,10 @@
         <v>268</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -12828,7 +12917,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -12849,13 +12938,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>211</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -12887,7 +12976,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -12908,13 +12997,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -12946,7 +13035,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -12967,7 +13056,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -12999,7 +13088,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -13020,10 +13109,10 @@
         <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>227</v>
@@ -13058,7 +13147,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>38</v>
@@ -13220,7 +13309,7 @@
         <v>16</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>26</v>
@@ -13231,7 +13320,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -13255,16 +13344,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -13287,7 +13376,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -13308,13 +13397,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -828,7 +828,7 @@
     <t>lead: 25</t>
   </si>
   <si>
-    <t>mars_sapphire</t>
+    <t>mars_gold</t>
   </si>
   <si>
     <t>green_sapphire: 5</t>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -4016,17 +4016,17 @@
       <c r="Q25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>36</v>
+      <c r="R25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>36</v>
@@ -4034,8 +4034,8 @@
       <c r="W25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X25" s="1" t="s">
-        <v>36</v>
+      <c r="X25" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Y25" s="1" t="s">
         <v>36</v>
@@ -4046,8 +4046,8 @@
       <c r="AA25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB25" s="1" t="s">
-        <v>36</v>
+      <c r="AB25" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC25" s="1" t="s">
         <v>36</v>
@@ -4064,8 +4064,8 @@
       <c r="AG25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AH25" s="1" t="s">
-        <v>36</v>
+      <c r="AH25" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI25" s="1" t="s">
         <v>36</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -1705,7 +1705,10 @@
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
     <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
-    <col min="46" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -6572,7 +6575,10 @@
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
     <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
-    <col min="46" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -9211,7 +9217,10 @@
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
     <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
-    <col min="46" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -11116,7 +11125,10 @@
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
     <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
-    <col min="46" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -13382,7 +13394,10 @@
     <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
     <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
-    <col min="46" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
+    <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
   <si>
     <t>Vein ID</t>
   </si>
@@ -510,13 +510,10 @@
     <t>normal_magnetite</t>
   </si>
   <si>
-    <t>magnetite: 70 [1]</t>
-  </si>
-  <si>
-    <t>vanadium_magnetite: 25</t>
-  </si>
-  <si>
-    <t>gold: 10</t>
+    <t>magnetite: 60 [1]</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 30</t>
   </si>
   <si>
     <t>chromite: 5</t>
@@ -732,10 +729,7 @@
     <t>chalcopyrite: 55</t>
   </si>
   <si>
-    <t>zeolite: 15</t>
-  </si>
-  <si>
-    <t>cassiterite: 5</t>
+    <t>zeolite: 20</t>
   </si>
   <si>
     <t>realgar: 15</t>
@@ -3894,7 +3888,7 @@
         <v>38</v>
       </c>
       <c r="C24" s="3">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="D24" s="3">
         <v>0.4</v>
@@ -4589,10 +4583,10 @@
         <v>165</v>
       </c>
       <c r="L31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -4657,7 +4651,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -4678,16 +4672,16 @@
         <v>30</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="M32" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>36</v>
@@ -4752,37 +4746,37 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="3">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="D33" s="3">
         <v>0.25</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="F33" s="3">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="G33" s="3">
         <v>36</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="M33" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>35</v>
@@ -4847,7 +4841,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -4868,13 +4862,13 @@
         <v>35</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>35</v>
@@ -4939,7 +4933,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -5025,7 +5019,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
@@ -5046,16 +5040,16 @@
         <v>26</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>36</v>
@@ -5120,7 +5114,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>31</v>
@@ -5141,13 +5135,13 @@
         <v>40</v>
       </c>
       <c r="J37" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>35</v>
@@ -5212,7 +5206,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>31</v>
@@ -5233,13 +5227,13 @@
         <v>40</v>
       </c>
       <c r="J38" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>35</v>
@@ -5304,7 +5298,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>38</v>
@@ -5328,16 +5322,16 @@
         <v>4</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="L39" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>35</v>
@@ -5402,7 +5396,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>31</v>
@@ -5423,16 +5417,16 @@
         <v>40</v>
       </c>
       <c r="J40" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="L40" s="3" t="s">
+      <c r="M40" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>35</v>
@@ -5497,7 +5491,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>31</v>
@@ -5518,13 +5512,13 @@
         <v>40</v>
       </c>
       <c r="J41" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>35</v>
@@ -5589,7 +5583,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>31</v>
@@ -5610,13 +5604,13 @@
         <v>40</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>36</v>
@@ -5681,7 +5675,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>38</v>
@@ -5705,16 +5699,16 @@
         <v>6</v>
       </c>
       <c r="J43" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="L43" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>35</v>
@@ -5779,7 +5773,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
@@ -5800,13 +5794,13 @@
         <v>45</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>36</v>
@@ -5871,7 +5865,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>101</v>
@@ -5895,10 +5889,10 @@
         <v>10</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>141</v>
@@ -5969,7 +5963,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
@@ -5990,13 +5984,13 @@
         <v>40</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>35</v>
@@ -6061,7 +6055,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>31</v>
@@ -6082,13 +6076,13 @@
         <v>50</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>109</v>
@@ -6156,7 +6150,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>31</v>
@@ -6177,10 +6171,10 @@
         <v>50</v>
       </c>
       <c r="J48" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>113</v>
@@ -6248,13 +6242,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D49" s="3">
         <v>0.25</v>
@@ -6269,16 +6263,13 @@
         <v>50</v>
       </c>
       <c r="J49" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>36</v>
@@ -6343,7 +6334,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>31</v>
@@ -6364,13 +6355,13 @@
         <v>50</v>
       </c>
       <c r="J50" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>36</v>
@@ -6435,7 +6426,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>31</v>
@@ -6456,13 +6447,13 @@
         <v>50</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>35</v>
@@ -6653,13 +6644,13 @@
         <v>22</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>25</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>26</v>
@@ -6668,12 +6659,12 @@
         <v>28</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -6694,13 +6685,13 @@
         <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -6759,7 +6750,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -6783,7 +6774,7 @@
         <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>73</v>
@@ -6845,7 +6836,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -6869,13 +6860,13 @@
         <v>32</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -6934,7 +6925,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -6961,7 +6952,7 @@
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>78</v>
@@ -7029,7 +7020,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -7118,7 +7109,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>101</v>
@@ -7148,7 +7139,7 @@
         <v>103</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -7207,7 +7198,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -7228,10 +7219,10 @@
         <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>35</v>
@@ -7290,7 +7281,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -7311,10 +7302,10 @@
         <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>119</v>
@@ -7379,7 +7370,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -7400,13 +7391,13 @@
         <v>50</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>118</v>
@@ -7468,7 +7459,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -7489,13 +7480,13 @@
         <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>135</v>
@@ -7557,7 +7548,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>101</v>
@@ -7581,16 +7572,16 @@
         <v>9</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -7649,7 +7640,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -7738,7 +7729,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -7827,7 +7818,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -7848,19 +7839,19 @@
         <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="N15" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>118</v>
@@ -7922,7 +7913,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -7943,13 +7934,13 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>118</v>
@@ -8011,7 +8002,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -8032,10 +8023,10 @@
         <v>55</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>129</v>
@@ -8100,7 +8091,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -8121,13 +8112,13 @@
         <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>35</v>
@@ -8186,7 +8177,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -8207,13 +8198,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>118</v>
@@ -8275,7 +8266,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>38</v>
@@ -8299,16 +8290,16 @@
         <v>6</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>35</v>
@@ -8367,7 +8358,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -8388,13 +8379,13 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>118</v>
@@ -8456,7 +8447,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -8477,13 +8468,13 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>134</v>
@@ -8545,7 +8536,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -8566,16 +8557,16 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -8634,7 +8625,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -8658,7 +8649,7 @@
         <v>81</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>83</v>
@@ -8723,7 +8714,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -8744,16 +8735,16 @@
         <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -8812,7 +8803,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -8833,10 +8824,10 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>113</v>
@@ -8898,7 +8889,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -8928,7 +8919,7 @@
         <v>55</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>35</v>
@@ -8987,7 +8978,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -9008,19 +8999,19 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>109</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -9079,7 +9070,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -9100,16 +9091,16 @@
         <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -9273,16 +9264,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>26</v>
@@ -9290,7 +9281,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>31</v>
@@ -9311,16 +9302,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>93</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -9355,7 +9346,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -9376,13 +9367,13 @@
         <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>35</v>
@@ -9417,7 +9408,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>101</v>
@@ -9441,19 +9432,19 @@
         <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>35</v>
@@ -9488,7 +9479,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -9509,16 +9500,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>111</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>35</v>
@@ -9553,7 +9544,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -9577,13 +9568,13 @@
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -9618,7 +9609,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -9639,16 +9630,16 @@
         <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -9683,7 +9674,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>38</v>
@@ -9707,16 +9698,16 @@
         <v>7</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -9751,7 +9742,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -9772,16 +9763,16 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>129</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>131</v>
@@ -9819,7 +9810,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -9843,13 +9834,13 @@
         <v>10</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>135</v>
@@ -9887,7 +9878,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>101</v>
@@ -9911,13 +9902,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>35</v>
@@ -9952,7 +9943,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -9979,16 +9970,16 @@
         <v>141</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>35</v>
@@ -10023,7 +10014,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -10091,7 +10082,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>31</v>
@@ -10112,13 +10103,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>65</v>
@@ -10159,7 +10150,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
@@ -10180,16 +10171,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>36</v>
@@ -10224,7 +10215,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -10245,19 +10236,19 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="M16" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>35</v>
@@ -10292,7 +10283,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -10322,7 +10313,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>35</v>
@@ -10357,7 +10348,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -10378,16 +10369,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="M18" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -10422,7 +10413,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -10443,16 +10434,16 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>36</v>
@@ -10487,7 +10478,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -10508,16 +10499,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -10552,7 +10543,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -10573,16 +10564,16 @@
         <v>35</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="M21" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -10617,7 +10608,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -10638,16 +10629,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>389</v>
-      </c>
       <c r="M22" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -10682,7 +10673,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -10709,7 +10700,7 @@
         <v>76</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>78</v>
@@ -10718,7 +10709,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -10753,7 +10744,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -10774,13 +10765,13 @@
         <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>35</v>
@@ -10815,7 +10806,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -10836,16 +10827,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>35</v>
@@ -10880,7 +10871,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -10901,13 +10892,13 @@
         <v>35</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -10942,7 +10933,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -10963,16 +10954,16 @@
         <v>35</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -11007,7 +10998,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -11168,16 +11159,16 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>19</v>
@@ -11194,7 +11185,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -11218,7 +11209,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>35</v>
@@ -11250,7 +11241,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -11271,10 +11262,10 @@
         <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>94</v>
@@ -11309,7 +11300,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -11333,13 +11324,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>99</v>
@@ -11374,7 +11365,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>101</v>
@@ -11398,16 +11389,16 @@
         <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="M5" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>36</v>
@@ -11439,7 +11430,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -11460,10 +11451,10 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>113</v>
@@ -11498,7 +11489,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
@@ -11528,7 +11519,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -11560,7 +11551,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>31</v>
@@ -11581,16 +11572,16 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>118</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -11622,7 +11613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>38</v>
@@ -11646,16 +11637,16 @@
         <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -11687,7 +11678,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -11708,13 +11699,13 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>125</v>
@@ -11749,7 +11740,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -11770,16 +11761,16 @@
         <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>131</v>
@@ -11814,7 +11805,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -11835,10 +11826,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>49</v>
@@ -11876,7 +11867,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>31</v>
@@ -11938,7 +11929,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>101</v>
@@ -11962,13 +11953,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>35</v>
@@ -12000,7 +11991,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -12024,16 +12015,16 @@
         <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>143</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>35</v>
@@ -12065,7 +12056,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -12092,7 +12083,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -12130,7 +12121,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -12151,13 +12142,13 @@
         <v>40</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>153</v>
@@ -12192,7 +12183,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -12213,16 +12204,16 @@
         <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>162</v>
@@ -12257,7 +12248,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>31</v>
@@ -12278,16 +12269,16 @@
         <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>462</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -12322,7 +12313,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>31</v>
@@ -12343,16 +12334,16 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="M20" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -12384,7 +12375,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -12405,13 +12396,13 @@
         <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>35</v>
@@ -12443,7 +12434,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -12470,10 +12461,10 @@
         <v>69</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>35</v>
@@ -12505,7 +12496,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>31</v>
@@ -12526,13 +12517,13 @@
         <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>35</v>
@@ -12564,7 +12555,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>31</v>
@@ -12585,7 +12576,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -12617,7 +12608,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>31</v>
@@ -12638,16 +12629,16 @@
         <v>31</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>482</v>
-      </c>
       <c r="M25" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>36</v>
@@ -12679,7 +12670,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>31</v>
@@ -12738,7 +12729,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>31</v>
@@ -12759,13 +12750,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -12797,7 +12788,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
@@ -12818,13 +12809,13 @@
         <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>35</v>
@@ -12856,7 +12847,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
@@ -12877,16 +12868,16 @@
         <v>50</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>35</v>
@@ -12918,7 +12909,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
@@ -12948,10 +12939,10 @@
         <v>77</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>35</v>
@@ -12983,7 +12974,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -13004,13 +12995,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>35</v>
@@ -13042,7 +13033,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
@@ -13063,13 +13054,13 @@
         <v>45</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>35</v>
@@ -13101,7 +13092,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>31</v>
@@ -13122,13 +13113,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -13160,7 +13151,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>31</v>
@@ -13181,13 +13172,13 @@
         <v>50</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -13219,7 +13210,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>31</v>
@@ -13240,13 +13231,13 @@
         <v>45</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>35</v>
@@ -13278,7 +13269,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>38</v>
@@ -13442,24 +13433,24 @@
         <v>16</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>38</v>
@@ -13483,16 +13474,16 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -13521,7 +13512,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -13542,13 +13533,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3">
         <v>32</v>
@@ -6351,68 +6351,68 @@
       <c r="K5" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>25</v>
+      <c r="P5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>25</v>
+      <c r="X5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>25</v>
+      <c r="Z5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>25</v>
+      <c r="AB5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6432,7 +6432,7 @@
         <v>60</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -6521,10 +6521,10 @@
         <v>60</v>
       </c>
       <c r="F7" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>332</v>
@@ -6610,10 +6610,10 @@
         <v>60</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>334</v>
@@ -6710,68 +6710,68 @@
       <c r="K9" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>25</v>
+      <c r="P9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X9" s="2" t="s">
-        <v>25</v>
+      <c r="X9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z9" s="2" t="s">
-        <v>25</v>
+      <c r="Z9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ9" s="2" t="s">
-        <v>25</v>
+      <c r="AB9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -6791,10 +6791,10 @@
         <v>60</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>338</v>
@@ -6874,7 +6874,7 @@
         <v>120</v>
       </c>
       <c r="D11" s="3">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -6891,68 +6891,68 @@
       <c r="K11" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>25</v>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X11" s="2" t="s">
-        <v>25</v>
+      <c r="X11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>25</v>
+      <c r="Z11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ11" s="2" t="s">
-        <v>25</v>
+      <c r="AB11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -6972,10 +6972,10 @@
         <v>60</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G12" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>342</v>
@@ -7061,10 +7061,10 @@
         <v>60</v>
       </c>
       <c r="F13" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G13" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>344</v>
@@ -7158,68 +7158,68 @@
       <c r="J14" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>25</v>
+      <c r="P14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X14" s="2" t="s">
-        <v>25</v>
+      <c r="X14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z14" s="2" t="s">
-        <v>25</v>
+      <c r="Z14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ14" s="2" t="s">
-        <v>25</v>
+      <c r="AB14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -7239,10 +7239,10 @@
         <v>60</v>
       </c>
       <c r="F15" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>348</v>
@@ -7336,68 +7336,68 @@
       <c r="J16" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>25</v>
+      <c r="P16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X16" s="2" t="s">
-        <v>25</v>
+      <c r="X16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z16" s="2" t="s">
-        <v>25</v>
+      <c r="Z16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ16" s="2" t="s">
-        <v>25</v>
+      <c r="AB16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G18" s="3">
         <v>36</v>
@@ -7690,10 +7690,10 @@
         <v>60</v>
       </c>
       <c r="F20" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G20" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>359</v>
@@ -7779,10 +7779,10 @@
         <v>60</v>
       </c>
       <c r="F21" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G21" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>361</v>
@@ -7868,10 +7868,10 @@
         <v>60</v>
       </c>
       <c r="F22" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G22" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>363</v>
@@ -7957,10 +7957,10 @@
         <v>60</v>
       </c>
       <c r="F23" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G23" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>365</v>
@@ -8043,16 +8043,16 @@
         <v>60</v>
       </c>
       <c r="D24" s="3">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E24" s="3">
         <v>60</v>
       </c>
       <c r="F24" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G24" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>368</v>
@@ -8146,68 +8146,68 @@
       <c r="J25" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>25</v>
+      <c r="P25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X25" s="2" t="s">
-        <v>25</v>
+      <c r="X25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z25" s="2" t="s">
-        <v>25</v>
+      <c r="Z25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ25" s="2" t="s">
-        <v>25</v>
+      <c r="AB25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -8227,10 +8227,10 @@
         <v>60</v>
       </c>
       <c r="F26" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G26" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>372</v>
@@ -8316,10 +8316,10 @@
         <v>60</v>
       </c>
       <c r="F27" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G27" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>374</v>
@@ -8405,10 +8405,10 @@
         <v>60</v>
       </c>
       <c r="F28" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G28" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>376</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1090,12 +1090,6 @@
   </si>
   <si>
     <t>cinnabar: 25</t>
-  </si>
-  <si>
-    <t>surface_native_silver</t>
-  </si>
-  <si>
-    <t>silver: 100 [1]</t>
   </si>
   <si>
     <t>surface_hematite</t>
@@ -5898,7 +5892,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28571319580078" customWidth="1" style="3"/>
@@ -6058,7 +6052,7 @@
         <v>140</v>
       </c>
       <c r="D2" s="3">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E2" s="3">
         <v>-50</v>
@@ -6153,7 +6147,7 @@
         <v>210</v>
       </c>
       <c r="D3" s="3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E3" s="3">
         <v>-50</v>
@@ -6245,7 +6239,7 @@
         <v>240</v>
       </c>
       <c r="D4" s="3">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -6331,19 +6325,19 @@
         <v>20</v>
       </c>
       <c r="C5" s="3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D5" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>-30</v>
       </c>
       <c r="F5" s="3">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>327</v>
@@ -6426,13 +6420,13 @@
         <v>90</v>
       </c>
       <c r="D6" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F6" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -6515,13 +6509,13 @@
         <v>35</v>
       </c>
       <c r="D7" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F7" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -6604,13 +6598,13 @@
         <v>30</v>
       </c>
       <c r="D8" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G8" s="3">
         <v>15</v>
@@ -6690,16 +6684,16 @@
         <v>20</v>
       </c>
       <c r="C9" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D9" s="3">
         <v>0.3</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F9" s="3">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <v>15</v>
@@ -6785,13 +6779,13 @@
         <v>130</v>
       </c>
       <c r="D10" s="3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E10" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G10" s="3">
         <v>5</v>
@@ -6966,13 +6960,13 @@
         <v>90</v>
       </c>
       <c r="D12" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F12" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G12" s="3">
         <v>5</v>
@@ -7055,13 +7049,13 @@
         <v>24</v>
       </c>
       <c r="D13" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E13" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F13" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G13" s="3">
         <v>15</v>
@@ -7233,13 +7227,13 @@
         <v>90</v>
       </c>
       <c r="D15" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G15" s="3">
         <v>15</v>
@@ -7405,22 +7399,25 @@
         <v>351</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3">
         <v>0.8</v>
       </c>
       <c r="E17" s="3">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="3">
-        <v>20</v>
+        <v>-45</v>
       </c>
       <c r="G17" s="3">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="H17" s="3">
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>346</v>
@@ -7500,7 +7497,7 @@
         <v>220</v>
       </c>
       <c r="D18" s="3">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -7509,7 +7506,7 @@
         <v>60</v>
       </c>
       <c r="G18" s="3">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>353</v>
@@ -7589,7 +7586,7 @@
         <v>120</v>
       </c>
       <c r="D19" s="3">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="E19" s="3">
         <v>-50</v>
@@ -7630,14 +7627,14 @@
       <c r="V19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W19" s="2" t="s">
-        <v>25</v>
+      <c r="W19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y19" s="2" t="s">
-        <v>25</v>
+      <c r="Y19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>25</v>
@@ -7681,28 +7678,28 @@
         <v>20</v>
       </c>
       <c r="C20" s="3">
+        <v>45</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G20" s="3">
         <v>15</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E20" s="3">
-        <v>60</v>
-      </c>
-      <c r="F20" s="3">
-        <v>70</v>
-      </c>
-      <c r="G20" s="3">
-        <v>5</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>25</v>
+      <c r="P20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>25</v>
@@ -7716,23 +7713,23 @@
       <c r="U20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>26</v>
+      <c r="V20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y20" s="1" t="s">
-        <v>26</v>
+      <c r="Y20" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA20" s="1" t="s">
-        <v>26</v>
+      <c r="AA20" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>25</v>
@@ -7746,8 +7743,8 @@
       <c r="AE20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF20" s="2" t="s">
-        <v>25</v>
+      <c r="AF20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>25</v>
@@ -7770,16 +7767,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="3">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D21" s="3">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G21" s="3">
         <v>15</v>
@@ -7787,14 +7784,14 @@
       <c r="J21" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="P21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>25</v>
+      <c r="P21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>25</v>
@@ -7805,47 +7802,47 @@
       <c r="U21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V21" s="1" t="s">
-        <v>26</v>
+      <c r="V21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>25</v>
+      <c r="X21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z21" s="2" t="s">
-        <v>25</v>
+      <c r="Z21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>25</v>
+      <c r="AB21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI21" s="2" t="s">
-        <v>25</v>
+      <c r="AI21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ21" s="2" t="s">
         <v>25</v>
@@ -7859,31 +7856,34 @@
         <v>20</v>
       </c>
       <c r="C22" s="3">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="D22" s="3">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E22" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F22" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G22" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>363</v>
       </c>
+      <c r="K22" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R22" s="1" t="s">
-        <v>26</v>
+      <c r="R22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="S22" s="2" t="s">
         <v>25</v>
@@ -7900,8 +7900,8 @@
       <c r="W22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X22" s="1" t="s">
-        <v>26</v>
+      <c r="X22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>25</v>
@@ -7912,8 +7912,8 @@
       <c r="AA22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB22" s="1" t="s">
-        <v>26</v>
+      <c r="AB22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>26</v>
@@ -7942,30 +7942,27 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E23" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="K23" s="3" t="s">
         <v>366</v>
       </c>
       <c r="P23" s="2" t="s">
@@ -7974,17 +7971,17 @@
       <c r="Q23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>25</v>
+      <c r="R23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V23" s="2" t="s">
         <v>25</v>
@@ -7992,44 +7989,44 @@
       <c r="W23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X23" s="2" t="s">
-        <v>25</v>
+      <c r="X23" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z23" s="1" t="s">
-        <v>26</v>
+      <c r="Z23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>26</v>
+      <c r="AB23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ23" s="2" t="s">
-        <v>25</v>
+      <c r="AG23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -8040,28 +8037,28 @@
         <v>20</v>
       </c>
       <c r="C24" s="3">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="D24" s="3">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="E24" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="G24" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>25</v>
+      <c r="P24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>26</v>
@@ -8075,47 +8072,47 @@
       <c r="U24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>25</v>
+      <c r="V24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA24" s="2" t="s">
-        <v>25</v>
+      <c r="Y24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG24" s="2" t="s">
-        <v>25</v>
+      <c r="AC24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI24" s="2" t="s">
-        <v>25</v>
+      <c r="AI24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ24" s="1" t="s">
         <v>26</v>
@@ -8129,28 +8126,28 @@
         <v>20</v>
       </c>
       <c r="C25" s="3">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="D25" s="3">
         <v>0.25</v>
       </c>
       <c r="E25" s="3">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="3">
-        <v>170</v>
+        <v>-5</v>
       </c>
       <c r="G25" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>26</v>
+      <c r="P25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>26</v>
@@ -8164,47 +8161,47 @@
       <c r="U25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>26</v>
+      <c r="V25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA25" s="1" t="s">
-        <v>26</v>
+      <c r="Y25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG25" s="1" t="s">
-        <v>26</v>
+      <c r="AC25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI25" s="1" t="s">
-        <v>26</v>
+      <c r="AI25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ25" s="1" t="s">
         <v>26</v>
@@ -8218,16 +8215,16 @@
         <v>20</v>
       </c>
       <c r="C26" s="3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D26" s="3">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E26" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G26" s="3">
         <v>15</v>
@@ -8307,19 +8304,19 @@
         <v>20</v>
       </c>
       <c r="C27" s="3">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3">
         <v>0.2</v>
       </c>
       <c r="E27" s="3">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="F27" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G27" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>374</v>
@@ -8330,17 +8327,17 @@
       <c r="Q27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>26</v>
+      <c r="R27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>25</v>
@@ -8348,132 +8345,43 @@
       <c r="W27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X27" s="1" t="s">
-        <v>26</v>
+      <c r="X27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z27" s="2" t="s">
-        <v>25</v>
+      <c r="Z27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE27" s="2" t="s">
-        <v>25</v>
+      <c r="AB27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="3">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>60</v>
-      </c>
-      <c r="F28" s="3">
-        <v>70</v>
-      </c>
-      <c r="G28" s="3">
-        <v>15</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ28" s="2" t="s">
+      <c r="AG27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -8606,13 +8514,13 @@
         <v>311</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>314</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>185</v>
@@ -8626,7 +8534,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -8647,13 +8555,13 @@
         <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
@@ -8712,7 +8620,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -8733,13 +8641,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>45</v>
@@ -8801,7 +8709,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -8822,10 +8730,10 @@
         <v>55</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -8884,7 +8792,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -8905,10 +8813,10 @@
         <v>45</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>167</v>
@@ -8970,7 +8878,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>34</v>
@@ -9065,7 +8973,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -9086,7 +8994,7 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>76</v>
@@ -9095,10 +9003,10 @@
         <v>254</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>25</v>
@@ -9157,7 +9065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>82</v>
@@ -9181,13 +9089,13 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>26</v>
@@ -9246,7 +9154,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -9335,7 +9243,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -9356,16 +9264,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
@@ -9424,7 +9332,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
@@ -9448,16 +9356,16 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>25</v>
@@ -9516,7 +9424,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -9537,19 +9445,19 @@
         <v>40</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>417</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>45</v>
@@ -9611,7 +9519,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -9632,7 +9540,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>299</v>
@@ -9700,7 +9608,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -9721,10 +9629,10 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>122</v>
@@ -9789,7 +9697,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -9878,7 +9786,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>82</v>
@@ -9905,13 +9813,13 @@
         <v>104</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>25</v>
@@ -9970,7 +9878,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -9991,16 +9899,16 @@
         <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>25</v>
@@ -10059,7 +9967,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -10080,13 +9988,13 @@
         <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>131</v>
@@ -10148,7 +10056,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -10169,13 +10077,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>45</v>
@@ -10237,7 +10145,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -10261,7 +10169,7 @@
         <v>161</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>256</v>
@@ -10326,7 +10234,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -10347,16 +10255,16 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>25</v>
@@ -10415,7 +10323,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -10436,16 +10344,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -10504,7 +10412,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -10528,7 +10436,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>54</v>
@@ -10590,7 +10498,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
@@ -10617,7 +10525,7 @@
         <v>207</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>209</v>
@@ -10679,7 +10587,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
@@ -10706,7 +10614,7 @@
         <v>234</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -10765,7 +10673,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
@@ -10786,16 +10694,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>122</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -10854,7 +10762,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -10875,13 +10783,13 @@
         <v>50</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>45</v>
@@ -10943,7 +10851,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>20</v>
@@ -10964,13 +10872,13 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>96</v>
@@ -11032,7 +10940,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="608">
   <si>
     <t>Vein ID</t>
   </si>
@@ -972,175 +972,619 @@
     <t>tuff</t>
   </si>
   <si>
+    <t>deep_lazurite_calcite</t>
+  </si>
+  <si>
+    <t>lazurite: 5 [1]</t>
+  </si>
+  <si>
+    <t>sodalite: 4</t>
+  </si>
+  <si>
+    <t>lapis: 3</t>
+  </si>
+  <si>
+    <t>calcite: 3</t>
+  </si>
+  <si>
     <t>deep_graphite</t>
   </si>
   <si>
-    <t>graphite: 100 [1]</t>
-  </si>
-  <si>
-    <t>diamond: 67</t>
+    <t>graphite: 6 [1]</t>
+  </si>
+  <si>
+    <t>diamond: 4</t>
   </si>
   <si>
     <t>deep_tin</t>
   </si>
   <si>
-    <t>cassiterite: 100 [1]</t>
-  </si>
-  <si>
-    <t>tin: 14</t>
+    <t>cassiterite: 7 [1]</t>
+  </si>
+  <si>
+    <t>tin: 1</t>
+  </si>
+  <si>
+    <t>deep_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite: 3</t>
+  </si>
+  <si>
+    <t>ilmenite: 7 [1]</t>
+  </si>
+  <si>
+    <t>deep_copper_tin</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 7</t>
+  </si>
+  <si>
+    <t>zeolite: 3</t>
+  </si>
+  <si>
+    <t>cassiterite: 3</t>
+  </si>
+  <si>
+    <t>deep_thorianite</t>
+  </si>
+  <si>
+    <t>thorium: 4</t>
+  </si>
+  <si>
+    <t>uraninite: 2</t>
+  </si>
+  <si>
+    <t>emerald: 1</t>
+  </si>
+  <si>
+    <t>beryllium: 2 [1]</t>
   </si>
   <si>
     <t>normal_coal</t>
   </si>
   <si>
-    <t>coal: 100 [1]</t>
+    <t>coal: 10 [1]</t>
   </si>
   <si>
     <t>high_lead</t>
   </si>
   <si>
-    <t>lead: 100 [1]</t>
-  </si>
-  <si>
-    <t>silver: 67</t>
+    <t>lead: 6</t>
+  </si>
+  <si>
+    <t>silver: 4</t>
   </si>
   <si>
     <t>surface_mica</t>
   </si>
   <si>
-    <t>mica: 100 [1]</t>
+    <t>mica: 10 [1]</t>
+  </si>
+  <si>
+    <t>deep_nickel</t>
+  </si>
+  <si>
+    <t>garnierite: 7 [1]</t>
+  </si>
+  <si>
+    <t>nickel: 4</t>
+  </si>
+  <si>
+    <t>cobaltite: 5</t>
+  </si>
+  <si>
+    <t>pentlandite: 3</t>
+  </si>
+  <si>
+    <t>high_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite: 50 [1]</t>
+  </si>
+  <si>
+    <t>copper: 30</t>
   </si>
   <si>
     <t>surface_gold</t>
   </si>
   <si>
-    <t>gold: 100 [1]</t>
+    <t>gold: 1</t>
   </si>
   <si>
     <t>surface_sphalerite</t>
   </si>
   <si>
-    <t>sphalerite: 100 [1]</t>
+    <t>sphalerite: 1</t>
   </si>
   <si>
     <t>high_tin</t>
   </si>
   <si>
-    <t>tin: 67</t>
+    <t>tin: 4</t>
+  </si>
+  <si>
+    <t>cassiterite: 6</t>
   </si>
   <si>
     <t>surface_salpeter</t>
   </si>
   <si>
-    <t>saltpeter: 100 [1]</t>
+    <t>saltpeter: 20 [1]</t>
   </si>
   <si>
     <t>high_coal</t>
   </si>
   <si>
-    <t>diamond: 11</t>
-  </si>
-  <si>
-    <t>surface_cobalt</t>
-  </si>
-  <si>
-    <t>cobalt: 100 [1]</t>
+    <t>coal: 9</t>
+  </si>
+  <si>
+    <t>diamond: 1</t>
+  </si>
+  <si>
+    <t>deep_sapphire</t>
+  </si>
+  <si>
+    <t>almandine: 8 [1]</t>
+  </si>
+  <si>
+    <t>pyrope: 12</t>
+  </si>
+  <si>
+    <t>sapphire: 16</t>
+  </si>
+  <si>
+    <t>green_sapphire: 13</t>
+  </si>
+  <si>
+    <t>normal_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 35 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 20</t>
+  </si>
+  <si>
+    <t>copper: 10</t>
+  </si>
+  <si>
+    <t>high_realgar</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 40 [1]</t>
+  </si>
+  <si>
+    <t>zeolite: 20</t>
+  </si>
+  <si>
+    <t>realgar: 15</t>
   </si>
   <si>
     <t>surface_native_copper</t>
   </si>
   <si>
-    <t>copper: 100 [1]</t>
+    <t>copper: 10 [1]</t>
+  </si>
+  <si>
+    <t>normal_galena</t>
+  </si>
+  <si>
+    <t>galena: 7 [1]</t>
+  </si>
+  <si>
+    <t>silver: 2</t>
+  </si>
+  <si>
+    <t>deep_mineral_sand</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand: 8</t>
+  </si>
+  <si>
+    <t>granitic_mineral_sand: 4</t>
+  </si>
+  <si>
+    <t>fullers_earth: 4</t>
+  </si>
+  <si>
+    <t>gypsum: 5</t>
+  </si>
+  <si>
+    <t>surface_sylvite_salt</t>
+  </si>
+  <si>
+    <t>salt: 6</t>
+  </si>
+  <si>
+    <t>rock_salt: 4</t>
+  </si>
+  <si>
+    <t>normal_salt</t>
+  </si>
+  <si>
+    <t>rock_salt: 3</t>
+  </si>
+  <si>
+    <t>borax: 1</t>
+  </si>
+  <si>
+    <t>deep_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite: 6 [1]</t>
+  </si>
+  <si>
+    <t>monazite: 3</t>
+  </si>
+  <si>
+    <t>neodymium: 1</t>
+  </si>
+  <si>
+    <t>normal_quartz</t>
+  </si>
+  <si>
+    <t>quartzite: 9 [1]</t>
+  </si>
+  <si>
+    <t>barite: 3</t>
   </si>
   <si>
     <t>high_sulfur</t>
   </si>
   <si>
-    <t>sulfur: 100 [1]</t>
+    <t>sulfur: 1</t>
+  </si>
+  <si>
+    <t>normal_quartz_borax</t>
+  </si>
+  <si>
+    <t>quartzite: 6</t>
   </si>
   <si>
     <t>surface_limonite</t>
   </si>
   <si>
-    <t>yellow_limonite: 100 [1]</t>
+    <t>yellow_limonite: 20 [1]</t>
+  </si>
+  <si>
+    <t>deep_asbestos</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 5 [1]</t>
+  </si>
+  <si>
+    <t>asbestos: 3</t>
+  </si>
+  <si>
+    <t>diatomite: 1</t>
+  </si>
+  <si>
+    <t>deep_copper_iron</t>
+  </si>
+  <si>
+    <t>chalcopyrite: 6 [1]</t>
+  </si>
+  <si>
+    <t>pyrite: 3</t>
+  </si>
+  <si>
+    <t>copper: 2</t>
+  </si>
+  <si>
+    <t>normal_spodumene</t>
+  </si>
+  <si>
+    <t>spodumene: 15 [1]</t>
+  </si>
+  <si>
+    <t>rock_salt: 5</t>
   </si>
   <si>
     <t>high_gypsum</t>
   </si>
   <si>
-    <t>gypsum: 100 [1]</t>
+    <t>gypsum: 10 [1]</t>
+  </si>
+  <si>
+    <t>deep_apatite</t>
+  </si>
+  <si>
+    <t>apatite: 8</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate: 6</t>
+  </si>
+  <si>
+    <t>pyrochlore: 2</t>
   </si>
   <si>
     <t>deep_sulfur</t>
   </si>
   <si>
-    <t>normal_tin</t>
-  </si>
-  <si>
-    <t>tin: 100 [1]</t>
+    <t>sulfur: 10 [1]</t>
+  </si>
+  <si>
+    <t>deep_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter: 12 [1]</t>
+  </si>
+  <si>
+    <t>diatomite: 5</t>
+  </si>
+  <si>
+    <t>electrotine: 4</t>
+  </si>
+  <si>
+    <t>alunite: 4</t>
+  </si>
+  <si>
+    <t>deep_molybdenum</t>
+  </si>
+  <si>
+    <t>wulfenite: 4</t>
+  </si>
+  <si>
+    <t>molybdenite: 8 [1]</t>
+  </si>
+  <si>
+    <t>molybdenum: 1</t>
+  </si>
+  <si>
+    <t>powellite: 1</t>
+  </si>
+  <si>
+    <t>deep_big_redstone</t>
+  </si>
+  <si>
+    <t>redstone: 10</t>
+  </si>
+  <si>
+    <t>ruby: 6</t>
+  </si>
+  <si>
+    <t>cinnabar: 4</t>
   </si>
   <si>
     <t>deep_redstone</t>
   </si>
   <si>
-    <t>redstone: 100 [1]</t>
-  </si>
-  <si>
-    <t>ruby: 50</t>
-  </si>
-  <si>
-    <t>cinnabar: 25</t>
+    <t>redstone: 4 [1]</t>
+  </si>
+  <si>
+    <t>ruby: 2</t>
+  </si>
+  <si>
+    <t>cinnabar: 1</t>
+  </si>
+  <si>
+    <t>surface_cobaltite</t>
+  </si>
+  <si>
+    <t>cobaltite: 10 [1]</t>
+  </si>
+  <si>
+    <t>deep_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite: 6</t>
+  </si>
+  <si>
+    <t>tungstate: 6</t>
+  </si>
+  <si>
+    <t>lithium: 2</t>
+  </si>
+  <si>
+    <t>normal_iron</t>
+  </si>
+  <si>
+    <t>hematite: 4</t>
+  </si>
+  <si>
+    <t>yellow_limonite: 7 [1]</t>
+  </si>
+  <si>
+    <t>normal_gold</t>
+  </si>
+  <si>
+    <t>gold: 4</t>
+  </si>
+  <si>
+    <t>magnetite: 3</t>
+  </si>
+  <si>
+    <t>normal_asbestos</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 6</t>
+  </si>
+  <si>
+    <t>asbestos: 1</t>
   </si>
   <si>
     <t>surface_hematite</t>
   </si>
   <si>
-    <t>hematite: 100 [1]</t>
+    <t>hematite: 10 [1]</t>
   </si>
   <si>
     <t>surface_malachite</t>
   </si>
   <si>
-    <t>malachite: 100 [1]</t>
-  </si>
-  <si>
-    <t>surface_sylvite_quartz</t>
-  </si>
-  <si>
-    <t>rock_salt: 100 [1]</t>
-  </si>
-  <si>
-    <t>quartzite: 100</t>
+    <t>malachite: 1</t>
+  </si>
+  <si>
+    <t>deep_topaz</t>
+  </si>
+  <si>
+    <t>blue_topaz: 7 [1]</t>
+  </si>
+  <si>
+    <t>topaz: 5</t>
+  </si>
+  <si>
+    <t>chalcocite: 3</t>
+  </si>
+  <si>
+    <t>bornite: 1</t>
+  </si>
+  <si>
+    <t>normal_mica</t>
+  </si>
+  <si>
+    <t>mica: 7</t>
+  </si>
+  <si>
+    <t>kyanite: 5</t>
+  </si>
+  <si>
+    <t>deep_bismuth</t>
+  </si>
+  <si>
+    <t>bismuth: 9</t>
+  </si>
+  <si>
+    <t>silver: 8</t>
+  </si>
+  <si>
+    <t>gold: 8</t>
+  </si>
+  <si>
+    <t>electrotine: 4 [1]</t>
+  </si>
+  <si>
+    <t>deep_magnetite_olivine</t>
+  </si>
+  <si>
+    <t>bentonite: 9 [1]</t>
+  </si>
+  <si>
+    <t>magnesite: 4</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 12</t>
+  </si>
+  <si>
+    <t>deep_manganese</t>
+  </si>
+  <si>
+    <t>grossular: 9</t>
+  </si>
+  <si>
+    <t>pyrolusite: 8</t>
+  </si>
+  <si>
+    <t>tantalite: 4 [1]</t>
+  </si>
+  <si>
+    <t>normal_garnierite</t>
+  </si>
+  <si>
+    <t>garnierite: 12</t>
+  </si>
+  <si>
+    <t>nickel: 4 [1]</t>
+  </si>
+  <si>
+    <t>cobaltite: 7</t>
+  </si>
+  <si>
+    <t>deep_tantalite</t>
+  </si>
+  <si>
+    <t>grossular: 12 [1]</t>
+  </si>
+  <si>
+    <t>spessartine: 10</t>
+  </si>
+  <si>
+    <t>tantalite: 6</t>
   </si>
   <si>
     <t>surface_tricalcium_phosphate</t>
   </si>
   <si>
-    <t>tricalcium_phosphate: 100 [1]</t>
+    <t>tricalcium_phosphate: 1</t>
+  </si>
+  <si>
+    <t>normal_tarkianite</t>
+  </si>
+  <si>
+    <t>tarkianite: 35 [1]</t>
   </si>
   <si>
     <t>high_bismuth</t>
   </si>
   <si>
-    <t>bismuth: 100 [1]</t>
+    <t>bismuth: 1</t>
+  </si>
+  <si>
+    <t>deep_banded_iron</t>
+  </si>
+  <si>
+    <t>goethite: 6 [1]</t>
+  </si>
+  <si>
+    <t>hematite: 3</t>
+  </si>
+  <si>
+    <t>normal_cassiterite</t>
+  </si>
+  <si>
+    <t>cassiterite: 8 [1]</t>
+  </si>
+  <si>
+    <t>tin: 2</t>
   </si>
   <si>
     <t>surface_magnetite</t>
   </si>
   <si>
-    <t>magnetite: 100 [1]</t>
+    <t>magnetite: 20 [1]</t>
   </si>
   <si>
     <t>surface_nickel</t>
   </si>
   <si>
-    <t>garnierite: 100 [1]</t>
+    <t>garnierite: 1</t>
+  </si>
+  <si>
+    <t>deep_kyanite</t>
+  </si>
+  <si>
+    <t>kyanite: 12 [1]</t>
+  </si>
+  <si>
+    <t>mica: 8</t>
+  </si>
+  <si>
+    <t>pollucite: 5</t>
   </si>
   <si>
     <t>surface_tetrahedrite</t>
   </si>
   <si>
-    <t>tetrahedrite: 100 [1]</t>
+    <t>tetrahedrite: 1</t>
+  </si>
+  <si>
+    <t>deep_iron</t>
+  </si>
+  <si>
+    <t>goethite: 7 [1]</t>
+  </si>
+  <si>
+    <t>malachite: 5</t>
+  </si>
+  <si>
+    <t>deep_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite: 12 [1]</t>
+  </si>
+  <si>
+    <t>vanadium_magnetite: 7</t>
   </si>
   <si>
     <t>mars_stone</t>
@@ -1215,9 +1659,6 @@
     <t>emerald: 50</t>
   </si>
   <si>
-    <t>realgar: 15</t>
-  </si>
-  <si>
     <t>mars_neodynium</t>
   </si>
   <si>
@@ -1275,12 +1716,6 @@
     <t>mars_stibnite</t>
   </si>
   <si>
-    <t>tetrahedrite: 50 [1]</t>
-  </si>
-  <si>
-    <t>copper: 30</t>
-  </si>
-  <si>
     <t>deep_mars_sheldonite</t>
   </si>
   <si>
@@ -1300,9 +1735,6 @@
   </si>
   <si>
     <t>grossular: 10</t>
-  </si>
-  <si>
-    <t>spessartine: 10</t>
   </si>
   <si>
     <t>pyrolusite: 40 [1]</t>
@@ -5892,7 +6324,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28571319580078" customWidth="1" style="3"/>
@@ -5904,10 +6336,10 @@
     <col min="7" max="7" width="9.140625" customWidth="1" style="3"/>
     <col min="8" max="8" width="9.140625" customWidth="1" style="3"/>
     <col min="9" max="9" width="9.140625" customWidth="1" style="3"/>
-    <col min="10" max="10" width="32.85714340209961" customWidth="1" style="3"/>
-    <col min="11" max="11" width="15.714285850524902" customWidth="1" style="3"/>
-    <col min="12" max="12" width="14" customWidth="1" style="3"/>
-    <col min="13" max="13" width="9.140625" customWidth="1" style="3"/>
+    <col min="10" max="10" width="27.285715103149414" customWidth="1" style="3"/>
+    <col min="11" max="11" width="27" customWidth="1" style="3"/>
+    <col min="12" max="12" width="17.285715103149414" customWidth="1" style="3"/>
+    <col min="13" max="13" width="22.14285659790039" customWidth="1" style="3"/>
     <col min="14" max="14" width="9.140625" customWidth="1" style="3"/>
     <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
     <col min="16" max="16" width="10.857142448425293" customWidth="1" style="3"/>
@@ -6049,10 +6481,10 @@
         <v>82</v>
       </c>
       <c r="C2" s="3">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="D2" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E2" s="3">
         <v>-50</v>
@@ -6061,10 +6493,10 @@
         <v>20</v>
       </c>
       <c r="H2" s="3">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I2" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>319</v>
@@ -6072,6 +6504,12 @@
       <c r="K2" s="3" t="s">
         <v>320</v>
       </c>
+      <c r="L2" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
       </c>
@@ -6093,44 +6531,44 @@
       <c r="V2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>26</v>
+      <c r="W2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>26</v>
+      <c r="Y2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>25</v>
+      <c r="AC2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG2" s="2" t="s">
-        <v>25</v>
+      <c r="AG2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI2" s="2" t="s">
-        <v>25</v>
+      <c r="AI2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>25</v>
@@ -6138,31 +6576,34 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="D3" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E3" s="3">
         <v>-50</v>
       </c>
       <c r="F3" s="3">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>150</v>
+      </c>
+      <c r="I3" s="3">
+        <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>25</v>
@@ -6185,44 +6626,44 @@
       <c r="V3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>25</v>
+      <c r="W3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>25</v>
+      <c r="Y3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>26</v>
+      <c r="AC3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG3" s="1" t="s">
-        <v>26</v>
+      <c r="AG3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI3" s="1" t="s">
-        <v>26</v>
+      <c r="AI3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>25</v>
@@ -6230,28 +6671,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="D4" s="3">
         <v>0.2</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F4" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -6259,17 +6703,17 @@
       <c r="Q4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>26</v>
+      <c r="R4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>25</v>
@@ -6277,79 +6721,79 @@
       <c r="W4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>26</v>
+      <c r="X4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z4" s="2" t="s">
-        <v>25</v>
+      <c r="Z4" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE4" s="2" t="s">
-        <v>25</v>
+      <c r="AB4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>26</v>
+      <c r="AG4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="3">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="D5" s="3">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="E5" s="3">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>26</v>
+        <v>331</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
@@ -6363,47 +6807,47 @@
       <c r="U5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>26</v>
+      <c r="V5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>26</v>
+      <c r="Y5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG5" s="1" t="s">
-        <v>26</v>
+      <c r="AC5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI5" s="1" t="s">
-        <v>26</v>
+      <c r="AI5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ5" s="1" t="s">
         <v>26</v>
@@ -6411,28 +6855,34 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="3">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="D6" s="3">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="E6" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F6" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>26</v>
@@ -6455,20 +6905,20 @@
       <c r="V6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W6" s="1" t="s">
-        <v>26</v>
+      <c r="W6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>26</v>
+      <c r="Y6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA6" s="1" t="s">
-        <v>26</v>
+      <c r="AA6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>25</v>
@@ -6500,34 +6950,43 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="3">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="D7" s="3">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="E7" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F7" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>26</v>
+        <v>337</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>25</v>
@@ -6541,23 +7000,23 @@
       <c r="U7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>25</v>
+      <c r="V7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>25</v>
+      <c r="Y7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>25</v>
+      <c r="AA7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>25</v>
@@ -6571,8 +7030,8 @@
       <c r="AE7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF7" s="1" t="s">
-        <v>26</v>
+      <c r="AF7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>25</v>
@@ -6589,67 +7048,67 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="3">
-        <v>30</v>
+        <v>340</v>
       </c>
       <c r="D8" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>26</v>
+        <v>342</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>25</v>
+      <c r="AA8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>25</v>
@@ -6660,49 +7119,49 @@
       <c r="AE8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF8" s="1" t="s">
-        <v>26</v>
+      <c r="AF8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH8" s="2" t="s">
-        <v>25</v>
+      <c r="AH8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AI8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ8" s="2" t="s">
-        <v>25</v>
+      <c r="AJ8" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E9" s="3">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>26</v>
@@ -6770,16 +7229,16 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="3">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E10" s="3">
         <v>-20</v>
@@ -6791,7 +7250,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>26</v>
@@ -6814,20 +7273,20 @@
       <c r="V10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W10" s="2" t="s">
-        <v>25</v>
+      <c r="W10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y10" s="2" t="s">
-        <v>25</v>
+      <c r="Y10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA10" s="2" t="s">
-        <v>25</v>
+      <c r="AA10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>25</v>
@@ -6859,126 +7318,138 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="3">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="D11" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E11" s="3">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F11" s="3">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="G11" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>26</v>
+        <v>350</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X11" s="1" t="s">
-        <v>26</v>
+      <c r="X11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z11" s="1" t="s">
-        <v>26</v>
+      <c r="Z11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
-        <v>26</v>
+      <c r="AB11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="E12" s="3">
-        <v>-20</v>
+        <v>110</v>
       </c>
       <c r="F12" s="3">
-        <v>-5</v>
+        <v>160</v>
       </c>
       <c r="G12" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>25</v>
+        <v>354</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>25</v>
@@ -6992,47 +7463,47 @@
       <c r="U12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>25</v>
+      <c r="V12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>25</v>
+      <c r="Y12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG12" s="1" t="s">
-        <v>26</v>
+      <c r="AC12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI12" s="1" t="s">
-        <v>26</v>
+      <c r="AI12" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ12" s="2" t="s">
         <v>25</v>
@@ -7040,16 +7511,16 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="3">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E13" s="3">
         <v>-20</v>
@@ -7058,10 +7529,10 @@
         <v>-5</v>
       </c>
       <c r="G13" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>26</v>
@@ -7129,28 +7600,28 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="3">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D14" s="3">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="3">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F14" s="3">
-        <v>170</v>
+        <v>-5</v>
       </c>
       <c r="G14" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>26</v>
@@ -7158,17 +7629,17 @@
       <c r="Q14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>26</v>
+      <c r="R14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>26</v>
@@ -7176,76 +7647,79 @@
       <c r="W14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X14" s="1" t="s">
-        <v>26</v>
+      <c r="X14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z14" s="1" t="s">
-        <v>26</v>
+      <c r="Z14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>26</v>
+      <c r="AB14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
-        <v>26</v>
+      <c r="AG14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>25</v>
+        <v>361</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>26</v>
@@ -7259,47 +7733,47 @@
       <c r="U15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>25</v>
+      <c r="V15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>25</v>
+      <c r="Y15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>25</v>
+      <c r="AC15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AI15" s="2" t="s">
-        <v>25</v>
+      <c r="AI15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ15" s="1" t="s">
         <v>26</v>
@@ -7307,28 +7781,28 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="D16" s="3">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E16" s="3">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="3">
-        <v>170</v>
+        <v>-5</v>
       </c>
       <c r="G16" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>26</v>
@@ -7336,180 +7810,192 @@
       <c r="Q16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>26</v>
+      <c r="R16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>26</v>
+      <c r="W16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ16" s="1" t="s">
-        <v>26</v>
+      <c r="AG16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E17" s="3">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F17" s="3">
-        <v>-45</v>
+        <v>170</v>
       </c>
       <c r="G17" s="3">
-        <v>18</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>25</v>
+        <v>366</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X17" s="2" t="s">
-        <v>25</v>
+      <c r="X17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z17" s="2" t="s">
-        <v>25</v>
+      <c r="Z17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ17" s="2" t="s">
-        <v>25</v>
+      <c r="AB17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C18" s="3">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D18" s="3">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="3">
+        <v>20</v>
+      </c>
+      <c r="H18" s="3">
         <v>60</v>
       </c>
-      <c r="G18" s="3">
-        <v>26</v>
+      <c r="I18" s="3">
+        <v>10</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>353</v>
+        <v>369</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>372</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>25</v>
@@ -7577,40 +8063,40 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D19" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="3">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G19" s="3">
         <v>20</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>25</v>
+        <v>376</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>25</v>
@@ -7624,8 +8110,8 @@
       <c r="U19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>25</v>
+      <c r="V19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>26</v>
@@ -7654,8 +8140,8 @@
       <c r="AE19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF19" s="2" t="s">
-        <v>25</v>
+      <c r="AF19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG19" s="2" t="s">
         <v>25</v>
@@ -7672,28 +8158,37 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="D20" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E20" s="3">
-        <v>-20</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3">
-        <v>-5</v>
+        <v>170</v>
       </c>
       <c r="G20" s="3">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="H20" s="3">
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>359</v>
+        <v>378</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>26</v>
@@ -7716,20 +8211,20 @@
       <c r="V20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W20" s="2" t="s">
-        <v>25</v>
+      <c r="W20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y20" s="2" t="s">
-        <v>25</v>
+      <c r="Y20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA20" s="2" t="s">
-        <v>25</v>
+      <c r="AA20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>25</v>
@@ -7761,13 +8256,13 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D21" s="3">
         <v>0.2</v>
@@ -7782,16 +8277,16 @@
         <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>26</v>
+        <v>382</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>25</v>
@@ -7802,47 +8297,47 @@
       <c r="U21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>25</v>
+      <c r="V21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X21" s="1" t="s">
-        <v>26</v>
+      <c r="X21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z21" s="1" t="s">
-        <v>26</v>
+      <c r="Z21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG21" s="1" t="s">
-        <v>26</v>
+      <c r="AB21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI21" s="1" t="s">
-        <v>26</v>
+      <c r="AI21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ21" s="2" t="s">
         <v>25</v>
@@ -7850,31 +8345,31 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="3">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="D22" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E22" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="G22" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -7942,28 +8437,37 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="3">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="D23" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E23" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>366</v>
+        <v>387</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>390</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>25</v>
@@ -8031,67 +8535,70 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="3">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="3">
-        <v>170</v>
+        <v>-5</v>
       </c>
       <c r="G24" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>26</v>
+        <v>392</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB24" s="1" t="s">
-        <v>26</v>
+      <c r="AA24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>26</v>
@@ -8102,46 +8609,55 @@
       <c r="AE24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF24" s="1" t="s">
-        <v>26</v>
+      <c r="AF24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AH24" s="1" t="s">
-        <v>26</v>
+      <c r="AH24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ24" s="1" t="s">
-        <v>26</v>
+      <c r="AJ24" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="E25" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="G25" s="3">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="H25" s="3">
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>370</v>
+        <v>392</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>396</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -8209,28 +8725,34 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="3">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="D26" s="3">
         <v>0.15</v>
       </c>
       <c r="E26" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>372</v>
+        <v>398</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -8238,17 +8760,17 @@
       <c r="Q26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>26</v>
+      <c r="R26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>25</v>
@@ -8256,70 +8778,76 @@
       <c r="W26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X26" s="1" t="s">
-        <v>26</v>
+      <c r="X26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z26" s="2" t="s">
-        <v>25</v>
+      <c r="Z26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE26" s="2" t="s">
-        <v>25</v>
+      <c r="AB26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ26" s="1" t="s">
-        <v>26</v>
+      <c r="AG26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C27" s="3">
-        <v>7</v>
+        <v>170</v>
       </c>
       <c r="D27" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E27" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="G27" s="3">
         <v>10</v>
       </c>
+      <c r="H27" s="3">
+        <v>4</v>
+      </c>
       <c r="J27" s="3" t="s">
-        <v>374</v>
+        <v>402</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>403</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>25</v>
@@ -8327,17 +8855,17 @@
       <c r="Q27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>25</v>
+      <c r="R27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>25</v>
@@ -8345,43 +8873,3605 @@
       <c r="W27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X27" s="2" t="s">
-        <v>25</v>
+      <c r="X27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z27" s="1" t="s">
-        <v>26</v>
+      <c r="Z27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>26</v>
+      <c r="AB27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ27" s="2" t="s">
+      <c r="AG27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="3">
+        <v>120</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="3">
+        <v>100</v>
+      </c>
+      <c r="F28" s="3">
+        <v>170</v>
+      </c>
+      <c r="G28" s="3">
+        <v>10</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="3">
+        <v>190</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>60</v>
+      </c>
+      <c r="H29" s="3">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="3">
+        <v>90</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G30" s="3">
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="3">
+        <v>240</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E31" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F31" s="3">
+        <v>20</v>
+      </c>
+      <c r="G31" s="3">
+        <v>22</v>
+      </c>
+      <c r="H31" s="3">
+        <v>5</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="3">
+        <v>320</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F32" s="3">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3">
+        <v>32</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ32" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="3">
+        <v>190</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>60</v>
+      </c>
+      <c r="G33" s="3">
+        <v>15</v>
+      </c>
+      <c r="H33" s="3">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ33" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="3">
+        <v>180</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>100</v>
+      </c>
+      <c r="F34" s="3">
+        <v>170</v>
+      </c>
+      <c r="G34" s="3">
+        <v>10</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ34" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="3">
+        <v>240</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F35" s="3">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3">
+        <v>24</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E36" s="3">
+        <v>-60</v>
+      </c>
+      <c r="F36" s="3">
+        <v>-45</v>
+      </c>
+      <c r="G36" s="3">
+        <v>18</v>
+      </c>
+      <c r="H36" s="3">
+        <v>5</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ36" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="3">
+        <v>310</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F37" s="3">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3">
+        <v>19</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ37" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="3">
+        <v>260</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E38" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F38" s="3">
+        <v>20</v>
+      </c>
+      <c r="G38" s="3">
+        <v>25</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="3">
+        <v>320</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F39" s="3">
+        <v>20</v>
+      </c>
+      <c r="G39" s="3">
+        <v>29</v>
+      </c>
+      <c r="H39" s="3">
+        <v>5</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="3">
+        <v>120</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F40" s="3">
+        <v>20</v>
+      </c>
+      <c r="G40" s="3">
+        <v>20</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ40" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="3">
+        <v>90</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E41" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F41" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G41" s="3">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ41" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="3">
+        <v>390</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E42" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F42" s="3">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3">
+        <v>12</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ42" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="3">
+        <v>185</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>60</v>
+      </c>
+      <c r="G43" s="3">
+        <v>15</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ43" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="3">
+        <v>160</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>60</v>
+      </c>
+      <c r="G44" s="3">
+        <v>15</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ44" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="3">
+        <v>190</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>60</v>
+      </c>
+      <c r="G45" s="3">
+        <v>15</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="3">
+        <v>45</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E46" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F46" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G46" s="3">
+        <v>15</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ46" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="3">
+        <v>32</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E47" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F47" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G47" s="3">
+        <v>15</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ47" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="3">
+        <v>280</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E48" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F48" s="3">
+        <v>20</v>
+      </c>
+      <c r="G48" s="3">
+        <v>14</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ48" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="3">
+        <v>180</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>60</v>
+      </c>
+      <c r="G49" s="3">
+        <v>10</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ49" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="3">
+        <v>310</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E50" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F50" s="3">
+        <v>20</v>
+      </c>
+      <c r="H50" s="3">
+        <v>60</v>
+      </c>
+      <c r="I50" s="3">
+        <v>10</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ50" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="3">
+        <v>210</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E51" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F51" s="3">
+        <v>20</v>
+      </c>
+      <c r="G51" s="3">
+        <v>24</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ51" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="3">
+        <v>290</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E52" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F52" s="3">
+        <v>20</v>
+      </c>
+      <c r="G52" s="3">
+        <v>24</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ52" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="3">
+        <v>190</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>60</v>
+      </c>
+      <c r="G53" s="3">
+        <v>15</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ53" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="3">
+        <v>340</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E54" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F54" s="3">
+        <v>20</v>
+      </c>
+      <c r="G54" s="3">
+        <v>18</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ54" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="3">
+        <v>60</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E55" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F55" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G55" s="3">
+        <v>10</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ55" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="3">
+        <v>140</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>60</v>
+      </c>
+      <c r="H56" s="3">
+        <v>60</v>
+      </c>
+      <c r="I56" s="3">
+        <v>10</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ56" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="3">
+        <v>150</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>170</v>
+      </c>
+      <c r="G57" s="3">
+        <v>20</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ57" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="3">
+        <v>380</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E58" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F58" s="3">
+        <v>20</v>
+      </c>
+      <c r="G58" s="3">
+        <v>32</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ58" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="3">
+        <v>220</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>60</v>
+      </c>
+      <c r="G59" s="3">
+        <v>16</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ59" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="3">
+        <v>90</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F60" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G60" s="3">
+        <v>15</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ60" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="3">
+        <v>60</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E61" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F61" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G61" s="3">
+        <v>15</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3">
+        <v>210</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E62" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F62" s="3">
+        <v>20</v>
+      </c>
+      <c r="G62" s="3">
+        <v>22</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ62" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="3">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E63" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F63" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G63" s="3">
+        <v>10</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ63" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="3">
+        <v>210</v>
+      </c>
+      <c r="D64" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E64" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F64" s="3">
+        <v>20</v>
+      </c>
+      <c r="G64" s="3">
+        <v>24</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="3">
+        <v>210</v>
+      </c>
+      <c r="D65" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F65" s="3">
+        <v>20</v>
+      </c>
+      <c r="G65" s="3">
+        <v>28</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ65" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -8514,13 +12604,13 @@
         <v>311</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>375</v>
+        <v>523</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>314</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>376</v>
+        <v>524</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>185</v>
@@ -8534,7 +12624,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>377</v>
+        <v>525</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -8555,13 +12645,13 @@
         <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>378</v>
+        <v>526</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>379</v>
+        <v>527</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>380</v>
+        <v>528</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
@@ -8620,7 +12710,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>381</v>
+        <v>529</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -8641,13 +12731,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>382</v>
+        <v>530</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>383</v>
+        <v>531</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>384</v>
+        <v>532</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>45</v>
@@ -8709,7 +12799,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>385</v>
+        <v>533</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -8730,10 +12820,10 @@
         <v>55</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>386</v>
+        <v>534</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>387</v>
+        <v>535</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -8792,7 +12882,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>536</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -8813,10 +12903,10 @@
         <v>45</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>389</v>
+        <v>537</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>390</v>
+        <v>538</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>167</v>
@@ -8878,7 +12968,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>391</v>
+        <v>539</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>34</v>
@@ -8973,7 +13063,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>392</v>
+        <v>540</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -8994,7 +13084,7 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>393</v>
+        <v>541</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>76</v>
@@ -9003,10 +13093,10 @@
         <v>254</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>394</v>
+        <v>542</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>395</v>
+        <v>543</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>25</v>
@@ -9065,7 +13155,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>396</v>
+        <v>544</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>82</v>
@@ -9089,13 +13179,13 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>397</v>
+        <v>545</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>26</v>
@@ -9154,7 +13244,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>400</v>
+        <v>547</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -9243,7 +13333,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>401</v>
+        <v>548</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -9264,16 +13354,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>403</v>
+        <v>550</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>404</v>
+        <v>551</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>405</v>
+        <v>552</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
@@ -9332,7 +13422,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>406</v>
+        <v>553</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
@@ -9356,16 +13446,16 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>407</v>
+        <v>554</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>408</v>
+        <v>555</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>409</v>
+        <v>556</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>410</v>
+        <v>557</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>25</v>
@@ -9424,7 +13514,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>411</v>
+        <v>558</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -9445,19 +13535,19 @@
         <v>40</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>412</v>
+        <v>559</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>413</v>
+        <v>560</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>414</v>
+        <v>561</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>415</v>
+        <v>562</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>45</v>
@@ -9519,7 +13609,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>416</v>
+        <v>563</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -9540,7 +13630,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>417</v>
+        <v>564</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>299</v>
@@ -9608,7 +13698,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>418</v>
+        <v>565</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -9629,10 +13719,10 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>420</v>
+        <v>355</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>122</v>
@@ -9697,7 +13787,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>421</v>
+        <v>566</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -9786,7 +13876,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>422</v>
+        <v>567</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>82</v>
@@ -9813,13 +13903,13 @@
         <v>104</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>423</v>
+        <v>568</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>424</v>
+        <v>569</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>425</v>
+        <v>570</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>25</v>
@@ -9878,7 +13968,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>426</v>
+        <v>571</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -9899,16 +13989,16 @@
         <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>427</v>
+        <v>572</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>428</v>
+        <v>493</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>429</v>
+        <v>573</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>430</v>
+        <v>574</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>25</v>
@@ -9967,7 +14057,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>431</v>
+        <v>575</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -9988,13 +14078,13 @@
         <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>432</v>
+        <v>576</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>433</v>
+        <v>577</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>434</v>
+        <v>578</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>131</v>
@@ -10056,7 +14146,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>435</v>
+        <v>579</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -10077,13 +14167,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>436</v>
+        <v>580</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>437</v>
+        <v>581</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>438</v>
+        <v>582</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>45</v>
@@ -10145,7 +14235,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>439</v>
+        <v>583</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -10169,7 +14259,7 @@
         <v>161</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>440</v>
+        <v>584</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>256</v>
@@ -10234,7 +14324,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>441</v>
+        <v>585</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -10255,16 +14345,16 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>442</v>
+        <v>586</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>425</v>
+        <v>570</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>443</v>
+        <v>587</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>444</v>
+        <v>588</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>25</v>
@@ -10323,7 +14413,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>445</v>
+        <v>589</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -10344,16 +14434,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>446</v>
+        <v>590</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>447</v>
+        <v>591</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>448</v>
+        <v>592</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -10412,7 +14502,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>449</v>
+        <v>593</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -10436,7 +14526,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>379</v>
+        <v>527</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>54</v>
@@ -10498,7 +14588,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>450</v>
+        <v>594</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
@@ -10525,7 +14615,7 @@
         <v>207</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>451</v>
+        <v>595</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>209</v>
@@ -10587,7 +14677,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>452</v>
+        <v>596</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
@@ -10614,7 +14704,7 @@
         <v>234</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>453</v>
+        <v>597</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -10673,7 +14763,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>454</v>
+        <v>598</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
@@ -10694,16 +14784,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>455</v>
+        <v>599</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>456</v>
+        <v>600</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>122</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>457</v>
+        <v>601</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -10762,7 +14852,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>458</v>
+        <v>602</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -10783,13 +14873,13 @@
         <v>50</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>459</v>
+        <v>603</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>456</v>
+        <v>600</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>460</v>
+        <v>604</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>45</v>
@@ -10851,7 +14941,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>461</v>
+        <v>605</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>20</v>
@@ -10872,13 +14962,13 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>446</v>
+        <v>590</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>447</v>
+        <v>591</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>462</v>
+        <v>606</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>96</v>
@@ -10940,7 +15030,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>463</v>
+        <v>607</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -6484,7 +6484,7 @@
         <v>130</v>
       </c>
       <c r="D2" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E2" s="3">
         <v>-50</v>
@@ -6585,7 +6585,7 @@
         <v>140</v>
       </c>
       <c r="D3" s="3">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E3" s="3">
         <v>-50</v>
@@ -6680,7 +6680,7 @@
         <v>210</v>
       </c>
       <c r="D4" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E4" s="3">
         <v>-50</v>
@@ -6689,7 +6689,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>327</v>
@@ -6772,7 +6772,7 @@
         <v>310</v>
       </c>
       <c r="D5" s="3">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E5" s="3">
         <v>-50</v>
@@ -6781,7 +6781,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>330</v>
@@ -6864,7 +6864,7 @@
         <v>210</v>
       </c>
       <c r="D6" s="3">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E6" s="3">
         <v>-50</v>
@@ -6873,7 +6873,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>333</v>
@@ -6959,7 +6959,7 @@
         <v>270</v>
       </c>
       <c r="D7" s="3">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="E7" s="3">
         <v>-50</v>
@@ -6968,7 +6968,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>337</v>
@@ -7327,7 +7327,7 @@
         <v>180</v>
       </c>
       <c r="D11" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E11" s="3">
         <v>-50</v>
@@ -7336,7 +7336,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="3">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>349</v>
@@ -7422,7 +7422,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3">
         <v>0.25</v>
@@ -7971,7 +7971,7 @@
         <v>180</v>
       </c>
       <c r="D18" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E18" s="3">
         <v>-50</v>
@@ -8164,7 +8164,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="3">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3">
         <v>0.25</v>
@@ -8446,7 +8446,7 @@
         <v>190</v>
       </c>
       <c r="D23" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E23" s="3">
         <v>-50</v>
@@ -8455,7 +8455,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>387</v>
@@ -8734,7 +8734,7 @@
         <v>290</v>
       </c>
       <c r="D26" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E26" s="3">
         <v>-50</v>
@@ -8743,7 +8743,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>398</v>
@@ -9197,7 +9197,7 @@
         <v>190</v>
       </c>
       <c r="D31" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E31" s="3">
         <v>-50</v>
@@ -9206,7 +9206,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H31" s="3">
         <v>5</v>
@@ -9295,7 +9295,7 @@
         <v>270</v>
       </c>
       <c r="D32" s="3">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="E32" s="3">
         <v>-50</v>
@@ -9304,7 +9304,7 @@
         <v>20</v>
       </c>
       <c r="G32" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>415</v>
@@ -9577,7 +9577,7 @@
         <v>190</v>
       </c>
       <c r="D35" s="3">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="E35" s="3">
         <v>-50</v>
@@ -9586,7 +9586,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>424</v>
@@ -9669,10 +9669,10 @@
         <v>34</v>
       </c>
       <c r="C36" s="3">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D36" s="3">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="E36" s="3">
         <v>-60</v>
@@ -9681,7 +9681,7 @@
         <v>-45</v>
       </c>
       <c r="G36" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3">
         <v>5</v>
@@ -9764,7 +9764,7 @@
         <v>260</v>
       </c>
       <c r="D37" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E37" s="3">
         <v>-50</v>
@@ -9773,7 +9773,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>430</v>
@@ -9862,7 +9862,7 @@
         <v>210</v>
       </c>
       <c r="D38" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E38" s="3">
         <v>-50</v>
@@ -9871,7 +9871,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>435</v>
@@ -9960,7 +9960,7 @@
         <v>270</v>
       </c>
       <c r="D39" s="3">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="E39" s="3">
         <v>-50</v>
@@ -9969,7 +9969,7 @@
         <v>20</v>
       </c>
       <c r="G39" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H39" s="3">
         <v>5</v>
@@ -10058,7 +10058,7 @@
         <v>120</v>
       </c>
       <c r="D40" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E40" s="3">
         <v>-50</v>
@@ -10067,7 +10067,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>444</v>
@@ -10242,7 +10242,7 @@
         <v>340</v>
       </c>
       <c r="D42" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E42" s="3">
         <v>-50</v>
@@ -10251,7 +10251,7 @@
         <v>20</v>
       </c>
       <c r="G42" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>450</v>
@@ -10791,7 +10791,7 @@
         <v>230</v>
       </c>
       <c r="D48" s="3">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E48" s="3">
         <v>-50</v>
@@ -10800,7 +10800,7 @@
         <v>20</v>
       </c>
       <c r="G48" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>467</v>
@@ -10981,7 +10981,7 @@
         <v>140</v>
       </c>
       <c r="D50" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E50" s="3">
         <v>-50</v>
@@ -11082,7 +11082,7 @@
         <v>160</v>
       </c>
       <c r="D51" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E51" s="3">
         <v>-50</v>
@@ -11091,7 +11091,7 @@
         <v>20</v>
       </c>
       <c r="G51" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>480</v>
@@ -11180,7 +11180,7 @@
         <v>240</v>
       </c>
       <c r="D52" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E52" s="3">
         <v>-50</v>
@@ -11189,7 +11189,7 @@
         <v>20</v>
       </c>
       <c r="G52" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>484</v>
@@ -11370,7 +11370,7 @@
         <v>290</v>
       </c>
       <c r="D54" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E54" s="3">
         <v>-50</v>
@@ -11379,7 +11379,7 @@
         <v>20</v>
       </c>
       <c r="G54" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>492</v>
@@ -11744,7 +11744,7 @@
         <v>280</v>
       </c>
       <c r="D58" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E58" s="3">
         <v>-50</v>
@@ -11753,7 +11753,7 @@
         <v>20</v>
       </c>
       <c r="G58" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>502</v>
@@ -12109,7 +12109,7 @@
         <v>160</v>
       </c>
       <c r="D62" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E62" s="3">
         <v>-50</v>
@@ -12118,7 +12118,7 @@
         <v>20</v>
       </c>
       <c r="G62" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>512</v>
@@ -12293,7 +12293,7 @@
         <v>160</v>
       </c>
       <c r="D64" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E64" s="3">
         <v>-50</v>
@@ -12302,7 +12302,7 @@
         <v>20</v>
       </c>
       <c r="G64" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>518</v>
@@ -12391,7 +12391,7 @@
         <v>160</v>
       </c>
       <c r="D65" s="3">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="E65" s="3">
         <v>-50</v>
@@ -12400,7 +12400,7 @@
         <v>20</v>
       </c>
       <c r="G65" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>521</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="618">
   <si>
     <t>Vein ID</t>
   </si>
@@ -936,6 +936,12 @@
     <t>pentlandite: 15</t>
   </si>
   <si>
+    <t>black_sand</t>
+  </si>
+  <si>
+    <t>brown_sand</t>
+  </si>
+  <si>
     <t>chalk</t>
   </si>
   <si>
@@ -951,6 +957,9 @@
     <t>dolomite</t>
   </si>
   <si>
+    <t>green_sand</t>
+  </si>
+  <si>
     <t>limestone</t>
   </si>
   <si>
@@ -960,9 +969,15 @@
     <t>phyllite</t>
   </si>
   <si>
+    <t>pink_sand</t>
+  </si>
+  <si>
     <t>quartzite</t>
   </si>
   <si>
+    <t>red_sand</t>
+  </si>
+  <si>
     <t>shale</t>
   </si>
   <si>
@@ -972,6 +987,12 @@
     <t>tuff</t>
   </si>
   <si>
+    <t>white_sand</t>
+  </si>
+  <si>
+    <t>yellow_sand</t>
+  </si>
+  <si>
     <t>deep_lazurite_calcite</t>
   </si>
   <si>
@@ -1041,6 +1062,12 @@
     <t>beryllium: 2 [1]</t>
   </si>
   <si>
+    <t>sand_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 1</t>
+  </si>
+  <si>
     <t>normal_coal</t>
   </si>
   <si>
@@ -1242,6 +1269,12 @@
     <t>quartzite: 6</t>
   </si>
   <si>
+    <t>sand_mineral_sand</t>
+  </si>
+  <si>
+    <t>glauconite_sand: 5</t>
+  </si>
+  <si>
     <t>surface_limonite</t>
   </si>
   <si>
@@ -1696,9 +1729,6 @@
   </si>
   <si>
     <t>soapstone: 15</t>
-  </si>
-  <si>
-    <t>glauconite_sand: 5</t>
   </si>
   <si>
     <t>trona: 25</t>
@@ -1963,7 +1993,14 @@
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
     <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="9.140625" customWidth="1" style="3"/>
+    <col min="50" max="50" width="9.140625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9.140625" customWidth="1" style="3"/>
+    <col min="52" max="52" width="9.140625" customWidth="1" style="3"/>
+    <col min="53" max="53" width="9.140625" customWidth="1" style="3"/>
+    <col min="54" max="54" width="9.140625" customWidth="1" style="3"/>
+    <col min="55" max="55" width="9.140625" customWidth="1" style="3"/>
+    <col min="56" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -4232,7 +4269,14 @@
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
     <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="9.140625" customWidth="1" style="3"/>
+    <col min="50" max="50" width="9.140625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9.140625" customWidth="1" style="3"/>
+    <col min="52" max="52" width="9.140625" customWidth="1" style="3"/>
+    <col min="53" max="53" width="9.140625" customWidth="1" style="3"/>
+    <col min="54" max="54" width="9.140625" customWidth="1" style="3"/>
+    <col min="55" max="55" width="9.140625" customWidth="1" style="3"/>
+    <col min="56" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -4467,7 +4511,14 @@
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
     <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="9.140625" customWidth="1" style="3"/>
+    <col min="50" max="50" width="9.140625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9.140625" customWidth="1" style="3"/>
+    <col min="52" max="52" width="9.140625" customWidth="1" style="3"/>
+    <col min="53" max="53" width="9.140625" customWidth="1" style="3"/>
+    <col min="54" max="54" width="9.140625" customWidth="1" style="3"/>
+    <col min="55" max="55" width="9.140625" customWidth="1" style="3"/>
+    <col min="56" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -6324,7 +6375,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ65"/>
+  <dimension ref="A1:AQ67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28571319580078" customWidth="1" style="3"/>
@@ -6344,38 +6395,45 @@
     <col min="15" max="15" width="9.140625" customWidth="1" style="3"/>
     <col min="16" max="16" width="10.857142448425293" customWidth="1" style="3"/>
     <col min="17" max="17" width="9.140625" customWidth="1" style="3"/>
-    <col min="18" max="18" width="9.140625" customWidth="1" style="3"/>
-    <col min="19" max="19" width="9.140625" customWidth="1" style="3"/>
-    <col min="20" max="20" width="12.142857551574707" customWidth="1" style="3"/>
-    <col min="21" max="21" width="17" customWidth="1" style="3"/>
-    <col min="22" max="22" width="9.140625" customWidth="1" style="3"/>
-    <col min="23" max="23" width="9.140625" customWidth="1" style="3"/>
-    <col min="24" max="24" width="11.142857551574707" customWidth="1" style="3"/>
+    <col min="18" max="18" width="14" customWidth="1" style="3"/>
+    <col min="19" max="19" width="15" customWidth="1" style="3"/>
+    <col min="20" max="20" width="9.140625" customWidth="1" style="3"/>
+    <col min="21" max="21" width="9.140625" customWidth="1" style="3"/>
+    <col min="22" max="22" width="12.142857551574707" customWidth="1" style="3"/>
+    <col min="23" max="23" width="17" customWidth="1" style="3"/>
+    <col min="24" max="24" width="9.140625" customWidth="1" style="3"/>
     <col min="25" max="25" width="9.140625" customWidth="1" style="3"/>
-    <col min="26" max="26" width="9.140625" customWidth="1" style="3"/>
-    <col min="27" max="27" width="9.142857551574707" customWidth="1" style="3"/>
-    <col min="28" max="28" width="12.428571701049805" customWidth="1" style="3"/>
-    <col min="29" max="29" width="9.140625" customWidth="1" style="3"/>
-    <col min="30" max="30" width="9.571428298950195" customWidth="1" style="3"/>
-    <col min="31" max="31" width="11.428571701049805" customWidth="1" style="3"/>
-    <col min="32" max="32" width="9.857142448425293" customWidth="1" style="3"/>
-    <col min="33" max="33" width="9.140625" customWidth="1" style="3"/>
-    <col min="34" max="34" width="9.140625" customWidth="1" style="3"/>
-    <col min="35" max="35" width="9.140625" customWidth="1" style="3"/>
-    <col min="36" max="36" width="9.140625" customWidth="1" style="3"/>
-    <col min="37" max="37" width="9.140625" customWidth="1" style="3"/>
+    <col min="26" max="26" width="11.142857551574707" customWidth="1" style="3"/>
+    <col min="27" max="27" width="9.140625" customWidth="1" style="3"/>
+    <col min="28" max="28" width="9.140625" customWidth="1" style="3"/>
+    <col min="29" max="29" width="9.142857551574707" customWidth="1" style="3"/>
+    <col min="30" max="30" width="14.428571701049805" customWidth="1" style="3"/>
+    <col min="31" max="31" width="12.428571701049805" customWidth="1" style="3"/>
+    <col min="32" max="32" width="9.140625" customWidth="1" style="3"/>
+    <col min="33" max="33" width="9.571428298950195" customWidth="1" style="3"/>
+    <col min="34" max="34" width="12.714285850524902" customWidth="1" style="3"/>
+    <col min="35" max="35" width="11.428571701049805" customWidth="1" style="3"/>
+    <col min="36" max="36" width="11.571428298950195" customWidth="1" style="3"/>
+    <col min="37" max="37" width="9.857142448425293" customWidth="1" style="3"/>
     <col min="38" max="38" width="9.140625" customWidth="1" style="3"/>
     <col min="39" max="39" width="9.140625" customWidth="1" style="3"/>
     <col min="40" max="40" width="9.140625" customWidth="1" style="3"/>
     <col min="41" max="41" width="9.140625" customWidth="1" style="3"/>
-    <col min="42" max="42" width="9.140625" customWidth="1" style="3"/>
-    <col min="43" max="43" width="9.140625" customWidth="1" style="3"/>
+    <col min="42" max="42" width="14.285714149475098" customWidth="1" style="3"/>
+    <col min="43" max="43" width="15.428571701049805" customWidth="1" style="3"/>
     <col min="44" max="44" width="9.140625" customWidth="1" style="3"/>
     <col min="45" max="45" width="9.140625" customWidth="1" style="3"/>
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
     <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="9.140625" customWidth="1" style="3"/>
+    <col min="50" max="50" width="9.140625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9.140625" customWidth="1" style="3"/>
+    <col min="52" max="52" width="9.140625" customWidth="1" style="3"/>
+    <col min="53" max="53" width="9.140625" customWidth="1" style="3"/>
+    <col min="54" max="54" width="9.140625" customWidth="1" style="3"/>
+    <col min="55" max="55" width="9.140625" customWidth="1" style="3"/>
+    <col min="56" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -6428,28 +6486,28 @@
         <v>309</v>
       </c>
       <c r="V1" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="AD1" s="4" t="s">
         <v>313</v>
@@ -6458,24 +6516,45 @@
         <v>314</v>
       </c>
       <c r="AF1" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="AK1" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>317</v>
+      <c r="AM1" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="AO1" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="AP1" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>82</v>
@@ -6499,16 +6578,16 @@
         <v>10</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
@@ -6540,26 +6619,26 @@
       <c r="Y2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>26</v>
+      <c r="Z2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>25</v>
+      <c r="AB2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>26</v>
@@ -6571,12 +6650,33 @@
         <v>26</v>
       </c>
       <c r="AJ2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>82</v>
@@ -6600,10 +6700,10 @@
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>25</v>
@@ -6626,8 +6726,8 @@
       <c r="V3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>26</v>
+      <c r="W3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>25</v>
@@ -6644,8 +6744,8 @@
       <c r="AB3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="2" t="s">
-        <v>25</v>
+      <c r="AC3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD3" s="2" t="s">
         <v>25</v>
@@ -6666,12 +6766,33 @@
         <v>25</v>
       </c>
       <c r="AJ3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -6692,10 +6813,10 @@
         <v>30</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -6727,26 +6848,26 @@
       <c r="Y4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>26</v>
+      <c r="Z4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF4" s="2" t="s">
-        <v>25</v>
+      <c r="AB4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG4" s="1" t="s">
         <v>26</v>
@@ -6758,12 +6879,33 @@
         <v>26</v>
       </c>
       <c r="AJ4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -6784,10 +6926,10 @@
         <v>24</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>25</v>
@@ -6795,11 +6937,11 @@
       <c r="Q5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>26</v>
+      <c r="R5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>26</v>
@@ -6807,35 +6949,35 @@
       <c r="U5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>25</v>
+      <c r="V5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>26</v>
+      <c r="X5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>25</v>
+      <c r="Z5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>25</v>
+      <c r="AB5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE5" s="2" t="s">
-        <v>25</v>
+      <c r="AE5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF5" s="2" t="s">
         <v>25</v>
@@ -6843,19 +6985,40 @@
       <c r="AG5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH5" s="1" t="s">
-        <v>26</v>
+      <c r="AH5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ5" s="1" t="s">
-        <v>26</v>
+      <c r="AJ5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
@@ -6876,13 +7039,13 @@
         <v>39</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>26</v>
@@ -6902,14 +7065,14 @@
       <c r="U6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>25</v>
+      <c r="V6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>26</v>
@@ -6923,8 +7086,8 @@
       <c r="AB6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC6" s="2" t="s">
-        <v>25</v>
+      <c r="AC6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>25</v>
@@ -6932,8 +7095,8 @@
       <c r="AE6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF6" s="1" t="s">
-        <v>26</v>
+      <c r="AF6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>25</v>
@@ -6945,12 +7108,33 @@
         <v>25</v>
       </c>
       <c r="AJ6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -6971,16 +7155,16 @@
         <v>28</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>25</v>
@@ -7003,8 +7187,8 @@
       <c r="V7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W7" s="1" t="s">
-        <v>26</v>
+      <c r="W7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>25</v>
@@ -7021,8 +7205,8 @@
       <c r="AB7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>25</v>
+      <c r="AC7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>25</v>
@@ -7043,33 +7227,54 @@
         <v>25</v>
       </c>
       <c r="AJ7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="3">
-        <v>340</v>
+        <v>190</v>
       </c>
       <c r="D8" s="3">
         <v>0.2</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F8" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>25</v>
@@ -7083,11 +7288,11 @@
       <c r="S8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>26</v>
+      <c r="T8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>25</v>
@@ -7095,8 +7300,8 @@
       <c r="W8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>26</v>
+      <c r="X8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>25</v>
@@ -7107,14 +7312,14 @@
       <c r="AA8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB8" s="1" t="s">
-        <v>26</v>
+      <c r="AB8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AD8" s="2" t="s">
-        <v>25</v>
+      <c r="AD8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AE8" s="2" t="s">
         <v>25</v>
@@ -7132,48 +7337,66 @@
         <v>25</v>
       </c>
       <c r="AJ8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="3">
-        <v>90</v>
+        <v>340</v>
       </c>
       <c r="D9" s="3">
         <v>0.2</v>
       </c>
       <c r="E9" s="3">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>26</v>
@@ -7187,49 +7410,70 @@
       <c r="W9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>26</v>
+      <c r="X9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>26</v>
+      <c r="AA9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>26</v>
+      <c r="AF9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -7238,19 +7482,22 @@
         <v>90</v>
       </c>
       <c r="D10" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E10" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F10" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>26</v>
@@ -7264,11 +7511,11 @@
       <c r="S10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>25</v>
+      <c r="T10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>26</v>
@@ -7276,85 +7523,97 @@
       <c r="W10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X10" s="2" t="s">
-        <v>25</v>
+      <c r="X10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z10" s="2" t="s">
-        <v>25</v>
+      <c r="Z10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>25</v>
+      <c r="AB10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE10" s="2" t="s">
-        <v>25</v>
+      <c r="AE10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG10" s="2" t="s">
-        <v>25</v>
+      <c r="AG10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI10" s="2" t="s">
-        <v>25</v>
+      <c r="AI10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F11" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G11" s="3">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>25</v>
+        <v>356</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>25</v>
@@ -7371,11 +7630,11 @@
       <c r="V11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>25</v>
+      <c r="W11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>26</v>
@@ -7389,8 +7648,8 @@
       <c r="AB11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC11" s="2" t="s">
-        <v>25</v>
+      <c r="AC11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD11" s="2" t="s">
         <v>25</v>
@@ -7411,45 +7670,69 @@
         <v>25</v>
       </c>
       <c r="AJ11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="D12" s="3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E12" s="3">
-        <v>110</v>
+        <v>-50</v>
       </c>
       <c r="F12" s="3">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="G12" s="3">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>26</v>
+        <v>360</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>25</v>
@@ -7463,11 +7746,11 @@
       <c r="U12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>26</v>
+      <c r="V12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>25</v>
@@ -7484,8 +7767,8 @@
       <c r="AB12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC12" s="2" t="s">
-        <v>25</v>
+      <c r="AC12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD12" s="2" t="s">
         <v>25</v>
@@ -7493,8 +7776,8 @@
       <c r="AE12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF12" s="1" t="s">
-        <v>26</v>
+      <c r="AF12" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>25</v>
@@ -7506,33 +7789,60 @@
         <v>25</v>
       </c>
       <c r="AJ12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ12" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="3">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D13" s="3">
         <v>0.25</v>
       </c>
       <c r="E13" s="3">
-        <v>-20</v>
+        <v>110</v>
       </c>
       <c r="F13" s="3">
-        <v>-5</v>
+        <v>160</v>
       </c>
       <c r="G13" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>26</v>
@@ -7552,29 +7862,29 @@
       <c r="U13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V13" s="1" t="s">
-        <v>26</v>
+      <c r="V13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>25</v>
+      <c r="X13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA13" s="2" t="s">
-        <v>25</v>
+      <c r="AA13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC13" s="2" t="s">
-        <v>25</v>
+      <c r="AC13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD13" s="2" t="s">
         <v>25</v>
@@ -7582,8 +7892,8 @@
       <c r="AE13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF13" s="1" t="s">
-        <v>26</v>
+      <c r="AF13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>25</v>
@@ -7595,18 +7905,39 @@
         <v>25</v>
       </c>
       <c r="AJ13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3">
         <v>0.25</v>
@@ -7618,10 +7949,10 @@
         <v>-5</v>
       </c>
       <c r="G14" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>26</v>
@@ -7641,23 +7972,23 @@
       <c r="U14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>26</v>
+      <c r="V14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA14" s="1" t="s">
-        <v>26</v>
+      <c r="AA14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>25</v>
@@ -7671,8 +8002,8 @@
       <c r="AE14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF14" s="1" t="s">
-        <v>26</v>
+      <c r="AF14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>25</v>
@@ -7684,36 +8015,54 @@
         <v>25</v>
       </c>
       <c r="AJ14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ14" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="3">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D15" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G15" s="3">
         <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>26</v>
@@ -7721,23 +8070,23 @@
       <c r="Q15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>26</v>
+      <c r="R15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>26</v>
@@ -7745,64 +8094,88 @@
       <c r="Y15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z15" s="1" t="s">
-        <v>26</v>
+      <c r="Z15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB15" s="1" t="s">
-        <v>26</v>
+      <c r="AB15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
-        <v>26</v>
+      <c r="AD15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ15" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3">
         <v>0.3</v>
       </c>
       <c r="E16" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>26</v>
@@ -7816,85 +8189,103 @@
       <c r="S16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>25</v>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>25</v>
+      <c r="W16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE16" s="2" t="s">
-        <v>25</v>
+      <c r="AE16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG16" s="2" t="s">
-        <v>25</v>
+      <c r="AG16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI16" s="2" t="s">
-        <v>25</v>
+      <c r="AI16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ16" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D17" s="3">
         <v>0.3</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="3">
-        <v>170</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>26</v>
@@ -7902,106 +8293,118 @@
       <c r="Q17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>26</v>
+      <c r="R17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ17" s="1" t="s">
-        <v>26</v>
+      <c r="Y17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ17" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="3">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="3">
-        <v>20</v>
-      </c>
-      <c r="H18" s="3">
-        <v>60</v>
-      </c>
-      <c r="I18" s="3">
-        <v>10</v>
+        <v>170</v>
+      </c>
+      <c r="G18" s="3">
+        <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>25</v>
+        <v>376</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>25</v>
@@ -8009,44 +8412,44 @@
       <c r="S18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>25</v>
+      <c r="T18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>25</v>
+      <c r="AA18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD18" s="1" t="s">
-        <v>26</v>
+      <c r="AD18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF18" s="2" t="s">
-        <v>25</v>
+      <c r="AF18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG18" s="1" t="s">
         <v>26</v>
@@ -8058,45 +8461,72 @@
         <v>26</v>
       </c>
       <c r="AJ18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ18" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C19" s="3">
         <v>180</v>
       </c>
       <c r="D19" s="3">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="3">
+        <v>20</v>
+      </c>
+      <c r="H19" s="3">
         <v>60</v>
       </c>
-      <c r="G19" s="3">
-        <v>20</v>
+      <c r="I19" s="3">
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>26</v>
+        <v>380</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>25</v>
@@ -8110,26 +8540,26 @@
       <c r="U19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>26</v>
+      <c r="V19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y19" s="1" t="s">
-        <v>26</v>
+      <c r="Y19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB19" s="2" t="s">
-        <v>25</v>
+      <c r="AA19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC19" s="2" t="s">
         <v>25</v>
@@ -8143,52 +8573,70 @@
       <c r="AF19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG19" s="2" t="s">
-        <v>25</v>
+      <c r="AG19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI19" s="2" t="s">
-        <v>25</v>
+      <c r="AI19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ19" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="D20" s="3">
         <v>0.25</v>
       </c>
       <c r="E20" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="G20" s="3">
         <v>20</v>
       </c>
-      <c r="H20" s="3">
-        <v>5</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>26</v>
@@ -8208,14 +8656,14 @@
       <c r="U20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>25</v>
+      <c r="V20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>26</v>
@@ -8229,8 +8677,8 @@
       <c r="AB20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC20" s="2" t="s">
-        <v>25</v>
+      <c r="AC20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD20" s="2" t="s">
         <v>25</v>
@@ -8238,8 +8686,8 @@
       <c r="AE20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF20" s="1" t="s">
-        <v>26</v>
+      <c r="AF20" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>25</v>
@@ -8251,33 +8699,63 @@
         <v>25</v>
       </c>
       <c r="AJ20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ20" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="3">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>90</v>
+      </c>
+      <c r="F21" s="3">
+        <v>170</v>
+      </c>
+      <c r="G21" s="3">
         <v>20</v>
       </c>
-      <c r="C21" s="3">
-        <v>24</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-5</v>
-      </c>
-      <c r="G21" s="3">
-        <v>15</v>
+      <c r="H21" s="3">
+        <v>5</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>389</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>26</v>
@@ -8297,29 +8775,29 @@
       <c r="U21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V21" s="1" t="s">
-        <v>26</v>
+      <c r="V21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y21" s="2" t="s">
-        <v>25</v>
+      <c r="X21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA21" s="2" t="s">
-        <v>25</v>
+      <c r="AA21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC21" s="2" t="s">
-        <v>25</v>
+      <c r="AC21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>25</v>
@@ -8327,8 +8805,8 @@
       <c r="AE21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF21" s="1" t="s">
-        <v>26</v>
+      <c r="AF21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG21" s="2" t="s">
         <v>25</v>
@@ -8340,54 +8818,72 @@
         <v>25</v>
       </c>
       <c r="AJ21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ21" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="3">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="D22" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F22" s="3">
-        <v>60</v>
+        <v>-5</v>
       </c>
       <c r="G22" s="3">
         <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>26</v>
+        <v>391</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>25</v>
@@ -8401,73 +8897,88 @@
       <c r="Y22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z22" s="1" t="s">
-        <v>26</v>
+      <c r="Z22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>26</v>
+      <c r="AB22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ22" s="1" t="s">
-        <v>26</v>
+      <c r="AG22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ22" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="3">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="D23" s="3">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="E23" s="3">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G23" s="3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>25</v>
@@ -8475,11 +8986,11 @@
       <c r="Q23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>26</v>
+      <c r="R23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>26</v>
@@ -8487,23 +8998,23 @@
       <c r="U23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V23" s="2" t="s">
-        <v>25</v>
+      <c r="V23" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA23" s="1" t="s">
-        <v>26</v>
+      <c r="X23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB23" s="1" t="s">
         <v>26</v>
@@ -8514,52 +9025,79 @@
       <c r="AD23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ23" s="1" t="s">
-        <v>26</v>
+      <c r="AE23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ23" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="3">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="D24" s="3">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="E24" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>25</v>
@@ -8567,11 +9105,11 @@
       <c r="Q24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>26</v>
+      <c r="R24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T24" s="1" t="s">
         <v>26</v>
@@ -8579,32 +9117,32 @@
       <c r="U24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y24" s="2" t="s">
-        <v>25</v>
+      <c r="V24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB24" s="1" t="s">
-        <v>26</v>
+      <c r="AA24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD24" s="1" t="s">
-        <v>26</v>
+      <c r="AD24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>26</v>
@@ -8612,52 +9150,67 @@
       <c r="AF24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ24" s="1" t="s">
-        <v>26</v>
+      <c r="AG24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ24" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="E25" s="3">
         <v>-20</v>
       </c>
       <c r="F25" s="3">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G25" s="3">
-        <v>20</v>
-      </c>
-      <c r="H25" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -8665,11 +9218,11 @@
       <c r="Q25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>26</v>
+      <c r="R25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T25" s="1" t="s">
         <v>26</v>
@@ -8677,20 +9230,20 @@
       <c r="U25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>26</v>
+      <c r="V25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z25" s="2" t="s">
-        <v>25</v>
+      <c r="Z25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA25" s="2" t="s">
         <v>25</v>
@@ -8704,55 +9257,79 @@
       <c r="AD25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ25" s="1" t="s">
-        <v>26</v>
+      <c r="AE25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ25" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="3">
+        <v>160</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="3">
-        <v>290</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-50</v>
-      </c>
-      <c r="F26" s="3">
-        <v>20</v>
-      </c>
-      <c r="G26" s="3">
-        <v>24</v>
+      <c r="H26" s="3">
+        <v>10</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -8766,17 +9343,17 @@
       <c r="S26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>25</v>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>25</v>
@@ -8793,11 +9370,11 @@
       <c r="AB26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD26" s="1" t="s">
-        <v>26</v>
+      <c r="AC26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>26</v>
@@ -8805,49 +9382,70 @@
       <c r="AF26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG26" s="1" t="s">
-        <v>26</v>
+      <c r="AG26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI26" s="1" t="s">
-        <v>26</v>
+      <c r="AI26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ26" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C27" s="3">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="D27" s="3">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G27" s="3">
-        <v>10</v>
-      </c>
-      <c r="H27" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>25</v>
@@ -8855,17 +9453,17 @@
       <c r="Q27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>26</v>
+      <c r="R27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>25</v>
@@ -8873,8 +9471,8 @@
       <c r="W27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X27" s="1" t="s">
-        <v>26</v>
+      <c r="X27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>25</v>
@@ -8897,58 +9495,85 @@
       <c r="AE27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ27" s="1" t="s">
-        <v>26</v>
+      <c r="AF27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ27" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C28" s="3">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="D28" s="3">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="E28" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="G28" s="3">
         <v>10</v>
       </c>
+      <c r="H28" s="3">
+        <v>4</v>
+      </c>
       <c r="J28" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>26</v>
+        <v>411</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>26</v>
@@ -8962,88 +9587,103 @@
       <c r="W28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>26</v>
+      <c r="X28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD28" s="1" t="s">
-        <v>26</v>
+      <c r="AA28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ28" s="1" t="s">
-        <v>26</v>
+      <c r="AF28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ28" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C29" s="3">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="D29" s="3">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" s="3">
-        <v>60</v>
-      </c>
-      <c r="H29" s="3">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3">
-        <v>5</v>
+        <v>170</v>
+      </c>
+      <c r="G29" s="3">
+        <v>10</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>414</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
@@ -9051,76 +9691,103 @@
       <c r="U29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>25</v>
+      <c r="V29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>25</v>
+      <c r="Y29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC29" s="2" t="s">
-        <v>25</v>
+      <c r="AC29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ29" s="1" t="s">
-        <v>26</v>
+      <c r="AE29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ29" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C30" s="3">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="D30" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E30" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3">
-        <v>-5</v>
-      </c>
-      <c r="G30" s="3">
-        <v>15</v>
+        <v>60</v>
+      </c>
+      <c r="H30" s="3">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3">
+        <v>5</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>405</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>25</v>
@@ -9128,11 +9795,11 @@
       <c r="Q30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>26</v>
+      <c r="R30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -9140,26 +9807,26 @@
       <c r="U30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>26</v>
+      <c r="V30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z30" s="2" t="s">
-        <v>25</v>
+      <c r="Z30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB30" s="1" t="s">
-        <v>26</v>
+      <c r="AB30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC30" s="2" t="s">
         <v>25</v>
@@ -9167,8 +9834,8 @@
       <c r="AD30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE30" s="2" t="s">
-        <v>25</v>
+      <c r="AE30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF30" s="2" t="s">
         <v>25</v>
@@ -9176,22 +9843,43 @@
       <c r="AG30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH30" s="1" t="s">
-        <v>26</v>
+      <c r="AH30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ30" s="1" t="s">
-        <v>26</v>
+      <c r="AJ30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ30" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C31" s="3">
         <v>190</v>
@@ -9200,25 +9888,25 @@
         <v>0.24</v>
       </c>
       <c r="E31" s="3">
-        <v>-50</v>
+        <v>-5</v>
       </c>
       <c r="F31" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3">
-        <v>32</v>
-      </c>
-      <c r="H31" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>413</v>
+        <v>398</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>418</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>25</v>
@@ -9226,11 +9914,11 @@
       <c r="Q31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>25</v>
+      <c r="R31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>25</v>
@@ -9250,8 +9938,8 @@
       <c r="Y31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z31" s="1" t="s">
-        <v>26</v>
+      <c r="Z31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA31" s="2" t="s">
         <v>25</v>
@@ -9259,70 +9947,82 @@
       <c r="AB31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC31" s="1" t="s">
-        <v>26</v>
+      <c r="AC31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AE31" s="1" t="s">
-        <v>26</v>
+      <c r="AE31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>25</v>
+      <c r="AG31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ31" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="3">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="D32" s="3">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="E32" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F32" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G32" s="3">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>26</v>
+        <v>420</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>25</v>
@@ -9330,11 +10030,11 @@
       <c r="S32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>25</v>
+      <c r="T32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>26</v>
@@ -9345,14 +10045,14 @@
       <c r="X32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA32" s="1" t="s">
-        <v>26</v>
+      <c r="Y32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>25</v>
@@ -9363,11 +10063,11 @@
       <c r="AD32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF32" s="1" t="s">
-        <v>26</v>
+      <c r="AE32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>25</v>
@@ -9379,12 +10079,33 @@
         <v>25</v>
       </c>
       <c r="AJ32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ32" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>34</v>
@@ -9393,31 +10114,34 @@
         <v>190</v>
       </c>
       <c r="D33" s="3">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F33" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G33" s="3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H33" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>26</v>
+        <v>423</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>25</v>
@@ -9431,8 +10155,8 @@
       <c r="U33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V33" s="1" t="s">
-        <v>26</v>
+      <c r="V33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W33" s="2" t="s">
         <v>25</v>
@@ -9443,23 +10167,23 @@
       <c r="Y33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z33" s="1" t="s">
-        <v>26</v>
+      <c r="Z33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE33" s="1" t="s">
-        <v>26</v>
+      <c r="AB33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF33" s="1" t="s">
         <v>26</v>
@@ -9474,33 +10198,63 @@
         <v>26</v>
       </c>
       <c r="AJ33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ33" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="3">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="D34" s="3">
-        <v>0.8</v>
+        <v>0.22</v>
       </c>
       <c r="E34" s="3">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F34" s="3">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="G34" s="3">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>26</v>
@@ -9508,23 +10262,23 @@
       <c r="Q34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>26</v>
+      <c r="R34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X34" s="1" t="s">
         <v>26</v>
@@ -9532,76 +10286,97 @@
       <c r="Y34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z34" s="1" t="s">
-        <v>26</v>
+      <c r="Z34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB34" s="1" t="s">
-        <v>26</v>
+      <c r="AB34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ34" s="1" t="s">
-        <v>26</v>
+      <c r="AD34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ34" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C35" s="3">
         <v>190</v>
       </c>
       <c r="D35" s="3">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="E35" s="3">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G35" s="3">
-        <v>34</v>
+        <v>15</v>
+      </c>
+      <c r="H35" s="3">
+        <v>8</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>25</v>
+        <v>431</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>25</v>
@@ -9618,23 +10393,23 @@
       <c r="V35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>26</v>
+      <c r="W35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB35" s="2" t="s">
-        <v>25</v>
+      <c r="AA35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC35" s="2" t="s">
         <v>25</v>
@@ -9645,55 +10420,73 @@
       <c r="AE35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG35" s="2" t="s">
-        <v>25</v>
+      <c r="AF35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI35" s="2" t="s">
-        <v>25</v>
+      <c r="AI35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ35" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C36" s="3">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="E36" s="3">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F36" s="3">
-        <v>-45</v>
+        <v>170</v>
       </c>
       <c r="G36" s="3">
-        <v>23</v>
-      </c>
-      <c r="H36" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>25</v>
+        <v>433</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>25</v>
@@ -9701,70 +10494,91 @@
       <c r="S36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>25</v>
+      <c r="T36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X36" s="2" t="s">
-        <v>25</v>
+      <c r="X36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z36" s="2" t="s">
-        <v>25</v>
+      <c r="Z36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC36" s="2" t="s">
-        <v>25</v>
+      <c r="AB36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG36" s="2" t="s">
-        <v>25</v>
+      <c r="AE36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI36" s="2" t="s">
-        <v>25</v>
+      <c r="AI36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ36" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="3">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="D37" s="3">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="E37" s="3">
         <v>-50</v>
@@ -9773,19 +10587,16 @@
         <v>20</v>
       </c>
       <c r="G37" s="3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>25</v>
@@ -9793,17 +10604,17 @@
       <c r="Q37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>26</v>
+      <c r="R37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>25</v>
@@ -9811,79 +10622,94 @@
       <c r="W37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB37" s="1" t="s">
-        <v>26</v>
+      <c r="X37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE37" s="1" t="s">
-        <v>26</v>
+      <c r="AD37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ37" s="1" t="s">
-        <v>26</v>
+      <c r="AG37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ37" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C38" s="3">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="D38" s="3">
-        <v>0.19</v>
+        <v>0.84</v>
       </c>
       <c r="E38" s="3">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F38" s="3">
-        <v>20</v>
+        <v>-45</v>
       </c>
       <c r="G38" s="3">
-        <v>35</v>
+        <v>23</v>
+      </c>
+      <c r="H38" s="3">
+        <v>5</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>25</v>
@@ -9906,8 +10732,8 @@
       <c r="V38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W38" s="1" t="s">
-        <v>26</v>
+      <c r="W38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>25</v>
@@ -9924,8 +10750,8 @@
       <c r="AB38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>25</v>
+      <c r="AC38" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>25</v>
@@ -9946,21 +10772,42 @@
         <v>25</v>
       </c>
       <c r="AJ38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ38" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C39" s="3">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D39" s="3">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="E39" s="3">
         <v>-50</v>
@@ -9969,19 +10816,19 @@
         <v>20</v>
       </c>
       <c r="G39" s="3">
-        <v>39</v>
-      </c>
-      <c r="H39" s="3">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>25</v>
@@ -9995,14 +10842,14 @@
       <c r="S39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V39" s="2" t="s">
-        <v>25</v>
+      <c r="T39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>26</v>
@@ -10010,17 +10857,17 @@
       <c r="X39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB39" s="2" t="s">
-        <v>25</v>
+      <c r="Y39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC39" s="2" t="s">
         <v>25</v>
@@ -10028,37 +10875,58 @@
       <c r="AD39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG39" s="2" t="s">
-        <v>25</v>
+      <c r="AE39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI39" s="2" t="s">
-        <v>25</v>
+      <c r="AI39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ39" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="3">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="D40" s="3">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="E40" s="3">
         <v>-50</v>
@@ -10067,16 +10935,19 @@
         <v>20</v>
       </c>
       <c r="G40" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>25</v>
@@ -10099,8 +10970,8 @@
       <c r="V40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W40" s="1" t="s">
-        <v>26</v>
+      <c r="W40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X40" s="2" t="s">
         <v>25</v>
@@ -10117,8 +10988,8 @@
       <c r="AB40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC40" s="2" t="s">
-        <v>25</v>
+      <c r="AC40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>25</v>
@@ -10139,39 +11010,69 @@
         <v>25</v>
       </c>
       <c r="AJ40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ40" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="3">
+        <v>270</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="E41" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F41" s="3">
         <v>20</v>
       </c>
-      <c r="C41" s="3">
-        <v>90</v>
-      </c>
-      <c r="D41" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E41" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F41" s="3">
-        <v>-5</v>
-      </c>
       <c r="G41" s="3">
+        <v>39</v>
+      </c>
+      <c r="H41" s="3">
         <v>5</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>26</v>
+        <v>451</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>25</v>
@@ -10185,8 +11086,8 @@
       <c r="U41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V41" s="1" t="s">
-        <v>26</v>
+      <c r="V41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>25</v>
@@ -10194,14 +11095,14 @@
       <c r="X41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA41" s="2" t="s">
-        <v>25</v>
+      <c r="Y41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA41" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>25</v>
@@ -10209,37 +11110,58 @@
       <c r="AC41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG41" s="1" t="s">
-        <v>26</v>
+      <c r="AD41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI41" s="1" t="s">
-        <v>26</v>
+      <c r="AI41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ41" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="3">
-        <v>340</v>
+        <v>120</v>
       </c>
       <c r="D42" s="3">
         <v>0.24</v>
@@ -10251,16 +11173,16 @@
         <v>20</v>
       </c>
       <c r="G42" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>25</v>
@@ -10289,14 +11211,14 @@
       <c r="X42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA42" s="2" t="s">
-        <v>25</v>
+      <c r="Y42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>25</v>
@@ -10304,73 +11226,91 @@
       <c r="AC42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE42" s="1" t="s">
-        <v>26</v>
+      <c r="AD42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG42" s="1" t="s">
-        <v>26</v>
+      <c r="AG42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI42" s="1" t="s">
-        <v>26</v>
+      <c r="AI42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ42" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C43" s="3">
-        <v>185</v>
+        <v>90</v>
       </c>
       <c r="D43" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F43" s="3">
-        <v>60</v>
+        <v>-5</v>
       </c>
       <c r="G43" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>26</v>
+        <v>459</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V43" s="2" t="s">
         <v>25</v>
@@ -10402,55 +11342,79 @@
       <c r="AE43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ43" s="1" t="s">
-        <v>26</v>
+      <c r="AF43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ43" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C44" s="3">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="D44" s="3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F44" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G44" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>26</v>
+        <v>462</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>25</v>
@@ -10464,8 +11428,8 @@
       <c r="U44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V44" s="1" t="s">
-        <v>26</v>
+      <c r="V44" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W44" s="2" t="s">
         <v>25</v>
@@ -10482,8 +11446,8 @@
       <c r="AA44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB44" s="2" t="s">
-        <v>25</v>
+      <c r="AB44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC44" s="2" t="s">
         <v>25</v>
@@ -10497,28 +11461,49 @@
       <c r="AF44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG44" s="2" t="s">
-        <v>25</v>
+      <c r="AG44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI44" s="2" t="s">
-        <v>25</v>
+      <c r="AI44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ44" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="3">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D45" s="3">
         <v>0.2</v>
@@ -10533,10 +11518,10 @@
         <v>15</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>25</v>
@@ -10550,17 +11535,17 @@
       <c r="S45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>25</v>
+      <c r="T45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>25</v>
@@ -10577,11 +11562,11 @@
       <c r="AB45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD45" s="1" t="s">
-        <v>26</v>
+      <c r="AC45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE45" s="1" t="s">
         <v>26</v>
@@ -10589,43 +11574,67 @@
       <c r="AF45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG45" s="1" t="s">
-        <v>26</v>
+      <c r="AG45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI45" s="1" t="s">
-        <v>26</v>
+      <c r="AI45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ45" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C46" s="3">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="D46" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E46" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="G46" s="3">
         <v>15</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>26</v>
@@ -10645,14 +11654,14 @@
       <c r="U46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V46" s="1" t="s">
-        <v>26</v>
+      <c r="V46" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X46" s="2" t="s">
-        <v>25</v>
+      <c r="X46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y46" s="2" t="s">
         <v>25</v>
@@ -10675,8 +11684,8 @@
       <c r="AE46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF46" s="1" t="s">
-        <v>26</v>
+      <c r="AF46" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AG46" s="2" t="s">
         <v>25</v>
@@ -10688,33 +11697,57 @@
         <v>25</v>
       </c>
       <c r="AJ46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ46" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C47" s="3">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="D47" s="3">
         <v>0.2</v>
       </c>
       <c r="E47" s="3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="G47" s="3">
         <v>15</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>472</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>25</v>
@@ -10722,17 +11755,17 @@
       <c r="Q47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>26</v>
+      <c r="R47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>25</v>
@@ -10740,14 +11773,14 @@
       <c r="W47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X47" s="1" t="s">
-        <v>26</v>
+      <c r="X47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z47" s="1" t="s">
-        <v>26</v>
+      <c r="Z47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA47" s="2" t="s">
         <v>25</v>
@@ -10755,70 +11788,82 @@
       <c r="AB47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF47" s="2" t="s">
-        <v>25</v>
+      <c r="AC47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF47" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AH47" s="1" t="s">
-        <v>26</v>
+      <c r="AH47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ47" s="1" t="s">
-        <v>26</v>
+      <c r="AJ47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ47" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C48" s="3">
-        <v>230</v>
+        <v>45</v>
       </c>
       <c r="D48" s="3">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="E48" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F48" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G48" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>25</v>
+        <v>474</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>25</v>
@@ -10835,20 +11880,20 @@
       <c r="V48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y48" s="1" t="s">
-        <v>26</v>
+      <c r="W48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA48" s="1" t="s">
-        <v>26</v>
+      <c r="AA48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>25</v>
@@ -10875,36 +11920,54 @@
         <v>25</v>
       </c>
       <c r="AJ48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ48" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="3">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="D49" s="3">
         <v>0.2</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F49" s="3">
-        <v>60</v>
+        <v>-5</v>
       </c>
       <c r="G49" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>25</v>
@@ -10918,17 +11981,17 @@
       <c r="S49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W49" s="2" t="s">
-        <v>25</v>
+      <c r="T49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X49" s="2" t="s">
         <v>25</v>
@@ -10942,20 +12005,20 @@
       <c r="AA49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD49" s="1" t="s">
-        <v>26</v>
+      <c r="AB49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE49" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF49" s="2" t="s">
-        <v>25</v>
+      <c r="AF49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG49" s="1" t="s">
         <v>26</v>
@@ -10967,21 +12030,42 @@
         <v>26</v>
       </c>
       <c r="AJ49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ49" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C50" s="3">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="D50" s="3">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="E50" s="3">
         <v>-50</v>
@@ -10989,23 +12073,20 @@
       <c r="F50" s="3">
         <v>20</v>
       </c>
-      <c r="H50" s="3">
-        <v>60</v>
-      </c>
-      <c r="I50" s="3">
-        <v>10</v>
+      <c r="G50" s="3">
+        <v>24</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>25</v>
@@ -11028,8 +12109,8 @@
       <c r="V50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W50" s="1" t="s">
-        <v>26</v>
+      <c r="W50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>25</v>
@@ -11046,8 +12127,8 @@
       <c r="AB50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC50" s="2" t="s">
-        <v>25</v>
+      <c r="AC50" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD50" s="2" t="s">
         <v>25</v>
@@ -11068,48 +12149,63 @@
         <v>25</v>
       </c>
       <c r="AJ50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ50" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C51" s="3">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D51" s="3">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="E51" s="3">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G51" s="3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>26</v>
+        <v>484</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R51" s="2" t="s">
         <v>25</v>
@@ -11123,8 +12219,8 @@
       <c r="U51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V51" s="1" t="s">
-        <v>26</v>
+      <c r="V51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>25</v>
@@ -11135,23 +12231,23 @@
       <c r="Y51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z51" s="1" t="s">
-        <v>26</v>
+      <c r="Z51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE51" s="1" t="s">
-        <v>26</v>
+      <c r="AB51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF51" s="1" t="s">
         <v>26</v>
@@ -11166,21 +12262,42 @@
         <v>26</v>
       </c>
       <c r="AJ51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ51" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C52" s="3">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="D52" s="3">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="E52" s="3">
         <v>-50</v>
@@ -11188,17 +12305,23 @@
       <c r="F52" s="3">
         <v>20</v>
       </c>
-      <c r="G52" s="3">
-        <v>34</v>
+      <c r="H52" s="3">
+        <v>60</v>
+      </c>
+      <c r="I52" s="3">
+        <v>10</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>489</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>25</v>
@@ -11206,26 +12329,26 @@
       <c r="Q52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>26</v>
+      <c r="R52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X52" s="1" t="s">
-        <v>26</v>
+      <c r="W52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y52" s="1" t="s">
         <v>26</v>
@@ -11236,11 +12359,11 @@
       <c r="AA52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC52" s="2" t="s">
-        <v>25</v>
+      <c r="AB52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD52" s="2" t="s">
         <v>25</v>
@@ -11254,64 +12377,88 @@
       <c r="AG52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH52" s="1" t="s">
-        <v>26</v>
+      <c r="AH52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ52" s="1" t="s">
-        <v>26</v>
+      <c r="AJ52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ52" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C53" s="3">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D53" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E53" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F53" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G53" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>26</v>
+        <v>288</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V53" s="2" t="s">
         <v>25</v>
@@ -11343,34 +12490,55 @@
       <c r="AE53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ53" s="1" t="s">
-        <v>26</v>
+      <c r="AF53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ53" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="3">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="D54" s="3">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="E54" s="3">
         <v>-50</v>
@@ -11379,19 +12547,16 @@
         <v>20</v>
       </c>
       <c r="G54" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>25</v>
@@ -11405,29 +12570,29 @@
       <c r="S54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>25</v>
+      <c r="T54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y54" s="2" t="s">
-        <v>25</v>
+      <c r="Y54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z54" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA54" s="2" t="s">
-        <v>25</v>
+      <c r="AA54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB54" s="2" t="s">
         <v>25</v>
@@ -11435,8 +12600,8 @@
       <c r="AC54" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD54" s="1" t="s">
-        <v>26</v>
+      <c r="AD54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE54" s="1" t="s">
         <v>26</v>
@@ -11444,43 +12609,70 @@
       <c r="AF54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG54" s="1" t="s">
-        <v>26</v>
+      <c r="AG54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI54" s="1" t="s">
-        <v>26</v>
+      <c r="AI54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ54" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C55" s="3">
+        <v>190</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3">
         <v>60</v>
       </c>
-      <c r="D55" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="E55" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F55" s="3">
-        <v>-5</v>
-      </c>
       <c r="G55" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>501</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>25</v>
@@ -11488,11 +12680,11 @@
       <c r="Q55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>26</v>
+      <c r="R55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T55" s="1" t="s">
         <v>26</v>
@@ -11500,26 +12692,26 @@
       <c r="U55" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X55" s="1" t="s">
-        <v>26</v>
+      <c r="V55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z55" s="2" t="s">
-        <v>25</v>
+      <c r="Z55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB55" s="1" t="s">
-        <v>26</v>
+      <c r="AB55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC55" s="2" t="s">
         <v>25</v>
@@ -11527,8 +12719,8 @@
       <c r="AD55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE55" s="2" t="s">
-        <v>25</v>
+      <c r="AE55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF55" s="2" t="s">
         <v>25</v>
@@ -11536,55 +12728,76 @@
       <c r="AG55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH55" s="1" t="s">
-        <v>26</v>
+      <c r="AH55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ55" s="1" t="s">
-        <v>26</v>
+      <c r="AJ55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ55" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C56" s="3">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="D56" s="3">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E56" s="3">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F56" s="3">
-        <v>60</v>
-      </c>
-      <c r="H56" s="3">
-        <v>60</v>
-      </c>
-      <c r="I56" s="3">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="G56" s="3">
+        <v>28</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>295</v>
+        <v>504</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>26</v>
+        <v>496</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>25</v>
@@ -11598,26 +12811,26 @@
       <c r="U56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="V56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W56" s="1" t="s">
-        <v>26</v>
+      <c r="V56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y56" s="1" t="s">
-        <v>26</v>
+      <c r="Y56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB56" s="2" t="s">
-        <v>25</v>
+      <c r="AA56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC56" s="2" t="s">
         <v>25</v>
@@ -11631,55 +12844,76 @@
       <c r="AF56" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG56" s="2" t="s">
-        <v>25</v>
+      <c r="AG56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI56" s="2" t="s">
-        <v>25</v>
+      <c r="AI56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ56" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C57" s="3">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D57" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F57" s="3">
-        <v>170</v>
+        <v>-5</v>
       </c>
       <c r="G57" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>26</v>
+        <v>507</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T57" s="1" t="s">
         <v>26</v>
@@ -11693,94 +12927,118 @@
       <c r="W57" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>26</v>
+      <c r="X57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD57" s="1" t="s">
-        <v>26</v>
+      <c r="AA57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE57" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ57" s="1" t="s">
-        <v>26</v>
+      <c r="AF57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ57" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C58" s="3">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="D58" s="3">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="E58" s="3">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>20</v>
-      </c>
-      <c r="G58" s="3">
-        <v>42</v>
+        <v>60</v>
+      </c>
+      <c r="H58" s="3">
+        <v>60</v>
+      </c>
+      <c r="I58" s="3">
+        <v>10</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>25</v>
@@ -11791,76 +13049,94 @@
       <c r="X58" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB58" s="1" t="s">
-        <v>26</v>
+      <c r="Y58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC58" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE58" s="1" t="s">
-        <v>26</v>
+      <c r="AD58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ58" s="1" t="s">
-        <v>26</v>
+      <c r="AG58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ58" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C59" s="3">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="D59" s="3">
         <v>0.25</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="G59" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>25</v>
+        <v>511</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>25</v>
@@ -11868,44 +13144,44 @@
       <c r="S59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>25</v>
+      <c r="T59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z59" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB59" s="2" t="s">
-        <v>25</v>
+      <c r="AA59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC59" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD59" s="1" t="s">
-        <v>26</v>
+      <c r="AD59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE59" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF59" s="2" t="s">
-        <v>25</v>
+      <c r="AF59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG59" s="1" t="s">
         <v>26</v>
@@ -11917,33 +13193,60 @@
         <v>26</v>
       </c>
       <c r="AJ59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ59" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C60" s="3">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="D60" s="3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E60" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F60" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G60" s="3">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>508</v>
+        <v>513</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>25</v>
@@ -11951,11 +13254,11 @@
       <c r="Q60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>26</v>
+      <c r="R60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T60" s="1" t="s">
         <v>26</v>
@@ -11963,20 +13266,20 @@
       <c r="U60" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X60" s="1" t="s">
-        <v>26</v>
+      <c r="V60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z60" s="2" t="s">
-        <v>25</v>
+      <c r="Z60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA60" s="2" t="s">
         <v>25</v>
@@ -11990,49 +13293,73 @@
       <c r="AD60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ60" s="1" t="s">
-        <v>26</v>
+      <c r="AE60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ60" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C61" s="3">
+        <v>220</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>60</v>
       </c>
-      <c r="D61" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E61" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F61" s="3">
-        <v>-5</v>
-      </c>
       <c r="G61" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>517</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>25</v>
@@ -12040,17 +13367,17 @@
       <c r="Q61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>26</v>
+      <c r="R61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V61" s="2" t="s">
         <v>25</v>
@@ -12058,8 +13385,8 @@
       <c r="W61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X61" s="1" t="s">
-        <v>26</v>
+      <c r="X61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>25</v>
@@ -12082,52 +13409,67 @@
       <c r="AE61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ61" s="1" t="s">
-        <v>26</v>
+      <c r="AF61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ61" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C62" s="3">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="D62" s="3">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="E62" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F62" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G62" s="3">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>25</v>
@@ -12141,17 +13483,17 @@
       <c r="S62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>25</v>
+      <c r="T62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>25</v>
@@ -12168,11 +13510,11 @@
       <c r="AB62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD62" s="1" t="s">
-        <v>26</v>
+      <c r="AC62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE62" s="1" t="s">
         <v>26</v>
@@ -12180,31 +13522,52 @@
       <c r="AF62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG62" s="1" t="s">
-        <v>26</v>
+      <c r="AG62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI62" s="1" t="s">
-        <v>26</v>
+      <c r="AI62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ62" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="3">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="D63" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E63" s="3">
         <v>-20</v>
@@ -12213,10 +13576,10 @@
         <v>-5</v>
       </c>
       <c r="G63" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>25</v>
@@ -12230,14 +13593,14 @@
       <c r="S63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>25</v>
+      <c r="T63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="W63" s="1" t="s">
         <v>26</v>
@@ -12245,23 +13608,23 @@
       <c r="X63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y63" s="1" t="s">
-        <v>26</v>
+      <c r="Y63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA63" s="1" t="s">
-        <v>26</v>
+      <c r="AA63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD63" s="1" t="s">
-        <v>26</v>
+      <c r="AC63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE63" s="1" t="s">
         <v>26</v>
@@ -12269,22 +13632,43 @@
       <c r="AF63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AG63" s="1" t="s">
-        <v>26</v>
+      <c r="AG63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI63" s="1" t="s">
-        <v>26</v>
+      <c r="AI63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ63" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>20</v>
@@ -12293,7 +13677,7 @@
         <v>160</v>
       </c>
       <c r="D64" s="3">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="E64" s="3">
         <v>-50</v>
@@ -12302,19 +13686,16 @@
         <v>20</v>
       </c>
       <c r="G64" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>22</v>
+        <v>524</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>25</v>
@@ -12322,17 +13703,17 @@
       <c r="Q64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U64" s="1" t="s">
-        <v>26</v>
+      <c r="R64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V64" s="2" t="s">
         <v>25</v>
@@ -12340,14 +13721,14 @@
       <c r="W64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X64" s="1" t="s">
-        <v>26</v>
+      <c r="X64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z64" s="1" t="s">
-        <v>26</v>
+      <c r="Z64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA64" s="2" t="s">
         <v>25</v>
@@ -12355,123 +13736,394 @@
       <c r="AB64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF64" s="2" t="s">
-        <v>25</v>
+      <c r="AC64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AG64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AH64" s="1" t="s">
-        <v>26</v>
+      <c r="AH64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ64" s="1" t="s">
-        <v>26</v>
+      <c r="AJ64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ64" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C65" s="3">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E65" s="3">
+        <v>-20</v>
+      </c>
+      <c r="F65" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G65" s="3">
+        <v>10</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ65" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="3">
         <v>160</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D66" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="E66" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F66" s="3">
+        <v>20</v>
+      </c>
+      <c r="G66" s="3">
+        <v>34</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ66" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="3">
+        <v>160</v>
+      </c>
+      <c r="D67" s="3">
         <v>0.29</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E67" s="3">
         <v>-50</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F67" s="3">
         <v>20</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G67" s="3">
         <v>38</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="L65" s="3" t="s">
+      <c r="J67" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ65" s="2" t="s">
+      <c r="P67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ67" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -12533,7 +14185,14 @@
     <col min="46" max="46" width="9.140625" customWidth="1" style="3"/>
     <col min="47" max="47" width="9.140625" customWidth="1" style="3"/>
     <col min="48" max="48" width="9.140625" customWidth="1" style="3"/>
-    <col min="49" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="9.140625" customWidth="1" style="3"/>
+    <col min="50" max="50" width="9.140625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9.140625" customWidth="1" style="3"/>
+    <col min="52" max="52" width="9.140625" customWidth="1" style="3"/>
+    <col min="53" max="53" width="9.140625" customWidth="1" style="3"/>
+    <col min="54" max="54" width="9.140625" customWidth="1" style="3"/>
+    <col min="55" max="55" width="9.140625" customWidth="1" style="3"/>
+    <col min="56" max="16384" width="9.140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1">
@@ -12574,16 +14233,16 @@
         <v>10</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>183</v>
@@ -12592,7 +14251,7 @@
         <v>13</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>15</v>
@@ -12601,22 +14260,22 @@
         <v>17</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>185</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG1" s="4" t="s">
         <v>187</v>
@@ -12624,7 +14283,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -12645,13 +14304,13 @@
         <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
@@ -12710,7 +14369,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -12731,13 +14390,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>45</v>
@@ -12799,7 +14458,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -12820,10 +14479,10 @@
         <v>55</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -12882,7 +14541,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -12903,10 +14562,10 @@
         <v>45</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>167</v>
@@ -12968,7 +14627,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>34</v>
@@ -13063,7 +14722,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -13084,7 +14743,7 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>76</v>
@@ -13093,10 +14752,10 @@
         <v>254</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>25</v>
@@ -13155,7 +14814,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>82</v>
@@ -13179,13 +14838,13 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>26</v>
@@ -13244,7 +14903,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -13333,7 +14992,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -13354,16 +15013,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
@@ -13422,7 +15081,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
@@ -13446,16 +15105,16 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>25</v>
@@ -13514,7 +15173,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -13535,19 +15194,19 @@
         <v>40</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>560</v>
+        <v>418</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>45</v>
@@ -13609,7 +15268,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -13630,7 +15289,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>299</v>
@@ -13698,7 +15357,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -13719,10 +15378,10 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>122</v>
@@ -13787,7 +15446,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -13876,7 +15535,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>82</v>
@@ -13903,13 +15562,13 @@
         <v>104</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>25</v>
@@ -13968,7 +15627,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -13989,16 +15648,16 @@
         <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>25</v>
@@ -14057,7 +15716,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -14078,13 +15737,13 @@
         <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>131</v>
@@ -14146,7 +15805,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -14167,13 +15826,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>45</v>
@@ -14235,7 +15894,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -14259,7 +15918,7 @@
         <v>161</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>256</v>
@@ -14324,7 +15983,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -14345,16 +16004,16 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>25</v>
@@ -14413,7 +16072,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -14434,16 +16093,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -14502,7 +16161,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -14526,7 +16185,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>54</v>
@@ -14588,7 +16247,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
@@ -14615,7 +16274,7 @@
         <v>207</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>209</v>
@@ -14677,7 +16336,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
@@ -14704,7 +16363,7 @@
         <v>234</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -14763,7 +16422,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
@@ -14784,16 +16443,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>122</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -14852,7 +16511,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -14873,13 +16532,13 @@
         <v>50</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>45</v>
@@ -14941,7 +16600,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>20</v>
@@ -14962,13 +16621,13 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>96</v>
@@ -15030,7 +16689,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="642">
   <si>
     <t>Vein ID</t>
   </si>
@@ -1041,6 +1041,18 @@
     <t>tin: 1</t>
   </si>
   <si>
+    <t>deep_galena</t>
+  </si>
+  <si>
+    <t>galena: 12 [1]</t>
+  </si>
+  <si>
+    <t>silver: 6</t>
+  </si>
+  <si>
+    <t>lead: 5</t>
+  </si>
+  <si>
     <t>deep_bauxite</t>
   </si>
   <si>
@@ -1660,6 +1672,12 @@
   </si>
   <si>
     <t>vanadium_magnetite: 7</t>
+  </si>
+  <si>
+    <t>deep_sphalerite</t>
+  </si>
+  <si>
+    <t>sphalerite: 7</t>
   </si>
   <si>
     <t>surface_bismuth</t>
@@ -6429,7 +6447,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ73"/>
+  <dimension ref="A1:AQ75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28571319580078" customWidth="1" style="3"/>
@@ -6739,7 +6757,7 @@
         <v>120</v>
       </c>
       <c r="D3" s="3">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="E3" s="3">
         <v>-50</v>
@@ -6748,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="I3" s="3">
         <v>9</v>
@@ -7087,10 +7105,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="3">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="D6" s="3">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="E6" s="3">
         <v>-50</v>
@@ -7099,13 +7117,16 @@
         <v>20</v>
       </c>
       <c r="G6" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>342</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>343</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>25</v>
@@ -7194,16 +7215,16 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="3">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="D7" s="3">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="E7" s="3">
         <v>-50</v>
@@ -7212,22 +7233,19 @@
         <v>20</v>
       </c>
       <c r="G7" s="3">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="L7" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>26</v>
+      <c r="P7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>25</v>
@@ -7247,8 +7265,8 @@
       <c r="W7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="1" t="s">
-        <v>26</v>
+      <c r="X7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>26</v>
@@ -7286,8 +7304,8 @@
       <c r="AJ7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK7" s="1" t="s">
-        <v>26</v>
+      <c r="AK7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL7" s="2" t="s">
         <v>25</v>
@@ -7316,10 +7334,10 @@
         <v>20</v>
       </c>
       <c r="C8" s="3">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="D8" s="3">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="E8" s="3">
         <v>-50</v>
@@ -7328,7 +7346,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="3">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>349</v>
@@ -7339,14 +7357,11 @@
       <c r="L8" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>25</v>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>25</v>
@@ -7366,8 +7381,8 @@
       <c r="W8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X8" s="2" t="s">
-        <v>25</v>
+      <c r="X8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>26</v>
@@ -7405,8 +7420,8 @@
       <c r="AJ8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK8" s="2" t="s">
-        <v>25</v>
+      <c r="AK8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL8" s="2" t="s">
         <v>25</v>
@@ -7429,40 +7444,49 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="3">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D9" s="3">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="E9" s="3">
-        <v>-5</v>
+        <v>-50</v>
       </c>
       <c r="F9" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G9" s="3">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>354</v>
       </c>
+      <c r="L9" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="P9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>26</v>
+      <c r="R9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>25</v>
@@ -7479,23 +7503,23 @@
       <c r="X9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y9" s="2" t="s">
-        <v>25</v>
+      <c r="Y9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA9" s="2" t="s">
-        <v>25</v>
+      <c r="AA9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>26</v>
+      <c r="AC9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE9" s="2" t="s">
         <v>25</v>
@@ -7506,14 +7530,14 @@
       <c r="AG9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH9" s="1" t="s">
-        <v>26</v>
+      <c r="AH9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ9" s="1" t="s">
-        <v>26</v>
+      <c r="AJ9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AK9" s="2" t="s">
         <v>25</v>
@@ -7530,40 +7554,37 @@
       <c r="AO9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AP9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ9" s="1" t="s">
-        <v>26</v>
+      <c r="AP9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D10" s="3">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="E10" s="3">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3">
-        <v>36</v>
-      </c>
-      <c r="H10" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
@@ -7571,23 +7592,23 @@
       <c r="Q10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>26</v>
+      <c r="R10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>25</v>
@@ -7595,8 +7616,8 @@
       <c r="Y10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z10" s="1" t="s">
-        <v>26</v>
+      <c r="Z10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA10" s="2" t="s">
         <v>25</v>
@@ -7607,11 +7628,11 @@
       <c r="AC10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AD10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>26</v>
+      <c r="AD10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF10" s="2" t="s">
         <v>25</v>
@@ -7619,14 +7640,14 @@
       <c r="AG10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH10" s="2" t="s">
-        <v>25</v>
+      <c r="AH10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AI10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ10" s="2" t="s">
-        <v>25</v>
+      <c r="AJ10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AK10" s="2" t="s">
         <v>25</v>
@@ -7634,55 +7655,55 @@
       <c r="AL10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM10" s="1" t="s">
-        <v>26</v>
+      <c r="AM10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ10" s="2" t="s">
-        <v>25</v>
+      <c r="AO10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D11" s="3">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="E11" s="3">
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="H11" s="3">
+        <v>10</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>26</v>
+        <v>360</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>25</v>
@@ -7702,23 +7723,23 @@
       <c r="W11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>26</v>
+      <c r="X11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>26</v>
+      <c r="AA11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD11" s="2" t="s">
         <v>25</v>
@@ -7726,32 +7747,32 @@
       <c r="AE11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG11" s="1" t="s">
-        <v>26</v>
+      <c r="AF11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI11" s="1" t="s">
-        <v>26</v>
+      <c r="AI11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL11" s="1" t="s">
-        <v>26</v>
+      <c r="AK11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN11" s="1" t="s">
-        <v>26</v>
+      <c r="AN11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO11" s="1" t="s">
         <v>26</v>
@@ -7765,28 +7786,31 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E12" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F12" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>363</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>26</v>
@@ -7800,17 +7824,17 @@
       <c r="S12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>25</v>
+      <c r="T12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X12" s="1" t="s">
         <v>26</v>
@@ -7818,14 +7842,14 @@
       <c r="Y12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z12" s="2" t="s">
-        <v>25</v>
+      <c r="Z12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB12" s="2" t="s">
-        <v>25</v>
+      <c r="AB12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC12" s="1" t="s">
         <v>26</v>
@@ -7833,20 +7857,20 @@
       <c r="AD12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG12" s="2" t="s">
-        <v>25</v>
+      <c r="AE12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI12" s="2" t="s">
-        <v>25</v>
+      <c r="AI12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ12" s="2" t="s">
         <v>25</v>
@@ -7854,17 +7878,17 @@
       <c r="AK12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO12" s="2" t="s">
-        <v>25</v>
+      <c r="AL12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP12" s="2" t="s">
         <v>25</v>
@@ -7875,43 +7899,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="3">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D13" s="3">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="E13" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F13" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G13" s="3">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="L13" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>25</v>
+      <c r="P13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>25</v>
@@ -7931,8 +7946,8 @@
       <c r="W13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X13" s="2" t="s">
-        <v>25</v>
+      <c r="X13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>26</v>
@@ -7970,8 +7985,8 @@
       <c r="AJ13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK13" s="2" t="s">
-        <v>25</v>
+      <c r="AK13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL13" s="2" t="s">
         <v>25</v>
@@ -7994,40 +8009,43 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="3">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="D14" s="3">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="E14" s="3">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F14" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G14" s="3">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>26</v>
+      <c r="P14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>25</v>
@@ -8035,32 +8053,32 @@
       <c r="S14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>26</v>
+      <c r="T14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z14" s="1" t="s">
-        <v>26</v>
+      <c r="Z14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>26</v>
+      <c r="AB14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>26</v>
@@ -8068,38 +8086,38 @@
       <c r="AD14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG14" s="1" t="s">
-        <v>26</v>
+      <c r="AE14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI14" s="1" t="s">
-        <v>26</v>
+      <c r="AI14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO14" s="1" t="s">
-        <v>26</v>
+      <c r="AK14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP14" s="2" t="s">
         <v>25</v>
@@ -8116,23 +8134,29 @@
         <v>20</v>
       </c>
       <c r="C15" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D15" s="3">
         <v>0.25</v>
       </c>
       <c r="E15" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="3">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>372</v>
       </c>
+      <c r="K15" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>374</v>
+      </c>
       <c r="P15" s="1" t="s">
         <v>26</v>
       </c>
@@ -8145,53 +8169,53 @@
       <c r="S15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>25</v>
+      <c r="T15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>25</v>
+      <c r="Y15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>25</v>
+      <c r="AE15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI15" s="2" t="s">
-        <v>25</v>
+      <c r="AI15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ15" s="2" t="s">
         <v>25</v>
@@ -8199,17 +8223,17 @@
       <c r="AK15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO15" s="2" t="s">
-        <v>25</v>
+      <c r="AL15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP15" s="2" t="s">
         <v>25</v>
@@ -8220,13 +8244,13 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D16" s="3">
         <v>0.25</v>
@@ -8241,7 +8265,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>26</v>
@@ -8270,20 +8294,20 @@
       <c r="X16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y16" s="1" t="s">
-        <v>26</v>
+      <c r="Y16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA16" s="1" t="s">
-        <v>26</v>
+      <c r="AA16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC16" s="1" t="s">
-        <v>26</v>
+      <c r="AC16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>25</v>
@@ -8330,31 +8354,28 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D17" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E17" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>26</v>
@@ -8368,17 +8389,17 @@
       <c r="S17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>26</v>
+      <c r="T17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X17" s="1" t="s">
         <v>26</v>
@@ -8386,14 +8407,14 @@
       <c r="Y17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z17" s="1" t="s">
-        <v>26</v>
+      <c r="Z17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB17" s="1" t="s">
-        <v>26</v>
+      <c r="AB17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC17" s="1" t="s">
         <v>26</v>
@@ -8401,20 +8422,20 @@
       <c r="AD17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG17" s="1" t="s">
-        <v>26</v>
+      <c r="AE17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI17" s="1" t="s">
-        <v>26</v>
+      <c r="AI17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ17" s="2" t="s">
         <v>25</v>
@@ -8422,17 +8443,17 @@
       <c r="AK17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO17" s="1" t="s">
-        <v>26</v>
+      <c r="AL17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP17" s="2" t="s">
         <v>25</v>
@@ -8443,7 +8464,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -8455,16 +8476,19 @@
         <v>0.3</v>
       </c>
       <c r="E18" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>381</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>26</v>
@@ -8478,53 +8502,53 @@
       <c r="S18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>25</v>
+      <c r="T18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>25</v>
+      <c r="Y18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>25</v>
+      <c r="AE18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI18" s="2" t="s">
-        <v>25</v>
+      <c r="AI18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ18" s="2" t="s">
         <v>25</v>
@@ -8532,17 +8556,17 @@
       <c r="AK18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO18" s="2" t="s">
-        <v>25</v>
+      <c r="AL18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP18" s="2" t="s">
         <v>25</v>
@@ -8553,28 +8577,28 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="3">
-        <v>90</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="3">
-        <v>160</v>
+        <v>-5</v>
       </c>
       <c r="G19" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>26</v>
@@ -8588,53 +8612,53 @@
       <c r="S19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>26</v>
+      <c r="T19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC19" s="1" t="s">
-        <v>26</v>
+      <c r="Y19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG19" s="1" t="s">
-        <v>26</v>
+      <c r="AE19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI19" s="1" t="s">
-        <v>26</v>
+      <c r="AI19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ19" s="2" t="s">
         <v>25</v>
@@ -8642,17 +8666,17 @@
       <c r="AK19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO19" s="1" t="s">
-        <v>26</v>
+      <c r="AL19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP19" s="2" t="s">
         <v>25</v>
@@ -8663,46 +8687,34 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="D20" s="3">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="3">
-        <v>-50</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3">
-        <v>20</v>
-      </c>
-      <c r="H20" s="3">
-        <v>60</v>
-      </c>
-      <c r="I20" s="3">
-        <v>10</v>
+        <v>160</v>
+      </c>
+      <c r="G20" s="3">
+        <v>30</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>25</v>
+        <v>360</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>25</v>
@@ -8710,41 +8722,41 @@
       <c r="S20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>25</v>
+      <c r="T20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC20" s="2" t="s">
-        <v>25</v>
+      <c r="AC20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE20" s="2" t="s">
-        <v>25</v>
+      <c r="AE20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>26</v>
@@ -8761,20 +8773,20 @@
       <c r="AJ20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK20" s="2" t="s">
-        <v>25</v>
+      <c r="AK20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM20" s="2" t="s">
-        <v>25</v>
+      <c r="AM20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO20" s="2" t="s">
-        <v>25</v>
+      <c r="AO20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP20" s="2" t="s">
         <v>25</v>
@@ -8785,36 +8797,39 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="3">
+        <v>180</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F21" s="3">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3">
+        <v>60</v>
+      </c>
+      <c r="I21" s="3">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="3">
-        <v>100</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="E21" s="3">
-        <v>10</v>
-      </c>
-      <c r="F21" s="3">
-        <v>70</v>
-      </c>
-      <c r="G21" s="3">
-        <v>32</v>
-      </c>
-      <c r="H21" s="3">
-        <v>10</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>389</v>
       </c>
       <c r="P21" s="2" t="s">
@@ -8829,53 +8844,53 @@
       <c r="S21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>26</v>
+      <c r="T21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>26</v>
+      <c r="Y21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>25</v>
+      <c r="AE21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI21" s="2" t="s">
-        <v>25</v>
+      <c r="AI21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ21" s="2" t="s">
         <v>25</v>
@@ -8883,17 +8898,17 @@
       <c r="AK21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO21" s="1" t="s">
-        <v>26</v>
+      <c r="AL21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP21" s="2" t="s">
         <v>25</v>
@@ -8907,31 +8922,40 @@
         <v>390</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D22" s="3">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="E22" s="3">
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G22" s="3">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="H22" s="3">
+        <v>10</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>26</v>
+      <c r="K22" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>25</v>
@@ -8951,8 +8975,8 @@
       <c r="W22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X22" s="1" t="s">
-        <v>26</v>
+      <c r="X22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>26</v>
@@ -8963,8 +8987,8 @@
       <c r="AA22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB22" s="1" t="s">
-        <v>26</v>
+      <c r="AB22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>26</v>
@@ -8975,32 +8999,32 @@
       <c r="AE22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG22" s="1" t="s">
-        <v>26</v>
+      <c r="AF22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI22" s="1" t="s">
-        <v>26</v>
+      <c r="AI22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL22" s="1" t="s">
-        <v>26</v>
+      <c r="AK22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN22" s="1" t="s">
-        <v>26</v>
+      <c r="AN22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO22" s="1" t="s">
         <v>26</v>
@@ -9014,13 +9038,13 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D23" s="3">
         <v>0.25</v>
@@ -9029,21 +9053,12 @@
         <v>-30</v>
       </c>
       <c r="F23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>20</v>
-      </c>
-      <c r="H23" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="L23" s="3" t="s">
         <v>395</v>
       </c>
       <c r="P23" s="1" t="s">
@@ -9136,26 +9151,35 @@
         <v>396</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3">
+        <v>70</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-30</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
         <v>20</v>
       </c>
-      <c r="C24" s="3">
-        <v>54</v>
-      </c>
-      <c r="D24" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>15</v>
+      <c r="H24" s="3">
+        <v>12</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>397</v>
       </c>
+      <c r="K24" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>399</v>
+      </c>
       <c r="P24" s="1" t="s">
         <v>26</v>
       </c>
@@ -9168,53 +9192,53 @@
       <c r="S24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>25</v>
+      <c r="T24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC24" s="2" t="s">
-        <v>25</v>
+      <c r="Y24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG24" s="2" t="s">
-        <v>25</v>
+      <c r="AE24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI24" s="2" t="s">
-        <v>25</v>
+      <c r="AI24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ24" s="2" t="s">
         <v>25</v>
@@ -9222,17 +9246,17 @@
       <c r="AK24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO24" s="2" t="s">
-        <v>25</v>
+      <c r="AL24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP24" s="2" t="s">
         <v>25</v>
@@ -9243,34 +9267,28 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="E25" s="3">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G25" s="3">
-        <v>25</v>
-      </c>
-      <c r="H25" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>26</v>
@@ -9299,20 +9317,20 @@
       <c r="X25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y25" s="1" t="s">
-        <v>26</v>
+      <c r="Y25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA25" s="1" t="s">
-        <v>26</v>
+      <c r="AA25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC25" s="1" t="s">
-        <v>26</v>
+      <c r="AC25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>25</v>
@@ -9359,43 +9377,40 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C26" s="3">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="D26" s="3">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="E26" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G26" s="3">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="H26" s="3">
+        <v>10</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="L26" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>25</v>
+      <c r="P26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>25</v>
@@ -9403,26 +9418,26 @@
       <c r="S26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X26" s="2" t="s">
-        <v>25</v>
+      <c r="T26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z26" s="1" t="s">
-        <v>26</v>
+      <c r="Z26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA26" s="1" t="s">
         <v>26</v>
@@ -9436,8 +9451,8 @@
       <c r="AD26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE26" s="1" t="s">
-        <v>26</v>
+      <c r="AE26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF26" s="2" t="s">
         <v>25</v>
@@ -9454,20 +9469,20 @@
       <c r="AJ26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK26" s="2" t="s">
-        <v>25</v>
+      <c r="AK26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM26" s="1" t="s">
-        <v>26</v>
+      <c r="AM26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO26" s="1" t="s">
-        <v>26</v>
+      <c r="AO26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP26" s="2" t="s">
         <v>25</v>
@@ -9478,32 +9493,38 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="3">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="D27" s="3">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="E27" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G27" s="3">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>408</v>
       </c>
+      <c r="M27" s="3" t="s">
+        <v>409</v>
+      </c>
       <c r="P27" s="2" t="s">
         <v>25</v>
       </c>
@@ -9531,20 +9552,20 @@
       <c r="X27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y27" s="2" t="s">
-        <v>25</v>
+      <c r="Y27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC27" s="2" t="s">
-        <v>25</v>
+      <c r="AA27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD27" s="2" t="s">
         <v>25</v>
@@ -9552,17 +9573,17 @@
       <c r="AE27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG27" s="1" t="s">
-        <v>26</v>
+      <c r="AF27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI27" s="1" t="s">
-        <v>26</v>
+      <c r="AI27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ27" s="2" t="s">
         <v>25</v>
@@ -9570,14 +9591,14 @@
       <c r="AK27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL27" s="1" t="s">
-        <v>26</v>
+      <c r="AL27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN27" s="1" t="s">
-        <v>26</v>
+      <c r="AN27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO27" s="1" t="s">
         <v>26</v>
@@ -9591,43 +9612,37 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C28" s="3">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="D28" s="3">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F28" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G28" s="3">
-        <v>27</v>
-      </c>
-      <c r="H28" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>26</v>
+        <v>412</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>25</v>
@@ -9647,23 +9662,23 @@
       <c r="W28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>26</v>
+      <c r="X28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA28" s="1" t="s">
-        <v>26</v>
+      <c r="AA28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC28" s="1" t="s">
-        <v>26</v>
+      <c r="AC28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD28" s="2" t="s">
         <v>25</v>
@@ -9686,8 +9701,8 @@
       <c r="AJ28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK28" s="1" t="s">
-        <v>26</v>
+      <c r="AK28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL28" s="1" t="s">
         <v>26</v>
@@ -9710,28 +9725,31 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C29" s="3">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="D29" s="3">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E29" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G29" s="3">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="H29" s="3">
+        <v>10</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>414</v>
@@ -9739,11 +9757,11 @@
       <c r="L29" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>25</v>
+      <c r="P29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>25</v>
@@ -9751,41 +9769,41 @@
       <c r="S29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>25</v>
+      <c r="T29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC29" s="2" t="s">
-        <v>25</v>
+      <c r="AC29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE29" s="2" t="s">
-        <v>25</v>
+      <c r="AE29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF29" s="1" t="s">
         <v>26</v>
@@ -9802,20 +9820,20 @@
       <c r="AJ29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK29" s="2" t="s">
-        <v>25</v>
+      <c r="AK29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM29" s="2" t="s">
-        <v>25</v>
+      <c r="AM29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO29" s="2" t="s">
-        <v>25</v>
+      <c r="AO29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP29" s="2" t="s">
         <v>25</v>
@@ -9829,25 +9847,22 @@
         <v>416</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C30" s="3">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="D30" s="3">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="E30" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F30" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G30" s="3">
-        <v>23</v>
-      </c>
-      <c r="H30" s="3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>417</v>
@@ -9855,6 +9870,9 @@
       <c r="K30" s="3" t="s">
         <v>418</v>
       </c>
+      <c r="L30" s="3" t="s">
+        <v>419</v>
+      </c>
       <c r="P30" s="2" t="s">
         <v>25</v>
       </c>
@@ -9867,17 +9885,17 @@
       <c r="S30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>26</v>
+      <c r="T30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>25</v>
@@ -9885,14 +9903,14 @@
       <c r="Y30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z30" s="1" t="s">
-        <v>26</v>
+      <c r="Z30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB30" s="2" t="s">
-        <v>25</v>
+      <c r="AB30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC30" s="2" t="s">
         <v>25</v>
@@ -9900,20 +9918,20 @@
       <c r="AD30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG30" s="2" t="s">
-        <v>25</v>
+      <c r="AE30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI30" s="2" t="s">
-        <v>25</v>
+      <c r="AI30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ30" s="2" t="s">
         <v>25</v>
@@ -9921,17 +9939,17 @@
       <c r="AK30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO30" s="1" t="s">
-        <v>26</v>
+      <c r="AL30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO30" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP30" s="2" t="s">
         <v>25</v>
@@ -9942,16 +9960,16 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D31" s="3">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="E31" s="3">
         <v>10</v>
@@ -9960,25 +9978,22 @@
         <v>70</v>
       </c>
       <c r="G31" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3">
         <v>10</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L31" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>26</v>
+      <c r="P31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>25</v>
@@ -9998,23 +10013,23 @@
       <c r="W31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>26</v>
+      <c r="X31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>26</v>
+      <c r="AA31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD31" s="2" t="s">
         <v>25</v>
@@ -10022,32 +10037,32 @@
       <c r="AE31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>26</v>
+      <c r="AF31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI31" s="1" t="s">
-        <v>26</v>
+      <c r="AI31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL31" s="1" t="s">
-        <v>26</v>
+      <c r="AK31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN31" s="1" t="s">
-        <v>26</v>
+      <c r="AN31" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO31" s="1" t="s">
         <v>26</v>
@@ -10067,22 +10082,22 @@
         <v>34</v>
       </c>
       <c r="C32" s="3">
+        <v>170</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3">
+        <v>70</v>
+      </c>
+      <c r="G32" s="3">
         <v>34</v>
       </c>
-      <c r="D32" s="3">
-        <v>0.27</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-60</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-45</v>
-      </c>
-      <c r="G32" s="3">
-        <v>21</v>
-      </c>
       <c r="H32" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>424</v>
@@ -10093,11 +10108,11 @@
       <c r="L32" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>25</v>
+      <c r="P32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>25</v>
@@ -10105,41 +10120,41 @@
       <c r="S32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA32" s="2" t="s">
-        <v>25</v>
+      <c r="T32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC32" s="2" t="s">
-        <v>25</v>
+      <c r="AC32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE32" s="2" t="s">
-        <v>25</v>
+      <c r="AE32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF32" s="1" t="s">
         <v>26</v>
@@ -10156,20 +10171,20 @@
       <c r="AJ32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK32" s="2" t="s">
-        <v>25</v>
+      <c r="AK32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM32" s="2" t="s">
-        <v>25</v>
+      <c r="AM32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO32" s="2" t="s">
-        <v>25</v>
+      <c r="AO32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP32" s="2" t="s">
         <v>25</v>
@@ -10183,31 +10198,40 @@
         <v>427</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C33" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D33" s="3">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F33" s="3">
-        <v>170</v>
+        <v>-45</v>
       </c>
       <c r="G33" s="3">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="H33" s="3">
+        <v>6</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>26</v>
+      <c r="K33" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>25</v>
@@ -10215,41 +10239,41 @@
       <c r="S33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA33" s="1" t="s">
-        <v>26</v>
+      <c r="T33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC33" s="1" t="s">
-        <v>26</v>
+      <c r="AC33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE33" s="1" t="s">
-        <v>26</v>
+      <c r="AE33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF33" s="1" t="s">
         <v>26</v>
@@ -10266,20 +10290,20 @@
       <c r="AJ33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK33" s="1" t="s">
-        <v>26</v>
+      <c r="AK33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM33" s="1" t="s">
-        <v>26</v>
+      <c r="AM33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO33" s="1" t="s">
-        <v>26</v>
+      <c r="AO33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP33" s="2" t="s">
         <v>25</v>
@@ -10290,34 +10314,28 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C34" s="3">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="D34" s="3">
-        <v>0.28</v>
+        <v>0.9</v>
       </c>
       <c r="E34" s="3">
-        <v>-30</v>
+        <v>100</v>
       </c>
       <c r="F34" s="3">
-        <v>70</v>
-      </c>
-      <c r="H34" s="3">
-        <v>30</v>
-      </c>
-      <c r="I34" s="3">
-        <v>5</v>
+        <v>170</v>
+      </c>
+      <c r="G34" s="3">
+        <v>15</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>26</v>
@@ -10331,53 +10349,53 @@
       <c r="S34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>25</v>
+      <c r="T34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC34" s="2" t="s">
-        <v>25</v>
+      <c r="Y34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC34" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG34" s="2" t="s">
-        <v>25</v>
+      <c r="AE34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG34" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI34" s="2" t="s">
-        <v>25</v>
+      <c r="AI34" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ34" s="2" t="s">
         <v>25</v>
@@ -10385,17 +10403,17 @@
       <c r="AK34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO34" s="2" t="s">
-        <v>25</v>
+      <c r="AL34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO34" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP34" s="2" t="s">
         <v>25</v>
@@ -10406,49 +10424,46 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C35" s="3">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="E35" s="3">
-        <v>-5</v>
+        <v>-30</v>
       </c>
       <c r="F35" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3">
-        <v>34</v>
+        <v>70</v>
+      </c>
+      <c r="H35" s="3">
+        <v>30</v>
+      </c>
+      <c r="I35" s="3">
+        <v>5</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>26</v>
+        <v>415</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>25</v>
@@ -10462,8 +10477,8 @@
       <c r="W35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X35" s="2" t="s">
-        <v>25</v>
+      <c r="X35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>25</v>
@@ -10480,8 +10495,8 @@
       <c r="AC35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AD35" s="1" t="s">
-        <v>26</v>
+      <c r="AD35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AE35" s="2" t="s">
         <v>25</v>
@@ -10492,17 +10507,17 @@
       <c r="AG35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH35" s="1" t="s">
-        <v>26</v>
+      <c r="AH35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AI35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK35" s="2" t="s">
-        <v>25</v>
+      <c r="AJ35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL35" s="2" t="s">
         <v>25</v>
@@ -10516,43 +10531,46 @@
       <c r="AO35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AP35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ35" s="1" t="s">
-        <v>26</v>
+      <c r="AP35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ35" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C36" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D36" s="3">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="E36" s="3">
-        <v>-50</v>
+        <v>-5</v>
       </c>
       <c r="F36" s="3">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3">
-        <v>150</v>
-      </c>
-      <c r="I36" s="3">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="G36" s="3">
+        <v>34</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>332</v>
+        <v>407</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>25</v>
@@ -10560,11 +10578,11 @@
       <c r="Q36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>25</v>
+      <c r="R36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="T36" s="2" t="s">
         <v>25</v>
@@ -10581,23 +10599,23 @@
       <c r="X36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y36" s="1" t="s">
-        <v>26</v>
+      <c r="Y36" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA36" s="1" t="s">
-        <v>26</v>
+      <c r="AA36" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD36" s="2" t="s">
-        <v>25</v>
+      <c r="AC36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AE36" s="2" t="s">
         <v>25</v>
@@ -10608,14 +10626,14 @@
       <c r="AG36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH36" s="2" t="s">
-        <v>25</v>
+      <c r="AH36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AI36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ36" s="2" t="s">
-        <v>25</v>
+      <c r="AJ36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AK36" s="2" t="s">
         <v>25</v>
@@ -10632,37 +10650,43 @@
       <c r="AO36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AP36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ36" s="2" t="s">
-        <v>25</v>
+      <c r="AP36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ36" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C37" s="3">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D37" s="3">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="E37" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F37" s="3">
-        <v>-5</v>
-      </c>
-      <c r="G37" s="3">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <v>150</v>
+      </c>
+      <c r="I37" s="3">
+        <v>18</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>435</v>
+        <v>331</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>25</v>
@@ -10676,41 +10700,41 @@
       <c r="S37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>26</v>
+      <c r="T37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA37" s="2" t="s">
-        <v>25</v>
+      <c r="Y37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC37" s="2" t="s">
-        <v>25</v>
+      <c r="AC37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE37" s="1" t="s">
-        <v>26</v>
+      <c r="AE37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF37" s="2" t="s">
         <v>25</v>
@@ -10733,14 +10757,14 @@
       <c r="AL37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM37" s="1" t="s">
-        <v>26</v>
+      <c r="AM37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO37" s="1" t="s">
-        <v>26</v>
+      <c r="AO37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP37" s="2" t="s">
         <v>25</v>
@@ -10751,36 +10775,27 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C38" s="3">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="D38" s="3">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E38" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F38" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G38" s="3">
-        <v>39</v>
-      </c>
-      <c r="H38" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="L38" s="3" t="s">
         <v>439</v>
       </c>
       <c r="P38" s="2" t="s">
@@ -10795,17 +10810,17 @@
       <c r="S38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>25</v>
+      <c r="T38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>25</v>
@@ -10813,14 +10828,14 @@
       <c r="Y38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>25</v>
+      <c r="Z38" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB38" s="1" t="s">
-        <v>26</v>
+      <c r="AB38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>25</v>
@@ -10828,20 +10843,20 @@
       <c r="AD38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG38" s="1" t="s">
-        <v>26</v>
+      <c r="AE38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI38" s="1" t="s">
-        <v>26</v>
+      <c r="AI38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>25</v>
@@ -10849,17 +10864,17 @@
       <c r="AK38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO38" s="2" t="s">
-        <v>25</v>
+      <c r="AL38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO38" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP38" s="2" t="s">
         <v>25</v>
@@ -10873,13 +10888,13 @@
         <v>440</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C39" s="3">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="E39" s="3">
         <v>-50</v>
@@ -10888,25 +10903,25 @@
         <v>20</v>
       </c>
       <c r="G39" s="3">
-        <v>49</v>
+        <v>39</v>
+      </c>
+      <c r="H39" s="3">
+        <v>5</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>441</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="M39" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>26</v>
+      <c r="P39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R39" s="2" t="s">
         <v>25</v>
@@ -10926,23 +10941,23 @@
       <c r="W39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>26</v>
+      <c r="X39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC39" s="1" t="s">
-        <v>26</v>
+      <c r="AA39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD39" s="2" t="s">
         <v>25</v>
@@ -10950,32 +10965,32 @@
       <c r="AE39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG39" s="2" t="s">
-        <v>25</v>
+      <c r="AF39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI39" s="2" t="s">
-        <v>25</v>
+      <c r="AI39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL39" s="2" t="s">
-        <v>25</v>
+      <c r="AK39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN39" s="2" t="s">
-        <v>25</v>
+      <c r="AN39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO39" s="2" t="s">
         <v>25</v>
@@ -10992,37 +11007,40 @@
         <v>444</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C40" s="3">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D40" s="3">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F40" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G40" s="3">
-        <v>22</v>
-      </c>
-      <c r="H40" s="3">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>445</v>
       </c>
       <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>25</v>
+      <c r="M40" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>25</v>
@@ -11030,71 +11048,71 @@
       <c r="S40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC40" s="2" t="s">
-        <v>25</v>
+      <c r="T40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG40" s="1" t="s">
-        <v>26</v>
+      <c r="AE40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI40" s="1" t="s">
-        <v>26</v>
+      <c r="AI40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO40" s="1" t="s">
-        <v>26</v>
+      <c r="AK40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP40" s="2" t="s">
         <v>25</v>
@@ -11105,34 +11123,40 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C41" s="3">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3">
-        <v>0.8</v>
+        <v>0.23</v>
       </c>
       <c r="E41" s="3">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="G41" s="3">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="H41" s="3">
+        <v>8</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>26</v>
+        <v>449</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>25</v>
@@ -11152,23 +11176,23 @@
       <c r="W41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y41" s="1" t="s">
-        <v>26</v>
+      <c r="X41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA41" s="1" t="s">
-        <v>26</v>
+      <c r="AA41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC41" s="1" t="s">
-        <v>26</v>
+      <c r="AC41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD41" s="2" t="s">
         <v>25</v>
@@ -11191,8 +11215,8 @@
       <c r="AJ41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK41" s="1" t="s">
-        <v>26</v>
+      <c r="AK41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL41" s="1" t="s">
         <v>26</v>
@@ -11215,40 +11239,34 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="3">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="D42" s="3">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E42" s="3">
-        <v>-50</v>
+        <v>90</v>
       </c>
       <c r="F42" s="3">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="G42" s="3">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="L42" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="P42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>25</v>
+      <c r="P42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>25</v>
@@ -11256,32 +11274,32 @@
       <c r="S42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X42" s="2" t="s">
-        <v>25</v>
+      <c r="T42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z42" s="2" t="s">
-        <v>25</v>
+      <c r="Z42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB42" s="2" t="s">
-        <v>25</v>
+      <c r="AB42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC42" s="1" t="s">
         <v>26</v>
@@ -11289,38 +11307,38 @@
       <c r="AD42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG42" s="2" t="s">
-        <v>25</v>
+      <c r="AE42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI42" s="2" t="s">
-        <v>25</v>
+      <c r="AI42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO42" s="2" t="s">
-        <v>25</v>
+      <c r="AK42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO42" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP42" s="2" t="s">
         <v>25</v>
@@ -11334,28 +11352,31 @@
         <v>453</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C43" s="3">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="D43" s="3">
-        <v>0.87</v>
+        <v>0.3</v>
       </c>
       <c r="E43" s="3">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F43" s="3">
-        <v>-45</v>
+        <v>20</v>
       </c>
       <c r="G43" s="3">
-        <v>39</v>
-      </c>
-      <c r="H43" s="3">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>454</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>25</v>
@@ -11444,38 +11465,32 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C44" s="3">
-        <v>260</v>
+        <v>34</v>
       </c>
       <c r="D44" s="3">
-        <v>0.22</v>
+        <v>0.87</v>
       </c>
       <c r="E44" s="3">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F44" s="3">
-        <v>20</v>
+        <v>-45</v>
       </c>
       <c r="G44" s="3">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="H44" s="3">
+        <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="L44" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="P44" s="2" t="s">
         <v>25</v>
       </c>
@@ -11488,53 +11503,53 @@
       <c r="S44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W44" s="1" t="s">
-        <v>26</v>
+      <c r="T44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC44" s="2" t="s">
-        <v>25</v>
+      <c r="Y44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG44" s="1" t="s">
-        <v>26</v>
+      <c r="AE44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG44" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI44" s="1" t="s">
-        <v>26</v>
+      <c r="AI44" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ44" s="2" t="s">
         <v>25</v>
@@ -11542,17 +11557,17 @@
       <c r="AK44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO44" s="1" t="s">
-        <v>26</v>
+      <c r="AL44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO44" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP44" s="2" t="s">
         <v>25</v>
@@ -11563,13 +11578,13 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="3">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="D45" s="3">
         <v>0.22</v>
@@ -11581,20 +11596,20 @@
         <v>20</v>
       </c>
       <c r="G45" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="P45" s="2" t="s">
         <v>25</v>
       </c>
@@ -11607,53 +11622,53 @@
       <c r="S45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>25</v>
+      <c r="T45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC45" s="1" t="s">
-        <v>26</v>
+      <c r="Y45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG45" s="2" t="s">
-        <v>25</v>
+      <c r="AE45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG45" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI45" s="2" t="s">
-        <v>25</v>
+      <c r="AI45" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ45" s="2" t="s">
         <v>25</v>
@@ -11661,17 +11676,17 @@
       <c r="AK45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO45" s="2" t="s">
-        <v>25</v>
+      <c r="AL45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO45" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP45" s="2" t="s">
         <v>25</v>
@@ -11682,16 +11697,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C46" s="3">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="D46" s="3">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="E46" s="3">
         <v>-50</v>
@@ -11700,18 +11715,18 @@
         <v>20</v>
       </c>
       <c r="G46" s="3">
-        <v>46</v>
-      </c>
-      <c r="H46" s="3">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="L46" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>468</v>
       </c>
       <c r="P46" s="2" t="s">
@@ -11804,13 +11819,13 @@
         <v>469</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C47" s="3">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="D47" s="3">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="E47" s="3">
         <v>-50</v>
@@ -11819,7 +11834,10 @@
         <v>20</v>
       </c>
       <c r="G47" s="3">
-        <v>32</v>
+        <v>46</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>470</v>
@@ -11926,25 +11944,31 @@
         <v>120</v>
       </c>
       <c r="D48" s="3">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="E48" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F48" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G48" s="3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="P48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>26</v>
+      <c r="K48" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>25</v>
@@ -11964,23 +11988,23 @@
       <c r="W48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y48" s="2" t="s">
-        <v>25</v>
+      <c r="X48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y48" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC48" s="2" t="s">
-        <v>25</v>
+      <c r="AA48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC48" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD48" s="2" t="s">
         <v>25</v>
@@ -11988,32 +12012,32 @@
       <c r="AE48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG48" s="1" t="s">
-        <v>26</v>
+      <c r="AF48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI48" s="1" t="s">
-        <v>26</v>
+      <c r="AI48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL48" s="1" t="s">
-        <v>26</v>
+      <c r="AK48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN48" s="1" t="s">
-        <v>26</v>
+      <c r="AN48" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO48" s="2" t="s">
         <v>25</v>
@@ -12027,40 +12051,34 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="3">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="D49" s="3">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="E49" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F49" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G49" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="L49" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="P49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>25</v>
+      <c r="P49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>25</v>
@@ -12080,8 +12098,8 @@
       <c r="W49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X49" s="2" t="s">
-        <v>25</v>
+      <c r="X49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>25</v>
@@ -12119,8 +12137,8 @@
       <c r="AJ49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK49" s="2" t="s">
-        <v>25</v>
+      <c r="AK49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL49" s="1" t="s">
         <v>26</v>
@@ -12146,25 +12164,22 @@
         <v>479</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C50" s="3">
-        <v>100</v>
+        <v>420</v>
       </c>
       <c r="D50" s="3">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F50" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G50" s="3">
-        <v>26</v>
-      </c>
-      <c r="H50" s="3">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>480</v>
@@ -12172,11 +12187,14 @@
       <c r="K50" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>26</v>
+      <c r="L50" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>25</v>
@@ -12184,32 +12202,32 @@
       <c r="S50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X50" s="1" t="s">
-        <v>26</v>
+      <c r="T50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z50" s="1" t="s">
-        <v>26</v>
+      <c r="Z50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB50" s="2" t="s">
-        <v>25</v>
+      <c r="AB50" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC50" s="2" t="s">
         <v>25</v>
@@ -12217,38 +12235,38 @@
       <c r="AD50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG50" s="2" t="s">
-        <v>25</v>
+      <c r="AE50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG50" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI50" s="2" t="s">
-        <v>25</v>
+      <c r="AI50" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO50" s="1" t="s">
-        <v>26</v>
+      <c r="AK50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP50" s="2" t="s">
         <v>25</v>
@@ -12259,16 +12277,16 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C51" s="3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D51" s="3">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="E51" s="3">
         <v>10</v>
@@ -12283,10 +12301,10 @@
         <v>10</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>26</v>
@@ -12300,17 +12318,17 @@
       <c r="S51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W51" s="2" t="s">
-        <v>25</v>
+      <c r="T51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X51" s="1" t="s">
         <v>26</v>
@@ -12318,14 +12336,14 @@
       <c r="Y51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z51" s="2" t="s">
-        <v>25</v>
+      <c r="Z51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB51" s="1" t="s">
-        <v>26</v>
+      <c r="AB51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC51" s="2" t="s">
         <v>25</v>
@@ -12333,20 +12351,20 @@
       <c r="AD51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG51" s="1" t="s">
-        <v>26</v>
+      <c r="AE51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI51" s="1" t="s">
-        <v>26</v>
+      <c r="AI51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ51" s="2" t="s">
         <v>25</v>
@@ -12354,17 +12372,17 @@
       <c r="AK51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO51" s="2" t="s">
-        <v>25</v>
+      <c r="AL51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP51" s="2" t="s">
         <v>25</v>
@@ -12375,16 +12393,16 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C52" s="3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D52" s="3">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="E52" s="3">
         <v>10</v>
@@ -12393,22 +12411,22 @@
         <v>70</v>
       </c>
       <c r="G52" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H52" s="3">
         <v>10</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>25</v>
+        <v>488</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>25</v>
@@ -12416,26 +12434,26 @@
       <c r="S52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X52" s="2" t="s">
-        <v>25</v>
+      <c r="T52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z52" s="1" t="s">
-        <v>26</v>
+      <c r="Z52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA52" s="2" t="s">
         <v>25</v>
@@ -12449,8 +12467,8 @@
       <c r="AD52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE52" s="1" t="s">
-        <v>26</v>
+      <c r="AE52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF52" s="1" t="s">
         <v>26</v>
@@ -12467,20 +12485,20 @@
       <c r="AJ52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK52" s="2" t="s">
-        <v>25</v>
+      <c r="AK52" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM52" s="1" t="s">
-        <v>26</v>
+      <c r="AM52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO52" s="1" t="s">
-        <v>26</v>
+      <c r="AO52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP52" s="2" t="s">
         <v>25</v>
@@ -12491,34 +12509,40 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C53" s="3">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D53" s="3">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E53" s="3">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="G53" s="3">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="H53" s="3">
+        <v>10</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>26</v>
+        <v>490</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>25</v>
@@ -12526,32 +12550,32 @@
       <c r="S53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X53" s="1" t="s">
-        <v>26</v>
+      <c r="T53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z53" s="2" t="s">
-        <v>25</v>
+      <c r="Z53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB53" s="2" t="s">
-        <v>25</v>
+      <c r="AB53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC53" s="2" t="s">
         <v>25</v>
@@ -12559,38 +12583,38 @@
       <c r="AD53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG53" s="2" t="s">
-        <v>25</v>
+      <c r="AE53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI53" s="2" t="s">
-        <v>25</v>
+      <c r="AI53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO53" s="2" t="s">
-        <v>25</v>
+      <c r="AK53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP53" s="2" t="s">
         <v>25</v>
@@ -12601,16 +12625,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C54" s="3">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D54" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E54" s="3">
         <v>-20</v>
@@ -12622,13 +12646,13 @@
         <v>15</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>25</v>
+        <v>493</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>25</v>
@@ -12636,32 +12660,32 @@
       <c r="S54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X54" s="2" t="s">
-        <v>25</v>
+      <c r="T54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z54" s="1" t="s">
-        <v>26</v>
+      <c r="Z54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB54" s="1" t="s">
-        <v>26</v>
+      <c r="AB54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC54" s="2" t="s">
         <v>25</v>
@@ -12669,38 +12693,38 @@
       <c r="AD54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG54" s="1" t="s">
-        <v>26</v>
+      <c r="AE54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI54" s="1" t="s">
-        <v>26</v>
+      <c r="AI54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO54" s="1" t="s">
-        <v>26</v>
+      <c r="AK54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP54" s="2" t="s">
         <v>25</v>
@@ -12711,38 +12735,29 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C55" s="3">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="D55" s="3">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="E55" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F55" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G55" s="3">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="L55" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="M55" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="P55" s="2" t="s">
         <v>25</v>
       </c>
@@ -12755,53 +12770,53 @@
       <c r="S55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W55" s="2" t="s">
-        <v>25</v>
+      <c r="T55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC55" s="1" t="s">
-        <v>26</v>
+      <c r="Y55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG55" s="2" t="s">
-        <v>25</v>
+      <c r="AE55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI55" s="2" t="s">
-        <v>25</v>
+      <c r="AI55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ55" s="2" t="s">
         <v>25</v>
@@ -12809,17 +12824,17 @@
       <c r="AK55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO55" s="2" t="s">
-        <v>25</v>
+      <c r="AL55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP55" s="2" t="s">
         <v>25</v>
@@ -12833,25 +12848,22 @@
         <v>496</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C56" s="3">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="D56" s="3">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="E56" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F56" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G56" s="3">
-        <v>23</v>
-      </c>
-      <c r="H56" s="3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>497</v>
@@ -12859,11 +12871,17 @@
       <c r="K56" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>26</v>
+      <c r="L56" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>25</v>
@@ -12883,23 +12901,23 @@
       <c r="W56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y56" s="2" t="s">
-        <v>25</v>
+      <c r="X56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC56" s="2" t="s">
-        <v>25</v>
+      <c r="AA56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD56" s="2" t="s">
         <v>25</v>
@@ -12907,32 +12925,32 @@
       <c r="AE56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG56" s="1" t="s">
-        <v>26</v>
+      <c r="AF56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI56" s="1" t="s">
-        <v>26</v>
+      <c r="AI56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL56" s="1" t="s">
-        <v>26</v>
+      <c r="AK56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN56" s="1" t="s">
-        <v>26</v>
+      <c r="AN56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO56" s="2" t="s">
         <v>25</v>
@@ -12946,46 +12964,40 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C57" s="3">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D57" s="3">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E57" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F57" s="3">
-        <v>20</v>
+        <v>70</v>
+      </c>
+      <c r="G57" s="3">
+        <v>23</v>
       </c>
       <c r="H57" s="3">
-        <v>60</v>
-      </c>
-      <c r="I57" s="3">
         <v>10</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="L57" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q57" s="2" t="s">
-        <v>25</v>
+      <c r="P57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>25</v>
@@ -13005,23 +13017,23 @@
       <c r="W57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>26</v>
+      <c r="X57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC57" s="1" t="s">
-        <v>26</v>
+      <c r="AA57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD57" s="2" t="s">
         <v>25</v>
@@ -13029,32 +13041,32 @@
       <c r="AE57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG57" s="2" t="s">
-        <v>25</v>
+      <c r="AF57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI57" s="2" t="s">
-        <v>25</v>
+      <c r="AI57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL57" s="2" t="s">
-        <v>25</v>
+      <c r="AK57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN57" s="2" t="s">
-        <v>25</v>
+      <c r="AN57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO57" s="2" t="s">
         <v>25</v>
@@ -13068,13 +13080,13 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C58" s="3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D58" s="3">
         <v>0.27</v>
@@ -13085,26 +13097,29 @@
       <c r="F58" s="3">
         <v>20</v>
       </c>
-      <c r="G58" s="3">
-        <v>41</v>
+      <c r="H58" s="3">
+        <v>60</v>
+      </c>
+      <c r="I58" s="3">
+        <v>10</v>
       </c>
       <c r="J58" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="P58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>26</v>
+      <c r="P58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R58" s="2" t="s">
         <v>25</v>
@@ -13124,23 +13139,23 @@
       <c r="W58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y58" s="2" t="s">
-        <v>25</v>
+      <c r="X58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC58" s="2" t="s">
-        <v>25</v>
+      <c r="AA58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD58" s="2" t="s">
         <v>25</v>
@@ -13148,32 +13163,32 @@
       <c r="AE58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG58" s="1" t="s">
-        <v>26</v>
+      <c r="AF58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI58" s="1" t="s">
-        <v>26</v>
+      <c r="AI58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL58" s="1" t="s">
-        <v>26</v>
+      <c r="AK58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN58" s="1" t="s">
-        <v>26</v>
+      <c r="AN58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO58" s="2" t="s">
         <v>25</v>
@@ -13193,23 +13208,32 @@
         <v>20</v>
       </c>
       <c r="C59" s="3">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="D59" s="3">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
       <c r="E59" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F59" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G59" s="3">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>509</v>
       </c>
+      <c r="K59" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="P59" s="1" t="s">
         <v>26</v>
       </c>
@@ -13246,8 +13270,8 @@
       <c r="AA59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB59" s="2" t="s">
-        <v>25</v>
+      <c r="AB59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC59" s="2" t="s">
         <v>25</v>
@@ -13258,17 +13282,17 @@
       <c r="AE59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG59" s="2" t="s">
-        <v>25</v>
+      <c r="AF59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI59" s="2" t="s">
-        <v>25</v>
+      <c r="AI59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ59" s="2" t="s">
         <v>25</v>
@@ -13276,14 +13300,14 @@
       <c r="AK59" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL59" s="2" t="s">
-        <v>25</v>
+      <c r="AL59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN59" s="2" t="s">
-        <v>25</v>
+      <c r="AN59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO59" s="2" t="s">
         <v>25</v>
@@ -13297,40 +13321,34 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C60" s="3">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="D60" s="3">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="E60" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F60" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G60" s="3">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="L60" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>25</v>
+      <c r="P60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>25</v>
@@ -13338,41 +13356,41 @@
       <c r="S60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA60" s="1" t="s">
-        <v>26</v>
+      <c r="T60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC60" s="1" t="s">
-        <v>26</v>
+      <c r="AC60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE60" s="1" t="s">
-        <v>26</v>
+      <c r="AE60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF60" s="2" t="s">
         <v>25</v>
@@ -13389,20 +13407,20 @@
       <c r="AJ60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK60" s="2" t="s">
-        <v>25</v>
+      <c r="AK60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM60" s="1" t="s">
-        <v>26</v>
+      <c r="AM60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO60" s="1" t="s">
-        <v>26</v>
+      <c r="AO60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP60" s="2" t="s">
         <v>25</v>
@@ -13416,25 +13434,22 @@
         <v>514</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C61" s="3">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="D61" s="3">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="E61" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F61" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G61" s="3">
-        <v>27</v>
-      </c>
-      <c r="H61" s="3">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>515</v>
@@ -13472,20 +13487,20 @@
       <c r="X61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y61" s="2" t="s">
-        <v>25</v>
+      <c r="Y61" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA61" s="2" t="s">
-        <v>25</v>
+      <c r="AA61" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC61" s="2" t="s">
-        <v>25</v>
+      <c r="AC61" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD61" s="2" t="s">
         <v>25</v>
@@ -13535,22 +13550,25 @@
         <v>518</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C62" s="3">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="D62" s="3">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E62" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G62" s="3">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="H62" s="3">
+        <v>10</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>519</v>
@@ -13559,9 +13577,6 @@
         <v>520</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="M62" s="3" t="s">
         <v>521</v>
       </c>
       <c r="P62" s="2" t="s">
@@ -13576,17 +13591,17 @@
       <c r="S62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>25</v>
+      <c r="T62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>25</v>
@@ -13594,14 +13609,14 @@
       <c r="Y62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z62" s="2" t="s">
-        <v>25</v>
+      <c r="Z62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB62" s="1" t="s">
-        <v>26</v>
+      <c r="AB62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC62" s="2" t="s">
         <v>25</v>
@@ -13609,20 +13624,20 @@
       <c r="AD62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG62" s="1" t="s">
-        <v>26</v>
+      <c r="AE62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI62" s="1" t="s">
-        <v>26</v>
+      <c r="AI62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ62" s="2" t="s">
         <v>25</v>
@@ -13630,17 +13645,17 @@
       <c r="AK62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO62" s="2" t="s">
-        <v>25</v>
+      <c r="AL62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP62" s="2" t="s">
         <v>25</v>
@@ -13657,23 +13672,32 @@
         <v>20</v>
       </c>
       <c r="C63" s="3">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="D63" s="3">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E63" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F63" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G63" s="3">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>523</v>
       </c>
+      <c r="K63" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="P63" s="2" t="s">
         <v>25</v>
       </c>
@@ -13686,17 +13710,17 @@
       <c r="S63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W63" s="1" t="s">
-        <v>26</v>
+      <c r="T63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X63" s="2" t="s">
         <v>25</v>
@@ -13704,14 +13728,14 @@
       <c r="Y63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z63" s="1" t="s">
-        <v>26</v>
+      <c r="Z63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB63" s="2" t="s">
-        <v>25</v>
+      <c r="AB63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC63" s="2" t="s">
         <v>25</v>
@@ -13719,20 +13743,20 @@
       <c r="AD63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG63" s="2" t="s">
-        <v>25</v>
+      <c r="AE63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI63" s="2" t="s">
-        <v>25</v>
+      <c r="AI63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ63" s="2" t="s">
         <v>25</v>
@@ -13740,17 +13764,17 @@
       <c r="AK63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO63" s="1" t="s">
-        <v>26</v>
+      <c r="AL63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP63" s="2" t="s">
         <v>25</v>
@@ -13761,43 +13785,34 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C64" s="3">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="D64" s="3">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="E64" s="3">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F64" s="3">
-        <v>70</v>
-      </c>
-      <c r="H64" s="3">
-        <v>60</v>
-      </c>
-      <c r="I64" s="3">
-        <v>10</v>
+        <v>-5</v>
+      </c>
+      <c r="G64" s="3">
+        <v>15</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>26</v>
+        <v>527</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R64" s="2" t="s">
         <v>25</v>
@@ -13805,32 +13820,32 @@
       <c r="S64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X64" s="1" t="s">
-        <v>26</v>
+      <c r="T64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z64" s="2" t="s">
-        <v>25</v>
+      <c r="Z64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB64" s="1" t="s">
-        <v>26</v>
+      <c r="AB64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC64" s="2" t="s">
         <v>25</v>
@@ -13838,38 +13853,38 @@
       <c r="AD64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG64" s="1" t="s">
-        <v>26</v>
+      <c r="AE64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI64" s="1" t="s">
-        <v>26</v>
+      <c r="AI64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO64" s="2" t="s">
-        <v>25</v>
+      <c r="AK64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP64" s="2" t="s">
         <v>25</v>
@@ -13880,40 +13895,43 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C65" s="3">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="D65" s="3">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E65" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F65" s="3">
-        <v>20</v>
-      </c>
-      <c r="G65" s="3">
-        <v>49</v>
+        <v>70</v>
+      </c>
+      <c r="H65" s="3">
+        <v>60</v>
+      </c>
+      <c r="I65" s="3">
+        <v>10</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q65" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R65" s="2" t="s">
         <v>25</v>
@@ -13921,26 +13939,26 @@
       <c r="S65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X65" s="2" t="s">
-        <v>25</v>
+      <c r="T65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z65" s="1" t="s">
-        <v>26</v>
+      <c r="Z65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA65" s="2" t="s">
         <v>25</v>
@@ -13954,8 +13972,8 @@
       <c r="AD65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE65" s="1" t="s">
-        <v>26</v>
+      <c r="AE65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF65" s="1" t="s">
         <v>26</v>
@@ -13972,20 +13990,20 @@
       <c r="AJ65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK65" s="2" t="s">
-        <v>25</v>
+      <c r="AK65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM65" s="1" t="s">
-        <v>26</v>
+      <c r="AM65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO65" s="1" t="s">
-        <v>26</v>
+      <c r="AO65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP65" s="2" t="s">
         <v>25</v>
@@ -13996,34 +14014,34 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C66" s="3">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="D66" s="3">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="E66" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F66" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G66" s="3">
-        <v>23</v>
-      </c>
-      <c r="H66" s="3">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>531</v>
+        <v>22</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>532</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>25</v>
@@ -14061,8 +14079,8 @@
       <c r="AA66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB66" s="2" t="s">
-        <v>25</v>
+      <c r="AB66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC66" s="2" t="s">
         <v>25</v>
@@ -14073,17 +14091,17 @@
       <c r="AE66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF66" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG66" s="2" t="s">
-        <v>25</v>
+      <c r="AF66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI66" s="2" t="s">
-        <v>25</v>
+      <c r="AI66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ66" s="2" t="s">
         <v>25</v>
@@ -14091,14 +14109,14 @@
       <c r="AK66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL66" s="2" t="s">
-        <v>25</v>
+      <c r="AL66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN66" s="2" t="s">
-        <v>25</v>
+      <c r="AN66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO66" s="1" t="s">
         <v>26</v>
@@ -14112,28 +14130,34 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C67" s="3">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D67" s="3">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="E67" s="3">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="F67" s="3">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="G67" s="3">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="H67" s="3">
+        <v>10</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>25</v>
@@ -14222,16 +14246,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C68" s="3">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D68" s="3">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="E68" s="3">
         <v>-20</v>
@@ -14243,7 +14267,7 @@
         <v>15</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>25</v>
@@ -14332,33 +14356,27 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C69" s="3">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="D69" s="3">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="E69" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F69" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G69" s="3">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="L69" s="3" t="s">
         <v>539</v>
       </c>
       <c r="P69" s="2" t="s">
@@ -14373,17 +14391,17 @@
       <c r="S69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T69" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U69" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W69" s="2" t="s">
-        <v>25</v>
+      <c r="T69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X69" s="2" t="s">
         <v>25</v>
@@ -14391,14 +14409,14 @@
       <c r="Y69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z69" s="2" t="s">
-        <v>25</v>
+      <c r="Z69" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB69" s="1" t="s">
-        <v>26</v>
+      <c r="AB69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC69" s="2" t="s">
         <v>25</v>
@@ -14406,20 +14424,20 @@
       <c r="AD69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE69" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG69" s="1" t="s">
-        <v>26</v>
+      <c r="AE69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI69" s="1" t="s">
-        <v>26</v>
+      <c r="AI69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ69" s="2" t="s">
         <v>25</v>
@@ -14427,17 +14445,17 @@
       <c r="AK69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM69" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO69" s="2" t="s">
-        <v>25</v>
+      <c r="AL69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO69" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP69" s="2" t="s">
         <v>25</v>
@@ -14454,23 +14472,29 @@
         <v>20</v>
       </c>
       <c r="C70" s="3">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="D70" s="3">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="E70" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F70" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G70" s="3">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>541</v>
       </c>
+      <c r="K70" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>543</v>
+      </c>
       <c r="P70" s="2" t="s">
         <v>25</v>
       </c>
@@ -14498,20 +14522,20 @@
       <c r="X70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y70" s="1" t="s">
-        <v>26</v>
+      <c r="Y70" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA70" s="1" t="s">
-        <v>26</v>
+      <c r="AA70" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB70" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC70" s="1" t="s">
-        <v>26</v>
+      <c r="AC70" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD70" s="2" t="s">
         <v>25</v>
@@ -14558,37 +14582,28 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C71" s="3">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="D71" s="3">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="E71" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F71" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G71" s="3">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>25</v>
@@ -14602,41 +14617,41 @@
       <c r="S71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W71" s="1" t="s">
-        <v>26</v>
+      <c r="T71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA71" s="2" t="s">
-        <v>25</v>
+      <c r="Y71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA71" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB71" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC71" s="2" t="s">
-        <v>25</v>
+      <c r="AC71" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE71" s="1" t="s">
-        <v>26</v>
+      <c r="AE71" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF71" s="1" t="s">
         <v>26</v>
@@ -14659,14 +14674,14 @@
       <c r="AL71" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM71" s="1" t="s">
-        <v>26</v>
+      <c r="AM71" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN71" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO71" s="1" t="s">
-        <v>26</v>
+      <c r="AO71" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP71" s="2" t="s">
         <v>25</v>
@@ -14677,7 +14692,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>20</v>
@@ -14686,7 +14701,7 @@
         <v>160</v>
       </c>
       <c r="D72" s="3">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="E72" s="3">
         <v>-50</v>
@@ -14695,22 +14710,25 @@
         <v>20</v>
       </c>
       <c r="G72" s="3">
+        <v>41</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="P72" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>26</v>
+      <c r="M72" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>25</v>
@@ -14718,26 +14736,26 @@
       <c r="S72" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T72" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U72" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V72" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W72" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X72" s="1" t="s">
-        <v>26</v>
+      <c r="T72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z72" s="2" t="s">
-        <v>25</v>
+      <c r="Z72" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA72" s="2" t="s">
         <v>25</v>
@@ -14751,8 +14769,8 @@
       <c r="AD72" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE72" s="2" t="s">
-        <v>25</v>
+      <c r="AE72" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF72" s="1" t="s">
         <v>26</v>
@@ -14769,20 +14787,20 @@
       <c r="AJ72" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK72" s="1" t="s">
-        <v>26</v>
+      <c r="AK72" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL72" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM72" s="2" t="s">
-        <v>25</v>
+      <c r="AM72" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN72" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO72" s="2" t="s">
-        <v>25</v>
+      <c r="AO72" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP72" s="2" t="s">
         <v>25</v>
@@ -14793,111 +14811,343 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C73" s="3">
+        <v>160</v>
+      </c>
+      <c r="D73" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="E73" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F73" s="3">
+        <v>20</v>
+      </c>
+      <c r="G73" s="3">
+        <v>45</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ73" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="3">
+        <v>180</v>
+      </c>
+      <c r="D74" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="E74" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F74" s="3">
+        <v>20</v>
+      </c>
+      <c r="G74" s="3">
+        <v>33</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ74" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="3">
         <v>60</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D75" s="3">
         <v>0.25</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E75" s="3">
         <v>-30</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F75" s="3">
         <v>-10</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G75" s="3">
         <v>15</v>
       </c>
-      <c r="J73" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ73" s="2" t="s">
+      <c r="J75" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ75" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -15037,13 +15287,13 @@
         <v>314</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>318</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>185</v>
@@ -15057,7 +15307,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -15078,13 +15328,13 @@
         <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>25</v>
@@ -15143,7 +15393,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -15164,13 +15414,13 @@
         <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>45</v>
@@ -15232,7 +15482,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -15253,10 +15503,10 @@
         <v>55</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>25</v>
@@ -15315,7 +15565,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -15336,10 +15586,10 @@
         <v>45</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>167</v>
@@ -15401,7 +15651,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>34</v>
@@ -15496,7 +15746,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -15517,7 +15767,7 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>76</v>
@@ -15526,10 +15776,10 @@
         <v>254</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>25</v>
@@ -15588,7 +15838,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>82</v>
@@ -15612,13 +15862,13 @@
         <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>26</v>
@@ -15677,7 +15927,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -15766,7 +16016,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -15787,16 +16037,16 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
@@ -15855,7 +16105,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
@@ -15879,16 +16129,16 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>25</v>
@@ -15947,7 +16197,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -15968,19 +16218,19 @@
         <v>40</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>45</v>
@@ -16042,7 +16292,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -16063,7 +16313,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>299</v>
@@ -16131,7 +16381,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -16152,10 +16402,10 @@
         <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>122</v>
@@ -16220,7 +16470,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -16309,7 +16559,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>82</v>
@@ -16336,13 +16586,13 @@
         <v>104</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>25</v>
@@ -16401,7 +16651,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -16422,16 +16672,16 @@
         <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>25</v>
@@ -16490,7 +16740,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -16511,13 +16761,13 @@
         <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>131</v>
@@ -16579,7 +16829,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -16600,13 +16850,13 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>45</v>
@@ -16668,7 +16918,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -16692,7 +16942,7 @@
         <v>161</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>256</v>
@@ -16757,7 +17007,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -16778,16 +17028,16 @@
         <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>25</v>
@@ -16846,7 +17096,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -16867,16 +17117,16 @@
         <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -16935,7 +17185,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -16959,7 +17209,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>54</v>
@@ -17021,7 +17271,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>20</v>
@@ -17048,7 +17298,7 @@
         <v>207</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>209</v>
@@ -17110,7 +17360,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
@@ -17137,7 +17387,7 @@
         <v>234</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>25</v>
@@ -17196,7 +17446,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
@@ -17217,16 +17467,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>122</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>25</v>
@@ -17285,7 +17535,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -17306,13 +17556,13 @@
         <v>50</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>45</v>
@@ -17374,7 +17624,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>20</v>
@@ -17395,13 +17645,13 @@
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>96</v>
@@ -17463,7 +17713,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -1299,6 +1299,9 @@
     <t>bornite: 9 [1]</t>
   </si>
   <si>
+    <t>sphalerite: 7</t>
+  </si>
+  <si>
     <t>deep_copper_sulfide</t>
   </si>
   <si>
@@ -1675,9 +1678,6 @@
   </si>
   <si>
     <t>deep_sphalerite</t>
-  </si>
-  <si>
-    <t>sphalerite: 7</t>
   </si>
   <si>
     <t>surface_bismuth</t>
@@ -10108,6 +10108,9 @@
       <c r="L32" s="3" t="s">
         <v>426</v>
       </c>
+      <c r="M32" s="3" t="s">
+        <v>427</v>
+      </c>
       <c r="P32" s="1" t="s">
         <v>26</v>
       </c>
@@ -10195,7 +10198,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>34</v>
@@ -10219,13 +10222,13 @@
         <v>6</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>25</v>
@@ -10314,7 +10317,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>20</v>
@@ -10335,7 +10338,7 @@
         <v>15</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>26</v>
@@ -10424,7 +10427,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>82</v>
@@ -10448,7 +10451,7 @@
         <v>5</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>415</v>
@@ -10540,7 +10543,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>20</v>
@@ -10570,7 +10573,7 @@
         <v>408</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>25</v>
@@ -10659,7 +10662,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>82</v>
@@ -10775,7 +10778,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>20</v>
@@ -10796,7 +10799,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>25</v>
@@ -10885,7 +10888,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>34</v>
@@ -10909,13 +10912,13 @@
         <v>5</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>25</v>
@@ -11004,7 +11007,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>20</v>
@@ -11025,16 +11028,16 @@
         <v>49</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>26</v>
@@ -11123,7 +11126,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>34</v>
@@ -11147,10 +11150,10 @@
         <v>8</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>25</v>
@@ -11239,7 +11242,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
@@ -11260,7 +11263,7 @@
         <v>15</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>26</v>
@@ -11349,7 +11352,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>20</v>
@@ -11370,13 +11373,13 @@
         <v>41</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>25</v>
@@ -11465,7 +11468,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>34</v>
@@ -11489,7 +11492,7 @@
         <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>25</v>
@@ -11578,7 +11581,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>20</v>
@@ -11599,16 +11602,16 @@
         <v>36</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>25</v>
@@ -11697,7 +11700,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>20</v>
@@ -11718,16 +11721,16 @@
         <v>42</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>25</v>
@@ -11816,7 +11819,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>34</v>
@@ -11840,13 +11843,13 @@
         <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>25</v>
@@ -11935,7 +11938,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>20</v>
@@ -11956,13 +11959,13 @@
         <v>32</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>25</v>
@@ -12051,7 +12054,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
@@ -12072,7 +12075,7 @@
         <v>15</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>26</v>
@@ -12161,7 +12164,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>20</v>
@@ -12182,13 +12185,13 @@
         <v>29</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>25</v>
@@ -12277,7 +12280,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>34</v>
@@ -12301,10 +12304,10 @@
         <v>10</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>26</v>
@@ -12393,7 +12396,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>34</v>
@@ -12417,10 +12420,10 @@
         <v>10</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>26</v>
@@ -12509,7 +12512,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>34</v>
@@ -12533,10 +12536,10 @@
         <v>10</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>25</v>
@@ -12625,7 +12628,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>20</v>
@@ -12646,7 +12649,7 @@
         <v>15</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>26</v>
@@ -12735,7 +12738,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>20</v>
@@ -12756,7 +12759,7 @@
         <v>15</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>25</v>
@@ -12845,7 +12848,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>20</v>
@@ -12866,16 +12869,16 @@
         <v>31</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>25</v>
@@ -12964,7 +12967,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>34</v>
@@ -12988,10 +12991,10 @@
         <v>10</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>26</v>
@@ -13080,7 +13083,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>82</v>
@@ -13104,16 +13107,16 @@
         <v>10</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>25</v>
@@ -13202,7 +13205,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>20</v>
@@ -13223,16 +13226,16 @@
         <v>41</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>288</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>26</v>
@@ -13321,7 +13324,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>20</v>
@@ -13342,7 +13345,7 @@
         <v>15</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>26</v>
@@ -13431,7 +13434,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>20</v>
@@ -13452,13 +13455,13 @@
         <v>41</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>25</v>
@@ -13547,7 +13550,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>34</v>
@@ -13571,13 +13574,13 @@
         <v>10</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>25</v>
@@ -13666,7 +13669,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>20</v>
@@ -13687,16 +13690,16 @@
         <v>35</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>25</v>
@@ -13785,7 +13788,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>20</v>
@@ -13806,7 +13809,7 @@
         <v>15</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>25</v>
@@ -13895,7 +13898,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>82</v>
@@ -13919,7 +13922,7 @@
         <v>10</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>295</v>
@@ -14014,7 +14017,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>20</v>
@@ -14035,13 +14038,13 @@
         <v>49</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>25</v>
@@ -14130,7 +14133,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>34</v>
@@ -14154,10 +14157,10 @@
         <v>10</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>25</v>
@@ -14246,7 +14249,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>20</v>
@@ -14267,7 +14270,7 @@
         <v>15</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>25</v>
@@ -14356,7 +14359,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>20</v>
@@ -14377,7 +14380,7 @@
         <v>15</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>25</v>
@@ -14466,7 +14469,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>20</v>
@@ -14487,13 +14490,13 @@
         <v>39</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>25</v>
@@ -14582,7 +14585,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>20</v>
@@ -14603,7 +14606,7 @@
         <v>15</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>25</v>
@@ -14692,7 +14695,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>20</v>
@@ -14713,7 +14716,7 @@
         <v>41</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>22</v>
@@ -14722,7 +14725,7 @@
         <v>45</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>25</v>
@@ -14811,7 +14814,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>20</v>
@@ -14832,10 +14835,10 @@
         <v>45</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>96</v>
@@ -14927,7 +14930,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>20</v>
@@ -14948,13 +14951,13 @@
         <v>33</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>553</v>
+        <v>427</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>25</v>
@@ -16224,7 +16227,7 @@
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>593</v>
@@ -16675,7 +16678,7 @@
         <v>606</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>607</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -1053,6 +1053,15 @@
     <t>lead: 5</t>
   </si>
   <si>
+    <t>normal_sphalerite</t>
+  </si>
+  <si>
+    <t>sphalerite: 10</t>
+  </si>
+  <si>
+    <t>galena: 3</t>
+  </si>
+  <si>
     <t>deep_bauxite</t>
   </si>
   <si>
@@ -1074,6 +1083,15 @@
     <t>cassiterite: 3</t>
   </si>
   <si>
+    <t>normal_asbestos_dry</t>
+  </si>
+  <si>
+    <t>cassiterite_sand: 6</t>
+  </si>
+  <si>
+    <t>asbestos: 1</t>
+  </si>
+  <si>
     <t>deep_thorianite</t>
   </si>
   <si>
@@ -1479,15 +1497,6 @@
     <t>magnetite: 3</t>
   </si>
   <si>
-    <t>normal_asbestos</t>
-  </si>
-  <si>
-    <t>cassiterite_sand: 6</t>
-  </si>
-  <si>
-    <t>asbestos: 1</t>
-  </si>
-  <si>
     <t>surface_hematite</t>
   </si>
   <si>
@@ -1606,15 +1615,6 @@
   </si>
   <si>
     <t>hematite: 3</t>
-  </si>
-  <si>
-    <t>normal_cassiterite</t>
-  </si>
-  <si>
-    <t>cassiterite: 8 [1]</t>
-  </si>
-  <si>
-    <t>tin: 2</t>
   </si>
   <si>
     <t>surface_magnetite</t>
@@ -7209,22 +7209,25 @@
         <v>345</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="D7" s="3">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="E7" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="H7" s="3">
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>346</v>
@@ -7244,41 +7247,41 @@
       <c r="S7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>25</v>
+      <c r="T7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>26</v>
+      <c r="Y7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC7" s="1" t="s">
-        <v>26</v>
+      <c r="AC7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>25</v>
+      <c r="AE7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>25</v>
@@ -7301,14 +7304,14 @@
       <c r="AL7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM7" s="2" t="s">
-        <v>25</v>
+      <c r="AM7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO7" s="2" t="s">
-        <v>25</v>
+      <c r="AO7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP7" s="2" t="s">
         <v>25</v>
@@ -7325,10 +7328,10 @@
         <v>20</v>
       </c>
       <c r="C8" s="3">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="D8" s="3">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="E8" s="3">
         <v>-50</v>
@@ -7337,7 +7340,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="3">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>349</v>
@@ -7345,14 +7348,11 @@
       <c r="K8" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>26</v>
+      <c r="P8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>25</v>
@@ -7372,8 +7372,8 @@
       <c r="W8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>26</v>
+      <c r="X8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>26</v>
@@ -7411,8 +7411,8 @@
       <c r="AJ8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK8" s="1" t="s">
-        <v>26</v>
+      <c r="AK8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL8" s="2" t="s">
         <v>25</v>
@@ -7435,16 +7435,16 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="3">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="D9" s="3">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="E9" s="3">
         <v>-50</v>
@@ -7453,25 +7453,22 @@
         <v>20</v>
       </c>
       <c r="G9" s="3">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>25</v>
+      <c r="P9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>25</v>
@@ -7491,8 +7488,8 @@
       <c r="W9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X9" s="2" t="s">
-        <v>25</v>
+      <c r="X9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>26</v>
@@ -7530,8 +7527,8 @@
       <c r="AJ9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK9" s="2" t="s">
-        <v>25</v>
+      <c r="AK9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL9" s="2" t="s">
         <v>25</v>
@@ -7554,52 +7551,58 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3">
+        <v>130</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3">
+        <v>70</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20</v>
+      </c>
+      <c r="H10" s="3">
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="3">
-        <v>190</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-5</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3">
-        <v>35</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="P10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>25</v>
+      <c r="R10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>25</v>
@@ -7607,89 +7610,95 @@
       <c r="Y10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z10" s="2" t="s">
-        <v>25</v>
+      <c r="Z10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB10" s="2" t="s">
-        <v>25</v>
+      <c r="AB10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AD10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
-        <v>26</v>
+      <c r="AD10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AK10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ10" s="1" t="s">
-        <v>26</v>
+      <c r="AL10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3">
+        <v>270</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F11" s="3">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3">
+        <v>31</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="3">
-        <v>230</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.28</v>
-      </c>
-      <c r="E11" s="3">
-        <v>10</v>
-      </c>
-      <c r="F11" s="3">
-        <v>70</v>
-      </c>
-      <c r="G11" s="3">
-        <v>34</v>
-      </c>
-      <c r="H11" s="3">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>360</v>
       </c>
+      <c r="L11" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="P11" s="2" t="s">
         <v>25</v>
       </c>
@@ -7702,41 +7711,41 @@
       <c r="S11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>26</v>
+      <c r="T11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>25</v>
+      <c r="Y11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC11" s="2" t="s">
-        <v>25</v>
+      <c r="AC11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE11" s="1" t="s">
-        <v>26</v>
+      <c r="AE11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF11" s="2" t="s">
         <v>25</v>
@@ -7759,14 +7768,14 @@
       <c r="AL11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM11" s="1" t="s">
-        <v>26</v>
+      <c r="AM11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO11" s="1" t="s">
-        <v>26</v>
+      <c r="AO11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP11" s="2" t="s">
         <v>25</v>
@@ -7777,147 +7786,147 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="D12" s="3">
         <v>0.2</v>
       </c>
       <c r="E12" s="3">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ12" s="2" t="s">
-        <v>25</v>
+        <v>364</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="D13" s="3">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="E13" s="3">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="G13" s="3">
+        <v>34</v>
+      </c>
+      <c r="H13" s="3">
         <v>10</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>26</v>
+        <v>366</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>25</v>
@@ -7925,41 +7934,41 @@
       <c r="S13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>26</v>
+      <c r="T13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC13" s="1" t="s">
-        <v>26</v>
+      <c r="AC13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE13" s="2" t="s">
-        <v>25</v>
+      <c r="AE13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF13" s="2" t="s">
         <v>25</v>
@@ -7976,20 +7985,20 @@
       <c r="AJ13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK13" s="1" t="s">
-        <v>26</v>
+      <c r="AK13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM13" s="2" t="s">
-        <v>25</v>
+      <c r="AM13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO13" s="2" t="s">
-        <v>25</v>
+      <c r="AO13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP13" s="2" t="s">
         <v>25</v>
@@ -8000,43 +8009,37 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="3">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="E14" s="3">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="F14" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="L14" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>25</v>
+      <c r="P14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>25</v>
@@ -8044,32 +8047,32 @@
       <c r="S14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>25</v>
+      <c r="T14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z14" s="2" t="s">
-        <v>25</v>
+      <c r="Z14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB14" s="2" t="s">
-        <v>25</v>
+      <c r="AB14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>26</v>
@@ -8077,38 +8080,38 @@
       <c r="AD14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG14" s="2" t="s">
-        <v>25</v>
+      <c r="AE14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI14" s="2" t="s">
-        <v>25</v>
+      <c r="AI14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO14" s="2" t="s">
-        <v>25</v>
+      <c r="AK14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP14" s="2" t="s">
         <v>25</v>
@@ -8119,34 +8122,28 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="3">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="E15" s="3">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="3">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G15" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>26</v>
@@ -8160,17 +8157,17 @@
       <c r="S15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>26</v>
+      <c r="T15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>26</v>
@@ -8178,14 +8175,14 @@
       <c r="Y15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z15" s="1" t="s">
-        <v>26</v>
+      <c r="Z15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB15" s="1" t="s">
-        <v>26</v>
+      <c r="AB15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC15" s="1" t="s">
         <v>26</v>
@@ -8193,20 +8190,20 @@
       <c r="AD15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG15" s="1" t="s">
-        <v>26</v>
+      <c r="AE15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI15" s="1" t="s">
-        <v>26</v>
+      <c r="AI15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ15" s="2" t="s">
         <v>25</v>
@@ -8214,17 +8211,17 @@
       <c r="AK15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO15" s="1" t="s">
-        <v>26</v>
+      <c r="AL15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP15" s="2" t="s">
         <v>25</v>
@@ -8235,34 +8232,43 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="D16" s="3">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="E16" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G16" s="3">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>26</v>
+      <c r="P16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>25</v>
@@ -8282,23 +8288,23 @@
       <c r="W16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>25</v>
+      <c r="X16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA16" s="2" t="s">
-        <v>25</v>
+      <c r="AA16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC16" s="2" t="s">
-        <v>25</v>
+      <c r="AC16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>25</v>
@@ -8321,8 +8327,8 @@
       <c r="AJ16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK16" s="1" t="s">
-        <v>26</v>
+      <c r="AK16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL16" s="2" t="s">
         <v>25</v>
@@ -8351,23 +8357,29 @@
         <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D17" s="3">
         <v>0.25</v>
       </c>
       <c r="E17" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F17" s="3">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>378</v>
       </c>
+      <c r="K17" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="P17" s="1" t="s">
         <v>26</v>
       </c>
@@ -8380,17 +8392,17 @@
       <c r="S17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>25</v>
+      <c r="T17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X17" s="1" t="s">
         <v>26</v>
@@ -8398,14 +8410,14 @@
       <c r="Y17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z17" s="2" t="s">
-        <v>25</v>
+      <c r="Z17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB17" s="2" t="s">
-        <v>25</v>
+      <c r="AB17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC17" s="1" t="s">
         <v>26</v>
@@ -8413,20 +8425,20 @@
       <c r="AD17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG17" s="2" t="s">
-        <v>25</v>
+      <c r="AE17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI17" s="2" t="s">
-        <v>25</v>
+      <c r="AI17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ17" s="2" t="s">
         <v>25</v>
@@ -8434,17 +8446,17 @@
       <c r="AK17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO17" s="2" t="s">
-        <v>25</v>
+      <c r="AL17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP17" s="2" t="s">
         <v>25</v>
@@ -8455,31 +8467,28 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="3">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D18" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G18" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>26</v>
@@ -8493,53 +8502,53 @@
       <c r="S18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>26</v>
+      <c r="T18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC18" s="1" t="s">
-        <v>26</v>
+      <c r="Y18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG18" s="1" t="s">
-        <v>26</v>
+      <c r="AE18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI18" s="1" t="s">
-        <v>26</v>
+      <c r="AI18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ18" s="2" t="s">
         <v>25</v>
@@ -8547,17 +8556,17 @@
       <c r="AK18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO18" s="1" t="s">
-        <v>26</v>
+      <c r="AL18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP18" s="2" t="s">
         <v>25</v>
@@ -8568,7 +8577,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -8577,7 +8586,7 @@
         <v>80</v>
       </c>
       <c r="D19" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="3">
         <v>-20</v>
@@ -8586,10 +8595,10 @@
         <v>-5</v>
       </c>
       <c r="G19" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>26</v>
@@ -8618,20 +8627,20 @@
       <c r="X19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="2" t="s">
-        <v>25</v>
+      <c r="Y19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA19" s="2" t="s">
-        <v>25</v>
+      <c r="AA19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC19" s="2" t="s">
-        <v>25</v>
+      <c r="AC19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>25</v>
@@ -8678,28 +8687,31 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E20" s="3">
-        <v>90</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="3">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>360</v>
+        <v>386</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>26</v>
@@ -8788,46 +8800,34 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="D21" s="3">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="E21" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="3">
+        <v>-5</v>
+      </c>
+      <c r="G21" s="3">
         <v>20</v>
       </c>
-      <c r="H21" s="3">
-        <v>60</v>
-      </c>
-      <c r="I21" s="3">
-        <v>10</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="M21" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>25</v>
+      <c r="P21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>25</v>
@@ -8847,8 +8847,8 @@
       <c r="W21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>25</v>
+      <c r="X21" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>25</v>
@@ -8859,8 +8859,8 @@
       <c r="AA21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB21" s="1" t="s">
-        <v>26</v>
+      <c r="AB21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC21" s="2" t="s">
         <v>25</v>
@@ -8871,32 +8871,32 @@
       <c r="AE21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG21" s="1" t="s">
-        <v>26</v>
+      <c r="AF21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI21" s="1" t="s">
-        <v>26</v>
+      <c r="AI21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL21" s="1" t="s">
-        <v>26</v>
+      <c r="AK21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN21" s="1" t="s">
-        <v>26</v>
+      <c r="AN21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO21" s="2" t="s">
         <v>25</v>
@@ -8913,40 +8913,31 @@
         <v>390</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="D22" s="3">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="E22" s="3">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="G22" s="3">
         <v>30</v>
       </c>
-      <c r="H22" s="3">
-        <v>10</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>25</v>
+        <v>366</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>25</v>
@@ -8966,8 +8957,8 @@
       <c r="W22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X22" s="2" t="s">
-        <v>25</v>
+      <c r="X22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>26</v>
@@ -8978,8 +8969,8 @@
       <c r="AA22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB22" s="2" t="s">
-        <v>25</v>
+      <c r="AB22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>26</v>
@@ -8990,32 +8981,32 @@
       <c r="AE22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>25</v>
+      <c r="AF22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI22" s="2" t="s">
-        <v>25</v>
+      <c r="AI22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL22" s="2" t="s">
-        <v>25</v>
+      <c r="AK22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN22" s="2" t="s">
-        <v>25</v>
+      <c r="AN22" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO22" s="1" t="s">
         <v>26</v>
@@ -9029,34 +9020,46 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="3">
+        <v>180</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F23" s="3">
+        <v>20</v>
+      </c>
+      <c r="H23" s="3">
+        <v>60</v>
+      </c>
+      <c r="I23" s="3">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="3">
-        <v>90</v>
-      </c>
-      <c r="D23" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-30</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>15</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="P23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>26</v>
+      <c r="P23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>25</v>
@@ -9064,41 +9067,41 @@
       <c r="S23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA23" s="1" t="s">
-        <v>26</v>
+      <c r="T23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC23" s="1" t="s">
-        <v>26</v>
+      <c r="AC23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE23" s="1" t="s">
-        <v>26</v>
+      <c r="AE23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>26</v>
@@ -9115,20 +9118,20 @@
       <c r="AJ23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK23" s="1" t="s">
-        <v>26</v>
+      <c r="AK23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM23" s="1" t="s">
-        <v>26</v>
+      <c r="AM23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO23" s="1" t="s">
-        <v>26</v>
+      <c r="AO23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP23" s="2" t="s">
         <v>25</v>
@@ -9145,22 +9148,22 @@
         <v>34</v>
       </c>
       <c r="C24" s="3">
+        <v>130</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3">
         <v>70</v>
       </c>
-      <c r="D24" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-30</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
       <c r="G24" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H24" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>397</v>
@@ -9171,11 +9174,11 @@
       <c r="L24" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>26</v>
+      <c r="P24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>25</v>
@@ -9195,8 +9198,8 @@
       <c r="W24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X24" s="1" t="s">
-        <v>26</v>
+      <c r="X24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y24" s="1" t="s">
         <v>26</v>
@@ -9207,8 +9210,8 @@
       <c r="AA24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>26</v>
+      <c r="AB24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>26</v>
@@ -9219,32 +9222,32 @@
       <c r="AE24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG24" s="1" t="s">
-        <v>26</v>
+      <c r="AF24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI24" s="1" t="s">
-        <v>26</v>
+      <c r="AI24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL24" s="1" t="s">
-        <v>26</v>
+      <c r="AK24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN24" s="1" t="s">
-        <v>26</v>
+      <c r="AN24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO24" s="1" t="s">
         <v>26</v>
@@ -9264,22 +9267,22 @@
         <v>20</v>
       </c>
       <c r="C25" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D25" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E25" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G25" s="3">
         <v>15</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>121</v>
+        <v>401</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>26</v>
@@ -9293,53 +9296,53 @@
       <c r="S25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>25</v>
+      <c r="T25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>25</v>
+      <c r="Y25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>25</v>
+      <c r="AE25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI25" s="2" t="s">
-        <v>25</v>
+      <c r="AI25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ25" s="2" t="s">
         <v>25</v>
@@ -9347,17 +9350,17 @@
       <c r="AK25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO25" s="2" t="s">
-        <v>25</v>
+      <c r="AL25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP25" s="2" t="s">
         <v>25</v>
@@ -9368,34 +9371,37 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="3">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="G26" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>405</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>26</v>
@@ -9409,17 +9415,17 @@
       <c r="S26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>25</v>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X26" s="1" t="s">
         <v>26</v>
@@ -9427,14 +9433,14 @@
       <c r="Y26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z26" s="2" t="s">
-        <v>25</v>
+      <c r="Z26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB26" s="2" t="s">
-        <v>25</v>
+      <c r="AB26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC26" s="1" t="s">
         <v>26</v>
@@ -9442,20 +9448,20 @@
       <c r="AD26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>25</v>
+      <c r="AE26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI26" s="2" t="s">
-        <v>25</v>
+      <c r="AI26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ26" s="2" t="s">
         <v>25</v>
@@ -9463,17 +9469,17 @@
       <c r="AK26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO26" s="2" t="s">
-        <v>25</v>
+      <c r="AL26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP26" s="2" t="s">
         <v>25</v>
@@ -9484,43 +9490,34 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="3">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="D27" s="3">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="E27" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F27" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G27" s="3">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>25</v>
+        <v>121</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>25</v>
@@ -9528,41 +9525,41 @@
       <c r="S27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA27" s="1" t="s">
-        <v>26</v>
+      <c r="T27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC27" s="1" t="s">
-        <v>26</v>
+      <c r="AC27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE27" s="1" t="s">
-        <v>26</v>
+      <c r="AE27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF27" s="2" t="s">
         <v>25</v>
@@ -9579,20 +9576,20 @@
       <c r="AJ27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK27" s="2" t="s">
-        <v>25</v>
+      <c r="AK27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM27" s="1" t="s">
-        <v>26</v>
+      <c r="AM27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO27" s="1" t="s">
-        <v>26</v>
+      <c r="AO27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP27" s="2" t="s">
         <v>25</v>
@@ -9603,37 +9600,40 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="3">
+        <v>150</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="E28" s="3">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3">
+        <v>70</v>
+      </c>
+      <c r="G28" s="3">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3">
+        <v>10</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="3">
-        <v>80</v>
-      </c>
-      <c r="D28" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E28" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F28" s="3">
-        <v>-5</v>
-      </c>
-      <c r="G28" s="3">
-        <v>15</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>25</v>
+      <c r="P28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>25</v>
@@ -9641,71 +9641,71 @@
       <c r="S28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC28" s="2" t="s">
-        <v>25</v>
+      <c r="T28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG28" s="1" t="s">
-        <v>26</v>
+      <c r="AE28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI28" s="1" t="s">
-        <v>26</v>
+      <c r="AI28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO28" s="1" t="s">
-        <v>26</v>
+      <c r="AK28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP28" s="2" t="s">
         <v>25</v>
@@ -9716,43 +9716,43 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C29" s="3">
         <v>190</v>
       </c>
       <c r="D29" s="3">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="E29" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F29" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G29" s="3">
-        <v>25</v>
-      </c>
-      <c r="H29" s="3">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K29" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="P29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>26</v>
+      <c r="P29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>25</v>
@@ -9772,8 +9772,8 @@
       <c r="W29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X29" s="1" t="s">
-        <v>26</v>
+      <c r="X29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y29" s="1" t="s">
         <v>26</v>
@@ -9784,8 +9784,8 @@
       <c r="AA29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB29" s="1" t="s">
-        <v>26</v>
+      <c r="AB29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC29" s="1" t="s">
         <v>26</v>
@@ -9796,32 +9796,32 @@
       <c r="AE29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG29" s="1" t="s">
-        <v>26</v>
+      <c r="AF29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI29" s="1" t="s">
-        <v>26</v>
+      <c r="AI29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL29" s="1" t="s">
-        <v>26</v>
+      <c r="AK29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN29" s="1" t="s">
-        <v>26</v>
+      <c r="AN29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO29" s="1" t="s">
         <v>26</v>
@@ -9841,19 +9841,19 @@
         <v>20</v>
       </c>
       <c r="C30" s="3">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="D30" s="3">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="E30" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F30" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G30" s="3">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>416</v>
@@ -9861,9 +9861,6 @@
       <c r="K30" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="P30" s="2" t="s">
         <v>25</v>
       </c>
@@ -9876,17 +9873,17 @@
       <c r="S30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>25</v>
+      <c r="T30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>25</v>
@@ -9894,8 +9891,8 @@
       <c r="Y30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z30" s="2" t="s">
-        <v>25</v>
+      <c r="Z30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA30" s="2" t="s">
         <v>25</v>
@@ -9909,8 +9906,8 @@
       <c r="AD30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE30" s="2" t="s">
-        <v>25</v>
+      <c r="AE30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF30" s="1" t="s">
         <v>26</v>
@@ -9933,14 +9930,14 @@
       <c r="AL30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM30" s="2" t="s">
-        <v>25</v>
+      <c r="AM30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO30" s="2" t="s">
-        <v>25</v>
+      <c r="AO30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP30" s="2" t="s">
         <v>25</v>
@@ -9951,16 +9948,16 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="3">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D31" s="3">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="E31" s="3">
         <v>10</v>
@@ -9969,22 +9966,25 @@
         <v>70</v>
       </c>
       <c r="G31" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H31" s="3">
         <v>10</v>
       </c>
       <c r="J31" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>25</v>
+      <c r="P31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>25</v>
@@ -10004,23 +10004,23 @@
       <c r="W31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y31" s="2" t="s">
-        <v>25</v>
+      <c r="X31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC31" s="2" t="s">
-        <v>25</v>
+      <c r="AA31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD31" s="2" t="s">
         <v>25</v>
@@ -10028,32 +10028,32 @@
       <c r="AE31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG31" s="2" t="s">
-        <v>25</v>
+      <c r="AF31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI31" s="2" t="s">
-        <v>25</v>
+      <c r="AI31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL31" s="2" t="s">
-        <v>25</v>
+      <c r="AK31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN31" s="2" t="s">
-        <v>25</v>
+      <c r="AN31" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO31" s="1" t="s">
         <v>26</v>
@@ -10067,43 +10067,40 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="3">
+        <v>290</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F32" s="3">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3">
+        <v>27</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="3">
-        <v>200</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0.29</v>
-      </c>
-      <c r="E32" s="3">
-        <v>10</v>
-      </c>
-      <c r="F32" s="3">
-        <v>70</v>
-      </c>
-      <c r="G32" s="3">
-        <v>32</v>
-      </c>
-      <c r="H32" s="3">
-        <v>10</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>26</v>
+      <c r="P32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>25</v>
@@ -10111,41 +10108,41 @@
       <c r="S32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA32" s="1" t="s">
-        <v>26</v>
+      <c r="T32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC32" s="1" t="s">
-        <v>26</v>
+      <c r="AC32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE32" s="1" t="s">
-        <v>26</v>
+      <c r="AE32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF32" s="1" t="s">
         <v>26</v>
@@ -10162,20 +10159,20 @@
       <c r="AJ32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK32" s="1" t="s">
-        <v>26</v>
+      <c r="AK32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM32" s="1" t="s">
-        <v>26</v>
+      <c r="AM32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO32" s="1" t="s">
-        <v>26</v>
+      <c r="AO32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP32" s="2" t="s">
         <v>25</v>
@@ -10186,38 +10183,35 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="3">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="D33" s="3">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="E33" s="3">
-        <v>-60</v>
+        <v>10</v>
       </c>
       <c r="F33" s="3">
-        <v>-45</v>
+        <v>70</v>
       </c>
       <c r="G33" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H33" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>429</v>
-      </c>
       <c r="P33" s="2" t="s">
         <v>25</v>
       </c>
@@ -10230,17 +10224,17 @@
       <c r="S33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>25</v>
+      <c r="T33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>25</v>
@@ -10248,14 +10242,14 @@
       <c r="Y33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z33" s="2" t="s">
-        <v>25</v>
+      <c r="Z33" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB33" s="1" t="s">
-        <v>26</v>
+      <c r="AB33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC33" s="2" t="s">
         <v>25</v>
@@ -10263,20 +10257,20 @@
       <c r="AD33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG33" s="1" t="s">
-        <v>26</v>
+      <c r="AE33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI33" s="1" t="s">
-        <v>26</v>
+      <c r="AI33" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ33" s="2" t="s">
         <v>25</v>
@@ -10284,17 +10278,17 @@
       <c r="AK33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO33" s="2" t="s">
-        <v>25</v>
+      <c r="AL33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO33" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP33" s="2" t="s">
         <v>25</v>
@@ -10305,27 +10299,36 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="3">
+        <v>150</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="E34" s="3">
+        <v>10</v>
+      </c>
+      <c r="F34" s="3">
+        <v>70</v>
+      </c>
+      <c r="G34" s="3">
+        <v>32</v>
+      </c>
+      <c r="H34" s="3">
+        <v>10</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="3">
-        <v>30</v>
-      </c>
-      <c r="D34" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="E34" s="3">
-        <v>100</v>
-      </c>
-      <c r="F34" s="3">
-        <v>170</v>
-      </c>
-      <c r="G34" s="3">
-        <v>15</v>
-      </c>
-      <c r="J34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>431</v>
       </c>
       <c r="P34" s="1" t="s">
@@ -10418,37 +10421,40 @@
         <v>432</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C35" s="3">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="D35" s="3">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="E35" s="3">
-        <v>-30</v>
+        <v>-60</v>
       </c>
       <c r="F35" s="3">
-        <v>70</v>
+        <v>-45</v>
+      </c>
+      <c r="G35" s="3">
+        <v>27</v>
       </c>
       <c r="H35" s="3">
-        <v>30</v>
-      </c>
-      <c r="I35" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>433</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>26</v>
+        <v>434</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>25</v>
@@ -10468,8 +10474,8 @@
       <c r="W35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X35" s="1" t="s">
-        <v>26</v>
+      <c r="X35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>25</v>
@@ -10480,8 +10486,8 @@
       <c r="AA35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB35" s="2" t="s">
-        <v>25</v>
+      <c r="AB35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC35" s="2" t="s">
         <v>25</v>
@@ -10492,32 +10498,32 @@
       <c r="AE35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG35" s="2" t="s">
-        <v>25</v>
+      <c r="AF35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI35" s="2" t="s">
-        <v>25</v>
+      <c r="AI35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL35" s="2" t="s">
-        <v>25</v>
+      <c r="AK35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN35" s="2" t="s">
-        <v>25</v>
+      <c r="AN35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO35" s="2" t="s">
         <v>25</v>
@@ -10531,159 +10537,150 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="3">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="D36" s="3">
-        <v>0.24</v>
+        <v>0.9</v>
       </c>
       <c r="E36" s="3">
-        <v>-5</v>
+        <v>100</v>
       </c>
       <c r="F36" s="3">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="G36" s="3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ36" s="1" t="s">
-        <v>26</v>
+        <v>437</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ36" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C37" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D37" s="3">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="E37" s="3">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="F37" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H37" s="3">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="I37" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>331</v>
+        <v>439</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>25</v>
+        <v>420</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R37" s="2" t="s">
         <v>25</v>
@@ -10703,23 +10700,23 @@
       <c r="W37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>26</v>
+      <c r="X37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA37" s="1" t="s">
-        <v>26</v>
+      <c r="AA37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC37" s="1" t="s">
-        <v>26</v>
+      <c r="AC37" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD37" s="2" t="s">
         <v>25</v>
@@ -10742,8 +10739,8 @@
       <c r="AJ37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK37" s="2" t="s">
-        <v>25</v>
+      <c r="AK37" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL37" s="2" t="s">
         <v>25</v>
@@ -10766,28 +10763,37 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="3">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="D38" s="3">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E38" s="3">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="F38" s="3">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>438</v>
+        <v>411</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>25</v>
@@ -10795,23 +10801,23 @@
       <c r="Q38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W38" s="1" t="s">
-        <v>26</v>
+      <c r="R38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>25</v>
@@ -10819,8 +10825,8 @@
       <c r="Y38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z38" s="1" t="s">
-        <v>26</v>
+      <c r="Z38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>25</v>
@@ -10831,11 +10837,11 @@
       <c r="AC38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE38" s="1" t="s">
-        <v>26</v>
+      <c r="AD38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>25</v>
@@ -10843,14 +10849,14 @@
       <c r="AG38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>25</v>
+      <c r="AH38" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ38" s="2" t="s">
-        <v>25</v>
+      <c r="AJ38" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AK38" s="2" t="s">
         <v>25</v>
@@ -10858,55 +10864,52 @@
       <c r="AL38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM38" s="1" t="s">
-        <v>26</v>
+      <c r="AM38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ38" s="2" t="s">
-        <v>25</v>
+      <c r="AO38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ38" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="C39" s="3">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="E39" s="3">
         <v>-50</v>
       </c>
       <c r="F39" s="3">
-        <v>20</v>
-      </c>
-      <c r="G39" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>5</v>
+        <v>150</v>
+      </c>
+      <c r="I39" s="3">
+        <v>18</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>440</v>
+        <v>331</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>25</v>
@@ -10935,20 +10938,20 @@
       <c r="X39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y39" s="2" t="s">
-        <v>25</v>
+      <c r="Y39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC39" s="2" t="s">
-        <v>25</v>
+      <c r="AA39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC39" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD39" s="2" t="s">
         <v>25</v>
@@ -10956,17 +10959,17 @@
       <c r="AE39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG39" s="1" t="s">
-        <v>26</v>
+      <c r="AF39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI39" s="1" t="s">
-        <v>26</v>
+      <c r="AI39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ39" s="2" t="s">
         <v>25</v>
@@ -10974,14 +10977,14 @@
       <c r="AK39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL39" s="1" t="s">
-        <v>26</v>
+      <c r="AL39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN39" s="1" t="s">
-        <v>26</v>
+      <c r="AN39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO39" s="2" t="s">
         <v>25</v>
@@ -11001,37 +11004,28 @@
         <v>20</v>
       </c>
       <c r="C40" s="3">
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="D40" s="3">
         <v>0.25</v>
       </c>
       <c r="E40" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F40" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G40" s="3">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>26</v>
+      <c r="P40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>25</v>
@@ -11039,41 +11033,41 @@
       <c r="S40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA40" s="1" t="s">
-        <v>26</v>
+      <c r="T40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC40" s="1" t="s">
-        <v>26</v>
+      <c r="AC40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE40" s="2" t="s">
-        <v>25</v>
+      <c r="AE40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AF40" s="2" t="s">
         <v>25</v>
@@ -11090,20 +11084,20 @@
       <c r="AJ40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK40" s="1" t="s">
-        <v>26</v>
+      <c r="AK40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM40" s="2" t="s">
-        <v>25</v>
+      <c r="AM40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AN40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO40" s="2" t="s">
-        <v>25</v>
+      <c r="AO40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP40" s="2" t="s">
         <v>25</v>
@@ -11114,35 +11108,38 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C41" s="3">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F41" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H41" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J41" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="P41" s="2" t="s">
         <v>25</v>
       </c>
@@ -11155,17 +11152,17 @@
       <c r="S41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W41" s="1" t="s">
-        <v>26</v>
+      <c r="T41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X41" s="2" t="s">
         <v>25</v>
@@ -11173,8 +11170,8 @@
       <c r="Y41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z41" s="1" t="s">
-        <v>26</v>
+      <c r="Z41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA41" s="2" t="s">
         <v>25</v>
@@ -11188,8 +11185,8 @@
       <c r="AD41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE41" s="1" t="s">
-        <v>26</v>
+      <c r="AE41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>26</v>
@@ -11212,14 +11209,14 @@
       <c r="AL41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM41" s="1" t="s">
-        <v>26</v>
+      <c r="AM41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO41" s="1" t="s">
-        <v>26</v>
+      <c r="AO41" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP41" s="2" t="s">
         <v>25</v>
@@ -11230,29 +11227,38 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="3">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="D42" s="3">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="E42" s="3">
-        <v>90</v>
+        <v>-50</v>
       </c>
       <c r="F42" s="3">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G42" s="3">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>451</v>
       </c>
+      <c r="M42" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="P42" s="1" t="s">
         <v>26</v>
       </c>
@@ -11265,17 +11271,17 @@
       <c r="S42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W42" s="1" t="s">
-        <v>26</v>
+      <c r="T42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X42" s="1" t="s">
         <v>26</v>
@@ -11283,14 +11289,14 @@
       <c r="Y42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z42" s="1" t="s">
-        <v>26</v>
+      <c r="Z42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB42" s="1" t="s">
-        <v>26</v>
+      <c r="AB42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC42" s="1" t="s">
         <v>26</v>
@@ -11298,20 +11304,20 @@
       <c r="AD42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG42" s="1" t="s">
-        <v>26</v>
+      <c r="AE42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI42" s="1" t="s">
-        <v>26</v>
+      <c r="AI42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ42" s="2" t="s">
         <v>25</v>
@@ -11319,17 +11325,17 @@
       <c r="AK42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO42" s="1" t="s">
-        <v>26</v>
+      <c r="AL42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP42" s="2" t="s">
         <v>25</v>
@@ -11340,33 +11346,33 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="3">
+        <v>220</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3">
+        <v>70</v>
+      </c>
+      <c r="G43" s="3">
         <v>20</v>
       </c>
-      <c r="C43" s="3">
-        <v>190</v>
-      </c>
-      <c r="D43" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="E43" s="3">
-        <v>-50</v>
-      </c>
-      <c r="F43" s="3">
-        <v>20</v>
-      </c>
-      <c r="G43" s="3">
-        <v>37</v>
+      <c r="H43" s="3">
+        <v>8</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="L43" s="3" t="s">
         <v>455</v>
       </c>
       <c r="P43" s="2" t="s">
@@ -11381,53 +11387,53 @@
       <c r="S43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>25</v>
+      <c r="T43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC43" s="1" t="s">
-        <v>26</v>
+      <c r="Y43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC43" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG43" s="2" t="s">
-        <v>25</v>
+      <c r="AE43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG43" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI43" s="2" t="s">
-        <v>25</v>
+      <c r="AI43" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ43" s="2" t="s">
         <v>25</v>
@@ -11435,17 +11441,17 @@
       <c r="AK43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO43" s="2" t="s">
-        <v>25</v>
+      <c r="AL43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO43" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP43" s="2" t="s">
         <v>25</v>
@@ -11459,34 +11465,31 @@
         <v>456</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C44" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D44" s="3">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="E44" s="3">
-        <v>-60</v>
+        <v>90</v>
       </c>
       <c r="F44" s="3">
-        <v>-45</v>
+        <v>140</v>
       </c>
       <c r="G44" s="3">
-        <v>35</v>
-      </c>
-      <c r="H44" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="P44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>25</v>
+      <c r="P44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>25</v>
@@ -11494,32 +11497,32 @@
       <c r="S44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X44" s="2" t="s">
-        <v>25</v>
+      <c r="T44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z44" s="2" t="s">
-        <v>25</v>
+      <c r="Z44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB44" s="2" t="s">
-        <v>25</v>
+      <c r="AB44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC44" s="1" t="s">
         <v>26</v>
@@ -11527,38 +11530,38 @@
       <c r="AD44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG44" s="2" t="s">
-        <v>25</v>
+      <c r="AE44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI44" s="2" t="s">
-        <v>25</v>
+      <c r="AI44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO44" s="2" t="s">
-        <v>25</v>
+      <c r="AK44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO44" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP44" s="2" t="s">
         <v>25</v>
@@ -11575,10 +11578,10 @@
         <v>20</v>
       </c>
       <c r="C45" s="3">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="D45" s="3">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="E45" s="3">
         <v>-50</v>
@@ -11587,7 +11590,7 @@
         <v>20</v>
       </c>
       <c r="G45" s="3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>459</v>
@@ -11598,9 +11601,6 @@
       <c r="L45" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="P45" s="2" t="s">
         <v>25</v>
       </c>
@@ -11613,53 +11613,53 @@
       <c r="S45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W45" s="1" t="s">
-        <v>26</v>
+      <c r="T45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC45" s="2" t="s">
-        <v>25</v>
+      <c r="Y45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC45" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG45" s="1" t="s">
-        <v>26</v>
+      <c r="AE45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI45" s="1" t="s">
-        <v>26</v>
+      <c r="AI45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ45" s="2" t="s">
         <v>25</v>
@@ -11667,17 +11667,17 @@
       <c r="AK45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO45" s="1" t="s">
-        <v>26</v>
+      <c r="AL45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP45" s="2" t="s">
         <v>25</v>
@@ -11688,43 +11688,37 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="3">
+        <v>34</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="E46" s="3">
+        <v>-60</v>
+      </c>
+      <c r="F46" s="3">
+        <v>-45</v>
+      </c>
+      <c r="G46" s="3">
+        <v>35</v>
+      </c>
+      <c r="H46" s="3">
+        <v>10</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="3">
-        <v>210</v>
-      </c>
-      <c r="D46" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="E46" s="3">
-        <v>-50</v>
-      </c>
-      <c r="F46" s="3">
-        <v>20</v>
-      </c>
-      <c r="G46" s="3">
-        <v>38</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>25</v>
+      <c r="P46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R46" s="2" t="s">
         <v>25</v>
@@ -11732,32 +11726,32 @@
       <c r="S46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X46" s="2" t="s">
-        <v>25</v>
+      <c r="T46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z46" s="2" t="s">
-        <v>25</v>
+      <c r="Z46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB46" s="2" t="s">
-        <v>25</v>
+      <c r="AB46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC46" s="1" t="s">
         <v>26</v>
@@ -11765,38 +11759,38 @@
       <c r="AD46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG46" s="2" t="s">
-        <v>25</v>
+      <c r="AE46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI46" s="2" t="s">
-        <v>25</v>
+      <c r="AI46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO46" s="2" t="s">
-        <v>25</v>
+      <c r="AK46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO46" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP46" s="2" t="s">
         <v>25</v>
@@ -11807,16 +11801,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C47" s="3">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D47" s="3">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="E47" s="3">
         <v>-50</v>
@@ -11825,19 +11819,19 @@
         <v>20</v>
       </c>
       <c r="G47" s="3">
-        <v>42</v>
-      </c>
-      <c r="H47" s="3">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>471</v>
+        <v>467</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>25</v>
@@ -11851,53 +11845,53 @@
       <c r="S47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W47" s="2" t="s">
-        <v>25</v>
+      <c r="T47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC47" s="1" t="s">
-        <v>26</v>
+      <c r="Y47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG47" s="2" t="s">
-        <v>25</v>
+      <c r="AE47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG47" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI47" s="2" t="s">
-        <v>25</v>
+      <c r="AI47" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ47" s="2" t="s">
         <v>25</v>
@@ -11905,17 +11899,17 @@
       <c r="AK47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO47" s="2" t="s">
-        <v>25</v>
+      <c r="AL47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO47" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP47" s="2" t="s">
         <v>25</v>
@@ -11926,16 +11920,16 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C48" s="3">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="D48" s="3">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="E48" s="3">
         <v>-50</v>
@@ -11944,16 +11938,19 @@
         <v>20</v>
       </c>
       <c r="G48" s="3">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J48" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>25</v>
@@ -12042,34 +12039,43 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="3">
+        <v>270</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="E49" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F49" s="3">
+        <v>20</v>
+      </c>
+      <c r="G49" s="3">
+        <v>42</v>
+      </c>
+      <c r="H49" s="3">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="3">
-        <v>120</v>
-      </c>
-      <c r="D49" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E49" s="3">
-        <v>-20</v>
-      </c>
-      <c r="F49" s="3">
-        <v>-5</v>
-      </c>
-      <c r="G49" s="3">
-        <v>15</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>26</v>
+      <c r="L49" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>25</v>
@@ -12089,23 +12095,23 @@
       <c r="W49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y49" s="2" t="s">
-        <v>25</v>
+      <c r="X49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC49" s="2" t="s">
-        <v>25</v>
+      <c r="AA49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC49" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD49" s="2" t="s">
         <v>25</v>
@@ -12113,32 +12119,32 @@
       <c r="AE49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG49" s="1" t="s">
-        <v>26</v>
+      <c r="AF49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI49" s="1" t="s">
-        <v>26</v>
+      <c r="AI49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL49" s="1" t="s">
-        <v>26</v>
+      <c r="AK49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN49" s="1" t="s">
-        <v>26</v>
+      <c r="AN49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO49" s="2" t="s">
         <v>25</v>
@@ -12152,13 +12158,13 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="3">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="D50" s="3">
         <v>0.27</v>
@@ -12170,16 +12176,16 @@
         <v>20</v>
       </c>
       <c r="G50" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>25</v>
@@ -12208,20 +12214,20 @@
       <c r="X50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y50" s="2" t="s">
-        <v>25</v>
+      <c r="Y50" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC50" s="2" t="s">
-        <v>25</v>
+      <c r="AA50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC50" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD50" s="2" t="s">
         <v>25</v>
@@ -12229,17 +12235,17 @@
       <c r="AE50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG50" s="1" t="s">
-        <v>26</v>
+      <c r="AF50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI50" s="1" t="s">
-        <v>26</v>
+      <c r="AI50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ50" s="2" t="s">
         <v>25</v>
@@ -12247,14 +12253,14 @@
       <c r="AK50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL50" s="1" t="s">
-        <v>26</v>
+      <c r="AL50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN50" s="1" t="s">
-        <v>26</v>
+      <c r="AN50" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO50" s="2" t="s">
         <v>25</v>
@@ -12268,34 +12274,28 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C51" s="3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D51" s="3">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F51" s="3">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="G51" s="3">
-        <v>24</v>
-      </c>
-      <c r="H51" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>483</v>
+        <v>100</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>26</v>
@@ -12309,17 +12309,17 @@
       <c r="S51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W51" s="1" t="s">
-        <v>26</v>
+      <c r="T51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X51" s="1" t="s">
         <v>26</v>
@@ -12327,14 +12327,14 @@
       <c r="Y51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z51" s="1" t="s">
-        <v>26</v>
+      <c r="Z51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB51" s="2" t="s">
-        <v>25</v>
+      <c r="AB51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC51" s="2" t="s">
         <v>25</v>
@@ -12342,20 +12342,20 @@
       <c r="AD51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG51" s="2" t="s">
-        <v>25</v>
+      <c r="AE51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI51" s="2" t="s">
-        <v>25</v>
+      <c r="AI51" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ51" s="2" t="s">
         <v>25</v>
@@ -12363,17 +12363,17 @@
       <c r="AK51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO51" s="1" t="s">
-        <v>26</v>
+      <c r="AL51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP51" s="2" t="s">
         <v>25</v>
@@ -12384,40 +12384,40 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="3">
+        <v>420</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="E52" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F52" s="3">
+        <v>20</v>
+      </c>
+      <c r="G52" s="3">
+        <v>25</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C52" s="3">
-        <v>140</v>
-      </c>
-      <c r="D52" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="E52" s="3">
-        <v>10</v>
-      </c>
-      <c r="F52" s="3">
-        <v>70</v>
-      </c>
-      <c r="G52" s="3">
-        <v>24</v>
-      </c>
-      <c r="H52" s="3">
-        <v>10</v>
-      </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>26</v>
+      <c r="P52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>25</v>
@@ -12437,8 +12437,8 @@
       <c r="W52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X52" s="1" t="s">
-        <v>26</v>
+      <c r="X52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>25</v>
@@ -12476,8 +12476,8 @@
       <c r="AJ52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK52" s="1" t="s">
-        <v>26</v>
+      <c r="AK52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AL52" s="1" t="s">
         <v>26</v>
@@ -12518,7 +12518,7 @@
         <v>70</v>
       </c>
       <c r="G53" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H53" s="3">
         <v>10</v>
@@ -12529,11 +12529,11 @@
       <c r="K53" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="P53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>25</v>
+      <c r="P53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>25</v>
@@ -12553,8 +12553,8 @@
       <c r="W53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X53" s="2" t="s">
-        <v>25</v>
+      <c r="X53" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>25</v>
@@ -12565,8 +12565,8 @@
       <c r="AA53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB53" s="1" t="s">
-        <v>26</v>
+      <c r="AB53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC53" s="2" t="s">
         <v>25</v>
@@ -12577,32 +12577,32 @@
       <c r="AE53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG53" s="1" t="s">
-        <v>26</v>
+      <c r="AF53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI53" s="1" t="s">
-        <v>26</v>
+      <c r="AI53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL53" s="1" t="s">
-        <v>26</v>
+      <c r="AK53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN53" s="1" t="s">
-        <v>26</v>
+      <c r="AN53" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO53" s="1" t="s">
         <v>26</v>
@@ -12619,25 +12619,31 @@
         <v>490</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C54" s="3">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="D54" s="3">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="E54" s="3">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="F54" s="3">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="G54" s="3">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="H54" s="3">
+        <v>10</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>23</v>
+        <v>491</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>26</v>
@@ -12675,8 +12681,8 @@
       <c r="AA54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB54" s="2" t="s">
-        <v>25</v>
+      <c r="AB54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC54" s="2" t="s">
         <v>25</v>
@@ -12687,17 +12693,17 @@
       <c r="AE54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG54" s="2" t="s">
-        <v>25</v>
+      <c r="AF54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI54" s="2" t="s">
-        <v>25</v>
+      <c r="AI54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ54" s="2" t="s">
         <v>25</v>
@@ -12705,14 +12711,14 @@
       <c r="AK54" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL54" s="2" t="s">
-        <v>25</v>
+      <c r="AL54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN54" s="2" t="s">
-        <v>25</v>
+      <c r="AN54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO54" s="2" t="s">
         <v>25</v>
@@ -12726,16 +12732,16 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C55" s="3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D55" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E55" s="3">
         <v>-20</v>
@@ -12747,13 +12753,13 @@
         <v>15</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>25</v>
@@ -12761,32 +12767,32 @@
       <c r="S55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X55" s="2" t="s">
-        <v>25</v>
+      <c r="T55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X55" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z55" s="1" t="s">
-        <v>26</v>
+      <c r="Z55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB55" s="1" t="s">
-        <v>26</v>
+      <c r="AB55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC55" s="2" t="s">
         <v>25</v>
@@ -12794,38 +12800,38 @@
       <c r="AD55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG55" s="1" t="s">
-        <v>26</v>
+      <c r="AE55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI55" s="1" t="s">
-        <v>26</v>
+      <c r="AI55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO55" s="1" t="s">
-        <v>26</v>
+      <c r="AK55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO55" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP55" s="2" t="s">
         <v>25</v>
@@ -12836,38 +12842,29 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C56" s="3">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="D56" s="3">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="E56" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F56" s="3">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G56" s="3">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="K56" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="P56" s="2" t="s">
         <v>25</v>
       </c>
@@ -12880,53 +12877,53 @@
       <c r="S56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W56" s="2" t="s">
-        <v>25</v>
+      <c r="T56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC56" s="1" t="s">
-        <v>26</v>
+      <c r="Y56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC56" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG56" s="2" t="s">
-        <v>25</v>
+      <c r="AE56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI56" s="2" t="s">
-        <v>25</v>
+      <c r="AI56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ56" s="2" t="s">
         <v>25</v>
@@ -12934,17 +12931,17 @@
       <c r="AK56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO56" s="2" t="s">
-        <v>25</v>
+      <c r="AL56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO56" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP56" s="2" t="s">
         <v>25</v>
@@ -12955,40 +12952,43 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="3">
+        <v>230</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="E57" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F57" s="3">
+        <v>20</v>
+      </c>
+      <c r="G57" s="3">
+        <v>27</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C57" s="3">
-        <v>150</v>
-      </c>
-      <c r="D57" s="3">
-        <v>0.28</v>
-      </c>
-      <c r="E57" s="3">
-        <v>10</v>
-      </c>
-      <c r="F57" s="3">
-        <v>70</v>
-      </c>
-      <c r="G57" s="3">
-        <v>21</v>
-      </c>
-      <c r="H57" s="3">
-        <v>10</v>
-      </c>
-      <c r="J57" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="L57" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>26</v>
+      <c r="M57" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>25</v>
@@ -13008,23 +13008,23 @@
       <c r="W57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y57" s="2" t="s">
-        <v>25</v>
+      <c r="X57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC57" s="2" t="s">
-        <v>25</v>
+      <c r="AA57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC57" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD57" s="2" t="s">
         <v>25</v>
@@ -13032,32 +13032,32 @@
       <c r="AE57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG57" s="1" t="s">
-        <v>26</v>
+      <c r="AF57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI57" s="1" t="s">
-        <v>26</v>
+      <c r="AI57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL57" s="1" t="s">
-        <v>26</v>
+      <c r="AK57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN57" s="1" t="s">
-        <v>26</v>
+      <c r="AN57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO57" s="2" t="s">
         <v>25</v>
@@ -13074,24 +13074,24 @@
         <v>500</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C58" s="3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D58" s="3">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E58" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3">
-        <v>20</v>
+        <v>70</v>
+      </c>
+      <c r="G58" s="3">
+        <v>21</v>
       </c>
       <c r="H58" s="3">
-        <v>60</v>
-      </c>
-      <c r="I58" s="3">
         <v>10</v>
       </c>
       <c r="J58" s="3" t="s">
@@ -13100,17 +13100,11 @@
       <c r="K58" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q58" s="2" t="s">
-        <v>25</v>
+      <c r="P58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R58" s="2" t="s">
         <v>25</v>
@@ -13130,23 +13124,23 @@
       <c r="W58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y58" s="1" t="s">
-        <v>26</v>
+      <c r="X58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC58" s="1" t="s">
-        <v>26</v>
+      <c r="AA58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD58" s="2" t="s">
         <v>25</v>
@@ -13154,32 +13148,32 @@
       <c r="AE58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG58" s="2" t="s">
-        <v>25</v>
+      <c r="AF58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI58" s="2" t="s">
-        <v>25</v>
+      <c r="AI58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL58" s="2" t="s">
-        <v>25</v>
+      <c r="AK58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN58" s="2" t="s">
-        <v>25</v>
+      <c r="AN58" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO58" s="2" t="s">
         <v>25</v>
@@ -13193,13 +13187,13 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C59" s="3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D59" s="3">
         <v>0.27</v>
@@ -13210,26 +13204,29 @@
       <c r="F59" s="3">
         <v>20</v>
       </c>
-      <c r="G59" s="3">
-        <v>37</v>
+      <c r="H59" s="3">
+        <v>60</v>
+      </c>
+      <c r="I59" s="3">
+        <v>10</v>
       </c>
       <c r="J59" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>26</v>
+      <c r="P59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>25</v>
@@ -13249,23 +13246,23 @@
       <c r="W59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>25</v>
+      <c r="X59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC59" s="2" t="s">
-        <v>25</v>
+      <c r="AA59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC59" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD59" s="2" t="s">
         <v>25</v>
@@ -13273,32 +13270,32 @@
       <c r="AE59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG59" s="1" t="s">
-        <v>26</v>
+      <c r="AF59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI59" s="1" t="s">
-        <v>26</v>
+      <c r="AI59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL59" s="1" t="s">
-        <v>26</v>
+      <c r="AK59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AM59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN59" s="1" t="s">
-        <v>26</v>
+      <c r="AN59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AO59" s="2" t="s">
         <v>25</v>
@@ -13312,29 +13309,38 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C60" s="3">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="D60" s="3">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
       <c r="E60" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F60" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G60" s="3">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J60" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>510</v>
       </c>
+      <c r="L60" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="P60" s="1" t="s">
         <v>26</v>
       </c>
@@ -13371,8 +13377,8 @@
       <c r="AA60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB60" s="2" t="s">
-        <v>25</v>
+      <c r="AB60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC60" s="2" t="s">
         <v>25</v>
@@ -13383,17 +13389,17 @@
       <c r="AE60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AF60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG60" s="2" t="s">
-        <v>25</v>
+      <c r="AF60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI60" s="2" t="s">
-        <v>25</v>
+      <c r="AI60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ60" s="2" t="s">
         <v>25</v>
@@ -13401,14 +13407,14 @@
       <c r="AK60" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL60" s="2" t="s">
-        <v>25</v>
+      <c r="AL60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AN60" s="2" t="s">
-        <v>25</v>
+      <c r="AN60" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO60" s="2" t="s">
         <v>25</v>
@@ -13422,40 +13428,34 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C61" s="3">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="D61" s="3">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="E61" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F61" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G61" s="3">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="K61" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="L61" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>25</v>
+      <c r="P61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>25</v>
@@ -13463,41 +13463,41 @@
       <c r="S61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA61" s="1" t="s">
-        <v>26</v>
+      <c r="T61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AB61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC61" s="1" t="s">
-        <v>26</v>
+      <c r="AC61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AD61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE61" s="1" t="s">
-        <v>26</v>
+      <c r="AE61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF61" s="2" t="s">
         <v>25</v>
@@ -13514,20 +13514,20 @@
       <c r="AJ61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK61" s="2" t="s">
-        <v>25</v>
+      <c r="AK61" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AM61" s="1" t="s">
-        <v>26</v>
+      <c r="AM61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AO61" s="1" t="s">
-        <v>26</v>
+      <c r="AO61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP61" s="2" t="s">
         <v>25</v>
@@ -13538,38 +13538,35 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3">
+        <v>240</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="E62" s="3">
+        <v>-50</v>
+      </c>
+      <c r="F62" s="3">
+        <v>20</v>
+      </c>
+      <c r="G62" s="3">
+        <v>37</v>
+      </c>
+      <c r="J62" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C62" s="3">
-        <v>130</v>
-      </c>
-      <c r="D62" s="3">
-        <v>0.28</v>
-      </c>
-      <c r="E62" s="3">
-        <v>10</v>
-      </c>
-      <c r="F62" s="3">
-        <v>70</v>
-      </c>
-      <c r="G62" s="3">
-        <v>25</v>
-      </c>
-      <c r="H62" s="3">
-        <v>10</v>
-      </c>
-      <c r="J62" s="3" t="s">
+      <c r="K62" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="L62" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>518</v>
-      </c>
       <c r="P62" s="2" t="s">
         <v>25</v>
       </c>
@@ -13597,20 +13594,20 @@
       <c r="X62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y62" s="2" t="s">
-        <v>25</v>
+      <c r="Y62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Z62" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA62" s="2" t="s">
-        <v>25</v>
+      <c r="AA62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AB62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC62" s="2" t="s">
-        <v>25</v>
+      <c r="AC62" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AD62" s="2" t="s">
         <v>25</v>
@@ -13657,38 +13654,38 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="3">
+        <v>170</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="E63" s="3">
+        <v>10</v>
+      </c>
+      <c r="F63" s="3">
+        <v>70</v>
+      </c>
+      <c r="G63" s="3">
+        <v>25</v>
+      </c>
+      <c r="H63" s="3">
+        <v>10</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="3">
-        <v>290</v>
-      </c>
-      <c r="D63" s="3">
-        <v>0.27</v>
-      </c>
-      <c r="E63" s="3">
-        <v>-50</v>
-      </c>
-      <c r="F63" s="3">
-        <v>20</v>
-      </c>
-      <c r="G63" s="3">
-        <v>31</v>
-      </c>
-      <c r="J63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="L63" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="L63" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>522</v>
-      </c>
       <c r="P63" s="2" t="s">
         <v>25</v>
       </c>
@@ -13701,17 +13698,17 @@
       <c r="S63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W63" s="2" t="s">
-        <v>25</v>
+      <c r="T63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="X63" s="2" t="s">
         <v>25</v>
@@ -13719,14 +13716,14 @@
       <c r="Y63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z63" s="2" t="s">
-        <v>25</v>
+      <c r="Z63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB63" s="1" t="s">
-        <v>26</v>
+      <c r="AB63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC63" s="2" t="s">
         <v>25</v>
@@ -13734,20 +13731,20 @@
       <c r="AD63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG63" s="1" t="s">
-        <v>26</v>
+      <c r="AE63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI63" s="1" t="s">
-        <v>26</v>
+      <c r="AI63" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ63" s="2" t="s">
         <v>25</v>
@@ -13755,17 +13752,17 @@
       <c r="AK63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO63" s="2" t="s">
-        <v>25</v>
+      <c r="AL63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO63" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP63" s="2" t="s">
         <v>25</v>
@@ -13776,29 +13773,38 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C64" s="3">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="D64" s="3">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="E64" s="3">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F64" s="3">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G64" s="3">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J64" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="K64" s="3" t="s">
         <v>524</v>
       </c>
+      <c r="L64" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="P64" s="2" t="s">
         <v>25</v>
       </c>
@@ -13811,17 +13817,17 @@
       <c r="S64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W64" s="1" t="s">
-        <v>26</v>
+      <c r="T64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="X64" s="2" t="s">
         <v>25</v>
@@ -13829,14 +13835,14 @@
       <c r="Y64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z64" s="1" t="s">
-        <v>26</v>
+      <c r="Z64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB64" s="2" t="s">
-        <v>25</v>
+      <c r="AB64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC64" s="2" t="s">
         <v>25</v>
@@ -13844,20 +13850,20 @@
       <c r="AD64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG64" s="2" t="s">
-        <v>25</v>
+      <c r="AE64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI64" s="2" t="s">
-        <v>25</v>
+      <c r="AI64" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ64" s="2" t="s">
         <v>25</v>
@@ -13865,17 +13871,17 @@
       <c r="AK64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO64" s="1" t="s">
-        <v>26</v>
+      <c r="AL64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO64" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP64" s="2" t="s">
         <v>25</v>
@@ -13886,43 +13892,34 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C65" s="3">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="D65" s="3">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="E65" s="3">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F65" s="3">
-        <v>70</v>
-      </c>
-      <c r="H65" s="3">
-        <v>60</v>
-      </c>
-      <c r="I65" s="3">
-        <v>10</v>
+        <v>-5</v>
+      </c>
+      <c r="G65" s="3">
+        <v>15</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>26</v>
+        <v>527</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="R65" s="2" t="s">
         <v>25</v>
@@ -13930,32 +13927,32 @@
       <c r="S65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X65" s="1" t="s">
-        <v>26</v>
+      <c r="T65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z65" s="2" t="s">
-        <v>25</v>
+      <c r="Z65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AA65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB65" s="1" t="s">
-        <v>26</v>
+      <c r="AB65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AC65" s="2" t="s">
         <v>25</v>
@@ -13963,38 +13960,38 @@
       <c r="AD65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG65" s="1" t="s">
-        <v>26</v>
+      <c r="AE65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AH65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI65" s="1" t="s">
-        <v>26</v>
+      <c r="AI65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AJ65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM65" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO65" s="2" t="s">
-        <v>25</v>
+      <c r="AK65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO65" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AP65" s="2" t="s">
         <v>25</v>
@@ -14005,40 +14002,43 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C66" s="3">
-        <v>280</v>
+        <v>170</v>
       </c>
       <c r="D66" s="3">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E66" s="3">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="F66" s="3">
-        <v>20</v>
-      </c>
-      <c r="G66" s="3">
-        <v>45</v>
+        <v>70</v>
+      </c>
+      <c r="H66" s="3">
+        <v>60</v>
+      </c>
+      <c r="I66" s="3">
+        <v>10</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q66" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R66" s="2" t="s">
         <v>25</v>
@@ -14046,26 +14046,26 @@
       <c r="S66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X66" s="2" t="s">
-        <v>25</v>
+      <c r="T66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Y66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z66" s="1" t="s">
-        <v>26</v>
+      <c r="Z66" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AA66" s="2" t="s">
         <v>25</v>
@@ -14079,8 +14079,8 @@
       <c r="AD66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE66" s="1" t="s">
-        <v>26</v>
+      <c r="AE66" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AF66" s="1" t="s">
         <v>26</v>
@@ -14097,20 +14097,20 @@
       <c r="AJ66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK66" s="2" t="s">
-        <v>25</v>
+      <c r="AK66" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AL66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AM66" s="1" t="s">
-        <v>26</v>
+      <c r="AM66" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AN66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AO66" s="1" t="s">
-        <v>26</v>
+      <c r="AO66" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="AP66" s="2" t="s">
         <v>25</v>
@@ -14124,30 +14124,30 @@
         <v>530</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C67" s="3">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="D67" s="3">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="E67" s="3">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F67" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G67" s="3">
-        <v>21</v>
-      </c>
-      <c r="H67" s="3">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>531</v>
       </c>
       <c r="K67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>532</v>
       </c>
       <c r="P67" s="2" t="s">
@@ -14186,8 +14186,8 @@
       <c r="AA67" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB67" s="2" t="s">
-        <v>25</v>
+      <c r="AB67" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AC67" s="2" t="s">
         <v>25</v>
@@ -14198,17 +14198,17 @@
       <c r="AE67" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF67" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG67" s="2" t="s">
-        <v>25</v>
+      <c r="AF67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG67" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AH67" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AI67" s="2" t="s">
-        <v>25</v>
+      <c r="AI67" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AJ67" s="2" t="s">
         <v>25</v>
@@ -14216,14 +14216,14 @@
       <c r="AK67" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AL67" s="2" t="s">
-        <v>25</v>
+      <c r="AL67" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AM67" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN67" s="2" t="s">
-        <v>25</v>
+      <c r="AN67" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="AO67" s="1" t="s">
         <v>26</v>
@@ -14939,10 +14939,10 @@
         <v>29</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>550</v>
@@ -15055,7 +15055,7 @@
         <v>15</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>26</v>
@@ -16215,7 +16215,7 @@
         <v>243</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>590</v>
@@ -16666,7 +16666,7 @@
         <v>603</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>604</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
   <si>
     <t>Materials</t>
   </si>
@@ -132,682 +132,679 @@
     <t>22%</t>
   </si>
   <si>
+    <t>#tfg:nether/is_lava_floes</t>
+  </si>
+  <si>
+    <t>beneath_gold</t>
+  </si>
+  <si>
+    <t>gold 50 [1] / pyrite 40 / chalcocite 20</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_lush_hollow</t>
+  </si>
+  <si>
+    <t>beneath_phlogopite</t>
+  </si>
+  <si>
+    <t>disc_vein</t>
+  </si>
+  <si>
+    <t>phlogopite 15 [1] / sulfur 7 / apatite 3</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_basalt_deltas</t>
+  </si>
+  <si>
+    <t>beneath_phosphate</t>
+  </si>
+  <si>
+    <t>tricalcium_phosphate 24 [1] / apatite 16 / pyrite 4</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_tar_pools</t>
+  </si>
+  <si>
+    <t>beneath_coal_bituminous</t>
+  </si>
+  <si>
+    <t>coal 18 [1] / pyrite 9</t>
+  </si>
+  <si>
+    <t>28%</t>
+  </si>
+  <si>
+    <t>beneath_coal_anthracite</t>
+  </si>
+  <si>
+    <t>anthracite 60 [1] / graphite 20</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_decaying_caverns</t>
+  </si>
+  <si>
+    <t>beneath_copper_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite 15 [1] / stibnite 9 / silver 3</t>
+  </si>
+  <si>
+    <t>beneath_iron_banded</t>
+  </si>
+  <si>
+    <t>goethite 15 [1] / yellow_limonite 12 / malachite 12</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_webbed_lair</t>
+  </si>
+  <si>
+    <t>beneath_nickel</t>
+  </si>
+  <si>
+    <t>pentlandite 24 [1] / garnierite 12 / cobaltite 8</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_thorny_brambles</t>
+  </si>
+  <si>
+    <t>beneath_iron_magnetite</t>
+  </si>
+  <si>
+    <t>pipe_vein</t>
+  </si>
+  <si>
+    <t>magnetite 16 [1] / vanadium_magnetite 6 / gold 2</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_geothermal_springs</t>
+  </si>
+  <si>
+    <t>beneath_graphite</t>
+  </si>
+  <si>
+    <t>graphite 16 [1] / coal 4 / diamond 2</t>
+  </si>
+  <si>
+    <t>beneath_manganese</t>
+  </si>
+  <si>
+    <t>pyrolusite 21 [1] / grossular 12 / tantalite 6</t>
+  </si>
+  <si>
+    <t>beneath_copper_sulfide</t>
+  </si>
+  <si>
+    <t>chalcocite 12 [1] / pyrite 8 / bornite 4</t>
+  </si>
+  <si>
+    <t>beneath_coal_lignite</t>
+  </si>
+  <si>
+    <t>lignite 50 [1]</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>beneath_psg</t>
+  </si>
+  <si>
+    <t>irarsite 30 [1] / ruarsite 28 / ferhodsite 22</t>
+  </si>
+  <si>
+    <t>18%</t>
+  </si>
+  <si>
+    <t>beneath_realgar</t>
+  </si>
+  <si>
+    <t>realgar 24 [1] / stibnite 12 / cinnabar 4</t>
+  </si>
+  <si>
+    <t>beneath_quartz</t>
+  </si>
+  <si>
+    <t>nether_quartz 32 [1] / quartzite 20 / barite 12 / zeolite 8</t>
+  </si>
+  <si>
+    <t>beneath_iron_hematite</t>
+  </si>
+  <si>
+    <t>hematite 14 [1] / goethite 6</t>
+  </si>
+  <si>
+    <t>beneath_gold_rich</t>
+  </si>
+  <si>
+    <t>gold 40 [1] / magnetite 30 / electrotine 20</t>
+  </si>
+  <si>
     <t>#tfg:nether/is_ash_forest</t>
   </si>
   <si>
-    <t>beneath_gold</t>
-  </si>
-  <si>
-    <t>gold 50 [1] / pyrite 40 / chalcocite 20</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_lush_hollow</t>
-  </si>
-  <si>
-    <t>beneath_phlogopite</t>
-  </si>
-  <si>
-    <t>phlogopite 15 [1] / sulfur 7 / apatite 3</t>
+    <t>beneath_lead_silver</t>
+  </si>
+  <si>
+    <t>galena 24 [1] / silver 12 / lead 6</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_salt_caves</t>
+  </si>
+  <si>
+    <t>beneath_salt</t>
+  </si>
+  <si>
+    <t>salt 70 [1] / rock_salt 50 / trona 20</t>
+  </si>
+  <si>
+    <t>beneath_copper_native</t>
+  </si>
+  <si>
+    <t>copper 18 [1] / malachite 6</t>
+  </si>
+  <si>
+    <t>beneath_aluminium</t>
+  </si>
+  <si>
+    <t>alunite 20 [1] / zeolite 12 / barite 8</t>
+  </si>
+  <si>
+    <t>beneath_bismuth</t>
+  </si>
+  <si>
+    <t>bismuth 20 [1] / sulfur 18 [1] / saltpeter 15</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>beneath_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur 18 [1] / pyrite 8 / stibnite 2</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>beneath_tin</t>
+  </si>
+  <si>
+    <t>cassiterite 14 [1] / tin 4</t>
+  </si>
+  <si>
+    <t>beneath_redstone</t>
+  </si>
+  <si>
+    <t>redstone 60 [1] / cinnabar 30 / nether_quartz 20 / ruby 10</t>
+  </si>
+  <si>
+    <t>andesite</t>
+  </si>
+  <si>
+    <t>dacite</t>
+  </si>
+  <si>
+    <t>flavolite</t>
+  </si>
+  <si>
+    <t>rhyolite</t>
+  </si>
+  <si>
+    <t>sandy_jadestone</t>
+  </si>
+  <si>
+    <t>venus_stone</t>
+  </si>
+  <si>
+    <t>venus_manual_salt</t>
+  </si>
+  <si>
+    <t>salt 80 / rock_salt 10 / lepidolite 5 / spodumene 5</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>venus_manual_sulfur</t>
+  </si>
+  <si>
+    <t>sulfur 80 / pyrite 15 / sphalerite 5</t>
+  </si>
+  <si>
+    <t>glacio_stone</t>
+  </si>
+  <si>
+    <t>moon_deepslate</t>
+  </si>
+  <si>
+    <t>moon_stone</t>
+  </si>
+  <si>
+    <t>moon_mica</t>
+  </si>
+  <si>
+    <t>kyanite 35 [1] / mica 25 / bauxite 25 / aluminium 15 / olivine 5</t>
+  </si>
+  <si>
+    <t>moon_gold</t>
+  </si>
+  <si>
+    <t>green_sapphire 5 / bauxite 20 / magnetite 20 / gold 55 [1]</t>
+  </si>
+  <si>
+    <t>moon_sphalerite</t>
+  </si>
+  <si>
+    <t>desh 10 / sphalerite 50 [1] / pyrite 40</t>
+  </si>
+  <si>
+    <t>moon_manganese</t>
+  </si>
+  <si>
+    <t>grossular 30 / spessartine 20 / pyrolusite 20 / tantalite 10</t>
+  </si>
+  <si>
+    <t>moon_cassiterite</t>
+  </si>
+  <si>
+    <t>chalcopyrite 30 [1] / zeolite 5 / cassiterite 35 [1] / tin 15</t>
+  </si>
+  <si>
+    <t>moon_desh</t>
+  </si>
+  <si>
+    <t>desh 25 / ilmenite 30 [1] / aluminium 25 / armalcolite 20</t>
+  </si>
+  <si>
+    <t>moon_magnetite</t>
+  </si>
+  <si>
+    <t>magnetite 25 / vanadium_magnetite 15 / chromite 40 [2] / gold 15 / sapphire 5</t>
+  </si>
+  <si>
+    <t>moon_redstone</t>
+  </si>
+  <si>
+    <t>redstone 45 [1] / ruby 35 / cinnabar 20 / olivine 5</t>
+  </si>
+  <si>
+    <t>moon_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite 40 [1] / copper 15 / stibnite 20 / chalcocite 25</t>
+  </si>
+  <si>
+    <t>moon_saltpeter</t>
+  </si>
+  <si>
+    <t>saltpeter 35 [1] / soapstone 25 / electrotine 45 / talc 15</t>
+  </si>
+  <si>
+    <t>moon_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite 35 [1] / ilmenite 40 [1] / armalcolite 20</t>
+  </si>
+  <si>
+    <t>moon_molybdenum</t>
+  </si>
+  <si>
+    <t>wulfenite 40 [1] / molybdenite 30 [1] / powellite 15 / olivine 5</t>
+  </si>
+  <si>
+    <t>moon_scheelite</t>
+  </si>
+  <si>
+    <t>scheelite 40 [1] / tungstate 50 [2] / lithium 10</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>moon_silver</t>
+  </si>
+  <si>
+    <t>galena 30 / silver 45 [1] / lead 25 / olivine 5</t>
+  </si>
+  <si>
+    <t>moon_graphite</t>
+  </si>
+  <si>
+    <t>graphite 50 [1] / diamond 35 / olivine 10</t>
+  </si>
+  <si>
+    <t>moon_quartz</t>
+  </si>
+  <si>
+    <t>quartzite 20 / certus_quartz 45 [2] / nether_quartz 30 [1] / barite 5</t>
+  </si>
+  <si>
+    <t>moon_topaz</t>
+  </si>
+  <si>
+    <t>blue_topaz 35 [1] / topaz 25 [1] / chalcocite 25 [1] / bornite 15</t>
+  </si>
+  <si>
+    <t>moon_pyrolusite</t>
+  </si>
+  <si>
+    <t>pyrolusite 40 [2] / cobaltite 25 / cobalt 25 / tantalite 15</t>
+  </si>
+  <si>
+    <t>moon_garnet</t>
+  </si>
+  <si>
+    <t>red_garnet 10 / yellow_garnet 15 / amethyst 40 [1] / opal 40 [1]</t>
+  </si>
+  <si>
+    <t>moon_garnierite</t>
+  </si>
+  <si>
+    <t>garnierite 25 [1] / nickel 20 / cobaltite 20 / pentlandite 25 [1] / cobalt 15</t>
+  </si>
+  <si>
+    <t>moon_beryllium</t>
+  </si>
+  <si>
+    <t>beryllium 35 [1] / emerald 50 [2] / thorium 1 / olivine 5 / rock_salt 20</t>
+  </si>
+  <si>
+    <t>moon_sheldonite</t>
+  </si>
+  <si>
+    <t>bornite 35 [1] / cooperite 25 / platinum 15 / nickel 25</t>
+  </si>
+  <si>
+    <t>moon_sapphire</t>
+  </si>
+  <si>
+    <t>almandine 35 [1] / pyrope 25 / sapphire 15 / green_sapphire 15 / olivine 2</t>
+  </si>
+  <si>
+    <t>moon_monazite</t>
+  </si>
+  <si>
+    <t>bastnasite 50 [1] / monazite 25 / neodymium 5 / olivine 1</t>
+  </si>
+  <si>
+    <t>moon_gypsum</t>
+  </si>
+  <si>
+    <t>borax 20 / calcite 25 / alunite 15 / gypsum 35 [1] / olivine 5</t>
+  </si>
+  <si>
+    <t>moon_apatite</t>
+  </si>
+  <si>
+    <t>apatite 25 / tricalcium_phosphate 35 / pyrochlore 40 [1] / olivine 5</t>
+  </si>
+  <si>
+    <t>moon_lubricant</t>
+  </si>
+  <si>
+    <t>soapstone 30 / talc 20 / glauconite_sand 25 / pentlandite 15 / trona 10</t>
+  </si>
+  <si>
+    <t>black_sand</t>
+  </si>
+  <si>
+    <t>brown_sand</t>
+  </si>
+  <si>
+    <t>chalk</t>
+  </si>
+  <si>
+    <t>chert</t>
+  </si>
+  <si>
+    <t>claystone</t>
+  </si>
+  <si>
+    <t>conglomerate</t>
+  </si>
+  <si>
+    <t>dolomite</t>
+  </si>
+  <si>
+    <t>green_sand</t>
+  </si>
+  <si>
+    <t>limestone</t>
+  </si>
+  <si>
+    <t>pink_sand</t>
+  </si>
+  <si>
+    <t>quartzite</t>
+  </si>
+  <si>
+    <t>red_sand</t>
+  </si>
+  <si>
+    <t>shale</t>
+  </si>
+  <si>
+    <t>white_sand</t>
+  </si>
+  <si>
+    <t>yellow_sand</t>
+  </si>
+  <si>
+    <t>deep_lazurite_calcite</t>
+  </si>
+  <si>
+    <t>lazurite 10 [1] / sodalite 8 / lapis 6 / calcite 6</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>sand_basaltic</t>
+  </si>
+  <si>
+    <t>basaltic_mineral_sand 8 / glauconite_sand 5 / garnet_sand 1</t>
+  </si>
+  <si>
+    <t>deep_graphite</t>
+  </si>
+  <si>
+    <t>graphite 14 [1] / coal 4 / diamond 2</t>
+  </si>
+  <si>
+    <t>normal_copper_gypsum</t>
+  </si>
+  <si>
+    <t>chalcocite 48 [1] / gypsum 12 / cobalt 20 / sulfur 8</t>
+  </si>
+  <si>
+    <t>#tfg:earth/is_karst</t>
+  </si>
+  <si>
+    <t>deep_tin</t>
+  </si>
+  <si>
+    <t>cassiterite 14 [1] / tin 2</t>
+  </si>
+  <si>
+    <t>deep_galena</t>
+  </si>
+  <si>
+    <t>galena 12 [1] / silver 6 / lead 5</t>
+  </si>
+  <si>
+    <t>normal_sphalerite</t>
+  </si>
+  <si>
+    <t>sphalerite 10 / galena 3</t>
+  </si>
+  <si>
+    <t>deep_bauxite</t>
+  </si>
+  <si>
+    <t>bauxite 6 / ilmenite 14 [1]</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>deep_copper_tin</t>
+  </si>
+  <si>
+    <t>chalcopyrite 7 / zeolite 3 / cassiterite 3</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>normal_asbestos_dry</t>
+  </si>
+  <si>
+    <t>cassiterite 6 / asbestos 1</t>
+  </si>
+  <si>
+    <t>#tfg:earth/is_dry</t>
+  </si>
+  <si>
+    <t>deep_thorianite</t>
+  </si>
+  <si>
+    <t>thorium 8 / uraninite 4 / emerald 2 / beryllium 4 [1]</t>
+  </si>
+  <si>
+    <t>21%</t>
+  </si>
+  <si>
+    <t>sand_tin</t>
+  </si>
+  <si>
+    <t>cassiterite_sand 1</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>normal_coal</t>
+  </si>
+  <si>
+    <t>lignite 70 [1] / coal 30</t>
+  </si>
+  <si>
+    <t>high_lead</t>
+  </si>
+  <si>
+    <t>lead 6 / silver 4</t>
+  </si>
+  <si>
+    <t>#tfg:earth/is_mountain</t>
+  </si>
+  <si>
+    <t>surface_mica</t>
+  </si>
+  <si>
+    <t>mica 100 [1]</t>
+  </si>
+  <si>
+    <t>deep_nickel</t>
+  </si>
+  <si>
+    <t>garnierite 14 [1] / nickel 8 / cobaltite 10 / pentlandite 6</t>
+  </si>
+  <si>
+    <t>high_tetrahedrite</t>
+  </si>
+  <si>
+    <t>tetrahedrite 50 [1] / copper 30 / stibnite 20</t>
+  </si>
+  <si>
+    <t>surface_gold</t>
+  </si>
+  <si>
+    <t>gold 1</t>
+  </si>
+  <si>
+    <t>surface_sphalerite</t>
+  </si>
+  <si>
+    <t>sphalerite 1</t>
+  </si>
+  <si>
+    <t>high_tin</t>
+  </si>
+  <si>
+    <t>tin 4 / cassiterite 6</t>
+  </si>
+  <si>
+    <t>surface_salpeter</t>
+  </si>
+  <si>
+    <t>saltpeter 100 [1]</t>
+  </si>
+  <si>
+    <t>high_coal</t>
+  </si>
+  <si>
+    <t>coal 50 [1]</t>
+  </si>
+  <si>
+    <t>deep_sapphire</t>
+  </si>
+  <si>
+    <t>almandine 8 [1] / pyrope 12 / sapphire 16 / green_sapphire 13</t>
+  </si>
+  <si>
+    <t>normal_copper</t>
+  </si>
+  <si>
+    <t>chalcopyrite 35 [1] / pyrite 20 / copper 10</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>high_bismuth_mountain</t>
+  </si>
+  <si>
+    <t>bismuth 1</t>
+  </si>
+  <si>
+    <t>high_realgar</t>
+  </si>
+  <si>
+    <t>chalcopyrite 40 [1] / zeolite 20 / realgar 10</t>
+  </si>
+  <si>
+    <t>#tfg:earth/is_hill</t>
+  </si>
+  <si>
+    <t>surface_native_copper</t>
+  </si>
+  <si>
+    <t>copper 100 [1]</t>
+  </si>
+  <si>
+    <t>normal_galena</t>
+  </si>
+  <si>
+    <t>galena 70 [1] / silver 20</t>
+  </si>
+  <si>
+    <t>surface_sylvite_salt</t>
+  </si>
+  <si>
+    <t>salt 6 / rock_salt 4</t>
+  </si>
+  <si>
+    <t>normal_salt</t>
+  </si>
+  <si>
+    <t>salt 60 [1] / rock_salt 30 / borax 10</t>
   </si>
   <si>
     <t>26%</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_basalt_deltas</t>
-  </si>
-  <si>
-    <t>beneath_phosphate</t>
-  </si>
-  <si>
-    <t>tricalcium_phosphate 24 [1] / apatite 16 / pyrite 4</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_tar_pools</t>
-  </si>
-  <si>
-    <t>beneath_coal_bituminous</t>
-  </si>
-  <si>
-    <t>coal 18 [1] / pyrite 9</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>beneath_coal_anthracite</t>
-  </si>
-  <si>
-    <t>anthracite 60 [1] / graphite 20</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_decaying_caverns</t>
-  </si>
-  <si>
-    <t>beneath_copper_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite 15 [1] / stibnite 9 / silver 3</t>
-  </si>
-  <si>
-    <t>beneath_iron_banded</t>
-  </si>
-  <si>
-    <t>goethite 15 [1] / yellow_limonite 12 / malachite 12</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_webbed_lair</t>
-  </si>
-  <si>
-    <t>beneath_nickel</t>
-  </si>
-  <si>
-    <t>pentlandite 24 [1] / garnierite 12 / cobaltite 8</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_thorny_brambles</t>
-  </si>
-  <si>
-    <t>beneath_iron_magnetite</t>
-  </si>
-  <si>
-    <t>pipe_vein</t>
-  </si>
-  <si>
-    <t>magnetite 16 [1] / vanadium_magnetite 6 / gold 2</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_geothermal_springs</t>
-  </si>
-  <si>
-    <t>beneath_graphite</t>
-  </si>
-  <si>
-    <t>graphite 16 [1] / coal 4 / diamond 2</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_lava_floes</t>
-  </si>
-  <si>
-    <t>beneath_manganese</t>
-  </si>
-  <si>
-    <t>pyrolusite 21 [1] / grossular 12 / tantalite 6</t>
-  </si>
-  <si>
-    <t>beneath_copper_sulfide</t>
-  </si>
-  <si>
-    <t>chalcocite 12 [1] / pyrite 8 / bornite 4</t>
-  </si>
-  <si>
-    <t>beneath_coal_lignite</t>
-  </si>
-  <si>
-    <t>lignite 50 [1]</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>beneath_psg</t>
-  </si>
-  <si>
-    <t>disc_vein</t>
-  </si>
-  <si>
-    <t>irarsite 30 [1] / ruarsite 28 / ferhodsite 22</t>
-  </si>
-  <si>
-    <t>19%</t>
-  </si>
-  <si>
-    <t>beneath_realgar</t>
-  </si>
-  <si>
-    <t>realgar 24 [1] / stibnite 12 / cinnabar 4</t>
-  </si>
-  <si>
-    <t>beneath_quartz</t>
-  </si>
-  <si>
-    <t>nether_quartz 32 [1] / quartzite 20 / barite 12 / zeolite 8</t>
-  </si>
-  <si>
-    <t>beneath_iron_hematite</t>
-  </si>
-  <si>
-    <t>hematite 14 [1] / goethite 6</t>
-  </si>
-  <si>
-    <t>beneath_gold_rich</t>
-  </si>
-  <si>
-    <t>gold 40 [1] / magnetite 30 / electrotine 20</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>beneath_lead_silver</t>
-  </si>
-  <si>
-    <t>galena 24 [1] / silver 12 / lead 6</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_salt_caves</t>
-  </si>
-  <si>
-    <t>beneath_salt</t>
-  </si>
-  <si>
-    <t>salt 70 [1] / rock_salt 50 / trona 20</t>
-  </si>
-  <si>
-    <t>beneath_copper_native</t>
-  </si>
-  <si>
-    <t>copper 18 [1] / malachite 6</t>
-  </si>
-  <si>
-    <t>beneath_aluminium</t>
-  </si>
-  <si>
-    <t>alunite 20 [1] / zeolite 12 / barite 8</t>
-  </si>
-  <si>
-    <t>beneath_bismuth</t>
-  </si>
-  <si>
-    <t>bismuth 20 [1] / sulfur 18 [1] / saltpeter 15</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>beneath_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur 18 [1] / pyrite 8 / stibnite 2</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>beneath_tin</t>
-  </si>
-  <si>
-    <t>cassiterite 14 [1] / tin 4</t>
-  </si>
-  <si>
-    <t>beneath_redstone</t>
-  </si>
-  <si>
-    <t>redstone 60 [1] / cinnabar 30 / nether_quartz 20 / ruby 10</t>
-  </si>
-  <si>
-    <t>andesite</t>
-  </si>
-  <si>
-    <t>dacite</t>
-  </si>
-  <si>
-    <t>flavolite</t>
-  </si>
-  <si>
-    <t>rhyolite</t>
-  </si>
-  <si>
-    <t>sandy_jadestone</t>
-  </si>
-  <si>
-    <t>venus_stone</t>
-  </si>
-  <si>
-    <t>venus_manual_salt</t>
-  </si>
-  <si>
-    <t>salt 80 / rock_salt 10 / lepidolite 5 / spodumene 5</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>venus_manual_sulfur</t>
-  </si>
-  <si>
-    <t>sulfur 80 / pyrite 15 / sphalerite 5</t>
-  </si>
-  <si>
-    <t>glacio_stone</t>
-  </si>
-  <si>
-    <t>moon_deepslate</t>
-  </si>
-  <si>
-    <t>moon_stone</t>
-  </si>
-  <si>
-    <t>moon_mica</t>
-  </si>
-  <si>
-    <t>kyanite 35 [1] / mica 25 / bauxite 25 / aluminium 15 / olivine 5</t>
-  </si>
-  <si>
-    <t>moon_gold</t>
-  </si>
-  <si>
-    <t>green_sapphire 5 / bauxite 20 / magnetite 20 / gold 55 [1]</t>
-  </si>
-  <si>
-    <t>moon_sphalerite</t>
-  </si>
-  <si>
-    <t>desh 10 / sphalerite 50 [1] / pyrite 40</t>
-  </si>
-  <si>
-    <t>moon_manganese</t>
-  </si>
-  <si>
-    <t>grossular 30 / spessartine 20 / pyrolusite 20 / tantalite 10</t>
-  </si>
-  <si>
-    <t>moon_cassiterite</t>
-  </si>
-  <si>
-    <t>chalcopyrite 30 [1] / zeolite 5 / cassiterite 35 [1] / tin 15</t>
-  </si>
-  <si>
-    <t>moon_desh</t>
-  </si>
-  <si>
-    <t>desh 25 / ilmenite 30 [1] / aluminium 25 / armalcolite 20</t>
-  </si>
-  <si>
-    <t>moon_magnetite</t>
-  </si>
-  <si>
-    <t>magnetite 25 / vanadium_magnetite 15 / chromite 40 [2] / gold 15 / sapphire 5</t>
-  </si>
-  <si>
-    <t>moon_redstone</t>
-  </si>
-  <si>
-    <t>redstone 45 [1] / ruby 35 / cinnabar 20 / olivine 5</t>
-  </si>
-  <si>
-    <t>moon_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite 40 [1] / copper 15 / stibnite 20 / chalcocite 25</t>
-  </si>
-  <si>
-    <t>moon_saltpeter</t>
-  </si>
-  <si>
-    <t>saltpeter 35 [1] / soapstone 25 / electrotine 45 / talc 15</t>
-  </si>
-  <si>
-    <t>moon_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite 35 [1] / ilmenite 40 [1] / armalcolite 20</t>
-  </si>
-  <si>
-    <t>moon_molybdenum</t>
-  </si>
-  <si>
-    <t>wulfenite 40 [1] / molybdenite 30 [1] / powellite 15 / olivine 5</t>
-  </si>
-  <si>
-    <t>moon_scheelite</t>
-  </si>
-  <si>
-    <t>scheelite 40 [1] / tungstate 50 [2] / lithium 10</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>moon_silver</t>
-  </si>
-  <si>
-    <t>galena 30 / silver 45 [1] / lead 25 / olivine 5</t>
-  </si>
-  <si>
-    <t>moon_graphite</t>
-  </si>
-  <si>
-    <t>graphite 50 [1] / diamond 35 / olivine 10</t>
-  </si>
-  <si>
-    <t>moon_quartz</t>
-  </si>
-  <si>
-    <t>quartzite 20 / certus_quartz 45 [2] / nether_quartz 30 [1] / barite 5</t>
-  </si>
-  <si>
-    <t>moon_topaz</t>
-  </si>
-  <si>
-    <t>blue_topaz 35 [1] / topaz 25 [1] / chalcocite 25 [1] / bornite 15</t>
-  </si>
-  <si>
-    <t>moon_pyrolusite</t>
-  </si>
-  <si>
-    <t>pyrolusite 40 [2] / cobaltite 25 / cobalt 25 / tantalite 15</t>
-  </si>
-  <si>
-    <t>moon_garnet</t>
-  </si>
-  <si>
-    <t>red_garnet 10 / yellow_garnet 15 / amethyst 40 [1] / opal 40 [1]</t>
-  </si>
-  <si>
-    <t>moon_garnierite</t>
-  </si>
-  <si>
-    <t>garnierite 25 [1] / nickel 20 / cobaltite 20 / pentlandite 25 [1] / cobalt 15</t>
-  </si>
-  <si>
-    <t>moon_beryllium</t>
-  </si>
-  <si>
-    <t>beryllium 35 [1] / emerald 50 [2] / thorium 1 / olivine 5 / rock_salt 20</t>
-  </si>
-  <si>
-    <t>moon_sheldonite</t>
-  </si>
-  <si>
-    <t>bornite 35 [1] / cooperite 25 / platinum 15 / nickel 25</t>
-  </si>
-  <si>
-    <t>moon_sapphire</t>
-  </si>
-  <si>
-    <t>almandine 35 [1] / pyrope 25 / sapphire 15 / green_sapphire 15 / olivine 2</t>
-  </si>
-  <si>
-    <t>moon_monazite</t>
-  </si>
-  <si>
-    <t>bastnasite 50 [1] / monazite 25 / neodymium 5 / olivine 1</t>
-  </si>
-  <si>
-    <t>moon_gypsum</t>
-  </si>
-  <si>
-    <t>borax 20 / calcite 25 / alunite 15 / gypsum 35 [1] / olivine 5</t>
-  </si>
-  <si>
-    <t>moon_apatite</t>
-  </si>
-  <si>
-    <t>apatite 25 / tricalcium_phosphate 35 / pyrochlore 40 [1] / olivine 5</t>
-  </si>
-  <si>
-    <t>moon_lubricant</t>
-  </si>
-  <si>
-    <t>soapstone 30 / talc 20 / glauconite_sand 25 / pentlandite 15 / trona 10</t>
-  </si>
-  <si>
-    <t>black_sand</t>
-  </si>
-  <si>
-    <t>brown_sand</t>
-  </si>
-  <si>
-    <t>chalk</t>
-  </si>
-  <si>
-    <t>chert</t>
-  </si>
-  <si>
-    <t>claystone</t>
-  </si>
-  <si>
-    <t>conglomerate</t>
-  </si>
-  <si>
-    <t>dolomite</t>
-  </si>
-  <si>
-    <t>green_sand</t>
-  </si>
-  <si>
-    <t>limestone</t>
-  </si>
-  <si>
-    <t>pink_sand</t>
-  </si>
-  <si>
-    <t>quartzite</t>
-  </si>
-  <si>
-    <t>red_sand</t>
-  </si>
-  <si>
-    <t>shale</t>
-  </si>
-  <si>
-    <t>white_sand</t>
-  </si>
-  <si>
-    <t>yellow_sand</t>
-  </si>
-  <si>
-    <t>deep_lazurite_calcite</t>
-  </si>
-  <si>
-    <t>lazurite 10 [1] / sodalite 8 / lapis 6 / calcite 6</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>sand_basaltic</t>
-  </si>
-  <si>
-    <t>basaltic_mineral_sand 8 / glauconite_sand 5 / garnet_sand 1</t>
-  </si>
-  <si>
-    <t>deep_graphite</t>
-  </si>
-  <si>
-    <t>graphite 14 [1] / coal 4 / diamond 2</t>
-  </si>
-  <si>
-    <t>normal_copper_gypsum</t>
-  </si>
-  <si>
-    <t>chalcocite 48 [1] / gypsum 12 / cobalt 20 / sulfur 8</t>
-  </si>
-  <si>
-    <t>#tfg:earth/is_karst</t>
-  </si>
-  <si>
-    <t>deep_tin</t>
-  </si>
-  <si>
-    <t>cassiterite 14 [1] / tin 2</t>
-  </si>
-  <si>
-    <t>deep_galena</t>
-  </si>
-  <si>
-    <t>galena 12 [1] / silver 6 / lead 5</t>
-  </si>
-  <si>
-    <t>normal_sphalerite</t>
-  </si>
-  <si>
-    <t>sphalerite 10 / galena 3</t>
-  </si>
-  <si>
-    <t>deep_bauxite</t>
-  </si>
-  <si>
-    <t>bauxite 6 / ilmenite 14 [1]</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>deep_copper_tin</t>
-  </si>
-  <si>
-    <t>chalcopyrite 7 / zeolite 3 / cassiterite 3</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>normal_asbestos_dry</t>
-  </si>
-  <si>
-    <t>cassiterite 6 / asbestos 1</t>
-  </si>
-  <si>
-    <t>#tfg:earth/is_dry</t>
-  </si>
-  <si>
-    <t>deep_thorianite</t>
-  </si>
-  <si>
-    <t>thorium 8 / uraninite 4 / emerald 2 / beryllium 4 [1]</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>sand_tin</t>
-  </si>
-  <si>
-    <t>cassiterite_sand 1</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>normal_coal</t>
-  </si>
-  <si>
-    <t>lignite 70 [1] / coal 30</t>
-  </si>
-  <si>
-    <t>high_lead</t>
-  </si>
-  <si>
-    <t>lead 6 / silver 4</t>
-  </si>
-  <si>
-    <t>#tfg:earth/is_mountain</t>
-  </si>
-  <si>
-    <t>surface_mica</t>
-  </si>
-  <si>
-    <t>mica 100 [1]</t>
-  </si>
-  <si>
-    <t>deep_nickel</t>
-  </si>
-  <si>
-    <t>garnierite 14 [1] / nickel 8 / cobaltite 10 / pentlandite 6</t>
-  </si>
-  <si>
-    <t>high_tetrahedrite</t>
-  </si>
-  <si>
-    <t>tetrahedrite 50 [1] / copper 30 / stibnite 20</t>
-  </si>
-  <si>
-    <t>surface_gold</t>
-  </si>
-  <si>
-    <t>gold 1</t>
-  </si>
-  <si>
-    <t>surface_sphalerite</t>
-  </si>
-  <si>
-    <t>sphalerite 1</t>
-  </si>
-  <si>
-    <t>high_tin</t>
-  </si>
-  <si>
-    <t>tin 4 / cassiterite 6</t>
-  </si>
-  <si>
-    <t>surface_salpeter</t>
-  </si>
-  <si>
-    <t>saltpeter 100 [1]</t>
-  </si>
-  <si>
-    <t>high_coal</t>
-  </si>
-  <si>
-    <t>coal 50 [1]</t>
-  </si>
-  <si>
-    <t>deep_sapphire</t>
-  </si>
-  <si>
-    <t>almandine 8 [1] / pyrope 12 / sapphire 16 / green_sapphire 13</t>
-  </si>
-  <si>
-    <t>normal_copper</t>
-  </si>
-  <si>
-    <t>chalcopyrite 35 [1] / pyrite 20 / copper 10</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>high_bismuth_mountain</t>
-  </si>
-  <si>
-    <t>bismuth 1</t>
-  </si>
-  <si>
-    <t>high_realgar</t>
-  </si>
-  <si>
-    <t>chalcopyrite 40 [1] / zeolite 20 / realgar 10</t>
-  </si>
-  <si>
-    <t>#tfg:earth/is_hill</t>
-  </si>
-  <si>
-    <t>surface_native_copper</t>
-  </si>
-  <si>
-    <t>copper 100 [1]</t>
-  </si>
-  <si>
-    <t>normal_galena</t>
-  </si>
-  <si>
-    <t>galena 70 [1] / silver 20</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>surface_sylvite_salt</t>
-  </si>
-  <si>
-    <t>salt 6 / rock_salt 4</t>
-  </si>
-  <si>
-    <t>normal_salt</t>
-  </si>
-  <si>
-    <t>salt 60 [1] / rock_salt 30 / borax 10</t>
   </si>
   <si>
     <t>#tfg:earth/is_shore_island</t>
@@ -1724,10 +1721,10 @@
         <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -1739,13 +1736,16 @@
         <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" s="3">
-        <v>26</v>
+        <v>45</v>
+      </c>
+      <c r="J5" s="3">
+        <v>10</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>34</v>
@@ -1789,13 +1789,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3">
         <v>80</v>
@@ -1813,7 +1813,7 @@
         <v>25</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -1857,13 +1857,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="3">
         <v>140</v>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="3">
         <v>29</v>
@@ -1925,13 +1925,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3">
         <v>140</v>
@@ -1940,7 +1940,7 @@
         <v>190</v>
       </c>
       <c r="G8" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -1949,7 +1949,7 @@
         <v>27</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>33</v>
@@ -1993,13 +1993,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3">
         <v>80</v>
@@ -2011,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I9" s="3">
         <v>25</v>
@@ -2061,13 +2061,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3">
         <v>140</v>
@@ -2079,13 +2079,13 @@
         <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I10" s="3">
         <v>31</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>33</v>
@@ -2129,13 +2129,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3">
         <v>80</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>33</v>
@@ -2197,13 +2197,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3">
         <v>80</v>
@@ -2215,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" s="3">
         <v>60</v>
@@ -2224,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -2268,13 +2268,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -2283,19 +2283,19 @@
         <v>80</v>
       </c>
       <c r="G13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="I13" s="3">
+        <v>50</v>
+      </c>
       <c r="J13" s="3">
-        <v>60</v>
-      </c>
-      <c r="K13" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>34</v>
@@ -2342,7 +2342,7 @@
         <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>71</v>
@@ -2366,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -2428,13 +2428,13 @@
         <v>10</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" s="3">
         <v>27</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>33</v>
@@ -2502,7 +2502,7 @@
         <v>25</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>33</v>
@@ -2549,10 +2549,10 @@
         <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -2561,19 +2561,19 @@
         <v>80</v>
       </c>
       <c r="G17" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I17" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J17" s="3">
         <v>10</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>34</v>
@@ -2617,13 +2617,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" s="3">
         <v>80</v>
@@ -2641,7 +2641,7 @@
         <v>23</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>33</v>
@@ -2685,13 +2685,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="D19" s="3">
         <v>80</v>
@@ -2712,7 +2712,7 @@
         <v>15</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>33</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" s="3">
         <v>80</v>
@@ -2774,13 +2774,13 @@
         <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I20" s="3">
         <v>29</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>33</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
@@ -2842,13 +2842,13 @@
         <v>10</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I21" s="3">
         <v>23</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>34</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D22" s="3">
         <v>140</v>
@@ -2916,7 +2916,7 @@
         <v>27</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>33</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D23" s="3">
         <v>140</v>
@@ -2978,7 +2978,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J23" s="3">
         <v>60</v>
@@ -2987,7 +2987,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>33</v>
@@ -3031,13 +3031,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="3">
         <v>80</v>
@@ -3099,13 +3099,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D25" s="3">
         <v>80</v>
@@ -3126,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>33</v>
@@ -3170,13 +3170,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="D26" s="3">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>10</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J26" s="3">
         <v>60</v>
@@ -3197,7 +3197,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>34</v>
@@ -3241,13 +3241,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
@@ -3259,13 +3259,13 @@
         <v>10</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I27" s="3">
         <v>29</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>34</v>
@@ -3309,13 +3309,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D28" s="3">
         <v>140</v>
@@ -3333,7 +3333,7 @@
         <v>25</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>33</v>
@@ -3377,13 +3377,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
@@ -3395,7 +3395,7 @@
         <v>10</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="J29" s="3">
         <v>60</v>
@@ -3404,7 +3404,7 @@
         <v>12</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>34</v>
@@ -3561,39 +3561,39 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D2" s="3">
         <v>40</v>
@@ -3605,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I2" s="3">
         <v>20</v>
@@ -3614,7 +3614,7 @@
         <v>6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>34</v>
@@ -3643,13 +3643,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="3">
         <v>40</v>
@@ -3661,13 +3661,13 @@
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I3" s="3">
         <v>20</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>34</v>
@@ -3809,13 +3809,13 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>18</v>
@@ -3824,30 +3824,30 @@
         <v>20</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>22</v>
       </c>
       <c r="W1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="X1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="Y1" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>35</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
@@ -3900,13 +3900,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="D3" s="3">
         <v>10</v>
@@ -3918,7 +3918,7 @@
         <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" s="3">
         <v>35</v>
@@ -3927,7 +3927,7 @@
         <v>10</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
@@ -3962,13 +3962,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
@@ -3980,13 +3980,13 @@
         <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I4" s="3">
         <v>35</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>34</v>
@@ -4021,13 +4021,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="3">
         <v>5</v>
@@ -4039,13 +4039,13 @@
         <v>215</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I5" s="3">
         <v>30</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>34</v>
@@ -4080,13 +4080,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3">
         <v>10</v>
@@ -4104,7 +4104,7 @@
         <v>35</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -4139,13 +4139,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
@@ -4157,13 +4157,13 @@
         <v>230</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3">
         <v>30</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>34</v>
@@ -4198,13 +4198,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -4222,7 +4222,7 @@
         <v>50</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>33</v>
@@ -4257,13 +4257,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D9" s="3">
         <v>20</v>
@@ -4275,13 +4275,13 @@
         <v>250</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I9" s="3">
         <v>35</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>34</v>
@@ -4316,13 +4316,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10" s="3">
         <v>50</v>
@@ -4340,7 +4340,7 @@
         <v>35</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>34</v>
@@ -4375,13 +4375,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>30</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>34</v>
@@ -4434,13 +4434,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>200</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I12" s="3">
         <v>40</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -4493,13 +4493,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -4511,13 +4511,13 @@
         <v>245</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I13" s="3">
         <v>35</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>33</v>
@@ -4552,13 +4552,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -4570,13 +4570,13 @@
         <v>200</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I14" s="3">
         <v>20</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -4611,13 +4611,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D15" s="3">
         <v>20</v>
@@ -4629,13 +4629,13 @@
         <v>210</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I15" s="3">
         <v>30</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>33</v>
@@ -4670,13 +4670,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>260</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J16" s="3">
         <v>60</v>
@@ -4697,7 +4697,7 @@
         <v>9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>33</v>
@@ -4732,13 +4732,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D17" s="3">
         <v>10</v>
@@ -4756,7 +4756,7 @@
         <v>45</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>34</v>
@@ -4791,13 +4791,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         <v>210</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3">
         <v>45</v>
@@ -4818,7 +4818,7 @@
         <v>16</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>34</v>
@@ -4853,13 +4853,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" s="3">
         <v>20</v>
@@ -4877,7 +4877,7 @@
         <v>35</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>34</v>
@@ -4912,13 +4912,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D20" s="3">
         <v>10</v>
@@ -4930,7 +4930,7 @@
         <v>230</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I20" s="3">
         <v>35</v>
@@ -4939,7 +4939,7 @@
         <v>7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>34</v>
@@ -4974,13 +4974,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D21" s="3">
         <v>5</v>
@@ -4992,13 +4992,13 @@
         <v>250</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I21" s="3">
         <v>45</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>33</v>
@@ -5033,13 +5033,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>260</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J22" s="3">
         <v>70</v>
@@ -5060,7 +5060,7 @@
         <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>33</v>
@@ -5095,13 +5095,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>30</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>34</v>
@@ -5154,13 +5154,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -5172,7 +5172,7 @@
         <v>280</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I24" s="3">
         <v>28</v>
@@ -5181,7 +5181,7 @@
         <v>8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>33</v>
@@ -5216,13 +5216,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D25" s="3">
         <v>0</v>
@@ -5234,13 +5234,13 @@
         <v>310</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I25" s="3">
         <v>40</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>34</v>
@@ -5275,13 +5275,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D26" s="3">
         <v>10</v>
@@ -5302,7 +5302,7 @@
         <v>9</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>33</v>
@@ -5337,13 +5337,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
@@ -5361,7 +5361,7 @@
         <v>35</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>33</v>
@@ -5396,13 +5396,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>30</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>33</v>
@@ -5568,37 +5568,37 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="W1" s="5" t="s">
-        <v>183</v>
-      </c>
       <c r="X1" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA1" s="5" t="s">
         <v>20</v>
@@ -5610,10 +5610,10 @@
         <v>22</v>
       </c>
       <c r="AD1" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>23</v>
@@ -5622,22 +5622,22 @@
         <v>24</v>
       </c>
       <c r="AH1" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="AI1" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="AJ1" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="AK1" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AL1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AN1" s="5" t="s">
         <v>26</v>
@@ -5646,21 +5646,21 @@
         <v>27</v>
       </c>
       <c r="AP1" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="D2" s="3">
         <v>-50</v>
@@ -5672,7 +5672,7 @@
         <v>130</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J2" s="3">
         <v>60</v>
@@ -5681,7 +5681,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
@@ -5770,13 +5770,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D3" s="3">
         <v>-5</v>
@@ -5791,13 +5791,13 @@
         <v>190</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I3" s="3">
         <v>34</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
@@ -5886,13 +5886,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="D4" s="3">
         <v>-64</v>
@@ -5904,7 +5904,7 @@
         <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I4" s="3">
         <v>16</v>
@@ -5913,7 +5913,7 @@
         <v>6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>34</v>
@@ -6002,13 +6002,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D5" s="3">
         <v>-30</v>
@@ -6020,7 +6020,7 @@
         <v>190</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3">
         <v>35</v>
@@ -6029,7 +6029,7 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>34</v>
@@ -6118,13 +6118,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="3">
         <v>-50</v>
@@ -6136,13 +6136,13 @@
         <v>210</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I6" s="3">
         <v>33</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -6231,13 +6231,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D7" s="3">
         <v>-50</v>
@@ -6249,13 +6249,13 @@
         <v>230</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I7" s="3">
         <v>24</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>33</v>
@@ -6344,13 +6344,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="D8" s="3">
         <v>10</v>
@@ -6362,7 +6362,7 @@
         <v>150</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" s="3">
         <v>18</v>
@@ -6371,7 +6371,7 @@
         <v>10</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>33</v>
@@ -6460,13 +6460,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" s="3">
         <v>-50</v>
@@ -6478,13 +6478,13 @@
         <v>420</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I9" s="3">
         <v>27</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>33</v>
@@ -6573,13 +6573,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D10" s="3">
         <v>-50</v>
@@ -6591,13 +6591,13 @@
         <v>210</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I10" s="3">
         <v>42</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>34</v>
@@ -6686,13 +6686,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="D11" s="3">
         <v>10</v>
@@ -6704,7 +6704,7 @@
         <v>130</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="3">
         <v>20</v>
@@ -6713,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>33</v>
@@ -6802,13 +6802,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D12" s="3">
         <v>-50</v>
@@ -6820,13 +6820,13 @@
         <v>270</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" s="3">
         <v>31</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -6915,13 +6915,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D13" s="3">
         <v>-5</v>
@@ -6936,13 +6936,13 @@
         <v>270</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I13" s="3">
         <v>15</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>33</v>
@@ -7031,13 +7031,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D14" s="3">
         <v>10</v>
@@ -7049,7 +7049,7 @@
         <v>230</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14" s="3">
         <v>34</v>
@@ -7058,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -7147,13 +7147,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D15" s="3">
         <v>-30</v>
@@ -7168,13 +7168,13 @@
         <v>60</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I15" s="3">
         <v>25</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>34</v>
@@ -7263,13 +7263,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D16" s="3">
         <v>-20</v>
@@ -7284,13 +7284,13 @@
         <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I16" s="3">
         <v>10</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>34</v>
@@ -7379,13 +7379,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D17" s="3">
         <v>-50</v>
@@ -7397,13 +7397,13 @@
         <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I17" s="3">
         <v>39</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>33</v>
@@ -7492,13 +7492,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D18" s="3">
         <v>-30</v>
@@ -7519,7 +7519,7 @@
         <v>25</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>34</v>
@@ -7608,13 +7608,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D19" s="3">
         <v>-20</v>
@@ -7635,7 +7635,7 @@
         <v>15</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>34</v>
@@ -7724,13 +7724,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D20" s="3">
         <v>-20</v>
@@ -7751,7 +7751,7 @@
         <v>15</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>34</v>
@@ -7840,13 +7840,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D21" s="3">
         <v>-50</v>
@@ -7867,7 +7867,7 @@
         <v>35</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>34</v>
@@ -7956,13 +7956,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D22" s="3">
         <v>-20</v>
@@ -7983,7 +7983,7 @@
         <v>20</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>34</v>
@@ -8072,13 +8072,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D23" s="3">
         <v>90</v>
@@ -8090,13 +8090,13 @@
         <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I23" s="3">
         <v>30</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>34</v>
@@ -8185,13 +8185,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D24" s="3">
         <v>-50</v>
@@ -8212,7 +8212,7 @@
         <v>10</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>33</v>
@@ -8301,13 +8301,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D25" s="3">
         <v>10</v>
@@ -8319,7 +8319,7 @@
         <v>130</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I25" s="3">
         <v>30</v>
@@ -8328,7 +8328,7 @@
         <v>10</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>33</v>
@@ -8417,13 +8417,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D26" s="3">
         <v>-30</v>
@@ -8444,7 +8444,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>34</v>
@@ -8533,13 +8533,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="D27" s="3">
         <v>-30</v>
@@ -8563,7 +8563,7 @@
         <v>12</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>34</v>
@@ -8652,13 +8652,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D28" s="3">
         <v>-20</v>
@@ -8673,13 +8673,13 @@
         <v>70</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3">
         <v>15</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>34</v>
@@ -8768,13 +8768,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D29" s="3">
         <v>10</v>
@@ -8786,7 +8786,7 @@
         <v>150</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="I29" s="3">
         <v>23</v>
@@ -8795,7 +8795,7 @@
         <v>10</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>34</v>
@@ -8884,13 +8884,13 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D30" s="3">
         <v>-20</v>
@@ -8905,13 +8905,13 @@
         <v>80</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I30" s="3">
         <v>15</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>33</v>
@@ -9000,13 +9000,13 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D31" s="3">
         <v>10</v>
@@ -9018,7 +9018,7 @@
         <v>190</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>44</v>
+        <v>262</v>
       </c>
       <c r="I31" s="3">
         <v>25</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>34</v>
@@ -9116,13 +9116,13 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D32" s="3">
         <v>-50</v>
@@ -9140,7 +9140,7 @@
         <v>27</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>33</v>
@@ -9229,13 +9229,13 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="D33" s="3">
         <v>10</v>
@@ -9247,7 +9247,7 @@
         <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I33" s="3">
         <v>21</v>
@@ -9256,7 +9256,7 @@
         <v>10</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>33</v>
@@ -9345,13 +9345,13 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D34" s="3">
         <v>-5</v>
@@ -9366,13 +9366,13 @@
         <v>190</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I34" s="3">
         <v>34</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>33</v>
@@ -9461,13 +9461,13 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D35" s="3">
         <v>10</v>
@@ -9479,7 +9479,7 @@
         <v>150</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I35" s="3">
         <v>32</v>
@@ -9488,7 +9488,7 @@
         <v>10</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>34</v>
@@ -9577,13 +9577,13 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="D36" s="3">
         <v>-60</v>
@@ -9595,7 +9595,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I36" s="3">
         <v>27</v>
@@ -9607,7 +9607,7 @@
         <v>34</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>33</v>
@@ -9696,13 +9696,13 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D37" s="3">
         <v>100</v>
@@ -9714,13 +9714,13 @@
         <v>30</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I37" s="3">
         <v>15</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>34</v>
@@ -9809,13 +9809,13 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="D38" s="3">
         <v>-30</v>
@@ -9827,7 +9827,7 @@
         <v>190</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J38" s="3">
         <v>30</v>
@@ -9836,7 +9836,7 @@
         <v>5</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>34</v>
@@ -9925,13 +9925,13 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="D39" s="3">
         <v>-50</v>
@@ -9943,7 +9943,7 @@
         <v>140</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J39" s="3">
         <v>150</v>
@@ -9952,7 +9952,7 @@
         <v>18</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>33</v>
@@ -10041,13 +10041,13 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D40" s="3">
         <v>-20</v>
@@ -10068,7 +10068,7 @@
         <v>15</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>33</v>
@@ -10157,13 +10157,13 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D41" s="3">
         <v>-50</v>
@@ -10175,7 +10175,7 @@
         <v>190</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3">
         <v>35</v>
@@ -10184,7 +10184,7 @@
         <v>5</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>33</v>
@@ -10273,13 +10273,13 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D42" s="3">
         <v>-50</v>
@@ -10297,7 +10297,7 @@
         <v>45</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>34</v>
@@ -10386,13 +10386,13 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="D43" s="3">
         <v>10</v>
@@ -10404,7 +10404,7 @@
         <v>220</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I43" s="3">
         <v>20</v>
@@ -10413,7 +10413,7 @@
         <v>8</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>33</v>
@@ -10502,13 +10502,13 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D44" s="3">
         <v>90</v>
@@ -10520,13 +10520,13 @@
         <v>40</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I44" s="3">
         <v>15</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>34</v>
@@ -10615,13 +10615,13 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D45" s="3">
         <v>-50</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>33</v>
@@ -10728,13 +10728,13 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="D46" s="3">
         <v>-60</v>
@@ -10746,7 +10746,7 @@
         <v>34</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I46" s="3">
         <v>35</v>
@@ -10758,7 +10758,7 @@
         <v>34</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>34</v>
@@ -10847,13 +10847,13 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D47" s="3">
         <v>-50</v>
@@ -10871,7 +10871,7 @@
         <v>32</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>33</v>
@@ -10960,13 +10960,13 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D48" s="3">
         <v>-50</v>
@@ -10984,7 +10984,7 @@
         <v>38</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>33</v>
@@ -11073,13 +11073,13 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="D49" s="3">
         <v>-50</v>
@@ -11091,7 +11091,7 @@
         <v>270</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I49" s="3">
         <v>42</v>
@@ -11100,7 +11100,7 @@
         <v>5</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>33</v>
@@ -11189,13 +11189,13 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D50" s="3">
         <v>-50</v>
@@ -11207,13 +11207,13 @@
         <v>180</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I50" s="3">
         <v>28</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>33</v>
@@ -11302,13 +11302,13 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D51" s="3">
         <v>-20</v>
@@ -11323,13 +11323,13 @@
         <v>120</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I51" s="3">
         <v>15</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>34</v>
@@ -11418,13 +11418,13 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D52" s="3">
         <v>-50</v>
@@ -11436,13 +11436,13 @@
         <v>420</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I52" s="3">
         <v>25</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>33</v>
@@ -11531,13 +11531,13 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="D53" s="3">
         <v>10</v>
@@ -11549,7 +11549,7 @@
         <v>130</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I53" s="3">
         <v>24</v>
@@ -11558,7 +11558,7 @@
         <v>10</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>34</v>
@@ -11647,13 +11647,13 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="D54" s="3">
         <v>10</v>
@@ -11665,7 +11665,7 @@
         <v>140</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I54" s="3">
         <v>24</v>
@@ -11674,7 +11674,7 @@
         <v>10</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>34</v>
@@ -11763,13 +11763,13 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D55" s="3">
         <v>-20</v>
@@ -11790,7 +11790,7 @@
         <v>15</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>34</v>
@@ -11879,13 +11879,13 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D56" s="3">
         <v>-20</v>
@@ -11900,13 +11900,13 @@
         <v>70</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I56" s="3">
         <v>15</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>33</v>
@@ -11995,13 +11995,13 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D57" s="3">
         <v>-50</v>
@@ -12013,13 +12013,13 @@
         <v>230</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I57" s="3">
         <v>27</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>33</v>
@@ -12108,13 +12108,13 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="D58" s="3">
         <v>10</v>
@@ -12126,7 +12126,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I58" s="3">
         <v>21</v>
@@ -12135,7 +12135,7 @@
         <v>10</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>34</v>
@@ -12224,13 +12224,13 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="D59" s="3">
         <v>-50</v>
@@ -12242,7 +12242,7 @@
         <v>140</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J59" s="3">
         <v>60</v>
@@ -12251,7 +12251,7 @@
         <v>10</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>33</v>
@@ -12340,13 +12340,13 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D60" s="3">
         <v>-50</v>
@@ -12358,13 +12358,13 @@
         <v>160</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I60" s="3">
         <v>37</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>34</v>
@@ -12453,13 +12453,13 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D61" s="3">
         <v>-20</v>
@@ -12474,13 +12474,13 @@
         <v>90</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I61" s="3">
         <v>15</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>33</v>
@@ -12569,13 +12569,13 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D62" s="3">
         <v>-50</v>
@@ -12593,7 +12593,7 @@
         <v>37</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>33</v>
@@ -12682,13 +12682,13 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="D63" s="3">
         <v>10</v>
@@ -12700,7 +12700,7 @@
         <v>170</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I63" s="3">
         <v>25</v>
@@ -12709,7 +12709,7 @@
         <v>10</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>33</v>
@@ -12798,13 +12798,13 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D64" s="3">
         <v>-50</v>
@@ -12816,13 +12816,13 @@
         <v>290</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I64" s="3">
         <v>31</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>33</v>
@@ -12911,13 +12911,13 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D65" s="3">
         <v>-20</v>
@@ -12938,7 +12938,7 @@
         <v>15</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>33</v>
@@ -13027,13 +13027,13 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="D66" s="3">
         <v>10</v>
@@ -13045,7 +13045,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J66" s="3">
         <v>60</v>
@@ -13054,10 +13054,10 @@
         <v>10</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>34</v>
@@ -13146,13 +13146,13 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D67" s="3">
         <v>-50</v>
@@ -13164,13 +13164,13 @@
         <v>280</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I67" s="3">
         <v>45</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>33</v>
@@ -13259,13 +13259,13 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D68" s="3">
         <v>-20</v>
@@ -13286,7 +13286,7 @@
         <v>15</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>33</v>
@@ -13375,13 +13375,13 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D69" s="3">
         <v>-20</v>
@@ -13396,13 +13396,13 @@
         <v>90</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I69" s="3">
         <v>15</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>33</v>
@@ -13491,13 +13491,13 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D70" s="3">
         <v>-50</v>
@@ -13515,7 +13515,7 @@
         <v>35</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>33</v>
@@ -13604,13 +13604,13 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D71" s="3">
         <v>-20</v>
@@ -13625,13 +13625,13 @@
         <v>70</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I71" s="3">
         <v>15</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>33</v>
@@ -13720,13 +13720,13 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D72" s="3">
         <v>-50</v>
@@ -13738,13 +13738,13 @@
         <v>160</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I72" s="3">
         <v>37</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>33</v>
@@ -13833,13 +13833,13 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D73" s="3">
         <v>-50</v>
@@ -13851,13 +13851,13 @@
         <v>160</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I73" s="3">
         <v>41</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>34</v>
@@ -13946,13 +13946,13 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D74" s="3">
         <v>-50</v>
@@ -13970,7 +13970,7 @@
         <v>29</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>33</v>
@@ -14059,13 +14059,13 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D75" s="3">
         <v>-30</v>
@@ -14086,7 +14086,7 @@
         <v>15</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O75" s="1" t="s">
         <v>34</v>
@@ -14288,31 +14288,31 @@
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>183</v>
-      </c>
       <c r="V1" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="W1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>20</v>
@@ -14321,36 +14321,36 @@
         <v>22</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AB1" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD1" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>363</v>
-      </c>
       <c r="AE1" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -14362,13 +14362,13 @@
         <v>220</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I2" s="3">
         <v>20</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
@@ -14427,13 +14427,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -14445,13 +14445,13 @@
         <v>280</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I3" s="3">
         <v>50</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
@@ -14510,13 +14510,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
@@ -14528,13 +14528,13 @@
         <v>215</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I4" s="3">
         <v>55</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>33</v>
@@ -14593,13 +14593,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3">
         <v>80</v>
@@ -14617,7 +14617,7 @@
         <v>45</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>33</v>
@@ -14676,13 +14676,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -14694,7 +14694,7 @@
         <v>280</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I6" s="3">
         <v>65</v>
@@ -14703,7 +14703,7 @@
         <v>8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>33</v>
@@ -14762,13 +14762,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D7" s="3">
         <v>80</v>
@@ -14786,7 +14786,7 @@
         <v>45</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>33</v>
@@ -14845,13 +14845,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="D8" s="3">
         <v>-20</v>
@@ -14863,7 +14863,7 @@
         <v>350</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J8" s="3">
         <v>40</v>
@@ -14872,7 +14872,7 @@
         <v>8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>34</v>
@@ -14931,13 +14931,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
@@ -14949,13 +14949,13 @@
         <v>215</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I9" s="3">
         <v>45</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>33</v>
@@ -15014,13 +15014,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
@@ -15032,13 +15032,13 @@
         <v>215</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I10" s="3">
         <v>45</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>33</v>
@@ -15097,13 +15097,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -15115,7 +15115,7 @@
         <v>210</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I11" s="3">
         <v>40</v>
@@ -15124,7 +15124,7 @@
         <v>6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>33</v>
@@ -15183,13 +15183,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -15207,7 +15207,7 @@
         <v>40</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -15266,13 +15266,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -15290,7 +15290,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>33</v>
@@ -15349,13 +15349,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -15367,13 +15367,13 @@
         <v>210</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I14" s="3">
         <v>40</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>33</v>
@@ -15432,13 +15432,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D15" s="3">
         <v>-30</v>
@@ -15456,7 +15456,7 @@
         <v>60</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>33</v>
@@ -15515,13 +15515,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -15533,7 +15533,7 @@
         <v>220</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J16" s="3">
         <v>60</v>
@@ -15542,7 +15542,7 @@
         <v>9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>33</v>
@@ -15601,13 +15601,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -15625,7 +15625,7 @@
         <v>42</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>33</v>
@@ -15684,13 +15684,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -15708,7 +15708,7 @@
         <v>30</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>33</v>
@@ -15767,13 +15767,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D19" s="3">
         <v>0</v>
@@ -15791,7 +15791,7 @@
         <v>40</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>33</v>
@@ -15850,13 +15850,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
@@ -15868,13 +15868,13 @@
         <v>215</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I20" s="3">
         <v>50</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>33</v>
@@ -15933,13 +15933,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D21" s="3">
         <v>80</v>
@@ -15957,7 +15957,7 @@
         <v>45</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>33</v>
@@ -16016,13 +16016,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D22" s="3">
         <v>80</v>
@@ -16040,7 +16040,7 @@
         <v>45</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>33</v>
@@ -16099,13 +16099,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D23" s="3">
         <v>-30</v>
@@ -16123,7 +16123,7 @@
         <v>60</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>33</v>
@@ -16182,13 +16182,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -16200,13 +16200,13 @@
         <v>230</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I24" s="3">
         <v>40</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>33</v>
@@ -16265,13 +16265,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D25" s="3">
         <v>-30</v>
@@ -16289,7 +16289,7 @@
         <v>60</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>33</v>
@@ -16348,13 +16348,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D26" s="3">
         <v>80</v>
@@ -16372,7 +16372,7 @@
         <v>45</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>33</v>
@@ -16431,13 +16431,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
@@ -16449,13 +16449,13 @@
         <v>220</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I27" s="3">
         <v>50</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>33</v>
@@ -16514,13 +16514,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -16532,13 +16532,13 @@
         <v>210</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3">
         <v>40</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>33</v>
@@ -16597,13 +16597,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
@@ -16615,13 +16615,13 @@
         <v>250</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I29" s="3">
         <v>55</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>33</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="425">
   <si>
     <t>Materials</t>
   </si>
@@ -582,13 +582,19 @@
     <t>sand_basaltic</t>
   </si>
   <si>
-    <t>basaltic_mineral_sand 8 / glauconite_sand 5 / garnet_sand 1</t>
+    <t>basaltic_mineral_sand 8 / glauconite_sand 5 / garnet_sand 3</t>
+  </si>
+  <si>
+    <t>sand_garnet</t>
+  </si>
+  <si>
+    <t>glauconite_sand 3 / fullers_earth 3 / garnet_sand 4</t>
   </si>
   <si>
     <t>sand_granitic</t>
   </si>
   <si>
-    <t>granitic_mineral_sand 8 / fullers_earth 4 / garnet_sand 1</t>
+    <t>granitic_mineral_sand 8 / fullers_earth 4 / garnet_sand 3</t>
   </si>
   <si>
     <t>sand_tin</t>
@@ -1195,6 +1201,12 @@
   </si>
   <si>
     <t>#tfg:nether/is_thorny_brambles</t>
+  </si>
+  <si>
+    <t>beneath_molydbenum</t>
+  </si>
+  <si>
+    <t>wulfenite 20 [1] / molybdenite 10 / powellite 16</t>
   </si>
   <si>
     <t>beneath_nickel</t>
@@ -1365,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ75"/>
+  <dimension ref="A1:AQ76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.531091690063477" customWidth="1" style="4"/>
@@ -8010,7 +8022,7 @@
         <v>49</v>
       </c>
       <c r="G58" s="3">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>76</v>
@@ -8019,7 +8031,7 @@
         <v>34</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>48</v>
@@ -8027,8 +8039,8 @@
       <c r="P58" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q58" s="2" t="s">
-        <v>48</v>
+      <c r="Q58" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>49</v>
@@ -8063,8 +8075,8 @@
       <c r="AB58" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC58" s="2" t="s">
-        <v>48</v>
+      <c r="AC58" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AD58" s="2" t="s">
         <v>48</v>
@@ -8075,8 +8087,8 @@
       <c r="AF58" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG58" s="2" t="s">
-        <v>48</v>
+      <c r="AG58" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AH58" s="2" t="s">
         <v>48</v>
@@ -8126,13 +8138,13 @@
         <v>49</v>
       </c>
       <c r="G59" s="3">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="I59" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>47</v>
@@ -8143,8 +8155,8 @@
       <c r="P59" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q59" s="1" t="s">
-        <v>49</v>
+      <c r="Q59" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>49</v>
@@ -8179,8 +8191,8 @@
       <c r="AB59" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC59" s="1" t="s">
-        <v>49</v>
+      <c r="AC59" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AD59" s="2" t="s">
         <v>48</v>
@@ -8191,8 +8203,8 @@
       <c r="AF59" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG59" s="1" t="s">
-        <v>49</v>
+      <c r="AG59" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AH59" s="2" t="s">
         <v>48</v>
@@ -8224,67 +8236,67 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="D60" s="3">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="E60" s="3">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G60" s="3">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="I60" s="3">
         <v>15</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W60" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y60" s="1" t="s">
-        <v>49</v>
+      <c r="Y60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>48</v>
@@ -8295,11 +8307,11 @@
       <c r="AB60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD60" s="1" t="s">
-        <v>49</v>
+      <c r="AC60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE60" s="2" t="s">
         <v>48</v>
@@ -8307,35 +8319,35 @@
       <c r="AF60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG60" s="2" t="s">
-        <v>48</v>
+      <c r="AG60" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AH60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AI60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ60" s="1" t="s">
-        <v>49</v>
+      <c r="AI60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AK60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL60" s="1" t="s">
-        <v>49</v>
+      <c r="AL60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP60" s="2" t="s">
-        <v>48</v>
+      <c r="AN60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP60" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="61">
@@ -8346,34 +8358,34 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="D61" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="E61" s="3">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G61" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>198</v>
+        <v>68</v>
       </c>
       <c r="I61" s="3">
         <v>15</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>48</v>
+        <v>197</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>48</v>
@@ -8393,8 +8405,8 @@
       <c r="V61" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W61" s="2" t="s">
-        <v>48</v>
+      <c r="W61" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X61" s="2" t="s">
         <v>48</v>
@@ -8432,8 +8444,8 @@
       <c r="AI61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ61" s="2" t="s">
-        <v>48</v>
+      <c r="AJ61" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK61" s="2" t="s">
         <v>48</v>
@@ -8444,8 +8456,8 @@
       <c r="AM61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN61" s="2" t="s">
-        <v>48</v>
+      <c r="AN61" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO61" s="2" t="s">
         <v>48</v>
@@ -8456,40 +8468,40 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D62" s="3">
         <v>-20</v>
       </c>
       <c r="E62" s="3">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G62" s="3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>15</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>49</v>
+        <v>197</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>48</v>
@@ -8497,32 +8509,32 @@
       <c r="R62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W62" s="1" t="s">
-        <v>49</v>
+      <c r="S62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y62" s="2" t="s">
-        <v>48</v>
+      <c r="Y62" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA62" s="1" t="s">
-        <v>49</v>
+      <c r="AA62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB62" s="2" t="s">
         <v>48</v>
@@ -8530,35 +8542,35 @@
       <c r="AC62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE62" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF62" s="1" t="s">
-        <v>49</v>
+      <c r="AD62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH62" s="1" t="s">
-        <v>49</v>
+      <c r="AH62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ62" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK62" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM62" s="1" t="s">
-        <v>49</v>
+      <c r="AJ62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN62" s="2" t="s">
         <v>48</v>
@@ -8590,10 +8602,10 @@
         <v>49</v>
       </c>
       <c r="G63" s="3">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="I63" s="3">
         <v>15</v>
@@ -8637,8 +8649,8 @@
       <c r="Z63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA63" s="2" t="s">
-        <v>48</v>
+      <c r="AA63" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AB63" s="2" t="s">
         <v>48</v>
@@ -8649,17 +8661,17 @@
       <c r="AD63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AE63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF63" s="2" t="s">
-        <v>48</v>
+      <c r="AE63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF63" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH63" s="2" t="s">
-        <v>48</v>
+      <c r="AH63" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI63" s="2" t="s">
         <v>48</v>
@@ -8667,14 +8679,14 @@
       <c r="AJ63" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK63" s="2" t="s">
-        <v>48</v>
+      <c r="AK63" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AL63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AM63" s="2" t="s">
-        <v>48</v>
+      <c r="AM63" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AN63" s="2" t="s">
         <v>48</v>
@@ -8706,10 +8718,10 @@
         <v>49</v>
       </c>
       <c r="G64" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I64" s="3">
         <v>15</v>
@@ -8822,10 +8834,10 @@
         <v>49</v>
       </c>
       <c r="G65" s="3">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I65" s="3">
         <v>15</v>
@@ -8833,11 +8845,11 @@
       <c r="M65" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>48</v>
+      <c r="O65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>48</v>
@@ -8845,26 +8857,26 @@
       <c r="R65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>48</v>
+      <c r="S65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y65" s="1" t="s">
-        <v>49</v>
+      <c r="Y65" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z65" s="2" t="s">
         <v>48</v>
@@ -8878,8 +8890,8 @@
       <c r="AC65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD65" s="1" t="s">
-        <v>49</v>
+      <c r="AD65" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE65" s="2" t="s">
         <v>48</v>
@@ -8896,20 +8908,20 @@
       <c r="AI65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ65" s="2" t="s">
-        <v>48</v>
+      <c r="AJ65" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL65" s="1" t="s">
-        <v>49</v>
+      <c r="AL65" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN65" s="1" t="s">
-        <v>49</v>
+      <c r="AN65" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO65" s="2" t="s">
         <v>48</v>
@@ -9054,10 +9066,10 @@
         <v>49</v>
       </c>
       <c r="G67" s="3">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="I67" s="3">
         <v>15</v>
@@ -9101,8 +9113,8 @@
       <c r="Z67" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA67" s="1" t="s">
-        <v>49</v>
+      <c r="AA67" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB67" s="2" t="s">
         <v>48</v>
@@ -9113,17 +9125,17 @@
       <c r="AD67" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF67" s="1" t="s">
-        <v>49</v>
+      <c r="AE67" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF67" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG67" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH67" s="1" t="s">
-        <v>49</v>
+      <c r="AH67" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI67" s="2" t="s">
         <v>48</v>
@@ -9131,14 +9143,14 @@
       <c r="AJ67" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AK67" s="1" t="s">
-        <v>49</v>
+      <c r="AK67" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AL67" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AM67" s="1" t="s">
-        <v>49</v>
+      <c r="AM67" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN67" s="1" t="s">
         <v>49</v>
@@ -9170,22 +9182,22 @@
         <v>49</v>
       </c>
       <c r="G68" s="3">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="I68" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>49</v>
+      <c r="O68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>48</v>
@@ -9193,71 +9205,71 @@
       <c r="R68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB68" s="1" t="s">
-        <v>49</v>
+      <c r="S68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF68" s="2" t="s">
-        <v>48</v>
+      <c r="AD68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF68" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH68" s="2" t="s">
-        <v>48</v>
+      <c r="AH68" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM68" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN68" s="2" t="s">
-        <v>48</v>
+      <c r="AJ68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN68" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO68" s="2" t="s">
         <v>48</v>
@@ -9286,13 +9298,13 @@
         <v>49</v>
       </c>
       <c r="G69" s="3">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="I69" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>47</v>
@@ -9324,20 +9336,20 @@
       <c r="W69" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="X69" s="2" t="s">
-        <v>48</v>
+      <c r="X69" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Y69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z69" s="2" t="s">
-        <v>48</v>
+      <c r="Z69" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB69" s="2" t="s">
-        <v>48</v>
+      <c r="AB69" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC69" s="2" t="s">
         <v>48</v>
@@ -9402,10 +9414,10 @@
         <v>49</v>
       </c>
       <c r="G70" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="I70" s="3">
         <v>15</v>
@@ -9413,11 +9425,11 @@
       <c r="M70" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O70" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P70" s="2" t="s">
-        <v>48</v>
+      <c r="O70" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q70" s="2" t="s">
         <v>48</v>
@@ -9425,26 +9437,26 @@
       <c r="R70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W70" s="2" t="s">
-        <v>48</v>
+      <c r="S70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W70" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y70" s="1" t="s">
-        <v>49</v>
+      <c r="Y70" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>48</v>
@@ -9458,8 +9470,8 @@
       <c r="AC70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD70" s="1" t="s">
-        <v>49</v>
+      <c r="AD70" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE70" s="2" t="s">
         <v>48</v>
@@ -9476,20 +9488,20 @@
       <c r="AI70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ70" s="2" t="s">
-        <v>48</v>
+      <c r="AJ70" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL70" s="1" t="s">
-        <v>49</v>
+      <c r="AL70" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN70" s="1" t="s">
-        <v>49</v>
+      <c r="AN70" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO70" s="2" t="s">
         <v>48</v>
@@ -9518,22 +9530,22 @@
         <v>49</v>
       </c>
       <c r="G71" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I71" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P71" s="1" t="s">
-        <v>49</v>
+      <c r="O71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q71" s="2" t="s">
         <v>48</v>
@@ -9541,26 +9553,26 @@
       <c r="R71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S71" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U71" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V71" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W71" s="1" t="s">
-        <v>49</v>
+      <c r="S71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y71" s="2" t="s">
-        <v>48</v>
+      <c r="Y71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z71" s="2" t="s">
         <v>48</v>
@@ -9574,8 +9586,8 @@
       <c r="AC71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD71" s="2" t="s">
-        <v>48</v>
+      <c r="AD71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE71" s="2" t="s">
         <v>48</v>
@@ -9592,20 +9604,20 @@
       <c r="AI71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ71" s="1" t="s">
-        <v>49</v>
+      <c r="AJ71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AK71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL71" s="2" t="s">
-        <v>48</v>
+      <c r="AL71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN71" s="2" t="s">
-        <v>48</v>
+      <c r="AN71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO71" s="2" t="s">
         <v>48</v>
@@ -9637,10 +9649,10 @@
         <v>80</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I72" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>47</v>
@@ -9672,20 +9684,20 @@
       <c r="W72" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="X72" s="1" t="s">
-        <v>49</v>
+      <c r="X72" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z72" s="1" t="s">
-        <v>49</v>
+      <c r="Z72" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AA72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB72" s="1" t="s">
-        <v>49</v>
+      <c r="AB72" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC72" s="2" t="s">
         <v>48</v>
@@ -9753,7 +9765,7 @@
         <v>80</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I73" s="3">
         <v>15</v>
@@ -9761,11 +9773,11 @@
       <c r="M73" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O73" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P73" s="2" t="s">
-        <v>48</v>
+      <c r="O73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q73" s="2" t="s">
         <v>48</v>
@@ -9773,71 +9785,71 @@
       <c r="R73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W73" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X73" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z73" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB73" s="2" t="s">
-        <v>48</v>
+      <c r="S73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB73" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF73" s="1" t="s">
-        <v>49</v>
+      <c r="AD73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF73" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH73" s="1" t="s">
-        <v>49</v>
+      <c r="AH73" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ73" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN73" s="1" t="s">
-        <v>49</v>
+      <c r="AJ73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN73" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO73" s="2" t="s">
         <v>48</v>
@@ -9866,10 +9878,10 @@
         <v>49</v>
       </c>
       <c r="G74" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="I74" s="3">
         <v>15</v>
@@ -9889,41 +9901,41 @@
       <c r="R74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>48</v>
+      <c r="S74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z74" s="1" t="s">
-        <v>49</v>
+      <c r="X74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z74" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AA74" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB74" s="1" t="s">
-        <v>49</v>
+      <c r="AB74" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD74" s="2" t="s">
-        <v>48</v>
+      <c r="AD74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE74" s="1" t="s">
         <v>49</v>
@@ -9946,14 +9958,14 @@
       <c r="AK74" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AL74" s="2" t="s">
-        <v>48</v>
+      <c r="AL74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM74" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AN74" s="2" t="s">
-        <v>48</v>
+      <c r="AN74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO74" s="2" t="s">
         <v>48</v>
@@ -9982,10 +9994,10 @@
         <v>49</v>
       </c>
       <c r="G75" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="I75" s="3">
         <v>15</v>
@@ -10005,53 +10017,53 @@
       <c r="R75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V75" s="1" t="s">
-        <v>49</v>
+      <c r="S75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB75" s="2" t="s">
-        <v>48</v>
+      <c r="X75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF75" s="2" t="s">
-        <v>48</v>
+      <c r="AD75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH75" s="2" t="s">
-        <v>48</v>
+      <c r="AH75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI75" s="2" t="s">
         <v>48</v>
@@ -10059,22 +10071,138 @@
       <c r="AJ75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AK75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN75" s="1" t="s">
-        <v>49</v>
+      <c r="AK75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN75" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO75" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AP75" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D76" s="3">
+        <v>-20</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-5</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" s="3">
+        <v>90</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I76" s="3">
+        <v>15</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP76" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -10229,13 +10357,13 @@
         <v>30</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AE1" s="5" t="s">
         <v>36</v>
@@ -10244,18 +10372,18 @@
         <v>38</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D2" s="3">
         <v>-30</v>
@@ -10332,13 +10460,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D3" s="3">
         <v>-30</v>
@@ -10415,13 +10543,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D4" s="3">
         <v>-30</v>
@@ -10498,13 +10626,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -10584,13 +10712,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -10667,13 +10795,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D7" s="3">
         <v>-20</v>
@@ -10753,13 +10881,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -10771,7 +10899,7 @@
         <v>215</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I8" s="3">
         <v>55</v>
@@ -10836,13 +10964,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
@@ -10919,13 +11047,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
@@ -11002,13 +11130,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -11085,13 +11213,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -11171,13 +11299,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -11254,13 +11382,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -11337,13 +11465,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
@@ -11420,13 +11548,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -11503,13 +11631,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -11586,13 +11714,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -11604,7 +11732,7 @@
         <v>220</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I18" s="3">
         <v>20</v>
@@ -11669,13 +11797,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D19" s="3">
         <v>0</v>
@@ -11752,13 +11880,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
@@ -11838,13 +11966,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
@@ -11921,13 +12049,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -12004,13 +12132,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -12087,13 +12215,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -12105,7 +12233,7 @@
         <v>280</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I24" s="3">
         <v>50</v>
@@ -12170,13 +12298,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D25" s="3">
         <v>80</v>
@@ -12253,13 +12381,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D26" s="3">
         <v>80</v>
@@ -12336,13 +12464,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D27" s="3">
         <v>80</v>
@@ -12419,13 +12547,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D28" s="3">
         <v>80</v>
@@ -12502,13 +12630,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D29" s="3">
         <v>80</v>
@@ -12713,16 +12841,16 @@
         <v>26</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>36</v>
@@ -12730,13 +12858,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -12789,13 +12917,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -12848,13 +12976,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
@@ -12910,13 +13038,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
@@ -12969,13 +13097,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -13028,13 +13156,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
@@ -13087,13 +13215,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D8" s="3">
         <v>10</v>
@@ -13149,13 +13277,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D9" s="3">
         <v>5</v>
@@ -13208,13 +13336,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D10" s="3">
         <v>10</v>
@@ -13270,13 +13398,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -13332,13 +13460,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D12" s="3">
         <v>10</v>
@@ -13394,13 +13522,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -13453,13 +13581,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -13512,13 +13640,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D15" s="3">
         <v>5</v>
@@ -13571,13 +13699,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -13630,13 +13758,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -13689,13 +13817,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -13748,13 +13876,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D19" s="3">
         <v>20</v>
@@ -13807,13 +13935,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D20" s="3">
         <v>10</v>
@@ -13866,13 +13994,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D21" s="3">
         <v>20</v>
@@ -13925,13 +14053,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -13984,13 +14112,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -14046,13 +14174,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -14105,13 +14233,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D25" s="3">
         <v>20</v>
@@ -14164,13 +14292,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
@@ -14223,13 +14351,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D27" s="3">
         <v>50</v>
@@ -14282,13 +14410,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -14349,7 +14477,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.20575523376465" customWidth="1" style="4"/>
@@ -14460,16 +14588,16 @@
         <v>16</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>26</v>
@@ -14498,13 +14626,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D2" s="3">
         <v>80</v>
@@ -14525,7 +14653,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>48</v>
@@ -14569,13 +14697,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -14596,7 +14724,7 @@
         <v>15</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>49</v>
@@ -14640,13 +14768,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D4" s="3">
         <v>140</v>
@@ -14664,7 +14792,7 @@
         <v>27</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>48</v>
@@ -14708,13 +14836,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D5" s="3">
         <v>140</v>
@@ -14732,7 +14860,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>48</v>
@@ -14776,13 +14904,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D6" s="3">
         <v>140</v>
@@ -14800,7 +14928,7 @@
         <v>25</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>48</v>
@@ -14844,13 +14972,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D7" s="3">
         <v>80</v>
@@ -14868,7 +14996,7 @@
         <v>27</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>48</v>
@@ -14912,13 +15040,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D8" s="3">
         <v>80</v>
@@ -14936,7 +15064,7 @@
         <v>27</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>48</v>
@@ -14980,13 +15108,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D9" s="3">
         <v>80</v>
@@ -15004,7 +15132,7 @@
         <v>25</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>48</v>
@@ -15048,13 +15176,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D10" s="3">
         <v>80</v>
@@ -15072,7 +15200,7 @@
         <v>25</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>48</v>
@@ -15116,13 +15244,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -15140,7 +15268,7 @@
         <v>23</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>49</v>
@@ -15184,13 +15312,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -15211,7 +15339,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>49</v>
@@ -15255,13 +15383,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D13" s="3">
         <v>140</v>
@@ -15279,7 +15407,7 @@
         <v>31</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>48</v>
@@ -15323,13 +15451,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D14" s="3">
         <v>80</v>
@@ -15347,7 +15475,7 @@
         <v>29</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>48</v>
@@ -15391,13 +15519,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D15" s="3">
         <v>80</v>
@@ -15418,7 +15546,7 @@
         <v>8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>48</v>
@@ -15462,13 +15590,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D16" s="3">
         <v>140</v>
@@ -15486,7 +15614,7 @@
         <v>27</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>48</v>
@@ -15530,13 +15658,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -15554,7 +15682,7 @@
         <v>25</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>49</v>
@@ -15598,13 +15726,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D18" s="3">
         <v>80</v>
@@ -15625,7 +15753,7 @@
         <v>8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>48</v>
@@ -15669,31 +15797,31 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D19" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E19" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G19" s="3">
         <v>10</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="I19" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>48</v>
@@ -15710,26 +15838,26 @@
       <c r="S19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>49</v>
+      <c r="T19" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="V19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X19" s="2" t="s">
-        <v>48</v>
+      <c r="V19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Y19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z19" s="2" t="s">
-        <v>48</v>
+      <c r="Z19" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA19" s="1" t="s">
         <v>49</v>
@@ -15737,58 +15865,55 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E20" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G20" s="3">
         <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="I20" s="3">
-        <v>45</v>
-      </c>
-      <c r="J20" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>49</v>
+        <v>394</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>48</v>
+      <c r="R20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>48</v>
@@ -15796,67 +15921,70 @@
       <c r="X20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y20" s="2" t="s">
-        <v>48</v>
+      <c r="Y20" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA20" s="2" t="s">
-        <v>48</v>
+      <c r="AA20" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>80</v>
-      </c>
-      <c r="E21" s="3">
-        <v>140</v>
       </c>
       <c r="G21" s="3">
         <v>10</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="I21" s="3">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="J21" s="3">
+        <v>10</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>48</v>
+        <v>379</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>49</v>
+      <c r="R21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>48</v>
@@ -15864,70 +15992,67 @@
       <c r="X21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y21" s="1" t="s">
-        <v>49</v>
+      <c r="Y21" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA21" s="1" t="s">
-        <v>49</v>
+      <c r="AA21" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E22" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G22" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="I22" s="3">
-        <v>50</v>
-      </c>
-      <c r="J22" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>49</v>
+        <v>352</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>48</v>
+      <c r="R22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>48</v>
@@ -15935,70 +16060,70 @@
       <c r="X22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y22" s="2" t="s">
-        <v>48</v>
+      <c r="Y22" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA22" s="2" t="s">
-        <v>48</v>
+      <c r="AA22" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>80</v>
       </c>
-      <c r="E23" s="3">
-        <v>140</v>
-      </c>
       <c r="G23" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>88</v>
+        <v>159</v>
+      </c>
+      <c r="I23" s="3">
+        <v>50</v>
       </c>
       <c r="J23" s="3">
-        <v>60</v>
-      </c>
-      <c r="K23" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>48</v>
+        <v>391</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>49</v>
+      <c r="R23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>48</v>
@@ -16006,25 +16131,25 @@
       <c r="X23" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y23" s="1" t="s">
-        <v>49</v>
+      <c r="Y23" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA23" s="1" t="s">
-        <v>49</v>
+      <c r="AA23" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D24" s="3">
         <v>80</v>
@@ -16036,13 +16161,16 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" s="3">
-        <v>23</v>
+        <v>88</v>
+      </c>
+      <c r="J24" s="3">
+        <v>60</v>
+      </c>
+      <c r="K24" s="3">
+        <v>15</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>48</v>
@@ -16086,58 +16214,55 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D25" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G25" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="3">
-        <v>60</v>
-      </c>
-      <c r="K25" s="3">
-        <v>12</v>
+        <v>68</v>
+      </c>
+      <c r="I25" s="3">
+        <v>23</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>49</v>
+        <v>370</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>48</v>
+      <c r="R25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W25" s="2" t="s">
         <v>48</v>
@@ -16145,232 +16270,235 @@
       <c r="X25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y25" s="2" t="s">
-        <v>48</v>
+      <c r="Y25" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA25" s="2" t="s">
-        <v>48</v>
+      <c r="AA25" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D26" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="G26" s="3">
         <v>10</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="J26" s="3">
         <v>60</v>
       </c>
       <c r="K26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>48</v>
+        <v>379</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>49</v>
+      <c r="R26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U26" s="1" t="s">
-        <v>49</v>
+      <c r="U26" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA26" s="1" t="s">
-        <v>49</v>
+      <c r="W26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E27" s="3">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3">
         <v>10</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="3">
-        <v>29</v>
+        <v>147</v>
+      </c>
+      <c r="J27" s="3">
+        <v>60</v>
+      </c>
+      <c r="K27" s="3">
+        <v>10</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>49</v>
+        <v>388</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>48</v>
+      <c r="R27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U27" s="2" t="s">
-        <v>48</v>
+      <c r="U27" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA27" s="2" t="s">
-        <v>48</v>
+      <c r="W27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D28" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="G28" s="3">
         <v>10</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="I28" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>48</v>
+        <v>391</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>49</v>
+      <c r="R28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U28" s="1" t="s">
-        <v>49</v>
+      <c r="U28" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA28" s="1" t="s">
-        <v>49</v>
+      <c r="W28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D29" s="3">
         <v>140</v>
@@ -16388,7 +16516,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>48</v>
@@ -16427,6 +16555,74 @@
         <v>49</v>
       </c>
       <c r="AA29" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D30" s="3">
+        <v>140</v>
+      </c>
+      <c r="E30" s="3">
+        <v>190</v>
+      </c>
+      <c r="G30" s="3">
+        <v>10</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="3">
+        <v>25</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA30" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -16554,30 +16750,30 @@
         <v>23</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D2" s="3">
         <v>40</v>
@@ -16627,13 +16823,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D3" s="3">
         <v>40</v>
